--- a/Base_Interrupcoes.xlsx
+++ b/Base_Interrupcoes.xlsx
@@ -466,7 +466,7 @@
       <c s="4" t="str" r="A7"/>
       <c s="7" t="inlineStr" r="T7">
         <is>
-          <t xml:space="preserve">Emissão: 02/10/2026</t>
+          <t xml:space="preserve">Emissão: 05/10/2026</t>
         </is>
       </c>
       <c s="5" t="str" r="V7"/>
@@ -475,7 +475,7 @@
       <c s="4" t="str" r="A8"/>
       <c s="8" t="inlineStr" r="F8">
         <is>
-          <t xml:space="preserve">Período: 01/10/2026 até 01/10/2026; Turno: Todos; Tempo: Calendário</t>
+          <t xml:space="preserve">Período: 01/10/2026 até 04/10/2026; Turno: Todos; Tempo: Calendário</t>
         </is>
       </c>
       <c s="5" t="str" r="V8"/>
@@ -783,11 +783,11 @@
         <v>46296.3395833333</v>
       </c>
       <c s="18" r="G19">
-        <v>46297.2918323264</v>
+        <v>46297.2909722222</v>
       </c>
       <c s="17" t="inlineStr" r="H19">
         <is>
-          <t xml:space="preserve">1.371</t>
+          <t xml:space="preserve">1.370</t>
         </is>
       </c>
       <c s="17" t="str" r="I19"/>
@@ -2779,11 +2779,11 @@
         <v>46296.6951388889</v>
       </c>
       <c s="18" r="G47">
-        <v>46297.2918323264</v>
+        <v>46296.7055555556</v>
       </c>
       <c s="17" t="inlineStr" r="H47">
         <is>
-          <t xml:space="preserve">859</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c s="17" t="str" r="I47"/>
@@ -2794,23 +2794,23 @@
       </c>
       <c s="16" t="inlineStr" r="K47">
         <is>
-          <t xml:space="preserve">Tempo Livre</t>
+          <t xml:space="preserve">Operacional</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="L47">
         <is>
-          <t xml:space="preserve">Tempo Livre</t>
+          <t xml:space="preserve">Operacional</t>
         </is>
       </c>
       <c s="16" t="str" r="M47"/>
       <c s="16" t="inlineStr" r="N47">
         <is>
-          <t xml:space="preserve">FALTA DEMANDA</t>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="O47">
         <is>
-          <t xml:space="preserve">tempo livre</t>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
         </is>
       </c>
       <c s="16" t="str" r="P47"/>
@@ -2834,10 +2834,14 @@
     <row r="48" ht="15.55" customHeight="0">
       <c s="19" t="inlineStr" r="A48">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 02</t>
-        </is>
-      </c>
-      <c s="20" t="str" r="B48"/>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B48">
+        <is>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
       <c s="21" t="inlineStr" r="D48">
         <is>
           <t xml:space="preserve">TURNO B</t>
@@ -2873,21 +2877,25 @@
       <c s="20" t="str" r="M48"/>
       <c s="20" t="inlineStr" r="N48">
         <is>
-          <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
+          <t xml:space="preserve">FALTA DEMANDA</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="O48">
         <is>
-          <t xml:space="preserve">Parada registrada automaticamente pelo sistema</t>
+          <t xml:space="preserve">falta de demanda</t>
         </is>
       </c>
       <c s="20" t="str" r="P48"/>
       <c s="20" t="inlineStr" r="R48">
         <is>
-          <t xml:space="preserve">49cef330-bdd1-11f1-8f07-f2050a003223</t>
-        </is>
-      </c>
-      <c s="20" t="str" r="S48"/>
+          <t xml:space="preserve">4a25c5c0-bdd1-11f1-86c2-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S48">
+        <is>
+          <t xml:space="preserve">10046135    </t>
+        </is>
+      </c>
       <c s="20" t="inlineStr" r="U48">
         <is>
           <t xml:space="preserve">Sim</t>
@@ -2898,7 +2906,7 @@
     <row r="49" ht="15.6" customHeight="0">
       <c s="15" t="inlineStr" r="A49">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 03</t>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
         </is>
       </c>
       <c s="16" t="str" r="B49"/>
@@ -2948,7 +2956,7 @@
       <c s="16" t="str" r="P49"/>
       <c s="16" t="inlineStr" r="R49">
         <is>
-          <t xml:space="preserve">49efe8b0-bdd1-11f1-cb5a-f2050a003223</t>
+          <t xml:space="preserve">49cef330-bdd1-11f1-8f07-f2050a003223</t>
         </is>
       </c>
       <c s="16" t="str" r="S49"/>
@@ -2959,79 +2967,3199 @@
       </c>
       <c s="5" t="str" r="V49"/>
     </row>
-    <row r="50" ht="15.55" customHeight="0">
-      <c s="23" t="inlineStr" r="A50">
+    <row r="50" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A50">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 03</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B50"/>
+      <c s="21" t="inlineStr" r="D50">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E50">
+        <v>46296.7013888889</v>
+      </c>
+      <c s="22" r="G50">
+        <v>46297.2840277778</v>
+      </c>
+      <c s="21" t="inlineStr" r="H50">
+        <is>
+          <t xml:space="preserve">839</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I50"/>
+      <c s="21" t="inlineStr" r="J50">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K50">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L50">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M50"/>
+      <c s="20" t="inlineStr" r="N50">
+        <is>
+          <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O50">
+        <is>
+          <t xml:space="preserve">Parada registrada automaticamente pelo sistema</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P50"/>
+      <c s="20" t="inlineStr" r="R50">
+        <is>
+          <t xml:space="preserve">49efe8b0-bdd1-11f1-cb5a-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="S50"/>
+      <c s="20" t="inlineStr" r="U50">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V50"/>
+    </row>
+    <row r="51" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A51">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B51">
+        <is>
+          <t xml:space="preserve">TR01-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D51">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E51">
+        <v>46296.70625</v>
+      </c>
+      <c s="18" r="G51">
+        <v>46297.2909722222</v>
+      </c>
+      <c s="17" t="inlineStr" r="H51">
+        <is>
+          <t xml:space="preserve">842</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I51"/>
+      <c s="17" t="inlineStr" r="J51">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K51">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L51">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M51"/>
+      <c s="16" t="inlineStr" r="N51">
+        <is>
+          <t xml:space="preserve">FALTA DEMANDA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O51">
+        <is>
+          <t xml:space="preserve">tempo livre</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P51"/>
+      <c s="16" t="inlineStr" r="R51">
+        <is>
+          <t xml:space="preserve">d0d36bd0-be4a-11f1-92d1-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S51">
+        <is>
+          <t xml:space="preserve">10046873    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U51">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V51"/>
+    </row>
+    <row r="52" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A52">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B52">
+        <is>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D52">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E52">
+        <v>46297.2916666667</v>
+      </c>
+      <c s="22" r="G52">
+        <v>46297.2986111111</v>
+      </c>
+      <c s="21" t="inlineStr" r="H52">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I52"/>
+      <c s="21" t="inlineStr" r="J52">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K52">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L52">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M52"/>
+      <c s="20" t="inlineStr" r="N52">
+        <is>
+          <t xml:space="preserve">DDS</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O52">
+        <is>
+          <t xml:space="preserve">DDS</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P52"/>
+      <c s="20" t="inlineStr" r="R52">
+        <is>
+          <t xml:space="preserve">942e4bd0-be4c-11f1-ca85-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S52">
+        <is>
+          <t xml:space="preserve">10047019    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U52">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V52"/>
+    </row>
+    <row r="53" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A53">
         <is>
           <t xml:space="preserve">TRANSVERSAL 05</t>
         </is>
       </c>
-      <c s="24" t="str" r="B50"/>
-      <c s="10" t="str" r="C50"/>
-      <c s="25" t="inlineStr" r="D50">
+      <c s="16" t="inlineStr" r="B53">
+        <is>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D53">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E53">
+        <v>46297.2916666667</v>
+      </c>
+      <c s="18" r="G53">
+        <v>46297.3055555556</v>
+      </c>
+      <c s="17" t="inlineStr" r="H53">
+        <is>
+          <t xml:space="preserve">20</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I53"/>
+      <c s="17" t="inlineStr" r="J53">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K53">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L53">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M53"/>
+      <c s="16" t="inlineStr" r="N53">
+        <is>
+          <t xml:space="preserve">DDS</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O53">
+        <is>
+          <t xml:space="preserve">dds com supervisor QUEDA DE MATERIAIS</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P53"/>
+      <c s="16" t="inlineStr" r="R53">
+        <is>
+          <t xml:space="preserve">167ccc00-be4e-11f1-cdcf-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S53">
+        <is>
+          <t xml:space="preserve">10046135    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U53">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V53"/>
+    </row>
+    <row r="54" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A54">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B54">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D54">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E54">
+        <v>46297.2916666667</v>
+      </c>
+      <c s="22" r="G54">
+        <v>46297.3020833333</v>
+      </c>
+      <c s="21" t="inlineStr" r="H54">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I54"/>
+      <c s="21" t="inlineStr" r="J54">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K54">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L54">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M54"/>
+      <c s="20" t="inlineStr" r="N54">
+        <is>
+          <t xml:space="preserve">DDS</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O54">
+        <is>
+          <t xml:space="preserve">dds e assinatura dos documentos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P54"/>
+      <c s="20" t="inlineStr" r="R54">
+        <is>
+          <t xml:space="preserve">61a3b7a0-be4b-11f1-9cbf-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S54">
+        <is>
+          <t xml:space="preserve">10046873    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U54">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V54"/>
+    </row>
+    <row r="55" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A55">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B55">
+        <is>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D55">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E55">
+        <v>46297.2993055556</v>
+      </c>
+      <c s="18" r="G55">
+        <v>46297.30625</v>
+      </c>
+      <c s="17" t="inlineStr" r="H55">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I55"/>
+      <c s="17" t="inlineStr" r="J55">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K55">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L55">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M55"/>
+      <c s="16" t="inlineStr" r="N55">
+        <is>
+          <t xml:space="preserve">ASSINATURA DE DOCUMENTOS</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O55">
+        <is>
+          <t xml:space="preserve">Assinatura de documentos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P55"/>
+      <c s="16" t="inlineStr" r="R55">
+        <is>
+          <t xml:space="preserve">b73f31c0-be4c-11f1-b255-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S55">
+        <is>
+          <t xml:space="preserve">10047019    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U55">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V55"/>
+    </row>
+    <row r="56" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A56">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B56">
+        <is>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D56">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E56">
+        <v>46297.3076388889</v>
+      </c>
+      <c s="22" r="G56">
+        <v>46297.4576388889</v>
+      </c>
+      <c s="21" t="inlineStr" r="H56">
+        <is>
+          <t xml:space="preserve">216</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I56"/>
+      <c s="21" t="inlineStr" r="J56">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K56">
+        <is>
+          <t xml:space="preserve">Manutenção Corretiva Mecânica</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L56">
+        <is>
+          <t xml:space="preserve">Manutenção Corretiva Mecânica</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M56"/>
+      <c s="20" t="inlineStr" r="N56">
+        <is>
+          <t xml:space="preserve">DESGASTADO</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O56">
+        <is>
+          <t xml:space="preserve">DESENROLADOR NÃO TÁ PEGANDO FREI</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="P56">
+        <is>
+          <t xml:space="preserve">000010033908</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="R56">
+        <is>
+          <t xml:space="preserve">fed415a0-be4c-11f1-c0ab-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S56">
+        <is>
+          <t xml:space="preserve">10047019    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U56">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V56"/>
+    </row>
+    <row r="57" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A57">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B57">
+        <is>
+          <t xml:space="preserve">TR01-MESA TRANSPORTADORA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D57">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E57">
+        <v>46297.3166666667</v>
+      </c>
+      <c s="18" r="G57">
+        <v>46297.31875</v>
+      </c>
+      <c s="17" t="inlineStr" r="H57">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I57"/>
+      <c s="17" t="inlineStr" r="J57">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K57">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L57">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M57"/>
+      <c s="16" t="inlineStr" r="N57">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE CHAPA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O57">
+        <is>
+          <t xml:space="preserve">ajustes da chapa</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P57"/>
+      <c s="16" t="inlineStr" r="R57">
+        <is>
+          <t xml:space="preserve">26ef9230-be4d-11f1-8af2-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S57">
+        <is>
+          <t xml:space="preserve">10046873    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U57">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V57"/>
+    </row>
+    <row r="58" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A58">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B58"/>
+      <c s="21" t="inlineStr" r="D58">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E58">
+        <v>46297.31875</v>
+      </c>
+      <c s="22" r="G58">
+        <v>46297.3243055556</v>
+      </c>
+      <c s="21" t="inlineStr" r="H58">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I58"/>
+      <c s="21" t="inlineStr" r="J58">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K58">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L58">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M58"/>
+      <c s="20" t="inlineStr" r="N58">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O58">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 8 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P58"/>
+      <c s="20" t="inlineStr" r="R58">
+        <is>
+          <t xml:space="preserve">92ba5400-be4d-11f1-bca1-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S58">
+        <is>
+          <t xml:space="preserve">10046873    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U58">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V58"/>
+    </row>
+    <row r="59" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A59">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B59">
+        <is>
+          <t xml:space="preserve">TR01-MESA TRANSPORTADORA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D59">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E59">
+        <v>46297.3256944444</v>
+      </c>
+      <c s="18" r="G59">
+        <v>46297.3333333333</v>
+      </c>
+      <c s="17" t="inlineStr" r="H59">
+        <is>
+          <t xml:space="preserve">11</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I59"/>
+      <c s="17" t="inlineStr" r="J59">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K59">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L59">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M59"/>
+      <c s="16" t="inlineStr" r="N59">
+        <is>
+          <t xml:space="preserve">PONTE ROLANTE INDISPONÍVEL</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O59">
+        <is>
+          <t xml:space="preserve">aguardando ponte retira material</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P59"/>
+      <c s="16" t="inlineStr" r="R59">
+        <is>
+          <t xml:space="preserve">f9c1cbf0-be4e-11f1-8e2e-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S59">
+        <is>
+          <t xml:space="preserve">10046873    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U59">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V59"/>
+    </row>
+    <row r="60" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A60">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B60"/>
+      <c s="21" t="inlineStr" r="D60">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E60">
+        <v>46297.3395833333</v>
+      </c>
+      <c s="22" r="G60">
+        <v>46297.3451388889</v>
+      </c>
+      <c s="21" t="inlineStr" r="H60">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I60"/>
+      <c s="21" t="inlineStr" r="J60">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K60">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L60">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M60"/>
+      <c s="20" t="inlineStr" r="N60">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O60">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 8 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P60"/>
+      <c s="20" t="inlineStr" r="R60">
+        <is>
+          <t xml:space="preserve">afbaa830-be51-11f1-a2b3-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S60">
+        <is>
+          <t xml:space="preserve">10046136    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U60">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V60"/>
+    </row>
+    <row r="61" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A61">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B61">
+        <is>
+          <t xml:space="preserve">TR05-MESA FIXA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D61">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E61">
+        <v>46297.3513888889</v>
+      </c>
+      <c s="18" r="G61">
+        <v>46297.3548611111</v>
+      </c>
+      <c s="17" t="inlineStr" r="H61">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I61"/>
+      <c s="17" t="inlineStr" r="J61">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K61">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L61">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M61"/>
+      <c s="16" t="inlineStr" r="N61">
+        <is>
+          <t xml:space="preserve">MESA CHEIA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O61">
+        <is>
+          <t xml:space="preserve">aguardando retirada do material 6000X1000..</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P61"/>
+      <c s="16" t="inlineStr" r="R61">
+        <is>
+          <t xml:space="preserve">1f9513f0-be54-11f1-802f-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S61">
+        <is>
+          <t xml:space="preserve">10046136    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U61">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V61"/>
+    </row>
+    <row r="62" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A62">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B62">
+        <is>
+          <t xml:space="preserve">TR05-MESA FIXA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D62">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E62">
+        <v>46297.3743055556</v>
+      </c>
+      <c s="22" r="G62">
+        <v>46297.3798611111</v>
+      </c>
+      <c s="21" t="inlineStr" r="H62">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I62"/>
+      <c s="21" t="inlineStr" r="J62">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K62">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L62">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M62"/>
+      <c s="20" t="inlineStr" r="N62">
+        <is>
+          <t xml:space="preserve">MESA CHEIA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O62">
+        <is>
+          <t xml:space="preserve">aguardando retirada do material 6000X1000..</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P62"/>
+      <c s="20" t="inlineStr" r="R62">
+        <is>
+          <t xml:space="preserve">a8e845b0-be58-11f1-8623-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S62">
+        <is>
+          <t xml:space="preserve">10046136    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U62">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V62"/>
+    </row>
+    <row r="63" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A63">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B63">
+        <is>
+          <t xml:space="preserve">TR05-MESA FIXA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D63">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E63">
+        <v>46297.3805555556</v>
+      </c>
+      <c s="18" r="G63">
+        <v>46297.3847222222</v>
+      </c>
+      <c s="17" t="inlineStr" r="H63">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I63"/>
+      <c s="17" t="inlineStr" r="J63">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K63">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L63">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M63"/>
+      <c s="16" t="inlineStr" r="N63">
+        <is>
+          <t xml:space="preserve">RETIRADA DE PNC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O63">
+        <is>
+          <t xml:space="preserve">Retirada de pnc.</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P63"/>
+      <c s="16" t="inlineStr" r="R63">
+        <is>
+          <t xml:space="preserve">07f951b0-be5a-11f1-cb2e-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S63">
+        <is>
+          <t xml:space="preserve">10046136    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U63">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V63"/>
+    </row>
+    <row r="64" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A64">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B64">
+        <is>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D64">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E64">
+        <v>46297.3854166667</v>
+      </c>
+      <c s="22" r="G64">
+        <v>46297.4013888889</v>
+      </c>
+      <c s="21" t="inlineStr" r="H64">
+        <is>
+          <t xml:space="preserve">23</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I64"/>
+      <c s="21" t="inlineStr" r="J64">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K64">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L64">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M64"/>
+      <c s="20" t="inlineStr" r="N64">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE CHAPA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O64">
+        <is>
+          <t xml:space="preserve">Passagem de chapa.</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P64"/>
+      <c s="20" t="inlineStr" r="R64">
+        <is>
+          <t xml:space="preserve">86620f60-be5f-11f1-bca0-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S64">
+        <is>
+          <t xml:space="preserve">10046136    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U64">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V64"/>
+    </row>
+    <row r="65" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A65">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B65">
+        <is>
+          <t xml:space="preserve">TR01-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D65">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E65">
+        <v>46297.3951388889</v>
+      </c>
+      <c s="18" r="G65">
+        <v>46297.4020833333</v>
+      </c>
+      <c s="17" t="inlineStr" r="H65">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I65"/>
+      <c s="17" t="inlineStr" r="J65">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K65">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L65">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M65"/>
+      <c s="16" t="inlineStr" r="N65">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O65">
+        <is>
+          <t xml:space="preserve">abastecimento</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P65"/>
+      <c s="16" t="inlineStr" r="R65">
+        <is>
+          <t xml:space="preserve">de5b7380-be5c-11f1-a21b-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S65">
+        <is>
+          <t xml:space="preserve">10047017    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U65">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V65"/>
+    </row>
+    <row r="66" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A66">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B66">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D66">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E66">
+        <v>46297.4125</v>
+      </c>
+      <c s="22" r="G66">
+        <v>46297.4145833333</v>
+      </c>
+      <c s="21" t="inlineStr" r="H66">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I66"/>
+      <c s="21" t="inlineStr" r="J66">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K66">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L66">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M66"/>
+      <c s="20" t="inlineStr" r="N66">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE CHAPA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O66">
+        <is>
+          <t xml:space="preserve">ajuste da chapa</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P66"/>
+      <c s="20" t="inlineStr" r="R66">
+        <is>
+          <t xml:space="preserve">75a48490-be60-11f1-8f02-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S66">
+        <is>
+          <t xml:space="preserve">10047017    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U66">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V66"/>
+    </row>
+    <row r="67" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A67">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B67">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D67">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E67">
+        <v>46297.4201388889</v>
+      </c>
+      <c s="18" r="G67">
+        <v>46297.4229166667</v>
+      </c>
+      <c s="17" t="inlineStr" r="H67">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I67"/>
+      <c s="17" t="inlineStr" r="J67">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K67">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L67">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M67"/>
+      <c s="16" t="inlineStr" r="N67">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE CHAPA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O67">
+        <is>
+          <t xml:space="preserve">ajustando chapa</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P67"/>
+      <c s="16" t="inlineStr" r="R67">
+        <is>
+          <t xml:space="preserve">e6fa1410-be61-11f1-c305-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S67">
+        <is>
+          <t xml:space="preserve">10047017    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U67">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V67"/>
+    </row>
+    <row r="68" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A68">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B68">
+        <is>
+          <t xml:space="preserve">TR05-MESA FIXA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D68">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E68">
+        <v>46297.4229166667</v>
+      </c>
+      <c s="22" r="G68">
+        <v>46297.4395833333</v>
+      </c>
+      <c s="21" t="inlineStr" r="H68">
+        <is>
+          <t xml:space="preserve">24</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I68"/>
+      <c s="21" t="inlineStr" r="J68">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K68">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L68">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M68"/>
+      <c s="20" t="inlineStr" r="N68">
+        <is>
+          <t xml:space="preserve">REPOSIÇÃO/TROCA DE INSUMO</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O68">
+        <is>
+          <t xml:space="preserve">Falta de extrado.</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P68"/>
+      <c s="20" t="inlineStr" r="R68">
+        <is>
+          <t xml:space="preserve">9000ccc0-be62-11f1-a66f-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S68">
+        <is>
+          <t xml:space="preserve">10046136    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U68">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V68"/>
+    </row>
+    <row r="69" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A69">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B69"/>
+      <c s="17" t="inlineStr" r="D69">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E69">
+        <v>46297.4270833333</v>
+      </c>
+      <c s="18" r="G69">
+        <v>46297.4368055556</v>
+      </c>
+      <c s="17" t="inlineStr" r="H69">
+        <is>
+          <t xml:space="preserve">14</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I69"/>
+      <c s="17" t="inlineStr" r="J69">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K69">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L69">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M69"/>
+      <c s="16" t="inlineStr" r="N69">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O69">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 14 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P69"/>
+      <c s="16" t="inlineStr" r="R69">
+        <is>
+          <t xml:space="preserve">59ca35a0-be63-11f1-97ef-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S69">
+        <is>
+          <t xml:space="preserve">10046879    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U69">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V69"/>
+    </row>
+    <row r="70" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A70">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B70"/>
+      <c s="21" t="inlineStr" r="D70">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E70">
+        <v>46297.4368055556</v>
+      </c>
+      <c s="22" r="G70">
+        <v>46297.4416666667</v>
+      </c>
+      <c s="21" t="inlineStr" r="H70">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I70"/>
+      <c s="21" t="inlineStr" r="J70">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K70">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L70">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M70"/>
+      <c s="20" t="inlineStr" r="N70">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O70">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 7 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P70"/>
+      <c s="20" t="inlineStr" r="R70">
+        <is>
+          <t xml:space="preserve">4fb4f670-be65-11f1-99b6-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S70">
+        <is>
+          <t xml:space="preserve">10046879    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U70">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V70"/>
+    </row>
+    <row r="71" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A71">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B71">
+        <is>
+          <t xml:space="preserve">TR05-MESA FIXA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D71">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E71">
+        <v>46297.44375</v>
+      </c>
+      <c s="18" r="G71">
+        <v>46297.4548611111</v>
+      </c>
+      <c s="17" t="inlineStr" r="H71">
+        <is>
+          <t xml:space="preserve">16</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I71"/>
+      <c s="17" t="inlineStr" r="J71">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K71">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L71">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M71"/>
+      <c s="16" t="inlineStr" r="N71">
+        <is>
+          <t xml:space="preserve">MESA CHEIA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O71">
+        <is>
+          <t xml:space="preserve">aguardando retirada do material 6000X1000..</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P71"/>
+      <c s="16" t="inlineStr" r="R71">
+        <is>
+          <t xml:space="preserve">ba6e04b0-be66-11f1-c1c2-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S71">
+        <is>
+          <t xml:space="preserve">10046136    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U71">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V71"/>
+    </row>
+    <row r="72" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A72">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B72">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D72">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E72">
+        <v>46297.4479166667</v>
+      </c>
+      <c s="22" r="G72">
+        <v>46297.4513888889</v>
+      </c>
+      <c s="21" t="inlineStr" r="H72">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I72"/>
+      <c s="21" t="inlineStr" r="J72">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K72">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L72">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M72"/>
+      <c s="20" t="inlineStr" r="N72">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE CHAPA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O72">
+        <is>
+          <t xml:space="preserve">ajuste da chapa</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P72"/>
+      <c s="20" t="inlineStr" r="R72">
+        <is>
+          <t xml:space="preserve">7a95c2a0-be67-11f1-a0e8-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S72">
+        <is>
+          <t xml:space="preserve">10046889    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U72">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V72"/>
+    </row>
+    <row r="73" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A73">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B73">
+        <is>
+          <t xml:space="preserve">TR01-MESA TRANSPORTADORA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D73">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E73">
+        <v>46297.4534722222</v>
+      </c>
+      <c s="18" r="G73">
+        <v>46297.4555555556</v>
+      </c>
+      <c s="17" t="inlineStr" r="H73">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I73"/>
+      <c s="17" t="inlineStr" r="J73">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K73">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L73">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M73"/>
+      <c s="16" t="inlineStr" r="N73">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE CHAPA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O73">
+        <is>
+          <t xml:space="preserve">ajuste da chapa</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P73"/>
+      <c s="16" t="inlineStr" r="R73">
+        <is>
+          <t xml:space="preserve">ad0b6f40-be68-11f1-8200-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S73">
+        <is>
+          <t xml:space="preserve">10046889    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U73">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V73"/>
+    </row>
+    <row r="74" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A74">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B74">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D74">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E74">
+        <v>46297.4576388889</v>
+      </c>
+      <c s="22" r="G74">
+        <v>46297.4638888889</v>
+      </c>
+      <c s="21" t="inlineStr" r="H74">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I74"/>
+      <c s="21" t="inlineStr" r="J74">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K74">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L74">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M74"/>
+      <c s="20" t="inlineStr" r="N74">
+        <is>
+          <t xml:space="preserve">AJUSTE NO ROLO ALIMENTADOR</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O74">
+        <is>
+          <t xml:space="preserve">chapa desalinhada corte com variação  de tamanho</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P74"/>
+      <c s="20" t="inlineStr" r="R74">
+        <is>
+          <t xml:space="preserve">835efd00-be69-11f1-ce19-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S74">
+        <is>
+          <t xml:space="preserve">10046889    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U74">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V74"/>
+    </row>
+    <row r="75" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A75">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B75">
+        <is>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D75">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E75">
+        <v>46297.4583333333</v>
+      </c>
+      <c s="18" r="G75">
+        <v>46297.5</v>
+      </c>
+      <c s="17" t="inlineStr" r="H75">
+        <is>
+          <t xml:space="preserve">60</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I75"/>
+      <c s="17" t="inlineStr" r="J75">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K75">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L75">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M75"/>
+      <c s="16" t="inlineStr" r="N75">
+        <is>
+          <t xml:space="preserve">ALMOÇO / JANTA / CEIA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O75">
+        <is>
+          <t xml:space="preserve">almoço</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P75"/>
+      <c s="16" t="inlineStr" r="R75">
+        <is>
+          <t xml:space="preserve">c9a7cd50-be73-11f1-9e0a-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S75">
+        <is>
+          <t xml:space="preserve">10047019    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U75">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V75"/>
+    </row>
+    <row r="76" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A76">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B76">
+        <is>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D76">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E76">
+        <v>46297.4604166667</v>
+      </c>
+      <c s="22" r="G76">
+        <v>46297.5076388889</v>
+      </c>
+      <c s="21" t="inlineStr" r="H76">
+        <is>
+          <t xml:space="preserve">68</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I76"/>
+      <c s="21" t="inlineStr" r="J76">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K76">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L76">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M76"/>
+      <c s="20" t="inlineStr" r="N76">
+        <is>
+          <t xml:space="preserve">ALMOÇO / JANTA / CEIA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O76">
+        <is>
+          <t xml:space="preserve">Almoço</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P76"/>
+      <c s="20" t="inlineStr" r="R76">
+        <is>
+          <t xml:space="preserve">01cfea50-be6a-11f1-8b38-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S76">
+        <is>
+          <t xml:space="preserve">10046136    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U76">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V76"/>
+    </row>
+    <row r="77" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A77">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B77"/>
+      <c s="17" t="inlineStr" r="D77">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E77">
+        <v>46297.4833333333</v>
+      </c>
+      <c s="18" r="G77">
+        <v>46297.4930555556</v>
+      </c>
+      <c s="17" t="inlineStr" r="H77">
+        <is>
+          <t xml:space="preserve">14</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I77"/>
+      <c s="17" t="inlineStr" r="J77">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K77">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L77">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M77"/>
+      <c s="16" t="inlineStr" r="N77">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O77">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 14 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P77"/>
+      <c s="16" t="inlineStr" r="R77">
+        <is>
+          <t xml:space="preserve">9b9306a0-be6e-11f1-8830-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S77">
+        <is>
+          <t xml:space="preserve">10046889    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U77">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V77"/>
+    </row>
+    <row r="78" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A78">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B78">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D78">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E78">
+        <v>46297.49375</v>
+      </c>
+      <c s="22" r="G78">
+        <v>46297.5090277778</v>
+      </c>
+      <c s="21" t="inlineStr" r="H78">
+        <is>
+          <t xml:space="preserve">22</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I78"/>
+      <c s="21" t="inlineStr" r="J78">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K78">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L78">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M78"/>
+      <c s="20" t="inlineStr" r="N78">
+        <is>
+          <t xml:space="preserve">AGUARDANDO INSPEÇÃO DE  QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O78">
+        <is>
+          <t xml:space="preserve">material com ponto de pressão 0,65 por 1200 de UD 2003935928  liberado pela a qualidade</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P78"/>
+      <c s="20" t="inlineStr" r="R78">
+        <is>
+          <t xml:space="preserve">c5ca4c60-be70-11f1-a710-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S78">
+        <is>
+          <t xml:space="preserve">10046889    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U78">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V78"/>
+    </row>
+    <row r="79" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A79">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B79">
+        <is>
+          <t xml:space="preserve">TR05-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D79">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E79">
+        <v>46297.5138888889</v>
+      </c>
+      <c s="18" r="G79">
+        <v>46297.5243055556</v>
+      </c>
+      <c s="17" t="inlineStr" r="H79">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I79"/>
+      <c s="17" t="inlineStr" r="J79">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K79">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L79">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M79"/>
+      <c s="16" t="inlineStr" r="N79">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O79">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P79"/>
+      <c s="16" t="inlineStr" r="R79">
+        <is>
+          <t xml:space="preserve">c940b1a0-be74-11f1-92f3-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S79">
+        <is>
+          <t xml:space="preserve">10046136    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U79">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V79"/>
+    </row>
+    <row r="80" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A80">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B80">
+        <is>
+          <t xml:space="preserve">TR05-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D80">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E80">
+        <v>46297.525</v>
+      </c>
+      <c s="22" r="G80">
+        <v>46297.53125</v>
+      </c>
+      <c s="21" t="inlineStr" r="H80">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I80"/>
+      <c s="21" t="inlineStr" r="J80">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K80">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L80">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M80"/>
+      <c s="20" t="inlineStr" r="N80">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE CHAPA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O80">
+        <is>
+          <t xml:space="preserve">Passagem de chapa.</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P80"/>
+      <c s="20" t="inlineStr" r="R80">
+        <is>
+          <t xml:space="preserve">4f463470-be78-11f1-c958-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S80">
+        <is>
+          <t xml:space="preserve">10046136    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U80">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V80"/>
+    </row>
+    <row r="81" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A81">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B81"/>
+      <c s="17" t="inlineStr" r="D81">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E81">
+        <v>46297.5305555556</v>
+      </c>
+      <c s="18" r="G81">
+        <v>46297.5409722222</v>
+      </c>
+      <c s="17" t="inlineStr" r="H81">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I81"/>
+      <c s="17" t="inlineStr" r="J81">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K81">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L81">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M81"/>
+      <c s="16" t="inlineStr" r="N81">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O81">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P81"/>
+      <c s="16" t="inlineStr" r="R81">
+        <is>
+          <t xml:space="preserve">1da26150-be78-11f1-9692-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S81">
+        <is>
+          <t xml:space="preserve">10046889    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U81">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V81"/>
+    </row>
+    <row r="82" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A82">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B82">
+        <is>
+          <t xml:space="preserve">TR05-MESA FIXA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D82">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E82">
+        <v>46297.5319444444</v>
+      </c>
+      <c s="22" r="G82">
+        <v>46297.5340277778</v>
+      </c>
+      <c s="21" t="inlineStr" r="H82">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I82"/>
+      <c s="21" t="inlineStr" r="J82">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K82">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L82">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M82"/>
+      <c s="20" t="inlineStr" r="N82">
+        <is>
+          <t xml:space="preserve">RETIRADA DE PNC</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O82">
+        <is>
+          <t xml:space="preserve">Retirada de pnc.</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P82"/>
+      <c s="20" t="inlineStr" r="R82">
+        <is>
+          <t xml:space="preserve">681a19d0-be78-11f1-87a3-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S82">
+        <is>
+          <t xml:space="preserve">10046136    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U82">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V82"/>
+    </row>
+    <row r="83" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A83">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B83">
+        <is>
+          <t xml:space="preserve">TR01-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D83">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E83">
+        <v>46297.5416666667</v>
+      </c>
+      <c s="18" r="G83">
+        <v>46297.5479166667</v>
+      </c>
+      <c s="17" t="inlineStr" r="H83">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I83"/>
+      <c s="17" t="inlineStr" r="J83">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K83">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L83">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M83"/>
+      <c s="16" t="inlineStr" r="N83">
+        <is>
+          <t xml:space="preserve">TROCA DAS CASTANHAS DO MANDRIL</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O83">
+        <is>
+          <t xml:space="preserve">troca das castanhas</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P83"/>
+      <c s="16" t="inlineStr" r="R83">
+        <is>
+          <t xml:space="preserve">1f4e5c40-be7b-11f1-b20b-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S83">
+        <is>
+          <t xml:space="preserve">10046889    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U83">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V83"/>
+    </row>
+    <row r="84" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A84">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B84">
+        <is>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D84">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E84">
+        <v>46297.5451388889</v>
+      </c>
+      <c s="22" r="G84">
+        <v>46297.5520833333</v>
+      </c>
+      <c s="21" t="inlineStr" r="H84">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I84"/>
+      <c s="21" t="inlineStr" r="J84">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K84">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L84">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M84"/>
+      <c s="20" t="inlineStr" r="N84">
+        <is>
+          <t xml:space="preserve">TROCA DAS CASTANHAS DO MANDRIL</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O84">
+        <is>
+          <t xml:space="preserve">retirar castanhas do mandril</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P84"/>
+      <c s="20" t="inlineStr" r="R84">
+        <is>
+          <t xml:space="preserve">2c0c8ca0-be7f-11f1-9d1f-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S84">
+        <is>
+          <t xml:space="preserve">10046882    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U84">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V84"/>
+    </row>
+    <row r="85" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A85">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B85">
+        <is>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D85">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E85">
+        <v>46297.5472222222</v>
+      </c>
+      <c s="18" r="G85">
+        <v>46297.6986111111</v>
+      </c>
+      <c s="17" t="inlineStr" r="H85">
+        <is>
+          <t xml:space="preserve">218</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I85"/>
+      <c s="17" t="inlineStr" r="J85">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K85">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L85">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M85"/>
+      <c s="16" t="inlineStr" r="N85">
+        <is>
+          <t xml:space="preserve">DESENVOLVIMENTO DE NOVOS PRODUTOS</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O85">
+        <is>
+          <t xml:space="preserve">desenvolvimento de novos produtos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P85"/>
+      <c s="16" t="inlineStr" r="R85">
+        <is>
+          <t xml:space="preserve">928f8490-be7b-11f1-8d21-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S85">
+        <is>
+          <t xml:space="preserve">10046136    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U85">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V85"/>
+    </row>
+    <row r="86" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A86">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B86">
+        <is>
+          <t xml:space="preserve">TR04-ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D86">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E86">
+        <v>46297.5527777778</v>
+      </c>
+      <c s="22" r="G86">
+        <v>46297.5597222222</v>
+      </c>
+      <c s="21" t="inlineStr" r="H86">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I86"/>
+      <c s="21" t="inlineStr" r="J86">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K86">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L86">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M86"/>
+      <c s="20" t="inlineStr" r="N86">
+        <is>
+          <t xml:space="preserve">SETUP COMPLETO</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O86">
+        <is>
+          <t xml:space="preserve">trocar 0.95x1.000 para 1.50x1.000 e fazer regulagem</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P86"/>
+      <c s="20" t="inlineStr" r="R86">
+        <is>
+          <t xml:space="preserve">7e0e33a0-be7f-11f1-9f15-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S86">
+        <is>
+          <t xml:space="preserve">10046882    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U86">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V86"/>
+    </row>
+    <row r="87" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A87">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B87">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D87">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E87">
+        <v>46297.5756944444</v>
+      </c>
+      <c s="18" r="G87">
+        <v>46297.5777777778</v>
+      </c>
+      <c s="17" t="inlineStr" r="H87">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I87"/>
+      <c s="17" t="inlineStr" r="J87">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K87">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L87">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M87"/>
+      <c s="16" t="inlineStr" r="N87">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE CHAPA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O87">
+        <is>
+          <t xml:space="preserve">ajuste da chapa</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P87"/>
+      <c s="16" t="inlineStr" r="R87">
+        <is>
+          <t xml:space="preserve">3631ad80-be81-11f1-8f52-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S87">
+        <is>
+          <t xml:space="preserve">10046890    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U87">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V87"/>
+    </row>
+    <row r="88" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A88">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B88"/>
+      <c s="21" t="inlineStr" r="D88">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E88">
+        <v>46297.5881944444</v>
+      </c>
+      <c s="22" r="G88">
+        <v>46297.5972106481</v>
+      </c>
+      <c s="21" t="inlineStr" r="H88">
+        <is>
+          <t xml:space="preserve">13</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I88"/>
+      <c s="21" t="inlineStr" r="J88">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K88">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L88">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M88"/>
+      <c s="20" t="inlineStr" r="N88">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O88">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 13 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P88"/>
+      <c s="20" t="inlineStr" r="R88">
+        <is>
+          <t xml:space="preserve">bb1a6b20-be83-11f1-9c73-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S88">
+        <is>
+          <t xml:space="preserve">10046890    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U88">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V88"/>
+    </row>
+    <row r="89" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A89">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B89">
+        <is>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D89">
         <is>
           <t xml:space="preserve">TURNO B</t>
         </is>
       </c>
-      <c s="26" r="E50">
-        <v>46296.7013888889</v>
-      </c>
-      <c s="10" t="str" r="F50"/>
-      <c s="26" r="G50">
-        <v>46297.2840277778</v>
-      </c>
-      <c s="25" t="inlineStr" r="H50">
-        <is>
-          <t xml:space="preserve">839</t>
-        </is>
-      </c>
-      <c s="25" t="str" r="I50"/>
-      <c s="25" t="inlineStr" r="J50">
-        <is>
-          <t xml:space="preserve">X</t>
-        </is>
-      </c>
-      <c s="24" t="inlineStr" r="K50">
+      <c s="18" r="E89">
+        <v>46297.6375</v>
+      </c>
+      <c s="18" r="G89">
+        <v>46300.295965162</v>
+      </c>
+      <c s="17" t="inlineStr" r="H89">
+        <is>
+          <t xml:space="preserve">3.828</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I89"/>
+      <c s="17" t="inlineStr" r="J89">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K89">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L89">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M89"/>
+      <c s="16" t="inlineStr" r="N89">
+        <is>
+          <t xml:space="preserve">QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O89">
+        <is>
+          <t xml:space="preserve">esperando movimentar bobina1.50x1.000</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P89"/>
+      <c s="16" t="inlineStr" r="R89">
+        <is>
+          <t xml:space="preserve">d982a500-be8d-11f1-8c09-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S89">
+        <is>
+          <t xml:space="preserve">10046892    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U89">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V89"/>
+    </row>
+    <row r="90" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A90">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B90">
+        <is>
+          <t xml:space="preserve">TR01-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D90">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E90">
+        <v>46297.6631944444</v>
+      </c>
+      <c s="22" r="G90">
+        <v>46297.6944444444</v>
+      </c>
+      <c s="21" t="inlineStr" r="H90">
+        <is>
+          <t xml:space="preserve">45</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I90"/>
+      <c s="21" t="inlineStr" r="J90">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K90">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L90">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M90"/>
+      <c s="20" t="inlineStr" r="N90">
+        <is>
+          <t xml:space="preserve">TREINAMENTO PERIÓDICO</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O90">
+        <is>
+          <t xml:space="preserve">treinamento</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P90"/>
+      <c s="20" t="inlineStr" r="R90">
+        <is>
+          <t xml:space="preserve">eabc07d0-be92-11f1-9d68-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S90">
+        <is>
+          <t xml:space="preserve">10046891    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U90">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V90"/>
+    </row>
+    <row r="91" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A91">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B91">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D91">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E91">
+        <v>46297.6951388889</v>
+      </c>
+      <c s="18" r="G91">
+        <v>46300.295965162</v>
+      </c>
+      <c s="17" t="inlineStr" r="H91">
+        <is>
+          <t xml:space="preserve">3.745</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I91"/>
+      <c s="17" t="inlineStr" r="J91">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K91">
         <is>
           <t xml:space="preserve">Tempo Livre</t>
         </is>
       </c>
-      <c s="24" t="inlineStr" r="L50">
+      <c s="16" t="inlineStr" r="L91">
         <is>
           <t xml:space="preserve">Tempo Livre</t>
         </is>
       </c>
-      <c s="24" t="str" r="M50"/>
-      <c s="24" t="inlineStr" r="N50">
+      <c s="16" t="str" r="M91"/>
+      <c s="16" t="inlineStr" r="N91">
         <is>
           <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
         </is>
       </c>
-      <c s="24" t="inlineStr" r="O50">
+      <c s="16" t="inlineStr" r="O91">
+        <is>
+          <t xml:space="preserve">tempo livre</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P91"/>
+      <c s="16" t="inlineStr" r="R91">
+        <is>
+          <t xml:space="preserve">518d6250-be99-11f1-ce88-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S91">
+        <is>
+          <t xml:space="preserve">10046891    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U91">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V91"/>
+    </row>
+    <row r="92" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A92">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B92"/>
+      <c s="21" t="inlineStr" r="D92">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E92">
+        <v>46297.7013888889</v>
+      </c>
+      <c s="22" r="G92">
+        <v>46300.2840277778</v>
+      </c>
+      <c s="21" t="inlineStr" r="H92">
+        <is>
+          <t xml:space="preserve">3.719</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I92"/>
+      <c s="21" t="inlineStr" r="J92">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K92">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L92">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M92"/>
+      <c s="20" t="inlineStr" r="N92">
+        <is>
+          <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O92">
         <is>
           <t xml:space="preserve">Parada registrada automaticamente pelo sistema</t>
         </is>
       </c>
-      <c s="24" t="str" r="P50"/>
-      <c s="10" t="str" r="Q50"/>
-      <c s="24" t="inlineStr" r="R50">
-        <is>
-          <t xml:space="preserve">4a25c5c0-bdd1-11f1-86c2-f2050a003223</t>
-        </is>
-      </c>
-      <c s="24" t="inlineStr" r="S50">
-        <is>
-          <t xml:space="preserve">10046135    </t>
-        </is>
-      </c>
-      <c s="10" t="str" r="T50"/>
-      <c s="24" t="inlineStr" r="U50">
-        <is>
-          <t xml:space="preserve">Sim</t>
-        </is>
-      </c>
-      <c s="11" t="str" r="V50"/>
-    </row>
-    <row r="51" ht="0.05" customHeight="1"/>
+      <c s="20" t="str" r="P92"/>
+      <c s="20" t="inlineStr" r="R92">
+        <is>
+          <t xml:space="preserve">74255240-be9a-11f1-80b5-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="S92"/>
+      <c s="20" t="inlineStr" r="U92">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V92"/>
+    </row>
+    <row r="93" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A93">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 03</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B93"/>
+      <c s="17" t="inlineStr" r="D93">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E93">
+        <v>46297.7013888889</v>
+      </c>
+      <c s="18" r="G93">
+        <v>46300.2840277778</v>
+      </c>
+      <c s="17" t="inlineStr" r="H93">
+        <is>
+          <t xml:space="preserve">3.719</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I93"/>
+      <c s="17" t="inlineStr" r="J93">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K93">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L93">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M93"/>
+      <c s="16" t="inlineStr" r="N93">
+        <is>
+          <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O93">
+        <is>
+          <t xml:space="preserve">Parada registrada automaticamente pelo sistema</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P93"/>
+      <c s="16" t="inlineStr" r="R93">
+        <is>
+          <t xml:space="preserve">743a60e0-be9a-11f1-9060-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="S93"/>
+      <c s="16" t="inlineStr" r="U93">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V93"/>
+    </row>
+    <row r="94" ht="15.55" customHeight="0">
+      <c s="23" t="inlineStr" r="A94">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="24" t="str" r="B94"/>
+      <c s="10" t="str" r="C94"/>
+      <c s="25" t="inlineStr" r="D94">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="26" r="E94">
+        <v>46297.7013888889</v>
+      </c>
+      <c s="10" t="str" r="F94"/>
+      <c s="26" r="G94">
+        <v>46300.2840277778</v>
+      </c>
+      <c s="25" t="inlineStr" r="H94">
+        <is>
+          <t xml:space="preserve">3.719</t>
+        </is>
+      </c>
+      <c s="25" t="str" r="I94"/>
+      <c s="25" t="inlineStr" r="J94">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="K94">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="L94">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="24" t="str" r="M94"/>
+      <c s="24" t="inlineStr" r="N94">
+        <is>
+          <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="O94">
+        <is>
+          <t xml:space="preserve">Parada registrada automaticamente pelo sistema</t>
+        </is>
+      </c>
+      <c s="24" t="str" r="P94"/>
+      <c s="10" t="str" r="Q94"/>
+      <c s="24" t="inlineStr" r="R94">
+        <is>
+          <t xml:space="preserve">746408f0-be9a-11f1-8d0b-f2050a003223</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="S94">
+        <is>
+          <t xml:space="preserve">10046136    </t>
+        </is>
+      </c>
+      <c s="10" t="str" r="T94"/>
+      <c s="24" t="inlineStr" r="U94">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="11" t="str" r="V94"/>
+    </row>
+    <row r="95" ht="0.05" customHeight="1"/>
   </sheetData>
   <mergeCells>
     <mergeCell ref="A3:B8"/>
@@ -3215,6 +6343,226 @@
     <mergeCell ref="P50:Q50"/>
     <mergeCell ref="S50:T50"/>
     <mergeCell ref="U50:V50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="P51:Q51"/>
+    <mergeCell ref="S51:T51"/>
+    <mergeCell ref="U51:V51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="P52:Q52"/>
+    <mergeCell ref="S52:T52"/>
+    <mergeCell ref="U52:V52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="E53:F53"/>
+    <mergeCell ref="P53:Q53"/>
+    <mergeCell ref="S53:T53"/>
+    <mergeCell ref="U53:V53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="E54:F54"/>
+    <mergeCell ref="P54:Q54"/>
+    <mergeCell ref="S54:T54"/>
+    <mergeCell ref="U54:V54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="E55:F55"/>
+    <mergeCell ref="P55:Q55"/>
+    <mergeCell ref="S55:T55"/>
+    <mergeCell ref="U55:V55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="P56:Q56"/>
+    <mergeCell ref="S56:T56"/>
+    <mergeCell ref="U56:V56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="P57:Q57"/>
+    <mergeCell ref="S57:T57"/>
+    <mergeCell ref="U57:V57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="P58:Q58"/>
+    <mergeCell ref="S58:T58"/>
+    <mergeCell ref="U58:V58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="P59:Q59"/>
+    <mergeCell ref="S59:T59"/>
+    <mergeCell ref="U59:V59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="P60:Q60"/>
+    <mergeCell ref="S60:T60"/>
+    <mergeCell ref="U60:V60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="P61:Q61"/>
+    <mergeCell ref="S61:T61"/>
+    <mergeCell ref="U61:V61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="E62:F62"/>
+    <mergeCell ref="P62:Q62"/>
+    <mergeCell ref="S62:T62"/>
+    <mergeCell ref="U62:V62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="P63:Q63"/>
+    <mergeCell ref="S63:T63"/>
+    <mergeCell ref="U63:V63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="E64:F64"/>
+    <mergeCell ref="P64:Q64"/>
+    <mergeCell ref="S64:T64"/>
+    <mergeCell ref="U64:V64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="P65:Q65"/>
+    <mergeCell ref="S65:T65"/>
+    <mergeCell ref="U65:V65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="P66:Q66"/>
+    <mergeCell ref="S66:T66"/>
+    <mergeCell ref="U66:V66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="P67:Q67"/>
+    <mergeCell ref="S67:T67"/>
+    <mergeCell ref="U67:V67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="E68:F68"/>
+    <mergeCell ref="P68:Q68"/>
+    <mergeCell ref="S68:T68"/>
+    <mergeCell ref="U68:V68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="E69:F69"/>
+    <mergeCell ref="P69:Q69"/>
+    <mergeCell ref="S69:T69"/>
+    <mergeCell ref="U69:V69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="P70:Q70"/>
+    <mergeCell ref="S70:T70"/>
+    <mergeCell ref="U70:V70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="E71:F71"/>
+    <mergeCell ref="P71:Q71"/>
+    <mergeCell ref="S71:T71"/>
+    <mergeCell ref="U71:V71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="P72:Q72"/>
+    <mergeCell ref="S72:T72"/>
+    <mergeCell ref="U72:V72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="P73:Q73"/>
+    <mergeCell ref="S73:T73"/>
+    <mergeCell ref="U73:V73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="P74:Q74"/>
+    <mergeCell ref="S74:T74"/>
+    <mergeCell ref="U74:V74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="P75:Q75"/>
+    <mergeCell ref="S75:T75"/>
+    <mergeCell ref="U75:V75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="E76:F76"/>
+    <mergeCell ref="P76:Q76"/>
+    <mergeCell ref="S76:T76"/>
+    <mergeCell ref="U76:V76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="E77:F77"/>
+    <mergeCell ref="P77:Q77"/>
+    <mergeCell ref="S77:T77"/>
+    <mergeCell ref="U77:V77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="E78:F78"/>
+    <mergeCell ref="P78:Q78"/>
+    <mergeCell ref="S78:T78"/>
+    <mergeCell ref="U78:V78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="E79:F79"/>
+    <mergeCell ref="P79:Q79"/>
+    <mergeCell ref="S79:T79"/>
+    <mergeCell ref="U79:V79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="E80:F80"/>
+    <mergeCell ref="P80:Q80"/>
+    <mergeCell ref="S80:T80"/>
+    <mergeCell ref="U80:V80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="E81:F81"/>
+    <mergeCell ref="P81:Q81"/>
+    <mergeCell ref="S81:T81"/>
+    <mergeCell ref="U81:V81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="E82:F82"/>
+    <mergeCell ref="P82:Q82"/>
+    <mergeCell ref="S82:T82"/>
+    <mergeCell ref="U82:V82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="E83:F83"/>
+    <mergeCell ref="P83:Q83"/>
+    <mergeCell ref="S83:T83"/>
+    <mergeCell ref="U83:V83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="E84:F84"/>
+    <mergeCell ref="P84:Q84"/>
+    <mergeCell ref="S84:T84"/>
+    <mergeCell ref="U84:V84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="E85:F85"/>
+    <mergeCell ref="P85:Q85"/>
+    <mergeCell ref="S85:T85"/>
+    <mergeCell ref="U85:V85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="E86:F86"/>
+    <mergeCell ref="P86:Q86"/>
+    <mergeCell ref="S86:T86"/>
+    <mergeCell ref="U86:V86"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="E87:F87"/>
+    <mergeCell ref="P87:Q87"/>
+    <mergeCell ref="S87:T87"/>
+    <mergeCell ref="U87:V87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="E88:F88"/>
+    <mergeCell ref="P88:Q88"/>
+    <mergeCell ref="S88:T88"/>
+    <mergeCell ref="U88:V88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="E89:F89"/>
+    <mergeCell ref="P89:Q89"/>
+    <mergeCell ref="S89:T89"/>
+    <mergeCell ref="U89:V89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="E90:F90"/>
+    <mergeCell ref="P90:Q90"/>
+    <mergeCell ref="S90:T90"/>
+    <mergeCell ref="U90:V90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="E91:F91"/>
+    <mergeCell ref="P91:Q91"/>
+    <mergeCell ref="S91:T91"/>
+    <mergeCell ref="U91:V91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="E92:F92"/>
+    <mergeCell ref="P92:Q92"/>
+    <mergeCell ref="S92:T92"/>
+    <mergeCell ref="U92:V92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="E93:F93"/>
+    <mergeCell ref="P93:Q93"/>
+    <mergeCell ref="S93:T93"/>
+    <mergeCell ref="U93:V93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="E94:F94"/>
+    <mergeCell ref="P94:Q94"/>
+    <mergeCell ref="S94:T94"/>
+    <mergeCell ref="U94:V94"/>
   </mergeCells>
   <pageMargins left="0.0393700787401575" right="0.0393700787401575" top="0.0393700787401575" bottom="0.0393700787401575" header="0.0393700787401575" footer="0.0393700787401575"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>

--- a/Base_Interrupcoes.xlsx
+++ b/Base_Interrupcoes.xlsx
@@ -253,16 +253,16 @@
     <xf applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" numFmtId="82" fontId="5" fillId="4" borderId="0">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" numFmtId="0" fontId="5" fillId="4" borderId="6">
+    <xf applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" numFmtId="0" fontId="5" fillId="3" borderId="6">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" numFmtId="0" fontId="5" fillId="4" borderId="7">
+    <xf applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" numFmtId="0" fontId="5" fillId="3" borderId="7">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" numFmtId="0" fontId="5" fillId="4" borderId="7">
+    <xf applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" numFmtId="0" fontId="5" fillId="3" borderId="7">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" numFmtId="82" fontId="5" fillId="4" borderId="7">
+    <xf applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" numFmtId="82" fontId="5" fillId="3" borderId="7">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -466,7 +466,7 @@
       <c s="4" t="str" r="A7"/>
       <c s="7" t="inlineStr" r="T7">
         <is>
-          <t xml:space="preserve">Emissão: 05/10/2026</t>
+          <t xml:space="preserve">Emissão: 06/10/2026</t>
         </is>
       </c>
       <c s="5" t="str" r="V7"/>
@@ -475,7 +475,7 @@
       <c s="4" t="str" r="A8"/>
       <c s="8" t="inlineStr" r="F8">
         <is>
-          <t xml:space="preserve">Período: 01/10/2026 até 04/10/2026; Turno: Todos; Tempo: Calendário</t>
+          <t xml:space="preserve">Período: 01/10/2026 até 05/10/2026; Turno: Todos; Tempo: Calendário</t>
         </is>
       </c>
       <c s="5" t="str" r="V8"/>
@@ -1790,18 +1790,18 @@
       </c>
       <c s="16" t="inlineStr" r="K33">
         <is>
-          <t xml:space="preserve">Operacional</t>
+          <t xml:space="preserve">Manutenção Corretiva Pontes Rolantes</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="L33">
         <is>
-          <t xml:space="preserve">Operacional</t>
+          <t xml:space="preserve">Manutenção Corretiva Pontes Rolantes</t>
         </is>
       </c>
       <c s="16" t="str" r="M33"/>
       <c s="16" t="inlineStr" r="N33">
         <is>
-          <t xml:space="preserve">MESA CHEIA</t>
+          <t xml:space="preserve">Ponte Rolante Quebrada</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="O33">
@@ -1809,7 +1809,11 @@
           <t xml:space="preserve">Ponte indisponível</t>
         </is>
       </c>
-      <c s="16" t="str" r="P33"/>
+      <c s="16" t="inlineStr" r="P33">
+        <is>
+          <t xml:space="preserve">000010034135</t>
+        </is>
+      </c>
       <c s="16" t="inlineStr" r="R33">
         <is>
           <t xml:space="preserve">bfc37850-bda8-11f1-b5f3-f2050a003223</t>
@@ -3106,12 +3110,12 @@
     <row r="52" ht="15.6" customHeight="0">
       <c s="19" t="inlineStr" r="A52">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 04</t>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="B52">
         <is>
-          <t xml:space="preserve">TR04-DESENROLADOR</t>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
         </is>
       </c>
       <c s="21" t="inlineStr" r="D52">
@@ -3123,11 +3127,11 @@
         <v>46297.2916666667</v>
       </c>
       <c s="22" r="G52">
-        <v>46297.2986111111</v>
+        <v>46297.3020833333</v>
       </c>
       <c s="21" t="inlineStr" r="H52">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c s="21" t="str" r="I52"/>
@@ -3154,18 +3158,18 @@
       </c>
       <c s="20" t="inlineStr" r="O52">
         <is>
-          <t xml:space="preserve">DDS</t>
+          <t xml:space="preserve">dds e assinatura dos documentos</t>
         </is>
       </c>
       <c s="20" t="str" r="P52"/>
       <c s="20" t="inlineStr" r="R52">
         <is>
-          <t xml:space="preserve">942e4bd0-be4c-11f1-ca85-f2050a003223</t>
+          <t xml:space="preserve">61a3b7a0-be4b-11f1-9cbf-f2050a003223</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="S52">
         <is>
-          <t xml:space="preserve">10047019    </t>
+          <t xml:space="preserve">10046873    </t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="U52">
@@ -3178,12 +3182,12 @@
     <row r="53" ht="15.55" customHeight="0">
       <c s="15" t="inlineStr" r="A53">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 05</t>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="B53">
         <is>
-          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
         </is>
       </c>
       <c s="17" t="inlineStr" r="D53">
@@ -3195,11 +3199,11 @@
         <v>46297.2916666667</v>
       </c>
       <c s="18" r="G53">
-        <v>46297.3055555556</v>
+        <v>46297.2986111111</v>
       </c>
       <c s="17" t="inlineStr" r="H53">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c s="17" t="str" r="I53"/>
@@ -3226,18 +3230,18 @@
       </c>
       <c s="16" t="inlineStr" r="O53">
         <is>
-          <t xml:space="preserve">dds com supervisor QUEDA DE MATERIAIS</t>
+          <t xml:space="preserve">DDS</t>
         </is>
       </c>
       <c s="16" t="str" r="P53"/>
       <c s="16" t="inlineStr" r="R53">
         <is>
-          <t xml:space="preserve">167ccc00-be4e-11f1-cdcf-f2050a003223</t>
+          <t xml:space="preserve">942e4bd0-be4c-11f1-ca85-f2050a003223</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="S53">
         <is>
-          <t xml:space="preserve">10046135    </t>
+          <t xml:space="preserve">10047019    </t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="U53">
@@ -3250,12 +3254,12 @@
     <row r="54" ht="15.6" customHeight="0">
       <c s="19" t="inlineStr" r="A54">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 01</t>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="B54">
         <is>
-          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
         </is>
       </c>
       <c s="21" t="inlineStr" r="D54">
@@ -3267,11 +3271,11 @@
         <v>46297.2916666667</v>
       </c>
       <c s="22" r="G54">
-        <v>46297.3020833333</v>
+        <v>46297.3055555556</v>
       </c>
       <c s="21" t="inlineStr" r="H54">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c s="21" t="str" r="I54"/>
@@ -3298,18 +3302,18 @@
       </c>
       <c s="20" t="inlineStr" r="O54">
         <is>
-          <t xml:space="preserve">dds e assinatura dos documentos</t>
+          <t xml:space="preserve">dds com supervisor QUEDA DE MATERIAIS</t>
         </is>
       </c>
       <c s="20" t="str" r="P54"/>
       <c s="20" t="inlineStr" r="R54">
         <is>
-          <t xml:space="preserve">61a3b7a0-be4b-11f1-9cbf-f2050a003223</t>
+          <t xml:space="preserve">167ccc00-be4e-11f1-cdcf-f2050a003223</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="S54">
         <is>
-          <t xml:space="preserve">10046873    </t>
+          <t xml:space="preserve">10046135    </t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="U54">
@@ -5763,11 +5767,11 @@
         <v>46297.6375</v>
       </c>
       <c s="18" r="G89">
-        <v>46300.295965162</v>
+        <v>46297.6666666667</v>
       </c>
       <c s="17" t="inlineStr" r="H89">
         <is>
-          <t xml:space="preserve">3.828</t>
+          <t xml:space="preserve">42</t>
         </is>
       </c>
       <c s="17" t="str" r="I89"/>
@@ -5890,12 +5894,12 @@
     <row r="91" ht="15.6" customHeight="0">
       <c s="15" t="inlineStr" r="A91">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 01</t>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="B91">
         <is>
-          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+          <t xml:space="preserve">TR04-CARRO DE ENTRADA</t>
         </is>
       </c>
       <c s="17" t="inlineStr" r="D91">
@@ -5904,14 +5908,14 @@
         </is>
       </c>
       <c s="18" r="E91">
-        <v>46297.6951388889</v>
+        <v>46297.6673611111</v>
       </c>
       <c s="18" r="G91">
-        <v>46300.295965162</v>
+        <v>46300.2909722222</v>
       </c>
       <c s="17" t="inlineStr" r="H91">
         <is>
-          <t xml:space="preserve">3.745</t>
+          <t xml:space="preserve">3.778</t>
         </is>
       </c>
       <c s="17" t="str" r="I91"/>
@@ -5933,23 +5937,23 @@
       <c s="16" t="str" r="M91"/>
       <c s="16" t="inlineStr" r="N91">
         <is>
-          <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
+          <t xml:space="preserve">FALTA DEMANDA</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="O91">
         <is>
-          <t xml:space="preserve">tempo livre</t>
+          <t xml:space="preserve">falta demanda</t>
         </is>
       </c>
       <c s="16" t="str" r="P91"/>
       <c s="16" t="inlineStr" r="R91">
         <is>
-          <t xml:space="preserve">518d6250-be99-11f1-ce88-f2050a003223</t>
+          <t xml:space="preserve">f9c30370-c0ca-11f1-b641-f2050a003223</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="S91">
         <is>
-          <t xml:space="preserve">10046891    </t>
+          <t xml:space="preserve">10046892    </t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="U91">
@@ -5962,24 +5966,28 @@
     <row r="92" ht="15.6" customHeight="0">
       <c s="19" t="inlineStr" r="A92">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 02</t>
-        </is>
-      </c>
-      <c s="20" t="str" r="B92"/>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B92">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
       <c s="21" t="inlineStr" r="D92">
         <is>
           <t xml:space="preserve">TURNO B</t>
         </is>
       </c>
       <c s="22" r="E92">
-        <v>46297.7013888889</v>
+        <v>46297.6951388889</v>
       </c>
       <c s="22" r="G92">
-        <v>46300.2840277778</v>
+        <v>46300.2909722222</v>
       </c>
       <c s="21" t="inlineStr" r="H92">
         <is>
-          <t xml:space="preserve">3.719</t>
+          <t xml:space="preserve">3.738</t>
         </is>
       </c>
       <c s="21" t="str" r="I92"/>
@@ -6006,16 +6014,20 @@
       </c>
       <c s="20" t="inlineStr" r="O92">
         <is>
-          <t xml:space="preserve">Parada registrada automaticamente pelo sistema</t>
+          <t xml:space="preserve">tempo livre</t>
         </is>
       </c>
       <c s="20" t="str" r="P92"/>
       <c s="20" t="inlineStr" r="R92">
         <is>
-          <t xml:space="preserve">74255240-be9a-11f1-80b5-f2050a003223</t>
-        </is>
-      </c>
-      <c s="20" t="str" r="S92"/>
+          <t xml:space="preserve">518d6250-be99-11f1-ce88-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S92">
+        <is>
+          <t xml:space="preserve">10046891    </t>
+        </is>
+      </c>
       <c s="20" t="inlineStr" r="U92">
         <is>
           <t xml:space="preserve">Sim</t>
@@ -6026,7 +6038,7 @@
     <row r="93" ht="15.55" customHeight="0">
       <c s="15" t="inlineStr" r="A93">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 03</t>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
         </is>
       </c>
       <c s="16" t="str" r="B93"/>
@@ -6076,7 +6088,7 @@
       <c s="16" t="str" r="P93"/>
       <c s="16" t="inlineStr" r="R93">
         <is>
-          <t xml:space="preserve">743a60e0-be9a-11f1-9060-f2050a003223</t>
+          <t xml:space="preserve">74255240-be9a-11f1-80b5-f2050a003223</t>
         </is>
       </c>
       <c s="16" t="str" r="S93"/>
@@ -6087,79 +6099,4431 @@
       </c>
       <c s="5" t="str" r="V93"/>
     </row>
-    <row r="94" ht="15.55" customHeight="0">
-      <c s="23" t="inlineStr" r="A94">
+    <row r="94" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A94">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 03</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B94"/>
+      <c s="21" t="inlineStr" r="D94">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E94">
+        <v>46297.7013888889</v>
+      </c>
+      <c s="22" r="G94">
+        <v>46300.2840277778</v>
+      </c>
+      <c s="21" t="inlineStr" r="H94">
+        <is>
+          <t xml:space="preserve">3.719</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I94"/>
+      <c s="21" t="inlineStr" r="J94">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K94">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L94">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M94"/>
+      <c s="20" t="inlineStr" r="N94">
+        <is>
+          <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O94">
+        <is>
+          <t xml:space="preserve">Parada registrada automaticamente pelo sistema</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P94"/>
+      <c s="20" t="inlineStr" r="R94">
+        <is>
+          <t xml:space="preserve">743a60e0-be9a-11f1-9060-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="S94"/>
+      <c s="20" t="inlineStr" r="U94">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V94"/>
+    </row>
+    <row r="95" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A95">
         <is>
           <t xml:space="preserve">TRANSVERSAL 05</t>
         </is>
       </c>
-      <c s="24" t="str" r="B94"/>
-      <c s="10" t="str" r="C94"/>
-      <c s="25" t="inlineStr" r="D94">
+      <c s="16" t="inlineStr" r="B95">
+        <is>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D95">
         <is>
           <t xml:space="preserve">TURNO B</t>
         </is>
       </c>
-      <c s="26" r="E94">
+      <c s="18" r="E95">
         <v>46297.7013888889</v>
       </c>
-      <c s="10" t="str" r="F94"/>
-      <c s="26" r="G94">
+      <c s="18" r="G95">
         <v>46300.2840277778</v>
       </c>
-      <c s="25" t="inlineStr" r="H94">
+      <c s="17" t="inlineStr" r="H95">
         <is>
           <t xml:space="preserve">3.719</t>
         </is>
       </c>
-      <c s="25" t="str" r="I94"/>
-      <c s="25" t="inlineStr" r="J94">
-        <is>
-          <t xml:space="preserve">X</t>
-        </is>
-      </c>
-      <c s="24" t="inlineStr" r="K94">
+      <c s="17" t="str" r="I95"/>
+      <c s="17" t="inlineStr" r="J95">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K95">
         <is>
           <t xml:space="preserve">Tempo Livre</t>
         </is>
       </c>
-      <c s="24" t="inlineStr" r="L94">
+      <c s="16" t="inlineStr" r="L95">
         <is>
           <t xml:space="preserve">Tempo Livre</t>
         </is>
       </c>
-      <c s="24" t="str" r="M94"/>
-      <c s="24" t="inlineStr" r="N94">
+      <c s="16" t="str" r="M95"/>
+      <c s="16" t="inlineStr" r="N95">
         <is>
           <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
         </is>
       </c>
-      <c s="24" t="inlineStr" r="O94">
+      <c s="16" t="inlineStr" r="O95">
+        <is>
+          <t xml:space="preserve">espera fim de semana</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P95"/>
+      <c s="16" t="inlineStr" r="R95">
+        <is>
+          <t xml:space="preserve">746408f0-be9a-11f1-8d0b-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S95">
+        <is>
+          <t xml:space="preserve">10046136    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U95">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V95"/>
+    </row>
+    <row r="96" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A96">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B96">
+        <is>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D96">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E96">
+        <v>46300.2916666667</v>
+      </c>
+      <c s="22" r="G96">
+        <v>46300.2986111111</v>
+      </c>
+      <c s="21" t="inlineStr" r="H96">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I96"/>
+      <c s="21" t="inlineStr" r="J96">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K96">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L96">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M96"/>
+      <c s="20" t="inlineStr" r="N96">
+        <is>
+          <t xml:space="preserve">DDS</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O96">
+        <is>
+          <t xml:space="preserve">dds</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P96"/>
+      <c s="20" t="inlineStr" r="R96">
+        <is>
+          <t xml:space="preserve">1176a761-c0ad-11f1-8444-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S96">
+        <is>
+          <t xml:space="preserve">10046136    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U96">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V96"/>
+    </row>
+    <row r="97" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A97">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B97">
+        <is>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D97">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E97">
+        <v>46300.2916666667</v>
+      </c>
+      <c s="18" r="G97">
+        <v>46300.2986111111</v>
+      </c>
+      <c s="17" t="inlineStr" r="H97">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I97"/>
+      <c s="17" t="inlineStr" r="J97">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K97">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L97">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M97"/>
+      <c s="16" t="inlineStr" r="N97">
+        <is>
+          <t xml:space="preserve">DDS</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O97">
+        <is>
+          <t xml:space="preserve">DDS</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P97"/>
+      <c s="16" t="inlineStr" r="R97">
+        <is>
+          <t xml:space="preserve">2a2a1a30-c0b2-11f1-9e79-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S97">
+        <is>
+          <t xml:space="preserve">10046892    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U97">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V97"/>
+    </row>
+    <row r="98" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A98">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B98">
+        <is>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D98">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E98">
+        <v>46300.2993055556</v>
+      </c>
+      <c s="22" r="G98">
+        <v>46300.30625</v>
+      </c>
+      <c s="21" t="inlineStr" r="H98">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I98"/>
+      <c s="21" t="inlineStr" r="J98">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K98">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L98">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M98"/>
+      <c s="20" t="inlineStr" r="N98">
+        <is>
+          <t xml:space="preserve">ASSINATURA DE DOCUMENTOS</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O98">
+        <is>
+          <t xml:space="preserve">Assinatura de documentos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P98"/>
+      <c s="20" t="inlineStr" r="R98">
+        <is>
+          <t xml:space="preserve">7f0aec50-c0b2-11f1-c142-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S98">
+        <is>
+          <t xml:space="preserve">10046892    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U98">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V98"/>
+    </row>
+    <row r="99" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A99">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B99">
+        <is>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D99">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E99">
+        <v>46300.2993055556</v>
+      </c>
+      <c s="18" r="G99">
+        <v>46300.3534722222</v>
+      </c>
+      <c s="17" t="inlineStr" r="H99">
+        <is>
+          <t xml:space="preserve">78</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I99"/>
+      <c s="17" t="inlineStr" r="J99">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K99">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L99">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M99"/>
+      <c s="16" t="inlineStr" r="N99">
+        <is>
+          <t xml:space="preserve">MELHORIA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O99">
+        <is>
+          <t xml:space="preserve">desenvolvimento de novo produto</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P99"/>
+      <c s="16" t="inlineStr" r="R99">
+        <is>
+          <t xml:space="preserve">23fa2fb0-c0ad-11f1-c249-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S99">
+        <is>
+          <t xml:space="preserve">10046136    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U99">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V99"/>
+    </row>
+    <row r="100" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A100">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B100">
+        <is>
+          <t xml:space="preserve">TR01-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D100">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E100">
+        <v>46300.3006944444</v>
+      </c>
+      <c s="22" r="G100">
+        <v>46300.3048611111</v>
+      </c>
+      <c s="21" t="inlineStr" r="H100">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I100"/>
+      <c s="21" t="inlineStr" r="J100">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K100">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L100">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M100"/>
+      <c s="20" t="inlineStr" r="N100">
+        <is>
+          <t xml:space="preserve">AGUARDANDO INSPEÇÃO DE  QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O100">
+        <is>
+          <t xml:space="preserve">aguardando espeto de qualidade</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P100"/>
+      <c s="20" t="inlineStr" r="R100">
+        <is>
+          <t xml:space="preserve">799b8c50-c0a5-11f1-ae45-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S100">
+        <is>
+          <t xml:space="preserve">10047268    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U100">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V100"/>
+    </row>
+    <row r="101" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A101">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B101">
+        <is>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D101">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E101">
+        <v>46300.3076388889</v>
+      </c>
+      <c s="18" r="G101">
+        <v>46300.3145833333</v>
+      </c>
+      <c s="17" t="inlineStr" r="H101">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I101"/>
+      <c s="17" t="inlineStr" r="J101">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K101">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L101">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M101"/>
+      <c s="16" t="inlineStr" r="N101">
+        <is>
+          <t xml:space="preserve">TROCA DAS CASTANHAS DO MANDRIL</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O101">
+        <is>
+          <t xml:space="preserve">colocar castanhas no mandril</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P101"/>
+      <c s="16" t="inlineStr" r="R101">
+        <is>
+          <t xml:space="preserve">ff62c210-c0b2-11f1-b333-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S101">
+        <is>
+          <t xml:space="preserve">10046892    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U101">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V101"/>
+    </row>
+    <row r="102" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A102">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B102">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D102">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E102">
+        <v>46300.3104166667</v>
+      </c>
+      <c s="22" r="G102">
+        <v>46300.3173611111</v>
+      </c>
+      <c s="21" t="inlineStr" r="H102">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I102"/>
+      <c s="21" t="inlineStr" r="J102">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K102">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L102">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M102"/>
+      <c s="20" t="inlineStr" r="N102">
+        <is>
+          <t xml:space="preserve">AJUSTE NO ROLO ALIMENTADOR</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O102">
+        <is>
+          <t xml:space="preserve">ajuste no rolo alimentador</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P102"/>
+      <c s="20" t="inlineStr" r="R102">
+        <is>
+          <t xml:space="preserve">5faa3e20-c0a7-11f1-8200-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S102">
+        <is>
+          <t xml:space="preserve">10047268    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U102">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V102"/>
+    </row>
+    <row r="103" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A103">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B103">
+        <is>
+          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D103">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E103">
+        <v>46300.3118055556</v>
+      </c>
+      <c s="18" r="G103">
+        <v>46300.3388888889</v>
+      </c>
+      <c s="17" t="inlineStr" r="H103">
+        <is>
+          <t xml:space="preserve">39</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I103"/>
+      <c s="17" t="inlineStr" r="J103">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K103">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L103">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M103"/>
+      <c s="16" t="inlineStr" r="N103">
+        <is>
+          <t xml:space="preserve">QUALIDADE DA MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O103">
+        <is>
+          <t xml:space="preserve">Esperando  a qualidade para verifica a bobina 2,25mm com variação de largura para 1,310mm
+obs: voltar bobina para o deposito material reprovado. UD 2003977951</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P103"/>
+      <c s="16" t="inlineStr" r="R103">
+        <is>
+          <t xml:space="preserve">cf85cd40-c0a7-11f1-be7f-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S103">
+        <is>
+          <t xml:space="preserve">10047272    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U103">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V103"/>
+    </row>
+    <row r="104" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A104">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B104">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D104">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E104">
+        <v>46300.3180555556</v>
+      </c>
+      <c s="22" r="G104">
+        <v>46300.325</v>
+      </c>
+      <c s="21" t="inlineStr" r="H104">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I104"/>
+      <c s="21" t="inlineStr" r="J104">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K104">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L104">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M104"/>
+      <c s="20" t="inlineStr" r="N104">
+        <is>
+          <t xml:space="preserve">AJUSTE DA MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O104">
+        <is>
+          <t xml:space="preserve">ajuste na mesa de 2MT PARA 2,40</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P104"/>
+      <c s="20" t="inlineStr" r="R104">
+        <is>
+          <t xml:space="preserve">e7d59910-c0a8-11f1-9ed2-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S104">
+        <is>
+          <t xml:space="preserve">10047268    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U104">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V104"/>
+    </row>
+    <row r="105" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A105">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B105">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D105">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E105">
+        <v>46300.3256944444</v>
+      </c>
+      <c s="18" r="G105">
+        <v>46300.3277777778</v>
+      </c>
+      <c s="17" t="inlineStr" r="H105">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I105"/>
+      <c s="17" t="inlineStr" r="J105">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K105">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L105">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M105"/>
+      <c s="16" t="inlineStr" r="N105">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE CHAPA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O105">
+        <is>
+          <t xml:space="preserve">ajeitando a chapa na mesa</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P105"/>
+      <c s="16" t="inlineStr" r="R105">
+        <is>
+          <t xml:space="preserve">604da2b0-c0aa-11f1-cb82-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S105">
+        <is>
+          <t xml:space="preserve">10047268    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U105">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V105"/>
+    </row>
+    <row r="106" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A106">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B106">
+        <is>
+          <t xml:space="preserve">TR01-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D106">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E106">
+        <v>46300.3284722222</v>
+      </c>
+      <c s="22" r="G106">
+        <v>46300.3305555556</v>
+      </c>
+      <c s="21" t="inlineStr" r="H106">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I106"/>
+      <c s="21" t="inlineStr" r="J106">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K106">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L106">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M106"/>
+      <c s="20" t="inlineStr" r="N106">
+        <is>
+          <t xml:space="preserve">AGUARDANDO INSPEÇÃO DE  QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O106">
+        <is>
+          <t xml:space="preserve">material liberado com uma leve oxidação  como tipo [A] [UD2003683061, 200363109</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P106"/>
+      <c s="20" t="inlineStr" r="R106">
+        <is>
+          <t xml:space="preserve">f7e7c150-c0aa-11f1-a5dc-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S106">
+        <is>
+          <t xml:space="preserve">10047268    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U106">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V106"/>
+    </row>
+    <row r="107" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A107">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B107">
+        <is>
+          <t xml:space="preserve">TR02-GUILHOTINA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D107">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E107">
+        <v>46300.3402777778</v>
+      </c>
+      <c s="18" r="G107">
+        <v>46300.3611111111</v>
+      </c>
+      <c s="17" t="inlineStr" r="H107">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I107"/>
+      <c s="17" t="inlineStr" r="J107">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K107">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L107">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M107"/>
+      <c s="16" t="inlineStr" r="N107">
+        <is>
+          <t xml:space="preserve">SETUP COMPLETO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O107">
+        <is>
+          <t xml:space="preserve">SETUP COMPLETO, retirada de castanhas, regulagem da guilhotina e endireitadeira</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P107"/>
+      <c s="16" t="inlineStr" r="R107">
+        <is>
+          <t xml:space="preserve">047ba2d0-c0ae-11f1-8397-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S107">
+        <is>
+          <t xml:space="preserve">10047276    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U107">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V107"/>
+    </row>
+    <row r="108" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A108">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B108">
+        <is>
+          <t xml:space="preserve">TR05-MESA FIXA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D108">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E108">
+        <v>46300.3583333333</v>
+      </c>
+      <c s="22" r="G108">
+        <v>46300.3777777778</v>
+      </c>
+      <c s="21" t="inlineStr" r="H108">
+        <is>
+          <t xml:space="preserve">28</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I108"/>
+      <c s="21" t="inlineStr" r="J108">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K108">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L108">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M108"/>
+      <c s="20" t="inlineStr" r="N108">
+        <is>
+          <t xml:space="preserve">MESA CHEIA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O108">
+        <is>
+          <t xml:space="preserve">aguardando retirada do material 6000X1000..</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P108"/>
+      <c s="20" t="inlineStr" r="R108">
+        <is>
+          <t xml:space="preserve">07986bd0-c0b1-11f1-9c95-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S108">
+        <is>
+          <t xml:space="preserve">10046136    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U108">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V108"/>
+    </row>
+    <row r="109" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A109">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B109">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D109">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E109">
+        <v>46300.3805555556</v>
+      </c>
+      <c s="18" r="G109">
+        <v>46300.3826388889</v>
+      </c>
+      <c s="17" t="inlineStr" r="H109">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I109"/>
+      <c s="17" t="inlineStr" r="J109">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K109">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L109">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M109"/>
+      <c s="16" t="inlineStr" r="N109">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE CHAPA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O109">
+        <is>
+          <t xml:space="preserve">ajustando chapa</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P109"/>
+      <c s="16" t="inlineStr" r="R109">
+        <is>
+          <t xml:space="preserve">88cfcf50-c0b5-11f1-b23d-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S109">
+        <is>
+          <t xml:space="preserve">10047268    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U109">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V109"/>
+    </row>
+    <row r="110" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A110">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B110">
+        <is>
+          <t xml:space="preserve">TR05-MESA FIXA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D110">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E110">
+        <v>46300.3861111111</v>
+      </c>
+      <c s="22" r="G110">
+        <v>46300.4020833333</v>
+      </c>
+      <c s="21" t="inlineStr" r="H110">
+        <is>
+          <t xml:space="preserve">23</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I110"/>
+      <c s="21" t="inlineStr" r="J110">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K110">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L110">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M110"/>
+      <c s="20" t="inlineStr" r="N110">
+        <is>
+          <t xml:space="preserve">MESA CHEIA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O110">
+        <is>
+          <t xml:space="preserve">aguardando retirada do material 6000X1000..</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P110"/>
+      <c s="20" t="inlineStr" r="R110">
+        <is>
+          <t xml:space="preserve">9dfd4c80-c0b6-11f1-b796-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S110">
+        <is>
+          <t xml:space="preserve">10046136    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U110">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V110"/>
+    </row>
+    <row r="111" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A111">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B111">
+        <is>
+          <t xml:space="preserve">TR04-ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D111">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E111">
+        <v>46300.3881944444</v>
+      </c>
+      <c s="18" r="G111">
+        <v>46300.3951388889</v>
+      </c>
+      <c s="17" t="inlineStr" r="H111">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I111"/>
+      <c s="17" t="inlineStr" r="J111">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K111">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L111">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M111"/>
+      <c s="16" t="inlineStr" r="N111">
+        <is>
+          <t xml:space="preserve">SETUP COMPLETO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O111">
+        <is>
+          <t xml:space="preserve">trocar 1.50x1.000 para 0.60x1.000 e fazer regulagem</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P111"/>
+      <c s="16" t="inlineStr" r="R111">
+        <is>
+          <t xml:space="preserve">9a9254c0-c0b9-11f1-8091-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S111">
+        <is>
+          <t xml:space="preserve">10046892    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U111">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V111"/>
+    </row>
+    <row r="112" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A112">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B112">
+        <is>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D112">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E112">
+        <v>46300.3958333333</v>
+      </c>
+      <c s="22" r="G112">
+        <v>46300.3993055556</v>
+      </c>
+      <c s="21" t="inlineStr" r="H112">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I112"/>
+      <c s="21" t="inlineStr" r="J112">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K112">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L112">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M112"/>
+      <c s="20" t="inlineStr" r="N112">
+        <is>
+          <t xml:space="preserve">QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O112">
+        <is>
+          <t xml:space="preserve">Bobina 0.60x1.000 de UD. 2003390329 com oxidação OBS. Inspetor de qualidade Alisson autorizou cortar</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P112"/>
+      <c s="20" t="inlineStr" r="R112">
+        <is>
+          <t xml:space="preserve">fcb77400-c0b9-11f1-b898-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S112">
+        <is>
+          <t xml:space="preserve">10046892    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U112">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V112"/>
+    </row>
+    <row r="113" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A113">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B113">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D113">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E113">
+        <v>46300.3965277778</v>
+      </c>
+      <c s="18" r="G113">
+        <v>46300.3993055556</v>
+      </c>
+      <c s="17" t="inlineStr" r="H113">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I113"/>
+      <c s="17" t="inlineStr" r="J113">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K113">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L113">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M113"/>
+      <c s="16" t="inlineStr" r="N113">
+        <is>
+          <t xml:space="preserve">AJUSTE DA MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O113">
+        <is>
+          <t xml:space="preserve">ajuste da mesa para tamanho de chapa</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P113"/>
+      <c s="16" t="inlineStr" r="R113">
+        <is>
+          <t xml:space="preserve">afbcfdb0-c0b8-11f1-bca4-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S113">
+        <is>
+          <t xml:space="preserve">10047268    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U113">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V113"/>
+    </row>
+    <row r="114" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A114">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B114">
+        <is>
+          <t xml:space="preserve">TR02-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D114">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E114">
+        <v>46300.4006944444</v>
+      </c>
+      <c s="22" r="G114">
+        <v>46301.2930115394</v>
+      </c>
+      <c s="21" t="inlineStr" r="H114">
+        <is>
+          <t xml:space="preserve">1.285</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I114"/>
+      <c s="21" t="inlineStr" r="J114">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K114">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L114">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M114"/>
+      <c s="20" t="inlineStr" r="N114">
+        <is>
+          <t xml:space="preserve">FALTA DEMANDA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O114">
+        <is>
+          <t xml:space="preserve">FALTA DE DEMANDA.</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P114"/>
+      <c s="20" t="inlineStr" r="R114">
+        <is>
+          <t xml:space="preserve">7e0b2b60-c0b9-11f1-a844-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="S114"/>
+      <c s="20" t="inlineStr" r="U114">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V114"/>
+    </row>
+    <row r="115" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A115">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B115">
+        <is>
+          <t xml:space="preserve">TR05-MESA FIXA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D115">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E115">
+        <v>46300.4083333333</v>
+      </c>
+      <c s="18" r="G115">
+        <v>46300.4284722222</v>
+      </c>
+      <c s="17" t="inlineStr" r="H115">
+        <is>
+          <t xml:space="preserve">29</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I115"/>
+      <c s="17" t="inlineStr" r="J115">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K115">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L115">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M115"/>
+      <c s="16" t="inlineStr" r="N115">
+        <is>
+          <t xml:space="preserve">MESA CHEIA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O115">
+        <is>
+          <t xml:space="preserve">aguardando retirada do material 6000X1000..</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P115"/>
+      <c s="16" t="inlineStr" r="R115">
+        <is>
+          <t xml:space="preserve">1aeca610-c0bb-11f1-cf7a-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S115">
+        <is>
+          <t xml:space="preserve">10046136    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U115">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V115"/>
+    </row>
+    <row r="116" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A116">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B116">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D116">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E116">
+        <v>46300.4145833333</v>
+      </c>
+      <c s="22" r="G116">
+        <v>46300.4173611111</v>
+      </c>
+      <c s="21" t="inlineStr" r="H116">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I116"/>
+      <c s="21" t="inlineStr" r="J116">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K116">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L116">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M116"/>
+      <c s="20" t="inlineStr" r="N116">
+        <is>
+          <t xml:space="preserve">QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O116">
+        <is>
+          <t xml:space="preserve">qualidade verificando material</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P116"/>
+      <c s="20" t="inlineStr" r="R116">
+        <is>
+          <t xml:space="preserve">524dc890-c0bc-11f1-83b5-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S116">
+        <is>
+          <t xml:space="preserve">10047269    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U116">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V116"/>
+    </row>
+    <row r="117" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A117">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B117">
+        <is>
+          <t xml:space="preserve">TR01-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D117">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E117">
+        <v>46300.4194444444</v>
+      </c>
+      <c s="18" r="G117">
+        <v>46300.4215277778</v>
+      </c>
+      <c s="17" t="inlineStr" r="H117">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I117"/>
+      <c s="17" t="inlineStr" r="J117">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K117">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L117">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M117"/>
+      <c s="16" t="inlineStr" r="N117">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE CHAPA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O117">
+        <is>
+          <t xml:space="preserve">ajuste na bobina bobina oval</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P117"/>
+      <c s="16" t="inlineStr" r="R117">
+        <is>
+          <t xml:space="preserve">5356deb0-c0bd-11f1-bdcb-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S117">
+        <is>
+          <t xml:space="preserve">10047269    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U117">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V117"/>
+    </row>
+    <row r="118" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A118">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B118"/>
+      <c s="21" t="inlineStr" r="D118">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E118">
+        <v>46300.4229166667</v>
+      </c>
+      <c s="22" r="G118">
+        <v>46300.4333333333</v>
+      </c>
+      <c s="21" t="inlineStr" r="H118">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I118"/>
+      <c s="21" t="inlineStr" r="J118">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K118">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L118">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M118"/>
+      <c s="20" t="inlineStr" r="N118">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O118">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P118"/>
+      <c s="20" t="inlineStr" r="R118">
+        <is>
+          <t xml:space="preserve">0379a8e0-c0be-11f1-8301-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S118">
+        <is>
+          <t xml:space="preserve">10047269    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U118">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V118"/>
+    </row>
+    <row r="119" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A119">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B119">
+        <is>
+          <t xml:space="preserve">TR05-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D119">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E119">
+        <v>46300.4333333333</v>
+      </c>
+      <c s="18" r="G119">
+        <v>46300.4361111111</v>
+      </c>
+      <c s="17" t="inlineStr" r="H119">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I119"/>
+      <c s="17" t="inlineStr" r="J119">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K119">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L119">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M119"/>
+      <c s="16" t="inlineStr" r="N119">
+        <is>
+          <t xml:space="preserve">RETIRADA DE PNC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O119">
+        <is>
+          <t xml:space="preserve">retirada de PNC</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P119"/>
+      <c s="16" t="inlineStr" r="R119">
+        <is>
+          <t xml:space="preserve">081edc10-c0c0-11f1-af4c-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S119">
+        <is>
+          <t xml:space="preserve">10046136    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U119">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V119"/>
+    </row>
+    <row r="120" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A120">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B120">
+        <is>
+          <t xml:space="preserve">TR01-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D120">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E120">
+        <v>46300.4340277778</v>
+      </c>
+      <c s="22" r="G120">
+        <v>46300.4354166667</v>
+      </c>
+      <c s="21" t="inlineStr" r="H120">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I120"/>
+      <c s="21" t="inlineStr" r="J120">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K120">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L120">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M120"/>
+      <c s="20" t="inlineStr" r="N120">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE CHAPA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O120">
+        <is>
+          <t xml:space="preserve">ajuste na bobina bobina oval</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P120"/>
+      <c s="20" t="inlineStr" r="R120">
+        <is>
+          <t xml:space="preserve">7e94f0a0-c0c0-11f1-addf-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S120">
+        <is>
+          <t xml:space="preserve">10047269    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U120">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V120"/>
+    </row>
+    <row r="121" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A121">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B121">
+        <is>
+          <t xml:space="preserve">TR01-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D121">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E121">
+        <v>46300.4361111111</v>
+      </c>
+      <c s="18" r="G121">
+        <v>46300.4381944444</v>
+      </c>
+      <c s="17" t="inlineStr" r="H121">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I121"/>
+      <c s="17" t="inlineStr" r="J121">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K121">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L121">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M121"/>
+      <c s="16" t="inlineStr" r="N121">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE CHAPA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O121">
+        <is>
+          <t xml:space="preserve">ajuste na bobina bobina oval</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P121"/>
+      <c s="16" t="inlineStr" r="R121">
+        <is>
+          <t xml:space="preserve">a349e9a1-c0c0-11f1-bec7-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S121">
+        <is>
+          <t xml:space="preserve">10047269    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U121">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V121"/>
+    </row>
+    <row r="122" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A122">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B122"/>
+      <c s="21" t="inlineStr" r="D122">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E122">
+        <v>46300.4375</v>
+      </c>
+      <c s="22" r="G122">
+        <v>46300.4479166667</v>
+      </c>
+      <c s="21" t="inlineStr" r="H122">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I122"/>
+      <c s="21" t="inlineStr" r="J122">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K122">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L122">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M122"/>
+      <c s="20" t="inlineStr" r="N122">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O122">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P122"/>
+      <c s="20" t="inlineStr" r="R122">
+        <is>
+          <t xml:space="preserve">e4a3f440-c0c0-11f1-973e-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S122">
+        <is>
+          <t xml:space="preserve">10046136    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U122">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V122"/>
+    </row>
+    <row r="123" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A123">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B123">
+        <is>
+          <t xml:space="preserve">TR01-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D123">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E123">
+        <v>46300.4395833333</v>
+      </c>
+      <c s="18" r="G123">
+        <v>46300.4444444444</v>
+      </c>
+      <c s="17" t="inlineStr" r="H123">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I123"/>
+      <c s="17" t="inlineStr" r="J123">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K123">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L123">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M123"/>
+      <c s="16" t="inlineStr" r="N123">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE CHAPA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O123">
+        <is>
+          <t xml:space="preserve">ajuste na bobina bobina oval</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P123"/>
+      <c s="16" t="inlineStr" r="R123">
+        <is>
+          <t xml:space="preserve">5000d910-c0c1-11f1-91a4-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S123">
+        <is>
+          <t xml:space="preserve">10047269    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U123">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V123"/>
+    </row>
+    <row r="124" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A124">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B124">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D124">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E124">
+        <v>46300.4451388889</v>
+      </c>
+      <c s="22" r="G124">
+        <v>46300.4548611111</v>
+      </c>
+      <c s="21" t="inlineStr" r="H124">
+        <is>
+          <t xml:space="preserve">14</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I124"/>
+      <c s="21" t="inlineStr" r="J124">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K124">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L124">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M124"/>
+      <c s="20" t="inlineStr" r="N124">
+        <is>
+          <t xml:space="preserve">QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O124">
+        <is>
+          <t xml:space="preserve">avaliando material</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P124"/>
+      <c s="20" t="inlineStr" r="R124">
+        <is>
+          <t xml:space="preserve">680e6bc0-c0c2-11f1-9226-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S124">
+        <is>
+          <t xml:space="preserve">10047269    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U124">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V124"/>
+    </row>
+    <row r="125" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A125">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B125">
+        <is>
+          <t xml:space="preserve">TR05-MESA FIXA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D125">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E125">
+        <v>46300.4486111111</v>
+      </c>
+      <c s="18" r="G125">
+        <v>46300.4625</v>
+      </c>
+      <c s="17" t="inlineStr" r="H125">
+        <is>
+          <t xml:space="preserve">20</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I125"/>
+      <c s="17" t="inlineStr" r="J125">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K125">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L125">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M125"/>
+      <c s="16" t="inlineStr" r="N125">
+        <is>
+          <t xml:space="preserve">MESA CHEIA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O125">
+        <is>
+          <t xml:space="preserve">aguardando retirada do material 6000X1000..</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P125"/>
+      <c s="16" t="inlineStr" r="R125">
+        <is>
+          <t xml:space="preserve">f8b33360-c0c5-11f1-8f9f-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S125">
+        <is>
+          <t xml:space="preserve">10046136    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U125">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V125"/>
+    </row>
+    <row r="126" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A126">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B126">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D126">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E126">
+        <v>46300.4631944444</v>
+      </c>
+      <c s="22" r="G126">
+        <v>46300.4680555556</v>
+      </c>
+      <c s="21" t="inlineStr" r="H126">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I126"/>
+      <c s="21" t="inlineStr" r="J126">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K126">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L126">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M126"/>
+      <c s="20" t="inlineStr" r="N126">
+        <is>
+          <t xml:space="preserve">AGUARDANDO INSPEÇÃO DE  QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O126">
+        <is>
+          <t xml:space="preserve">material liberado pela qualidade com uma leve oxidação  como tipo [A] UD 2003683109</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P126"/>
+      <c s="20" t="inlineStr" r="R126">
+        <is>
+          <t xml:space="preserve">12aab130-c0c6-11f1-ca26-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S126">
+        <is>
+          <t xml:space="preserve">10047269    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U126">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V126"/>
+    </row>
+    <row r="127" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A127">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B127">
+        <is>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D127">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E127">
+        <v>46300.4833333333</v>
+      </c>
+      <c s="18" r="G127">
+        <v>46300.4930555556</v>
+      </c>
+      <c s="17" t="inlineStr" r="H127">
+        <is>
+          <t xml:space="preserve">14</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I127"/>
+      <c s="17" t="inlineStr" r="J127">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K127">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L127">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M127"/>
+      <c s="16" t="inlineStr" r="N127">
+        <is>
+          <t xml:space="preserve">AGUARDANDO INSPEÇÃO DE  QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O127">
+        <is>
+          <t xml:space="preserve">0,60 x por 1000 bobina de UD 2003401644  com oxidação OBS. O Inspetor de qualidade autorizou cortar</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P127"/>
+      <c s="16" t="inlineStr" r="R127">
+        <is>
+          <t xml:space="preserve">7c1fc660-c0ca-11f1-ca81-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S127">
+        <is>
+          <t xml:space="preserve">10047456    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U127">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V127"/>
+    </row>
+    <row r="128" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A128">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B128">
+        <is>
+          <t xml:space="preserve">TR05-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D128">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E128">
+        <v>46300.4868055556</v>
+      </c>
+      <c s="22" r="G128">
+        <v>46300.4909722222</v>
+      </c>
+      <c s="21" t="inlineStr" r="H128">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I128"/>
+      <c s="21" t="inlineStr" r="J128">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K128">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L128">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M128"/>
+      <c s="20" t="inlineStr" r="N128">
+        <is>
+          <t xml:space="preserve">AJUSTE DA MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O128">
+        <is>
+          <t xml:space="preserve">Ajuste da mesa móvel</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P128"/>
+      <c s="20" t="inlineStr" r="R128">
+        <is>
+          <t xml:space="preserve">d1292f20-c0ca-11f1-b686-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S128">
+        <is>
+          <t xml:space="preserve">10046139    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U128">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V128"/>
+    </row>
+    <row r="129" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A129">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B129">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D129">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E129">
+        <v>46300.4888888889</v>
+      </c>
+      <c s="18" r="G129">
+        <v>46300.4909722222</v>
+      </c>
+      <c s="17" t="inlineStr" r="H129">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I129"/>
+      <c s="17" t="inlineStr" r="J129">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K129">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L129">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M129"/>
+      <c s="16" t="inlineStr" r="N129">
+        <is>
+          <t xml:space="preserve">AJUSTE DE MESA GUIA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O129">
+        <is>
+          <t xml:space="preserve">ajuste da chapa na mesa</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P129"/>
+      <c s="16" t="inlineStr" r="R129">
+        <is>
+          <t xml:space="preserve">50195e90-c0cb-11f1-862d-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S129">
+        <is>
+          <t xml:space="preserve">10047269    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U129">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V129"/>
+    </row>
+    <row r="130" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A130">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B130">
+        <is>
+          <t xml:space="preserve">TR05-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D130">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E130">
+        <v>46300.4972222222</v>
+      </c>
+      <c s="22" r="G130">
+        <v>46300.5159722222</v>
+      </c>
+      <c s="21" t="inlineStr" r="H130">
+        <is>
+          <t xml:space="preserve">27</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I130"/>
+      <c s="21" t="inlineStr" r="J130">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K130">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L130">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M130"/>
+      <c s="20" t="inlineStr" r="N130">
+        <is>
+          <t xml:space="preserve">MESA CHEIA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O130">
+        <is>
+          <t xml:space="preserve">aguardando retirada do material 6000X1000..</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P130"/>
+      <c s="20" t="inlineStr" r="R130">
+        <is>
+          <t xml:space="preserve">f4b12ef0-c0cc-11f1-a44e-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S130">
+        <is>
+          <t xml:space="preserve">10046139    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U130">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V130"/>
+    </row>
+    <row r="131" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A131">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B131">
+        <is>
+          <t xml:space="preserve">TR05-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D131">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E131">
+        <v>46300.5173611111</v>
+      </c>
+      <c s="18" r="G131">
+        <v>46300.5277777778</v>
+      </c>
+      <c s="17" t="inlineStr" r="H131">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I131"/>
+      <c s="17" t="inlineStr" r="J131">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K131">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L131">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M131"/>
+      <c s="16" t="inlineStr" r="N131">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O131">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P131"/>
+      <c s="16" t="inlineStr" r="R131">
+        <is>
+          <t xml:space="preserve">fbb798c0-c0d0-11f1-aa24-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S131">
+        <is>
+          <t xml:space="preserve">10046139    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U131">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V131"/>
+    </row>
+    <row r="132" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A132">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B132"/>
+      <c s="21" t="inlineStr" r="D132">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E132">
+        <v>46300.5347222222</v>
+      </c>
+      <c s="22" r="G132">
+        <v>46300.5402777778</v>
+      </c>
+      <c s="21" t="inlineStr" r="H132">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I132"/>
+      <c s="21" t="inlineStr" r="J132">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K132">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L132">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M132"/>
+      <c s="20" t="inlineStr" r="N132">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O132">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 8 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P132"/>
+      <c s="20" t="inlineStr" r="R132">
+        <is>
+          <t xml:space="preserve">79fe8880-c0d4-11f1-bb3d-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S132">
+        <is>
+          <t xml:space="preserve">10046139    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U132">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V132"/>
+    </row>
+    <row r="133" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A133">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B133">
+        <is>
+          <t xml:space="preserve">TR05-MESA FIXA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D133">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E133">
+        <v>46300.5430555556</v>
+      </c>
+      <c s="18" r="G133">
+        <v>46300.5597222222</v>
+      </c>
+      <c s="17" t="inlineStr" r="H133">
+        <is>
+          <t xml:space="preserve">24</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I133"/>
+      <c s="17" t="inlineStr" r="J133">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K133">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L133">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M133"/>
+      <c s="16" t="inlineStr" r="N133">
+        <is>
+          <t xml:space="preserve">MESA CHEIA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O133">
+        <is>
+          <t xml:space="preserve">aguardando retirada do material 6000X1000..</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P133"/>
+      <c s="16" t="inlineStr" r="R133">
+        <is>
+          <t xml:space="preserve">2c1712c0-c0d6-11f1-a6cf-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S133">
+        <is>
+          <t xml:space="preserve">10046139    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U133">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V133"/>
+    </row>
+    <row r="134" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A134">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B134">
+        <is>
+          <t xml:space="preserve">TR01-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D134">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E134">
+        <v>46300.5465277778</v>
+      </c>
+      <c s="22" r="G134">
+        <v>46300.5638888889</v>
+      </c>
+      <c s="21" t="inlineStr" r="H134">
+        <is>
+          <t xml:space="preserve">25</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I134"/>
+      <c s="21" t="inlineStr" r="J134">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K134">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L134">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M134"/>
+      <c s="20" t="inlineStr" r="N134">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE ESPECIAIS</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O134">
+        <is>
+          <t xml:space="preserve">volta bobina para o estoque material zim especial</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P134"/>
+      <c s="20" t="inlineStr" r="R134">
+        <is>
+          <t xml:space="preserve">f1f5fb00-c0d6-11f1-c60d-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S134">
+        <is>
+          <t xml:space="preserve">10047270    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U134">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V134"/>
+    </row>
+    <row r="135" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A135">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B135">
+        <is>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D135">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E135">
+        <v>46300.5625</v>
+      </c>
+      <c s="18" r="G135">
+        <v>46300.5694444444</v>
+      </c>
+      <c s="17" t="inlineStr" r="H135">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I135"/>
+      <c s="17" t="inlineStr" r="J135">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K135">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L135">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M135"/>
+      <c s="16" t="inlineStr" r="N135">
+        <is>
+          <t xml:space="preserve">SETUP COMPLETO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O135">
+        <is>
+          <t xml:space="preserve">trocar 0.60x1.000 para 1.20x1.000 e fazer regulagem</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P135"/>
+      <c s="16" t="inlineStr" r="R135">
+        <is>
+          <t xml:space="preserve">9c29cfc0-c0dc-11f1-844c-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S135">
+        <is>
+          <t xml:space="preserve">10047456    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U135">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V135"/>
+    </row>
+    <row r="136" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A136">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B136">
+        <is>
+          <t xml:space="preserve">TR05-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D136">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E136">
+        <v>46300.5631944444</v>
+      </c>
+      <c s="22" r="G136">
+        <v>46300.5694444444</v>
+      </c>
+      <c s="21" t="inlineStr" r="H136">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I136"/>
+      <c s="21" t="inlineStr" r="J136">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K136">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L136">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M136"/>
+      <c s="20" t="inlineStr" r="N136">
+        <is>
+          <t xml:space="preserve">MESA CHEIA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O136">
+        <is>
+          <t xml:space="preserve">aguardando retirada do material 6000X1000..</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P136"/>
+      <c s="20" t="inlineStr" r="R136">
+        <is>
+          <t xml:space="preserve">40f7c820-c0da-11f1-b39a-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S136">
+        <is>
+          <t xml:space="preserve">10046139    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U136">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V136"/>
+    </row>
+    <row r="137" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A137">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B137">
+        <is>
+          <t xml:space="preserve">TR01-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D137">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E137">
+        <v>46300.5645833333</v>
+      </c>
+      <c s="18" r="G137">
+        <v>46300.5694444444</v>
+      </c>
+      <c s="17" t="inlineStr" r="H137">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I137"/>
+      <c s="17" t="inlineStr" r="J137">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K137">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L137">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M137"/>
+      <c s="16" t="inlineStr" r="N137">
+        <is>
+          <t xml:space="preserve">MEP - ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O137">
+        <is>
+          <t xml:space="preserve">aguardando op de ponte do mep retira bobina e abastecer</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P137"/>
+      <c s="16" t="inlineStr" r="R137">
+        <is>
+          <t xml:space="preserve">8e160f90-c0da-11f1-9ec5-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S137">
+        <is>
+          <t xml:space="preserve">10047270    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U137">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V137"/>
+    </row>
+    <row r="138" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A138">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B138">
+        <is>
+          <t xml:space="preserve">TR01-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D138">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E138">
+        <v>46300.5701388889</v>
+      </c>
+      <c s="22" r="G138">
+        <v>46300.5777777778</v>
+      </c>
+      <c s="21" t="inlineStr" r="H138">
+        <is>
+          <t xml:space="preserve">11</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I138"/>
+      <c s="21" t="inlineStr" r="J138">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K138">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L138">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M138"/>
+      <c s="20" t="inlineStr" r="N138">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O138">
+        <is>
+          <t xml:space="preserve">abastecimento</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P138"/>
+      <c s="20" t="inlineStr" r="R138">
+        <is>
+          <t xml:space="preserve">57a2d2b0-c0dd-11f1-85dd-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S138">
+        <is>
+          <t xml:space="preserve">10047270    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U138">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V138"/>
+    </row>
+    <row r="139" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A139">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B139">
+        <is>
+          <t xml:space="preserve">TR05-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D139">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E139">
+        <v>46300.5722222222</v>
+      </c>
+      <c s="18" r="G139">
+        <v>46300.5826388889</v>
+      </c>
+      <c s="17" t="inlineStr" r="H139">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I139"/>
+      <c s="17" t="inlineStr" r="J139">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K139">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L139">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M139"/>
+      <c s="16" t="inlineStr" r="N139">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O139">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P139"/>
+      <c s="16" t="inlineStr" r="R139">
+        <is>
+          <t xml:space="preserve">01dee900-c0dc-11f1-b382-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S139">
+        <is>
+          <t xml:space="preserve">10046139    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U139">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V139"/>
+    </row>
+    <row r="140" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A140">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B140">
+        <is>
+          <t xml:space="preserve">TR05-MESA FIXA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D140">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E140">
+        <v>46300.5833333333</v>
+      </c>
+      <c s="22" r="G140">
+        <v>46300.6006944444</v>
+      </c>
+      <c s="21" t="inlineStr" r="H140">
+        <is>
+          <t xml:space="preserve">25</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I140"/>
+      <c s="21" t="inlineStr" r="J140">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K140">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L140">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M140"/>
+      <c s="20" t="inlineStr" r="N140">
+        <is>
+          <t xml:space="preserve">MESA CHEIA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O140">
+        <is>
+          <t xml:space="preserve">aguardando retirada do material 6000X1000..</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P140"/>
+      <c s="20" t="inlineStr" r="R140">
+        <is>
+          <t xml:space="preserve">b2b2e880-c0e1-11f1-8903-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S140">
+        <is>
+          <t xml:space="preserve">10046139    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U140">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V140"/>
+    </row>
+    <row r="141" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A141">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B141"/>
+      <c s="17" t="inlineStr" r="D141">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E141">
+        <v>46300.6027777778</v>
+      </c>
+      <c s="18" r="G141">
+        <v>46300.6097222222</v>
+      </c>
+      <c s="17" t="inlineStr" r="H141">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I141"/>
+      <c s="17" t="inlineStr" r="J141">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K141">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L141">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M141"/>
+      <c s="16" t="inlineStr" r="N141">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O141">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 10 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P141"/>
+      <c s="16" t="inlineStr" r="R141">
+        <is>
+          <t xml:space="preserve">37c58730-c0e2-11f1-c929-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S141">
+        <is>
+          <t xml:space="preserve">10047271    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U141">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V141"/>
+    </row>
+    <row r="142" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A142">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B142">
+        <is>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D142">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E142">
+        <v>46300.6145833333</v>
+      </c>
+      <c s="22" r="G142">
+        <v>46300.6215277778</v>
+      </c>
+      <c s="21" t="inlineStr" r="H142">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I142"/>
+      <c s="21" t="inlineStr" r="J142">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K142">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L142">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M142"/>
+      <c s="20" t="inlineStr" r="N142">
+        <is>
+          <t xml:space="preserve">QUALIDADE DA MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O142">
+        <is>
+          <t xml:space="preserve">Material 1.95mm 6000x1000 UD 12346645 está com oxidação o material foi liberado para cortar de 2m como pnc</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P142"/>
+      <c s="20" t="inlineStr" r="R142">
+        <is>
+          <t xml:space="preserve">bbc16940-c0e3-11f1-a925-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S142">
+        <is>
+          <t xml:space="preserve">10046139    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U142">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V142"/>
+    </row>
+    <row r="143" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A143">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B143">
+        <is>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D143">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E143">
+        <v>46300.625</v>
+      </c>
+      <c s="18" r="G143">
+        <v>46300.6319444444</v>
+      </c>
+      <c s="17" t="inlineStr" r="H143">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I143"/>
+      <c s="17" t="inlineStr" r="J143">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K143">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L143">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M143"/>
+      <c s="16" t="inlineStr" r="N143">
+        <is>
+          <t xml:space="preserve">QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O143">
+        <is>
+          <t xml:space="preserve">Bobina 1.20x1000  de UD.2003979964 com oxidação OBS. Inspetor de qualidade Davi autorizou cortar.</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P143"/>
+      <c s="16" t="inlineStr" r="R143">
+        <is>
+          <t xml:space="preserve">7918e8d0-c0e7-11f1-ae30-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S143">
+        <is>
+          <t xml:space="preserve">10048030    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U143">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V143"/>
+    </row>
+    <row r="144" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A144">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B144">
+        <is>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D144">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E144">
+        <v>46300.6354166667</v>
+      </c>
+      <c s="22" r="G144">
+        <v>46300.6458333333</v>
+      </c>
+      <c s="21" t="inlineStr" r="H144">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I144"/>
+      <c s="21" t="inlineStr" r="J144">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K144">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L144">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M144"/>
+      <c s="20" t="inlineStr" r="N144">
+        <is>
+          <t xml:space="preserve">QUALIDADE DA MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O144">
+        <is>
+          <t xml:space="preserve">Material 1.95mm 6000x1000 UD 12346645 está com oxidação o material foi liberado para cortar de 2m como pnc.</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P144"/>
+      <c s="20" t="inlineStr" r="R144">
+        <is>
+          <t xml:space="preserve">4a9d93f0-c0e9-11f1-c8f9-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S144">
+        <is>
+          <t xml:space="preserve">10046139    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U144">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V144"/>
+    </row>
+    <row r="145" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A145">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B145"/>
+      <c s="17" t="inlineStr" r="D145">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E145">
+        <v>46300.6375</v>
+      </c>
+      <c s="18" r="G145">
+        <v>46300.6458333333</v>
+      </c>
+      <c s="17" t="inlineStr" r="H145">
+        <is>
+          <t xml:space="preserve">12</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I145"/>
+      <c s="17" t="inlineStr" r="J145">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K145">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L145">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M145"/>
+      <c s="16" t="inlineStr" r="N145">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O145">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 12 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P145"/>
+      <c s="16" t="inlineStr" r="R145">
+        <is>
+          <t xml:space="preserve">3acd1db0-c0e9-11f1-8511-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S145">
+        <is>
+          <t xml:space="preserve">10047271    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U145">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V145"/>
+    </row>
+    <row r="146" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A146">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B146">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D146">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E146">
+        <v>46300.6479166667</v>
+      </c>
+      <c s="22" r="G146">
+        <v>46300.6506944444</v>
+      </c>
+      <c s="21" t="inlineStr" r="H146">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I146"/>
+      <c s="21" t="inlineStr" r="J146">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K146">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L146">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M146"/>
+      <c s="20" t="inlineStr" r="N146">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE CHAPA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O146">
+        <is>
+          <t xml:space="preserve">ajuste da chapa</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P146"/>
+      <c s="20" t="inlineStr" r="R146">
+        <is>
+          <t xml:space="preserve">46273c20-c0eb-11f1-a7e3-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S146">
+        <is>
+          <t xml:space="preserve">10047271    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U146">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V146"/>
+    </row>
+    <row r="147" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A147">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B147">
+        <is>
+          <t xml:space="preserve">TR05-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D147">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E147">
+        <v>46300.6583333333</v>
+      </c>
+      <c s="18" r="G147">
+        <v>46300.66875</v>
+      </c>
+      <c s="17" t="inlineStr" r="H147">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I147"/>
+      <c s="17" t="inlineStr" r="J147">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K147">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L147">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M147"/>
+      <c s="16" t="inlineStr" r="N147">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O147">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P147"/>
+      <c s="16" t="inlineStr" r="R147">
+        <is>
+          <t xml:space="preserve">4d89ba90-c0ed-11f1-cf1d-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S147">
+        <is>
+          <t xml:space="preserve">10046139    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U147">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V147"/>
+    </row>
+    <row r="148" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A148">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B148">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D148">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E148">
+        <v>46300.6645833333</v>
+      </c>
+      <c s="22" r="G148">
+        <v>46300.6659722222</v>
+      </c>
+      <c s="21" t="inlineStr" r="H148">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I148"/>
+      <c s="21" t="inlineStr" r="J148">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K148">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L148">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M148"/>
+      <c s="20" t="inlineStr" r="N148">
+        <is>
+          <t xml:space="preserve">QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O148">
+        <is>
+          <t xml:space="preserve">material com leve amassado na borda material foi liberado para estoque como bom UD:2003992458</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P148"/>
+      <c s="20" t="inlineStr" r="R148">
+        <is>
+          <t xml:space="preserve">adb51030-c0ee-11f1-a7de-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S148">
+        <is>
+          <t xml:space="preserve">10047271    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U148">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V148"/>
+    </row>
+    <row r="149" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A149">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B149">
+        <is>
+          <t xml:space="preserve">TR05-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D149">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E149">
+        <v>46300.6722222222</v>
+      </c>
+      <c s="18" r="G149">
+        <v>46300.675</v>
+      </c>
+      <c s="17" t="inlineStr" r="H149">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I149"/>
+      <c s="17" t="inlineStr" r="J149">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K149">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L149">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M149"/>
+      <c s="16" t="inlineStr" r="N149">
+        <is>
+          <t xml:space="preserve">RETIRADA DE PNC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O149">
+        <is>
+          <t xml:space="preserve">retirada de pnc</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P149"/>
+      <c s="16" t="inlineStr" r="R149">
+        <is>
+          <t xml:space="preserve">2e447b40-c0f0-11f1-aa7b-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S149">
+        <is>
+          <t xml:space="preserve">10046139    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U149">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V149"/>
+    </row>
+    <row r="150" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A150">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B150">
+        <is>
+          <t xml:space="preserve">TR05-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D150">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E150">
+        <v>46300.6777777778</v>
+      </c>
+      <c s="22" r="G150">
+        <v>46300.6798611111</v>
+      </c>
+      <c s="21" t="inlineStr" r="H150">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I150"/>
+      <c s="21" t="inlineStr" r="J150">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K150">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L150">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M150"/>
+      <c s="20" t="inlineStr" r="N150">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE FARDO</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O150">
+        <is>
+          <t xml:space="preserve">passagem de fardo</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P150"/>
+      <c s="20" t="inlineStr" r="R150">
+        <is>
+          <t xml:space="preserve">45ba13b0-c0f1-11f1-a6a5-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S150">
+        <is>
+          <t xml:space="preserve">10046139    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U150">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V150"/>
+    </row>
+    <row r="151" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A151">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B151">
+        <is>
+          <t xml:space="preserve">TR05-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D151">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E151">
+        <v>46300.6888888889</v>
+      </c>
+      <c s="18" r="G151">
+        <v>46300.6909722222</v>
+      </c>
+      <c s="17" t="inlineStr" r="H151">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I151"/>
+      <c s="17" t="inlineStr" r="J151">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K151">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L151">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M151"/>
+      <c s="16" t="inlineStr" r="N151">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE FARDO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O151">
+        <is>
+          <t xml:space="preserve">passagem de fardo</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P151"/>
+      <c s="16" t="inlineStr" r="R151">
+        <is>
+          <t xml:space="preserve">876b2d10-c0f3-11f1-97d6-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S151">
+        <is>
+          <t xml:space="preserve">10046139    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U151">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V151"/>
+    </row>
+    <row r="152" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A152">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B152">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D152">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E152">
+        <v>46300.6944444444</v>
+      </c>
+      <c s="22" r="G152">
+        <v>46301.2930115394</v>
+      </c>
+      <c s="21" t="inlineStr" r="H152">
+        <is>
+          <t xml:space="preserve">862</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I152"/>
+      <c s="21" t="inlineStr" r="J152">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K152">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L152">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M152"/>
+      <c s="20" t="inlineStr" r="N152">
+        <is>
+          <t xml:space="preserve">FALTA DEMANDA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O152">
+        <is>
+          <t xml:space="preserve">TEMPO LIVRE</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P152"/>
+      <c s="20" t="inlineStr" r="R152">
+        <is>
+          <t xml:space="preserve">47a9ce60-c0f4-11f1-947b-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S152">
+        <is>
+          <t xml:space="preserve">10047271    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U152">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V152"/>
+    </row>
+    <row r="153" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A153">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 03</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B153"/>
+      <c s="17" t="inlineStr" r="D153">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E153">
+        <v>46300.7013888889</v>
+      </c>
+      <c s="18" r="G153">
+        <v>46301.2840277778</v>
+      </c>
+      <c s="17" t="inlineStr" r="H153">
+        <is>
+          <t xml:space="preserve">839</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I153"/>
+      <c s="17" t="inlineStr" r="J153">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K153">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L153">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M153"/>
+      <c s="16" t="inlineStr" r="N153">
+        <is>
+          <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O153">
         <is>
           <t xml:space="preserve">Parada registrada automaticamente pelo sistema</t>
         </is>
       </c>
-      <c s="24" t="str" r="P94"/>
-      <c s="10" t="str" r="Q94"/>
-      <c s="24" t="inlineStr" r="R94">
-        <is>
-          <t xml:space="preserve">746408f0-be9a-11f1-8d0b-f2050a003223</t>
-        </is>
-      </c>
-      <c s="24" t="inlineStr" r="S94">
-        <is>
-          <t xml:space="preserve">10046136    </t>
-        </is>
-      </c>
-      <c s="10" t="str" r="T94"/>
-      <c s="24" t="inlineStr" r="U94">
-        <is>
-          <t xml:space="preserve">Sim</t>
-        </is>
-      </c>
-      <c s="11" t="str" r="V94"/>
-    </row>
-    <row r="95" ht="0.05" customHeight="1"/>
+      <c s="16" t="str" r="P153"/>
+      <c s="16" t="inlineStr" r="R153">
+        <is>
+          <t xml:space="preserve">f4dfe370-c0f5-11f1-c191-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="S153"/>
+      <c s="16" t="inlineStr" r="U153">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V153"/>
+    </row>
+    <row r="154" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A154">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B154"/>
+      <c s="21" t="inlineStr" r="D154">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E154">
+        <v>46300.7013888889</v>
+      </c>
+      <c s="22" r="G154">
+        <v>46301.2840277778</v>
+      </c>
+      <c s="21" t="inlineStr" r="H154">
+        <is>
+          <t xml:space="preserve">839</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I154"/>
+      <c s="21" t="inlineStr" r="J154">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K154">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L154">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M154"/>
+      <c s="20" t="inlineStr" r="N154">
+        <is>
+          <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O154">
+        <is>
+          <t xml:space="preserve">Parada registrada automaticamente pelo sistema</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P154"/>
+      <c s="20" t="inlineStr" r="R154">
+        <is>
+          <t xml:space="preserve">f4fe8f00-c0f5-11f1-ad1e-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S154">
+        <is>
+          <t xml:space="preserve">10048032    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U154">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V154"/>
+    </row>
+    <row r="155" ht="15.6" customHeight="0">
+      <c s="23" t="inlineStr" r="A155">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="B155">
+        <is>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="10" t="str" r="C155"/>
+      <c s="25" t="inlineStr" r="D155">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="26" r="E155">
+        <v>46300.7027777778</v>
+      </c>
+      <c s="10" t="str" r="F155"/>
+      <c s="26" r="G155">
+        <v>46301.2930115394</v>
+      </c>
+      <c s="25" t="inlineStr" r="H155">
+        <is>
+          <t xml:space="preserve">850</t>
+        </is>
+      </c>
+      <c s="25" t="str" r="I155"/>
+      <c s="25" t="inlineStr" r="J155">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="K155">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="L155">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="24" t="str" r="M155"/>
+      <c s="24" t="inlineStr" r="N155">
+        <is>
+          <t xml:space="preserve">FALTA DEMANDA</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="O155">
+        <is>
+          <t xml:space="preserve">falta de demanda</t>
+        </is>
+      </c>
+      <c s="24" t="str" r="P155"/>
+      <c s="10" t="str" r="Q155"/>
+      <c s="24" t="inlineStr" r="R155">
+        <is>
+          <t xml:space="preserve">5f2d05f0-c0f6-11f1-c35d-f2050a003223</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="S155">
+        <is>
+          <t xml:space="preserve">10046766    </t>
+        </is>
+      </c>
+      <c s="10" t="str" r="T155"/>
+      <c s="24" t="inlineStr" r="U155">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="11" t="str" r="V155"/>
+    </row>
   </sheetData>
   <mergeCells>
     <mergeCell ref="A3:B8"/>
@@ -6563,6 +10927,311 @@
     <mergeCell ref="P94:Q94"/>
     <mergeCell ref="S94:T94"/>
     <mergeCell ref="U94:V94"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="E95:F95"/>
+    <mergeCell ref="P95:Q95"/>
+    <mergeCell ref="S95:T95"/>
+    <mergeCell ref="U95:V95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="E96:F96"/>
+    <mergeCell ref="P96:Q96"/>
+    <mergeCell ref="S96:T96"/>
+    <mergeCell ref="U96:V96"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="E97:F97"/>
+    <mergeCell ref="P97:Q97"/>
+    <mergeCell ref="S97:T97"/>
+    <mergeCell ref="U97:V97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="E98:F98"/>
+    <mergeCell ref="P98:Q98"/>
+    <mergeCell ref="S98:T98"/>
+    <mergeCell ref="U98:V98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="E99:F99"/>
+    <mergeCell ref="P99:Q99"/>
+    <mergeCell ref="S99:T99"/>
+    <mergeCell ref="U99:V99"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="E100:F100"/>
+    <mergeCell ref="P100:Q100"/>
+    <mergeCell ref="S100:T100"/>
+    <mergeCell ref="U100:V100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="E101:F101"/>
+    <mergeCell ref="P101:Q101"/>
+    <mergeCell ref="S101:T101"/>
+    <mergeCell ref="U101:V101"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="E102:F102"/>
+    <mergeCell ref="P102:Q102"/>
+    <mergeCell ref="S102:T102"/>
+    <mergeCell ref="U102:V102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="E103:F103"/>
+    <mergeCell ref="P103:Q103"/>
+    <mergeCell ref="S103:T103"/>
+    <mergeCell ref="U103:V103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="E104:F104"/>
+    <mergeCell ref="P104:Q104"/>
+    <mergeCell ref="S104:T104"/>
+    <mergeCell ref="U104:V104"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="E105:F105"/>
+    <mergeCell ref="P105:Q105"/>
+    <mergeCell ref="S105:T105"/>
+    <mergeCell ref="U105:V105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="E106:F106"/>
+    <mergeCell ref="P106:Q106"/>
+    <mergeCell ref="S106:T106"/>
+    <mergeCell ref="U106:V106"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="E107:F107"/>
+    <mergeCell ref="P107:Q107"/>
+    <mergeCell ref="S107:T107"/>
+    <mergeCell ref="U107:V107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="E108:F108"/>
+    <mergeCell ref="P108:Q108"/>
+    <mergeCell ref="S108:T108"/>
+    <mergeCell ref="U108:V108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="E109:F109"/>
+    <mergeCell ref="P109:Q109"/>
+    <mergeCell ref="S109:T109"/>
+    <mergeCell ref="U109:V109"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="E110:F110"/>
+    <mergeCell ref="P110:Q110"/>
+    <mergeCell ref="S110:T110"/>
+    <mergeCell ref="U110:V110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="E111:F111"/>
+    <mergeCell ref="P111:Q111"/>
+    <mergeCell ref="S111:T111"/>
+    <mergeCell ref="U111:V111"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="E112:F112"/>
+    <mergeCell ref="P112:Q112"/>
+    <mergeCell ref="S112:T112"/>
+    <mergeCell ref="U112:V112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="E113:F113"/>
+    <mergeCell ref="P113:Q113"/>
+    <mergeCell ref="S113:T113"/>
+    <mergeCell ref="U113:V113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="E114:F114"/>
+    <mergeCell ref="P114:Q114"/>
+    <mergeCell ref="S114:T114"/>
+    <mergeCell ref="U114:V114"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="E115:F115"/>
+    <mergeCell ref="P115:Q115"/>
+    <mergeCell ref="S115:T115"/>
+    <mergeCell ref="U115:V115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="E116:F116"/>
+    <mergeCell ref="P116:Q116"/>
+    <mergeCell ref="S116:T116"/>
+    <mergeCell ref="U116:V116"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="E117:F117"/>
+    <mergeCell ref="P117:Q117"/>
+    <mergeCell ref="S117:T117"/>
+    <mergeCell ref="U117:V117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="E118:F118"/>
+    <mergeCell ref="P118:Q118"/>
+    <mergeCell ref="S118:T118"/>
+    <mergeCell ref="U118:V118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="E119:F119"/>
+    <mergeCell ref="P119:Q119"/>
+    <mergeCell ref="S119:T119"/>
+    <mergeCell ref="U119:V119"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="E120:F120"/>
+    <mergeCell ref="P120:Q120"/>
+    <mergeCell ref="S120:T120"/>
+    <mergeCell ref="U120:V120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="E121:F121"/>
+    <mergeCell ref="P121:Q121"/>
+    <mergeCell ref="S121:T121"/>
+    <mergeCell ref="U121:V121"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="E122:F122"/>
+    <mergeCell ref="P122:Q122"/>
+    <mergeCell ref="S122:T122"/>
+    <mergeCell ref="U122:V122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="E123:F123"/>
+    <mergeCell ref="P123:Q123"/>
+    <mergeCell ref="S123:T123"/>
+    <mergeCell ref="U123:V123"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="E124:F124"/>
+    <mergeCell ref="P124:Q124"/>
+    <mergeCell ref="S124:T124"/>
+    <mergeCell ref="U124:V124"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="E125:F125"/>
+    <mergeCell ref="P125:Q125"/>
+    <mergeCell ref="S125:T125"/>
+    <mergeCell ref="U125:V125"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="E126:F126"/>
+    <mergeCell ref="P126:Q126"/>
+    <mergeCell ref="S126:T126"/>
+    <mergeCell ref="U126:V126"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="E127:F127"/>
+    <mergeCell ref="P127:Q127"/>
+    <mergeCell ref="S127:T127"/>
+    <mergeCell ref="U127:V127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="E128:F128"/>
+    <mergeCell ref="P128:Q128"/>
+    <mergeCell ref="S128:T128"/>
+    <mergeCell ref="U128:V128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="E129:F129"/>
+    <mergeCell ref="P129:Q129"/>
+    <mergeCell ref="S129:T129"/>
+    <mergeCell ref="U129:V129"/>
+    <mergeCell ref="B130:C130"/>
+    <mergeCell ref="E130:F130"/>
+    <mergeCell ref="P130:Q130"/>
+    <mergeCell ref="S130:T130"/>
+    <mergeCell ref="U130:V130"/>
+    <mergeCell ref="B131:C131"/>
+    <mergeCell ref="E131:F131"/>
+    <mergeCell ref="P131:Q131"/>
+    <mergeCell ref="S131:T131"/>
+    <mergeCell ref="U131:V131"/>
+    <mergeCell ref="B132:C132"/>
+    <mergeCell ref="E132:F132"/>
+    <mergeCell ref="P132:Q132"/>
+    <mergeCell ref="S132:T132"/>
+    <mergeCell ref="U132:V132"/>
+    <mergeCell ref="B133:C133"/>
+    <mergeCell ref="E133:F133"/>
+    <mergeCell ref="P133:Q133"/>
+    <mergeCell ref="S133:T133"/>
+    <mergeCell ref="U133:V133"/>
+    <mergeCell ref="B134:C134"/>
+    <mergeCell ref="E134:F134"/>
+    <mergeCell ref="P134:Q134"/>
+    <mergeCell ref="S134:T134"/>
+    <mergeCell ref="U134:V134"/>
+    <mergeCell ref="B135:C135"/>
+    <mergeCell ref="E135:F135"/>
+    <mergeCell ref="P135:Q135"/>
+    <mergeCell ref="S135:T135"/>
+    <mergeCell ref="U135:V135"/>
+    <mergeCell ref="B136:C136"/>
+    <mergeCell ref="E136:F136"/>
+    <mergeCell ref="P136:Q136"/>
+    <mergeCell ref="S136:T136"/>
+    <mergeCell ref="U136:V136"/>
+    <mergeCell ref="B137:C137"/>
+    <mergeCell ref="E137:F137"/>
+    <mergeCell ref="P137:Q137"/>
+    <mergeCell ref="S137:T137"/>
+    <mergeCell ref="U137:V137"/>
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="E138:F138"/>
+    <mergeCell ref="P138:Q138"/>
+    <mergeCell ref="S138:T138"/>
+    <mergeCell ref="U138:V138"/>
+    <mergeCell ref="B139:C139"/>
+    <mergeCell ref="E139:F139"/>
+    <mergeCell ref="P139:Q139"/>
+    <mergeCell ref="S139:T139"/>
+    <mergeCell ref="U139:V139"/>
+    <mergeCell ref="B140:C140"/>
+    <mergeCell ref="E140:F140"/>
+    <mergeCell ref="P140:Q140"/>
+    <mergeCell ref="S140:T140"/>
+    <mergeCell ref="U140:V140"/>
+    <mergeCell ref="B141:C141"/>
+    <mergeCell ref="E141:F141"/>
+    <mergeCell ref="P141:Q141"/>
+    <mergeCell ref="S141:T141"/>
+    <mergeCell ref="U141:V141"/>
+    <mergeCell ref="B142:C142"/>
+    <mergeCell ref="E142:F142"/>
+    <mergeCell ref="P142:Q142"/>
+    <mergeCell ref="S142:T142"/>
+    <mergeCell ref="U142:V142"/>
+    <mergeCell ref="B143:C143"/>
+    <mergeCell ref="E143:F143"/>
+    <mergeCell ref="P143:Q143"/>
+    <mergeCell ref="S143:T143"/>
+    <mergeCell ref="U143:V143"/>
+    <mergeCell ref="B144:C144"/>
+    <mergeCell ref="E144:F144"/>
+    <mergeCell ref="P144:Q144"/>
+    <mergeCell ref="S144:T144"/>
+    <mergeCell ref="U144:V144"/>
+    <mergeCell ref="B145:C145"/>
+    <mergeCell ref="E145:F145"/>
+    <mergeCell ref="P145:Q145"/>
+    <mergeCell ref="S145:T145"/>
+    <mergeCell ref="U145:V145"/>
+    <mergeCell ref="B146:C146"/>
+    <mergeCell ref="E146:F146"/>
+    <mergeCell ref="P146:Q146"/>
+    <mergeCell ref="S146:T146"/>
+    <mergeCell ref="U146:V146"/>
+    <mergeCell ref="B147:C147"/>
+    <mergeCell ref="E147:F147"/>
+    <mergeCell ref="P147:Q147"/>
+    <mergeCell ref="S147:T147"/>
+    <mergeCell ref="U147:V147"/>
+    <mergeCell ref="B148:C148"/>
+    <mergeCell ref="E148:F148"/>
+    <mergeCell ref="P148:Q148"/>
+    <mergeCell ref="S148:T148"/>
+    <mergeCell ref="U148:V148"/>
+    <mergeCell ref="B149:C149"/>
+    <mergeCell ref="E149:F149"/>
+    <mergeCell ref="P149:Q149"/>
+    <mergeCell ref="S149:T149"/>
+    <mergeCell ref="U149:V149"/>
+    <mergeCell ref="B150:C150"/>
+    <mergeCell ref="E150:F150"/>
+    <mergeCell ref="P150:Q150"/>
+    <mergeCell ref="S150:T150"/>
+    <mergeCell ref="U150:V150"/>
+    <mergeCell ref="B151:C151"/>
+    <mergeCell ref="E151:F151"/>
+    <mergeCell ref="P151:Q151"/>
+    <mergeCell ref="S151:T151"/>
+    <mergeCell ref="U151:V151"/>
+    <mergeCell ref="B152:C152"/>
+    <mergeCell ref="E152:F152"/>
+    <mergeCell ref="P152:Q152"/>
+    <mergeCell ref="S152:T152"/>
+    <mergeCell ref="U152:V152"/>
+    <mergeCell ref="B153:C153"/>
+    <mergeCell ref="E153:F153"/>
+    <mergeCell ref="P153:Q153"/>
+    <mergeCell ref="S153:T153"/>
+    <mergeCell ref="U153:V153"/>
+    <mergeCell ref="B154:C154"/>
+    <mergeCell ref="E154:F154"/>
+    <mergeCell ref="P154:Q154"/>
+    <mergeCell ref="S154:T154"/>
+    <mergeCell ref="U154:V154"/>
+    <mergeCell ref="B155:C155"/>
+    <mergeCell ref="E155:F155"/>
+    <mergeCell ref="P155:Q155"/>
+    <mergeCell ref="S155:T155"/>
+    <mergeCell ref="U155:V155"/>
   </mergeCells>
   <pageMargins left="0.0393700787401575" right="0.0393700787401575" top="0.0393700787401575" bottom="0.0393700787401575" header="0.0393700787401575" footer="0.0393700787401575"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>

--- a/Base_Interrupcoes.xlsx
+++ b/Base_Interrupcoes.xlsx
@@ -466,7 +466,7 @@
       <c s="4" t="str" r="A7"/>
       <c s="7" t="inlineStr" r="T7">
         <is>
-          <t xml:space="preserve">Emissão: 06/10/2026</t>
+          <t xml:space="preserve">Emissão: 07/10/2026</t>
         </is>
       </c>
       <c s="5" t="str" r="V7"/>
@@ -475,7 +475,7 @@
       <c s="4" t="str" r="A8"/>
       <c s="8" t="inlineStr" r="F8">
         <is>
-          <t xml:space="preserve">Período: 01/10/2026 até 05/10/2026; Turno: Todos; Tempo: Calendário</t>
+          <t xml:space="preserve">Período: 01/10/2026 até 06/10/2026; Turno: Todos; Tempo: Calendário</t>
         </is>
       </c>
       <c s="5" t="str" r="V8"/>
@@ -1502,23 +1502,23 @@
       </c>
       <c s="16" t="inlineStr" r="K29">
         <is>
-          <t xml:space="preserve">Paradas Programadas</t>
+          <t xml:space="preserve">Operacional</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="L29">
         <is>
-          <t xml:space="preserve">Paradas Programadas</t>
+          <t xml:space="preserve">Operacional</t>
         </is>
       </c>
       <c s="16" t="str" r="M29"/>
       <c s="16" t="inlineStr" r="N29">
         <is>
-          <t xml:space="preserve">DESENVOLVIMENTO DE NOVOS PRODUTOS</t>
+          <t xml:space="preserve">MELHORIA</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="O29">
         <is>
-          <t xml:space="preserve">desenvolvimento de novo produto</t>
+          <t xml:space="preserve">Dificuldade com encaixe de material de 1000 na mesa externa</t>
         </is>
       </c>
       <c s="16" t="str" r="P29"/>
@@ -2838,14 +2838,10 @@
     <row r="48" ht="15.55" customHeight="0">
       <c s="19" t="inlineStr" r="A48">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 05</t>
-        </is>
-      </c>
-      <c s="20" t="inlineStr" r="B48">
-        <is>
-          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
-        </is>
-      </c>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B48"/>
       <c s="21" t="inlineStr" r="D48">
         <is>
           <t xml:space="preserve">TURNO B</t>
@@ -2881,25 +2877,21 @@
       <c s="20" t="str" r="M48"/>
       <c s="20" t="inlineStr" r="N48">
         <is>
-          <t xml:space="preserve">FALTA DEMANDA</t>
+          <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="O48">
         <is>
-          <t xml:space="preserve">falta de demanda</t>
+          <t xml:space="preserve">Parada registrada automaticamente pelo sistema</t>
         </is>
       </c>
       <c s="20" t="str" r="P48"/>
       <c s="20" t="inlineStr" r="R48">
         <is>
-          <t xml:space="preserve">4a25c5c0-bdd1-11f1-86c2-f2050a003223</t>
-        </is>
-      </c>
-      <c s="20" t="inlineStr" r="S48">
-        <is>
-          <t xml:space="preserve">10046135    </t>
-        </is>
-      </c>
+          <t xml:space="preserve">49cef330-bdd1-11f1-8f07-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="S48"/>
       <c s="20" t="inlineStr" r="U48">
         <is>
           <t xml:space="preserve">Sim</t>
@@ -2910,7 +2902,7 @@
     <row r="49" ht="15.6" customHeight="0">
       <c s="15" t="inlineStr" r="A49">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 02</t>
+          <t xml:space="preserve">TRANSVERSAL 03</t>
         </is>
       </c>
       <c s="16" t="str" r="B49"/>
@@ -2960,7 +2952,7 @@
       <c s="16" t="str" r="P49"/>
       <c s="16" t="inlineStr" r="R49">
         <is>
-          <t xml:space="preserve">49cef330-bdd1-11f1-8f07-f2050a003223</t>
+          <t xml:space="preserve">49efe8b0-bdd1-11f1-cb5a-f2050a003223</t>
         </is>
       </c>
       <c s="16" t="str" r="S49"/>
@@ -2974,10 +2966,14 @@
     <row r="50" ht="15.6" customHeight="0">
       <c s="19" t="inlineStr" r="A50">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 03</t>
-        </is>
-      </c>
-      <c s="20" t="str" r="B50"/>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B50">
+        <is>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
       <c s="21" t="inlineStr" r="D50">
         <is>
           <t xml:space="preserve">TURNO B</t>
@@ -3013,21 +3009,25 @@
       <c s="20" t="str" r="M50"/>
       <c s="20" t="inlineStr" r="N50">
         <is>
-          <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
+          <t xml:space="preserve">FALTA DEMANDA</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="O50">
         <is>
-          <t xml:space="preserve">Parada registrada automaticamente pelo sistema</t>
+          <t xml:space="preserve">falta de demanda</t>
         </is>
       </c>
       <c s="20" t="str" r="P50"/>
       <c s="20" t="inlineStr" r="R50">
         <is>
-          <t xml:space="preserve">49efe8b0-bdd1-11f1-cb5a-f2050a003223</t>
-        </is>
-      </c>
-      <c s="20" t="str" r="S50"/>
+          <t xml:space="preserve">4a25c5c0-bdd1-11f1-86c2-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S50">
+        <is>
+          <t xml:space="preserve">10046135    </t>
+        </is>
+      </c>
       <c s="20" t="inlineStr" r="U50">
         <is>
           <t xml:space="preserve">Sim</t>
@@ -3110,12 +3110,12 @@
     <row r="52" ht="15.6" customHeight="0">
       <c s="19" t="inlineStr" r="A52">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 01</t>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="B52">
         <is>
-          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
         </is>
       </c>
       <c s="21" t="inlineStr" r="D52">
@@ -3127,11 +3127,11 @@
         <v>46297.2916666667</v>
       </c>
       <c s="22" r="G52">
-        <v>46297.3020833333</v>
+        <v>46297.3055555556</v>
       </c>
       <c s="21" t="inlineStr" r="H52">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c s="21" t="str" r="I52"/>
@@ -3158,18 +3158,18 @@
       </c>
       <c s="20" t="inlineStr" r="O52">
         <is>
-          <t xml:space="preserve">dds e assinatura dos documentos</t>
+          <t xml:space="preserve">dds com supervisor QUEDA DE MATERIAIS</t>
         </is>
       </c>
       <c s="20" t="str" r="P52"/>
       <c s="20" t="inlineStr" r="R52">
         <is>
-          <t xml:space="preserve">61a3b7a0-be4b-11f1-9cbf-f2050a003223</t>
+          <t xml:space="preserve">167ccc00-be4e-11f1-cdcf-f2050a003223</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="S52">
         <is>
-          <t xml:space="preserve">10046873    </t>
+          <t xml:space="preserve">10046135    </t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="U52">
@@ -3182,12 +3182,12 @@
     <row r="53" ht="15.55" customHeight="0">
       <c s="15" t="inlineStr" r="A53">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 04</t>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="B53">
         <is>
-          <t xml:space="preserve">TR04-DESENROLADOR</t>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
         </is>
       </c>
       <c s="17" t="inlineStr" r="D53">
@@ -3199,11 +3199,11 @@
         <v>46297.2916666667</v>
       </c>
       <c s="18" r="G53">
-        <v>46297.2986111111</v>
+        <v>46297.3020833333</v>
       </c>
       <c s="17" t="inlineStr" r="H53">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c s="17" t="str" r="I53"/>
@@ -3230,18 +3230,18 @@
       </c>
       <c s="16" t="inlineStr" r="O53">
         <is>
-          <t xml:space="preserve">DDS</t>
+          <t xml:space="preserve">dds e assinatura dos documentos</t>
         </is>
       </c>
       <c s="16" t="str" r="P53"/>
       <c s="16" t="inlineStr" r="R53">
         <is>
-          <t xml:space="preserve">942e4bd0-be4c-11f1-ca85-f2050a003223</t>
+          <t xml:space="preserve">61a3b7a0-be4b-11f1-9cbf-f2050a003223</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="S53">
         <is>
-          <t xml:space="preserve">10047019    </t>
+          <t xml:space="preserve">10046873    </t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="U53">
@@ -3254,12 +3254,12 @@
     <row r="54" ht="15.6" customHeight="0">
       <c s="19" t="inlineStr" r="A54">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 05</t>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="B54">
         <is>
-          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
         </is>
       </c>
       <c s="21" t="inlineStr" r="D54">
@@ -3271,11 +3271,11 @@
         <v>46297.2916666667</v>
       </c>
       <c s="22" r="G54">
-        <v>46297.3055555556</v>
+        <v>46297.2986111111</v>
       </c>
       <c s="21" t="inlineStr" r="H54">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c s="21" t="str" r="I54"/>
@@ -3302,18 +3302,18 @@
       </c>
       <c s="20" t="inlineStr" r="O54">
         <is>
-          <t xml:space="preserve">dds com supervisor QUEDA DE MATERIAIS</t>
+          <t xml:space="preserve">DDS</t>
         </is>
       </c>
       <c s="20" t="str" r="P54"/>
       <c s="20" t="inlineStr" r="R54">
         <is>
-          <t xml:space="preserve">167ccc00-be4e-11f1-cdcf-f2050a003223</t>
+          <t xml:space="preserve">942e4bd0-be4c-11f1-ca85-f2050a003223</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="S54">
         <is>
-          <t xml:space="preserve">10046135    </t>
+          <t xml:space="preserve">10047019    </t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="U54">
@@ -5498,23 +5498,23 @@
       </c>
       <c s="16" t="inlineStr" r="K85">
         <is>
-          <t xml:space="preserve">Paradas Programadas</t>
+          <t xml:space="preserve">Operacional</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="L85">
         <is>
-          <t xml:space="preserve">Paradas Programadas</t>
+          <t xml:space="preserve">Operacional</t>
         </is>
       </c>
       <c s="16" t="str" r="M85"/>
       <c s="16" t="inlineStr" r="N85">
         <is>
-          <t xml:space="preserve">DESENVOLVIMENTO DE NOVOS PRODUTOS</t>
+          <t xml:space="preserve">MELHORIA</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="O85">
         <is>
-          <t xml:space="preserve">desenvolvimento de novos produtos</t>
+          <t xml:space="preserve">Ajuste na mesa de enfardamento externa</t>
         </is>
       </c>
       <c s="16" t="str" r="P85"/>
@@ -6238,12 +6238,12 @@
     <row r="96" ht="15.6" customHeight="0">
       <c s="19" t="inlineStr" r="A96">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 05</t>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="B96">
         <is>
-          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
         </is>
       </c>
       <c s="21" t="inlineStr" r="D96">
@@ -6286,18 +6286,18 @@
       </c>
       <c s="20" t="inlineStr" r="O96">
         <is>
-          <t xml:space="preserve">dds</t>
+          <t xml:space="preserve">DDS</t>
         </is>
       </c>
       <c s="20" t="str" r="P96"/>
       <c s="20" t="inlineStr" r="R96">
         <is>
-          <t xml:space="preserve">1176a761-c0ad-11f1-8444-f2050a003223</t>
+          <t xml:space="preserve">2a2a1a30-c0b2-11f1-9e79-f2050a003223</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="S96">
         <is>
-          <t xml:space="preserve">10046136    </t>
+          <t xml:space="preserve">10046892    </t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="U96">
@@ -6310,12 +6310,12 @@
     <row r="97" ht="15.6" customHeight="0">
       <c s="15" t="inlineStr" r="A97">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 04</t>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="B97">
         <is>
-          <t xml:space="preserve">TR04-DESENROLADOR</t>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
         </is>
       </c>
       <c s="17" t="inlineStr" r="D97">
@@ -6358,18 +6358,18 @@
       </c>
       <c s="16" t="inlineStr" r="O97">
         <is>
-          <t xml:space="preserve">DDS</t>
+          <t xml:space="preserve">dds</t>
         </is>
       </c>
       <c s="16" t="str" r="P97"/>
       <c s="16" t="inlineStr" r="R97">
         <is>
-          <t xml:space="preserve">2a2a1a30-c0b2-11f1-9e79-f2050a003223</t>
+          <t xml:space="preserve">1176a761-c0ad-11f1-8444-f2050a003223</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="S97">
         <is>
-          <t xml:space="preserve">10046892    </t>
+          <t xml:space="preserve">10046136    </t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="U97">
@@ -6502,7 +6502,7 @@
       </c>
       <c s="16" t="inlineStr" r="O99">
         <is>
-          <t xml:space="preserve">desenvolvimento de novo produto</t>
+          <t xml:space="preserve">Ajuste na mesa de enfardamento externa</t>
         </is>
       </c>
       <c s="16" t="str" r="P99"/>
@@ -7552,11 +7552,11 @@
         <v>46300.4006944444</v>
       </c>
       <c s="22" r="G114">
-        <v>46301.2930115394</v>
+        <v>46301.5673611111</v>
       </c>
       <c s="21" t="inlineStr" r="H114">
         <is>
-          <t xml:space="preserve">1.285</t>
+          <t xml:space="preserve">1.680</t>
         </is>
       </c>
       <c s="21" t="str" r="I114"/>
@@ -10264,11 +10264,11 @@
         <v>46300.6944444444</v>
       </c>
       <c s="22" r="G152">
-        <v>46301.2930115394</v>
+        <v>46300.7048611111</v>
       </c>
       <c s="21" t="inlineStr" r="H152">
         <is>
-          <t xml:space="preserve">862</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c s="21" t="str" r="I152"/>
@@ -10279,23 +10279,23 @@
       </c>
       <c s="20" t="inlineStr" r="K152">
         <is>
-          <t xml:space="preserve">Tempo Livre</t>
+          <t xml:space="preserve">Operacional</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="L152">
         <is>
-          <t xml:space="preserve">Tempo Livre</t>
+          <t xml:space="preserve">Operacional</t>
         </is>
       </c>
       <c s="20" t="str" r="M152"/>
       <c s="20" t="inlineStr" r="N152">
         <is>
-          <t xml:space="preserve">FALTA DEMANDA</t>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="O152">
         <is>
-          <t xml:space="preserve">TEMPO LIVRE</t>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
         </is>
       </c>
       <c s="20" t="str" r="P152"/>
@@ -10449,81 +10449,4922 @@
       <c s="5" t="str" r="V154"/>
     </row>
     <row r="155" ht="15.6" customHeight="0">
-      <c s="23" t="inlineStr" r="A155">
+      <c s="15" t="inlineStr" r="A155">
         <is>
           <t xml:space="preserve">TRANSVERSAL 05</t>
         </is>
       </c>
-      <c s="24" t="inlineStr" r="B155">
+      <c s="16" t="inlineStr" r="B155">
         <is>
           <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
         </is>
       </c>
-      <c s="10" t="str" r="C155"/>
-      <c s="25" t="inlineStr" r="D155">
+      <c s="17" t="inlineStr" r="D155">
         <is>
           <t xml:space="preserve">TURNO B</t>
         </is>
       </c>
-      <c s="26" r="E155">
+      <c s="18" r="E155">
         <v>46300.7027777778</v>
       </c>
-      <c s="10" t="str" r="F155"/>
-      <c s="26" r="G155">
-        <v>46301.2930115394</v>
-      </c>
-      <c s="25" t="inlineStr" r="H155">
-        <is>
-          <t xml:space="preserve">850</t>
-        </is>
-      </c>
-      <c s="25" t="str" r="I155"/>
-      <c s="25" t="inlineStr" r="J155">
-        <is>
-          <t xml:space="preserve">X</t>
-        </is>
-      </c>
-      <c s="24" t="inlineStr" r="K155">
+      <c s="18" r="G155">
+        <v>46301.2909722222</v>
+      </c>
+      <c s="17" t="inlineStr" r="H155">
+        <is>
+          <t xml:space="preserve">847</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I155"/>
+      <c s="17" t="inlineStr" r="J155">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K155">
         <is>
           <t xml:space="preserve">Tempo Livre</t>
         </is>
       </c>
-      <c s="24" t="inlineStr" r="L155">
+      <c s="16" t="inlineStr" r="L155">
         <is>
           <t xml:space="preserve">Tempo Livre</t>
         </is>
       </c>
-      <c s="24" t="str" r="M155"/>
-      <c s="24" t="inlineStr" r="N155">
+      <c s="16" t="str" r="M155"/>
+      <c s="16" t="inlineStr" r="N155">
         <is>
           <t xml:space="preserve">FALTA DEMANDA</t>
         </is>
       </c>
-      <c s="24" t="inlineStr" r="O155">
+      <c s="16" t="inlineStr" r="O155">
         <is>
           <t xml:space="preserve">falta de demanda</t>
         </is>
       </c>
-      <c s="24" t="str" r="P155"/>
-      <c s="10" t="str" r="Q155"/>
-      <c s="24" t="inlineStr" r="R155">
+      <c s="16" t="str" r="P155"/>
+      <c s="16" t="inlineStr" r="R155">
         <is>
           <t xml:space="preserve">5f2d05f0-c0f6-11f1-c35d-f2050a003223</t>
         </is>
       </c>
-      <c s="24" t="inlineStr" r="S155">
+      <c s="16" t="inlineStr" r="S155">
         <is>
           <t xml:space="preserve">10046766    </t>
         </is>
       </c>
-      <c s="10" t="str" r="T155"/>
-      <c s="24" t="inlineStr" r="U155">
-        <is>
-          <t xml:space="preserve">Sim</t>
-        </is>
-      </c>
-      <c s="11" t="str" r="V155"/>
-    </row>
+      <c s="16" t="inlineStr" r="U155">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V155"/>
+    </row>
+    <row r="156" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A156">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B156">
+        <is>
+          <t xml:space="preserve">TR01-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D156">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E156">
+        <v>46300.7055555556</v>
+      </c>
+      <c s="22" r="G156">
+        <v>46301.2909722222</v>
+      </c>
+      <c s="21" t="inlineStr" r="H156">
+        <is>
+          <t xml:space="preserve">843</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I156"/>
+      <c s="21" t="inlineStr" r="J156">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K156">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L156">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M156"/>
+      <c s="20" t="inlineStr" r="N156">
+        <is>
+          <t xml:space="preserve">FALTA DEMANDA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O156">
+        <is>
+          <t xml:space="preserve">tempo livre</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P156"/>
+      <c s="20" t="inlineStr" r="R156">
+        <is>
+          <t xml:space="preserve">ac9b7ab0-c16e-11f1-9d79-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S156">
+        <is>
+          <t xml:space="preserve">10047271    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U156">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V156"/>
+    </row>
+    <row r="157" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A157">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B157">
+        <is>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D157">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E157">
+        <v>46301.2916666667</v>
+      </c>
+      <c s="18" r="G157">
+        <v>46301.3055555556</v>
+      </c>
+      <c s="17" t="inlineStr" r="H157">
+        <is>
+          <t xml:space="preserve">20</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I157"/>
+      <c s="17" t="inlineStr" r="J157">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K157">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L157">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M157"/>
+      <c s="16" t="inlineStr" r="N157">
+        <is>
+          <t xml:space="preserve">DDS</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O157">
+        <is>
+          <t xml:space="preserve">dds</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P157"/>
+      <c s="16" t="inlineStr" r="R157">
+        <is>
+          <t xml:space="preserve">4ed80b10-c172-11f1-84a1-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S157">
+        <is>
+          <t xml:space="preserve">10046766    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U157">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V157"/>
+    </row>
+    <row r="158" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A158">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B158">
+        <is>
+          <t xml:space="preserve">TR01-MESA TRANSPORTADORA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D158">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E158">
+        <v>46301.2916666667</v>
+      </c>
+      <c s="22" r="G158">
+        <v>46301.3020833333</v>
+      </c>
+      <c s="21" t="inlineStr" r="H158">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I158"/>
+      <c s="21" t="inlineStr" r="J158">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K158">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L158">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M158"/>
+      <c s="20" t="inlineStr" r="N158">
+        <is>
+          <t xml:space="preserve">DDS</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O158">
+        <is>
+          <t xml:space="preserve">dds  e assinatura dos documentos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P158"/>
+      <c s="20" t="inlineStr" r="R158">
+        <is>
+          <t xml:space="preserve">fa2e6070-c16f-11f1-a1bf-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S158">
+        <is>
+          <t xml:space="preserve">10047271    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U158">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V158"/>
+    </row>
+    <row r="159" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A159">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B159">
+        <is>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D159">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E159">
+        <v>46301.2916666667</v>
+      </c>
+      <c s="18" r="G159">
+        <v>46301.2986111111</v>
+      </c>
+      <c s="17" t="inlineStr" r="H159">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I159"/>
+      <c s="17" t="inlineStr" r="J159">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K159">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L159">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M159"/>
+      <c s="16" t="inlineStr" r="N159">
+        <is>
+          <t xml:space="preserve">DDS</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O159">
+        <is>
+          <t xml:space="preserve">DDS</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P159"/>
+      <c s="16" t="inlineStr" r="R159">
+        <is>
+          <t xml:space="preserve">00542e40-c174-11f1-b395-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S159">
+        <is>
+          <t xml:space="preserve">10048032    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U159">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V159"/>
+    </row>
+    <row r="160" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A160">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B160">
+        <is>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D160">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E160">
+        <v>46301.2993055556</v>
+      </c>
+      <c s="22" r="G160">
+        <v>46301.30625</v>
+      </c>
+      <c s="21" t="inlineStr" r="H160">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I160"/>
+      <c s="21" t="inlineStr" r="J160">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K160">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L160">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M160"/>
+      <c s="20" t="inlineStr" r="N160">
+        <is>
+          <t xml:space="preserve">ASSINATURA DE DOCUMENTOS</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O160">
+        <is>
+          <t xml:space="preserve">Assinatura de documentos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P160"/>
+      <c s="20" t="inlineStr" r="R160">
+        <is>
+          <t xml:space="preserve">20b29e60-c174-11f1-b410-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S160">
+        <is>
+          <t xml:space="preserve">10048032    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U160">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V160"/>
+    </row>
+    <row r="161" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A161">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B161">
+        <is>
+          <t xml:space="preserve">TR04-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D161">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E161">
+        <v>46301.3090277778</v>
+      </c>
+      <c s="18" r="G161">
+        <v>46301.3159722222</v>
+      </c>
+      <c s="17" t="inlineStr" r="H161">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I161"/>
+      <c s="17" t="inlineStr" r="J161">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K161">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L161">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M161"/>
+      <c s="16" t="inlineStr" r="N161">
+        <is>
+          <t xml:space="preserve">RETIRADA DE PNC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O161">
+        <is>
+          <t xml:space="preserve">retirar pnc</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P161"/>
+      <c s="16" t="inlineStr" r="R161">
+        <is>
+          <t xml:space="preserve">474cf930-c174-11f1-c17b-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S161">
+        <is>
+          <t xml:space="preserve">10048032    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U161">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V161"/>
+    </row>
+    <row r="162" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A162">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B162">
+        <is>
+          <t xml:space="preserve">TR05-MESA FIXA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D162">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E162">
+        <v>46301.3263888889</v>
+      </c>
+      <c s="22" r="G162">
+        <v>46301.3284722222</v>
+      </c>
+      <c s="21" t="inlineStr" r="H162">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I162"/>
+      <c s="21" t="inlineStr" r="J162">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K162">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L162">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M162"/>
+      <c s="20" t="inlineStr" r="N162">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE FARDO</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O162">
+        <is>
+          <t xml:space="preserve">Passagem de fardo.</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P162"/>
+      <c s="20" t="inlineStr" r="R162">
+        <is>
+          <t xml:space="preserve">ba87ae50-c173-11f1-be87-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S162">
+        <is>
+          <t xml:space="preserve">10046766    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U162">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V162"/>
+    </row>
+    <row r="163" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A163">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B163">
+        <is>
+          <t xml:space="preserve">TR01-MESA TRANSPORTADORA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D163">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E163">
+        <v>46301.3319444444</v>
+      </c>
+      <c s="18" r="G163">
+        <v>46301.3423611111</v>
+      </c>
+      <c s="17" t="inlineStr" r="H163">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I163"/>
+      <c s="17" t="inlineStr" r="J163">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K163">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L163">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M163"/>
+      <c s="16" t="inlineStr" r="N163">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE CHAPA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O163">
+        <is>
+          <t xml:space="preserve">ajustando chapa chapa enganchada</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P163"/>
+      <c s="16" t="inlineStr" r="R163">
+        <is>
+          <t xml:space="preserve">e2665380-c174-11f1-c612-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S163">
+        <is>
+          <t xml:space="preserve">10047271    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U163">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V163"/>
+    </row>
+    <row r="164" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A164">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B164">
+        <is>
+          <t xml:space="preserve">TR05-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D164">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E164">
+        <v>46301.3409722222</v>
+      </c>
+      <c s="22" r="G164">
+        <v>46301.3506944444</v>
+      </c>
+      <c s="21" t="inlineStr" r="H164">
+        <is>
+          <t xml:space="preserve">14</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I164"/>
+      <c s="21" t="inlineStr" r="J164">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K164">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L164">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M164"/>
+      <c s="20" t="inlineStr" r="N164">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O164">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 14 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P164"/>
+      <c s="20" t="inlineStr" r="R164">
+        <is>
+          <t xml:space="preserve">b733c100-c176-11f1-8278-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S164">
+        <is>
+          <t xml:space="preserve">10046766    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U164">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V164"/>
+    </row>
+    <row r="165" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A165">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B165"/>
+      <c s="17" t="inlineStr" r="D165">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E165">
+        <v>46301.3465277778</v>
+      </c>
+      <c s="18" r="G165">
+        <v>46301.3555555556</v>
+      </c>
+      <c s="17" t="inlineStr" r="H165">
+        <is>
+          <t xml:space="preserve">13</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I165"/>
+      <c s="17" t="inlineStr" r="J165">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K165">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L165">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M165"/>
+      <c s="16" t="inlineStr" r="N165">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O165">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 13 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P165"/>
+      <c s="16" t="inlineStr" r="R165">
+        <is>
+          <t xml:space="preserve">cc5641b0-c177-11f1-abbb-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S165">
+        <is>
+          <t xml:space="preserve">10047271    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U165">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V165"/>
+    </row>
+    <row r="166" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A166">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B166">
+        <is>
+          <t xml:space="preserve">TR05-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D166">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E166">
+        <v>46301.3513888889</v>
+      </c>
+      <c s="22" r="G166">
+        <v>46301.3569444444</v>
+      </c>
+      <c s="21" t="inlineStr" r="H166">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I166"/>
+      <c s="21" t="inlineStr" r="J166">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K166">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L166">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M166"/>
+      <c s="20" t="inlineStr" r="N166">
+        <is>
+          <t xml:space="preserve">RETIRADA DE PNC</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O166">
+        <is>
+          <t xml:space="preserve">Retirada de pnc.</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P166"/>
+      <c s="20" t="inlineStr" r="R166">
+        <is>
+          <t xml:space="preserve">c8272181-c178-11f1-8f8a-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S166">
+        <is>
+          <t xml:space="preserve">10046766    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U166">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V166"/>
+    </row>
+    <row r="167" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A167">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B167">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D167">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E167">
+        <v>46301.35625</v>
+      </c>
+      <c s="18" r="G167">
+        <v>46301.3590277778</v>
+      </c>
+      <c s="17" t="inlineStr" r="H167">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I167"/>
+      <c s="17" t="inlineStr" r="J167">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K167">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L167">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M167"/>
+      <c s="16" t="inlineStr" r="N167">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE CHAPA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O167">
+        <is>
+          <t xml:space="preserve">ajustando chapa</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P167"/>
+      <c s="16" t="inlineStr" r="R167">
+        <is>
+          <t xml:space="preserve">a93d3380-c179-11f1-a3f6-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S167">
+        <is>
+          <t xml:space="preserve">10047271    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U167">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V167"/>
+    </row>
+    <row r="168" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A168">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B168">
+        <is>
+          <t xml:space="preserve">TR05-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D168">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E168">
+        <v>46301.3701388889</v>
+      </c>
+      <c s="22" r="G168">
+        <v>46301.3722222222</v>
+      </c>
+      <c s="21" t="inlineStr" r="H168">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I168"/>
+      <c s="21" t="inlineStr" r="J168">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K168">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L168">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M168"/>
+      <c s="20" t="inlineStr" r="N168">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE FARDO</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O168">
+        <is>
+          <t xml:space="preserve">passagem de fardo</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P168"/>
+      <c s="20" t="inlineStr" r="R168">
+        <is>
+          <t xml:space="preserve">99a07010-c17c-11f1-b791-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S168">
+        <is>
+          <t xml:space="preserve">10048112    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U168">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V168"/>
+    </row>
+    <row r="169" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A169">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B169">
+        <is>
+          <t xml:space="preserve">TR01-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D169">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E169">
+        <v>46301.3763888889</v>
+      </c>
+      <c s="18" r="G169">
+        <v>46301.3909722222</v>
+      </c>
+      <c s="17" t="inlineStr" r="H169">
+        <is>
+          <t xml:space="preserve">21</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I169"/>
+      <c s="17" t="inlineStr" r="J169">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K169">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L169">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M169"/>
+      <c s="16" t="inlineStr" r="N169">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O169">
+        <is>
+          <t xml:space="preserve">abstecimento bobina oval</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P169"/>
+      <c s="16" t="inlineStr" r="R169">
+        <is>
+          <t xml:space="preserve">cbd8eca0-c17d-11f1-9f6f-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S169">
+        <is>
+          <t xml:space="preserve">10047294    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U169">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V169"/>
+    </row>
+    <row r="170" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A170">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B170">
+        <is>
+          <t xml:space="preserve">TR05-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D170">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E170">
+        <v>46301.3784722222</v>
+      </c>
+      <c s="22" r="G170">
+        <v>46301.3819444444</v>
+      </c>
+      <c s="21" t="inlineStr" r="H170">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I170"/>
+      <c s="21" t="inlineStr" r="J170">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K170">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L170">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M170"/>
+      <c s="20" t="inlineStr" r="N170">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE FARDO</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O170">
+        <is>
+          <t xml:space="preserve">passagem de fardo</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P170"/>
+      <c s="20" t="inlineStr" r="R170">
+        <is>
+          <t xml:space="preserve">438e5f00-c17e-11f1-8f11-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S170">
+        <is>
+          <t xml:space="preserve">10048112    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U170">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V170"/>
+    </row>
+    <row r="171" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A171">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B171">
+        <is>
+          <t xml:space="preserve">TR05-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D171">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E171">
+        <v>46301.3888888889</v>
+      </c>
+      <c s="18" r="G171">
+        <v>46301.3951388889</v>
+      </c>
+      <c s="17" t="inlineStr" r="H171">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I171"/>
+      <c s="17" t="inlineStr" r="J171">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K171">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L171">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M171"/>
+      <c s="16" t="inlineStr" r="N171">
+        <is>
+          <t xml:space="preserve">MESA CHEIA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O171">
+        <is>
+          <t xml:space="preserve">aguardando retirada do material de 6000X1000</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P171"/>
+      <c s="16" t="inlineStr" r="R171">
+        <is>
+          <t xml:space="preserve">49214d90-c180-11f1-b0d9-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S171">
+        <is>
+          <t xml:space="preserve">10047447    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U171">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V171"/>
+    </row>
+    <row r="172" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A172">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B172">
+        <is>
+          <t xml:space="preserve">TR04-ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D172">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E172">
+        <v>46301.3923611111</v>
+      </c>
+      <c s="22" r="G172">
+        <v>46301.3993055556</v>
+      </c>
+      <c s="21" t="inlineStr" r="H172">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I172"/>
+      <c s="21" t="inlineStr" r="J172">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K172">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L172">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M172"/>
+      <c s="20" t="inlineStr" r="N172">
+        <is>
+          <t xml:space="preserve">SETUP COMPLETO</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O172">
+        <is>
+          <t xml:space="preserve">trocar 1.55x1000 para 0.95x1000 e fazer regulagem</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P172"/>
+      <c s="20" t="inlineStr" r="R172">
+        <is>
+          <t xml:space="preserve">29e4e7e0-c183-11f1-9d77-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S172">
+        <is>
+          <t xml:space="preserve">10048032    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U172">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V172"/>
+    </row>
+    <row r="173" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A173">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B173">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D173">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E173">
+        <v>46301.4034722222</v>
+      </c>
+      <c s="18" r="G173">
+        <v>46301.40625</v>
+      </c>
+      <c s="17" t="inlineStr" r="H173">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I173"/>
+      <c s="17" t="inlineStr" r="J173">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K173">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L173">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M173"/>
+      <c s="16" t="inlineStr" r="N173">
+        <is>
+          <t xml:space="preserve">AJUSTE DA MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O173">
+        <is>
+          <t xml:space="preserve">ajuste da mesa para tamanho de chapa</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P173"/>
+      <c s="16" t="inlineStr" r="R173">
+        <is>
+          <t xml:space="preserve">305d3f50-c183-11f1-8038-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S173">
+        <is>
+          <t xml:space="preserve">10047294    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U173">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V173"/>
+    </row>
+    <row r="174" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A174">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B174">
+        <is>
+          <t xml:space="preserve">TR05-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D174">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E174">
+        <v>46301.4069444444</v>
+      </c>
+      <c s="22" r="G174">
+        <v>46301.4173611111</v>
+      </c>
+      <c s="21" t="inlineStr" r="H174">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I174"/>
+      <c s="21" t="inlineStr" r="J174">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K174">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L174">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M174"/>
+      <c s="20" t="inlineStr" r="N174">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O174">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P174"/>
+      <c s="20" t="inlineStr" r="R174">
+        <is>
+          <t xml:space="preserve">029db5d0-c184-11f1-935e-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S174">
+        <is>
+          <t xml:space="preserve">10047448    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U174">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V174"/>
+    </row>
+    <row r="175" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A175">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B175">
+        <is>
+          <t xml:space="preserve">TR05-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D175">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E175">
+        <v>46301.4180555556</v>
+      </c>
+      <c s="18" r="G175">
+        <v>46301.4229166667</v>
+      </c>
+      <c s="17" t="inlineStr" r="H175">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I175"/>
+      <c s="17" t="inlineStr" r="J175">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K175">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L175">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M175"/>
+      <c s="16" t="inlineStr" r="N175">
+        <is>
+          <t xml:space="preserve">RETIRADA DE PNC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O175">
+        <is>
+          <t xml:space="preserve">RETIRADA DE PNC</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P175"/>
+      <c s="16" t="inlineStr" r="R175">
+        <is>
+          <t xml:space="preserve">af5190a0-c187-11f1-cee0-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S175">
+        <is>
+          <t xml:space="preserve">10047448    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U175">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V175"/>
+    </row>
+    <row r="176" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A176">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B176"/>
+      <c s="21" t="inlineStr" r="D176">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E176">
+        <v>46301.4326388889</v>
+      </c>
+      <c s="22" r="G176">
+        <v>46301.4423611111</v>
+      </c>
+      <c s="21" t="inlineStr" r="H176">
+        <is>
+          <t xml:space="preserve">14</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I176"/>
+      <c s="21" t="inlineStr" r="J176">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K176">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L176">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M176"/>
+      <c s="20" t="inlineStr" r="N176">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O176">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 14 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P176"/>
+      <c s="20" t="inlineStr" r="R176">
+        <is>
+          <t xml:space="preserve">22199be0-c189-11f1-cccc-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S176">
+        <is>
+          <t xml:space="preserve">10048036    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U176">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V176"/>
+    </row>
+    <row r="177" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A177">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B177"/>
+      <c s="17" t="inlineStr" r="D177">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E177">
+        <v>46301.4423611111</v>
+      </c>
+      <c s="18" r="G177">
+        <v>46301.4444444444</v>
+      </c>
+      <c s="17" t="inlineStr" r="H177">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I177"/>
+      <c s="17" t="inlineStr" r="J177">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K177">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L177">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M177"/>
+      <c s="16" t="inlineStr" r="N177">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O177">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 3 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P177"/>
+      <c s="16" t="inlineStr" r="R177">
+        <is>
+          <t xml:space="preserve">0c97dcd0-c18b-11f1-cd2d-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S177">
+        <is>
+          <t xml:space="preserve">10048036    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U177">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V177"/>
+    </row>
+    <row r="178" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A178">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B178">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D178">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E178">
+        <v>46301.4451388889</v>
+      </c>
+      <c s="22" r="G178">
+        <v>46301.4479166667</v>
+      </c>
+      <c s="21" t="inlineStr" r="H178">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I178"/>
+      <c s="21" t="inlineStr" r="J178">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K178">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L178">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M178"/>
+      <c s="20" t="inlineStr" r="N178">
+        <is>
+          <t xml:space="preserve">AJUSTE DA MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O178">
+        <is>
+          <t xml:space="preserve">ajuste da mesa par tamanho de chapa</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P178"/>
+      <c s="20" t="inlineStr" r="R178">
+        <is>
+          <t xml:space="preserve">8eebd0b0-c18b-11f1-942f-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S178">
+        <is>
+          <t xml:space="preserve">10048036    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U178">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V178"/>
+    </row>
+    <row r="179" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A179">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B179">
+        <is>
+          <t xml:space="preserve">TR01-MESA TRANSPORTADORA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D179">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E179">
+        <v>46301.4541666667</v>
+      </c>
+      <c s="18" r="G179">
+        <v>46301.4583333333</v>
+      </c>
+      <c s="17" t="inlineStr" r="H179">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I179"/>
+      <c s="17" t="inlineStr" r="J179">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K179">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L179">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M179"/>
+      <c s="16" t="inlineStr" r="N179">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE CHAPA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O179">
+        <is>
+          <t xml:space="preserve">ajustando chapa</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P179"/>
+      <c s="16" t="inlineStr" r="R179">
+        <is>
+          <t xml:space="preserve">850346d0-c18d-11f1-bd1b-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S179">
+        <is>
+          <t xml:space="preserve">10047299    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U179">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V179"/>
+    </row>
+    <row r="180" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A180">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B180">
+        <is>
+          <t xml:space="preserve">TR05-MESA FIXA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D180">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E180">
+        <v>46301.4597222222</v>
+      </c>
+      <c s="22" r="G180">
+        <v>46301.4625</v>
+      </c>
+      <c s="21" t="inlineStr" r="H180">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I180"/>
+      <c s="21" t="inlineStr" r="J180">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K180">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L180">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M180"/>
+      <c s="20" t="inlineStr" r="N180">
+        <is>
+          <t xml:space="preserve">RETIRADA DE PNC</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O180">
+        <is>
+          <t xml:space="preserve">Retirada de pnc</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P180"/>
+      <c s="20" t="inlineStr" r="R180">
+        <is>
+          <t xml:space="preserve">a253be30-c18e-11f1-b02f-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S180">
+        <is>
+          <t xml:space="preserve">10046888    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U180">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V180"/>
+    </row>
+    <row r="181" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A181">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B181">
+        <is>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D181">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E181">
+        <v>46301.4680555556</v>
+      </c>
+      <c s="18" r="G181">
+        <v>46301.4819444444</v>
+      </c>
+      <c s="17" t="inlineStr" r="H181">
+        <is>
+          <t xml:space="preserve">20</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I181"/>
+      <c s="17" t="inlineStr" r="J181">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K181">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L181">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M181"/>
+      <c s="16" t="inlineStr" r="N181">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE CHAPA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O181">
+        <is>
+          <t xml:space="preserve">Passagem de chapa.</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P181"/>
+      <c s="16" t="inlineStr" r="R181">
+        <is>
+          <t xml:space="preserve">f118fab0-c195-11f1-bc94-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S181">
+        <is>
+          <t xml:space="preserve">10046888    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U181">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V181"/>
+    </row>
+    <row r="182" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A182">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B182"/>
+      <c s="21" t="inlineStr" r="D182">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E182">
+        <v>46301.4923611111</v>
+      </c>
+      <c s="22" r="G182">
+        <v>46301.5006944444</v>
+      </c>
+      <c s="21" t="inlineStr" r="H182">
+        <is>
+          <t xml:space="preserve">12</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I182"/>
+      <c s="21" t="inlineStr" r="J182">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K182">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L182">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M182"/>
+      <c s="20" t="inlineStr" r="N182">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O182">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 12 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P182"/>
+      <c s="20" t="inlineStr" r="R182">
+        <is>
+          <t xml:space="preserve">345a5860-c195-11f1-8702-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S182">
+        <is>
+          <t xml:space="preserve">10047517    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U182">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V182"/>
+    </row>
+    <row r="183" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A183">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B183">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D183">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E183">
+        <v>46301.5013888889</v>
+      </c>
+      <c s="18" r="G183">
+        <v>46301.5034722222</v>
+      </c>
+      <c s="17" t="inlineStr" r="H183">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I183"/>
+      <c s="17" t="inlineStr" r="J183">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K183">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L183">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M183"/>
+      <c s="16" t="inlineStr" r="N183">
+        <is>
+          <t xml:space="preserve">RETIRADA DE INSUMOS</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O183">
+        <is>
+          <t xml:space="preserve">retirada de insunos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P183"/>
+      <c s="16" t="inlineStr" r="R183">
+        <is>
+          <t xml:space="preserve">ee58fae0-c196-11f1-b328-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S183">
+        <is>
+          <t xml:space="preserve">10047517    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U183">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V183"/>
+    </row>
+    <row r="184" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A184">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B184">
+        <is>
+          <t xml:space="preserve">TR04-ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D184">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E184">
+        <v>46301.5104166667</v>
+      </c>
+      <c s="22" r="G184">
+        <v>46301.5173611111</v>
+      </c>
+      <c s="21" t="inlineStr" r="H184">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I184"/>
+      <c s="21" t="inlineStr" r="J184">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K184">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L184">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M184"/>
+      <c s="20" t="inlineStr" r="N184">
+        <is>
+          <t xml:space="preserve">SETUP COMPLETO</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O184">
+        <is>
+          <t xml:space="preserve">trocar 0.95x1.000 para 0.90x1000 e fazer regulagem</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P184"/>
+      <c s="20" t="inlineStr" r="R184">
+        <is>
+          <t xml:space="preserve">8cf7fcb0-c19b-11f1-9560-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S184">
+        <is>
+          <t xml:space="preserve">10048229    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U184">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V184"/>
+    </row>
+    <row r="185" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A185">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B185">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D185">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E185">
+        <v>46301.5180555556</v>
+      </c>
+      <c s="18" r="G185">
+        <v>46301.5215277778</v>
+      </c>
+      <c s="17" t="inlineStr" r="H185">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I185"/>
+      <c s="17" t="inlineStr" r="J185">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K185">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L185">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M185"/>
+      <c s="16" t="inlineStr" r="N185">
+        <is>
+          <t xml:space="preserve">AJUSTE DA MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O185">
+        <is>
+          <t xml:space="preserve">ajuste da mesa de 2800para 3MT</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P185"/>
+      <c s="16" t="inlineStr" r="R185">
+        <is>
+          <t xml:space="preserve">3d289470-c19a-11f1-c7eb-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S185">
+        <is>
+          <t xml:space="preserve">10047518    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U185">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V185"/>
+    </row>
+    <row r="186" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A186">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B186">
+        <is>
+          <t xml:space="preserve">TR05-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D186">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E186">
+        <v>46301.525</v>
+      </c>
+      <c s="22" r="G186">
+        <v>46301.5305555556</v>
+      </c>
+      <c s="21" t="inlineStr" r="H186">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I186"/>
+      <c s="21" t="inlineStr" r="J186">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K186">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L186">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M186"/>
+      <c s="20" t="inlineStr" r="N186">
+        <is>
+          <t xml:space="preserve">MESA CHEIA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O186">
+        <is>
+          <t xml:space="preserve">aguardando retirada de material 6000x1200</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P186"/>
+      <c s="20" t="inlineStr" r="R186">
+        <is>
+          <t xml:space="preserve">c5566060-c19b-11f1-9283-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S186">
+        <is>
+          <t xml:space="preserve">10046767    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U186">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V186"/>
+    </row>
+    <row r="187" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A187">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B187">
+        <is>
+          <t xml:space="preserve">TR01-MESA TRANSPORTADORA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D187">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E187">
+        <v>46301.5270833333</v>
+      </c>
+      <c s="18" r="G187">
+        <v>46301.5340277778</v>
+      </c>
+      <c s="17" t="inlineStr" r="H187">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I187"/>
+      <c s="17" t="inlineStr" r="J187">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K187">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L187">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M187"/>
+      <c s="16" t="inlineStr" r="N187">
+        <is>
+          <t xml:space="preserve">PONTE ROLANTE INDISPONÍVEL</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O187">
+        <is>
+          <t xml:space="preserve">PONTE OCUPADA EXPEDIÇÃO</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P187"/>
+      <c s="16" t="inlineStr" r="R187">
+        <is>
+          <t xml:space="preserve">186865f0-c19c-11f1-91dc-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S187">
+        <is>
+          <t xml:space="preserve">10047518    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U187">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V187"/>
+    </row>
+    <row r="188" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A188">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B188">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D188">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E188">
+        <v>46301.5395833333</v>
+      </c>
+      <c s="22" r="G188">
+        <v>46301.5416666667</v>
+      </c>
+      <c s="21" t="inlineStr" r="H188">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I188"/>
+      <c s="21" t="inlineStr" r="J188">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K188">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L188">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M188"/>
+      <c s="20" t="inlineStr" r="N188">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE CHAPA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O188">
+        <is>
+          <t xml:space="preserve">ajuste da chapa</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P188"/>
+      <c s="20" t="inlineStr" r="R188">
+        <is>
+          <t xml:space="preserve">a4e4fd20-c19e-11f1-ccb0-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S188">
+        <is>
+          <t xml:space="preserve">10047518    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U188">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V188"/>
+    </row>
+    <row r="189" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A189">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B189">
+        <is>
+          <t xml:space="preserve">TR05-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D189">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E189">
+        <v>46301.5409722222</v>
+      </c>
+      <c s="18" r="G189">
+        <v>46301.5444444444</v>
+      </c>
+      <c s="17" t="inlineStr" r="H189">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I189"/>
+      <c s="17" t="inlineStr" r="J189">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K189">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L189">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M189"/>
+      <c s="16" t="inlineStr" r="N189">
+        <is>
+          <t xml:space="preserve">MESA CHEIA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O189">
+        <is>
+          <t xml:space="preserve">aguardando retirada do material 6000x1200</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P189"/>
+      <c s="16" t="inlineStr" r="R189">
+        <is>
+          <t xml:space="preserve">ef16fa10-c19e-11f1-b782-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S189">
+        <is>
+          <t xml:space="preserve">10046767    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U189">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V189"/>
+    </row>
+    <row r="190" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A190">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B190">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D190">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E190">
+        <v>46301.5472222222</v>
+      </c>
+      <c s="22" r="G190">
+        <v>46301.5493055556</v>
+      </c>
+      <c s="21" t="inlineStr" r="H190">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I190"/>
+      <c s="21" t="inlineStr" r="J190">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K190">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L190">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M190"/>
+      <c s="20" t="inlineStr" r="N190">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE CHAPA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O190">
+        <is>
+          <t xml:space="preserve">ajuste da chapa</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P190"/>
+      <c s="20" t="inlineStr" r="R190">
+        <is>
+          <t xml:space="preserve">3238d6f0-c1a0-11f1-c435-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S190">
+        <is>
+          <t xml:space="preserve">10047518    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U190">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V190"/>
+    </row>
+    <row r="191" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A191">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B191"/>
+      <c s="17" t="inlineStr" r="D191">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E191">
+        <v>46301.5534722222</v>
+      </c>
+      <c s="18" r="G191">
+        <v>46301.5638888889</v>
+      </c>
+      <c s="17" t="inlineStr" r="H191">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I191"/>
+      <c s="17" t="inlineStr" r="J191">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K191">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L191">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M191"/>
+      <c s="16" t="inlineStr" r="N191">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O191">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P191"/>
+      <c s="16" t="inlineStr" r="R191">
+        <is>
+          <t xml:space="preserve">7bfd76a0-c1a1-11f1-9a9b-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S191">
+        <is>
+          <t xml:space="preserve">10047518    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U191">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V191"/>
+    </row>
+    <row r="192" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A192">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B192">
+        <is>
+          <t xml:space="preserve">TR05-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D192">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E192">
+        <v>46301.5590277778</v>
+      </c>
+      <c s="22" r="G192">
+        <v>46301.5694444444</v>
+      </c>
+      <c s="21" t="inlineStr" r="H192">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I192"/>
+      <c s="21" t="inlineStr" r="J192">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K192">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L192">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M192"/>
+      <c s="20" t="inlineStr" r="N192">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O192">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P192"/>
+      <c s="20" t="inlineStr" r="R192">
+        <is>
+          <t xml:space="preserve">8de65020-c1a2-11f1-bdd6-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S192">
+        <is>
+          <t xml:space="preserve">10046767    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U192">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V192"/>
+    </row>
+    <row r="193" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A193">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B193">
+        <is>
+          <t xml:space="preserve">TR01-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D193">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E193">
+        <v>46301.5645833333</v>
+      </c>
+      <c s="18" r="G193">
+        <v>46301.5701388889</v>
+      </c>
+      <c s="17" t="inlineStr" r="H193">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I193"/>
+      <c s="17" t="inlineStr" r="J193">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K193">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L193">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M193"/>
+      <c s="16" t="inlineStr" r="N193">
+        <is>
+          <t xml:space="preserve">TROCA DAS CASTANHAS DO MANDRIL</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O193">
+        <is>
+          <t xml:space="preserve">troca das castanhas</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P193"/>
+      <c s="16" t="inlineStr" r="R193">
+        <is>
+          <t xml:space="preserve">5296fc20-c1a4-11f1-c704-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S193">
+        <is>
+          <t xml:space="preserve">10047518    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U193">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V193"/>
+    </row>
+    <row r="194" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A194">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B194">
+        <is>
+          <t xml:space="preserve">TR05-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D194">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E194">
+        <v>46301.5791666667</v>
+      </c>
+      <c s="22" r="G194">
+        <v>46301.5861111111</v>
+      </c>
+      <c s="21" t="inlineStr" r="H194">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I194"/>
+      <c s="21" t="inlineStr" r="J194">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K194">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L194">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M194"/>
+      <c s="20" t="inlineStr" r="N194">
+        <is>
+          <t xml:space="preserve">AGUARDANDO INSPEÇÃO DE  QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O194">
+        <is>
+          <t xml:space="preserve">aguardando a inspeção do material de ud 2003896686 inspetor da qualidade liberou passar o material como bom foi retirado 801 kg de pnc oxidação galvânica</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P194"/>
+      <c s="20" t="inlineStr" r="R194">
+        <is>
+          <t xml:space="preserve">8f1a3f70-c1a6-11f1-cc41-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S194">
+        <is>
+          <t xml:space="preserve">10046767    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U194">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V194"/>
+    </row>
+    <row r="195" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A195">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B195">
+        <is>
+          <t xml:space="preserve">TR01-MESA TRANSPORTADORA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D195">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E195">
+        <v>46301.58125</v>
+      </c>
+      <c s="18" r="G195">
+        <v>46301.5840277778</v>
+      </c>
+      <c s="17" t="inlineStr" r="H195">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I195"/>
+      <c s="17" t="inlineStr" r="J195">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K195">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L195">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M195"/>
+      <c s="16" t="inlineStr" r="N195">
+        <is>
+          <t xml:space="preserve">PESAGEM DE FARDO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O195">
+        <is>
+          <t xml:space="preserve">pesagem de fardo</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P195"/>
+      <c s="16" t="inlineStr" r="R195">
+        <is>
+          <t xml:space="preserve">0ba41d40-c1a7-11f1-c6cc-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S195">
+        <is>
+          <t xml:space="preserve">10048039    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U195">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V195"/>
+    </row>
+    <row r="196" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A196">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B196">
+        <is>
+          <t xml:space="preserve">TR05-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D196">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E196">
+        <v>46301.5888888889</v>
+      </c>
+      <c s="22" r="G196">
+        <v>46301.5909722222</v>
+      </c>
+      <c s="21" t="inlineStr" r="H196">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I196"/>
+      <c s="21" t="inlineStr" r="J196">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K196">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L196">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M196"/>
+      <c s="20" t="inlineStr" r="N196">
+        <is>
+          <t xml:space="preserve">AJUSTE DE MESA GUIA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O196">
+        <is>
+          <t xml:space="preserve">ajuste da mesa guia</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P196"/>
+      <c s="20" t="inlineStr" r="R196">
+        <is>
+          <t xml:space="preserve">8b9d14b0-c1a8-11f1-c2b0-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S196">
+        <is>
+          <t xml:space="preserve">10046767    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U196">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V196"/>
+    </row>
+    <row r="197" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A197">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B197">
+        <is>
+          <t xml:space="preserve">TR05-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D197">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E197">
+        <v>46301.5958333333</v>
+      </c>
+      <c s="18" r="G197">
+        <v>46301.5979166667</v>
+      </c>
+      <c s="17" t="inlineStr" r="H197">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I197"/>
+      <c s="17" t="inlineStr" r="J197">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K197">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L197">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M197"/>
+      <c s="16" t="inlineStr" r="N197">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE FARDO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O197">
+        <is>
+          <t xml:space="preserve">passagem de fardo</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P197"/>
+      <c s="16" t="inlineStr" r="R197">
+        <is>
+          <t xml:space="preserve">fc153c80-c1a9-11f1-9867-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S197">
+        <is>
+          <t xml:space="preserve">10046767    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U197">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V197"/>
+    </row>
+    <row r="198" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A198">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B198">
+        <is>
+          <t xml:space="preserve">TR01-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D198">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E198">
+        <v>46301.5958333333</v>
+      </c>
+      <c s="22" r="G198">
+        <v>46301.6034722222</v>
+      </c>
+      <c s="21" t="inlineStr" r="H198">
+        <is>
+          <t xml:space="preserve">11</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I198"/>
+      <c s="21" t="inlineStr" r="J198">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K198">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L198">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M198"/>
+      <c s="20" t="inlineStr" r="N198">
+        <is>
+          <t xml:space="preserve">AGUARDANDO INSPEÇÃO DE  QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O198">
+        <is>
+          <t xml:space="preserve">aguardando qualidade material com oxidação  UD:2003936092 foi liberado como bom</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P198"/>
+      <c s="20" t="inlineStr" r="R198">
+        <is>
+          <t xml:space="preserve">f8356a40-c1a9-11f1-ceba-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S198">
+        <is>
+          <t xml:space="preserve">10048039    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U198">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V198"/>
+    </row>
+    <row r="199" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A199">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B199">
+        <is>
+          <t xml:space="preserve">TR05-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D199">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E199">
+        <v>46301.6041666667</v>
+      </c>
+      <c s="18" r="G199">
+        <v>46301.6069444444</v>
+      </c>
+      <c s="17" t="inlineStr" r="H199">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I199"/>
+      <c s="17" t="inlineStr" r="J199">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K199">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L199">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M199"/>
+      <c s="16" t="inlineStr" r="N199">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE FARDO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O199">
+        <is>
+          <t xml:space="preserve">Passagem de fardo</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P199"/>
+      <c s="16" t="inlineStr" r="R199">
+        <is>
+          <t xml:space="preserve">a88ce390-c1ab-11f1-a2f9-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S199">
+        <is>
+          <t xml:space="preserve">10046767    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U199">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V199"/>
+    </row>
+    <row r="200" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A200">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B200">
+        <is>
+          <t xml:space="preserve">TR01-MESA TRANSPORTADORA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D200">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E200">
+        <v>46301.6076388889</v>
+      </c>
+      <c s="22" r="G200">
+        <v>46301.6104166667</v>
+      </c>
+      <c s="21" t="inlineStr" r="H200">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I200"/>
+      <c s="21" t="inlineStr" r="J200">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K200">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L200">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M200"/>
+      <c s="20" t="inlineStr" r="N200">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE CHAPA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O200">
+        <is>
+          <t xml:space="preserve">ajustando chapa</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P200"/>
+      <c s="20" t="inlineStr" r="R200">
+        <is>
+          <t xml:space="preserve">509d2e50-c1ac-11f1-9960-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S200">
+        <is>
+          <t xml:space="preserve">10048039    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U200">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V200"/>
+    </row>
+    <row r="201" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A201">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B201"/>
+      <c s="17" t="inlineStr" r="D201">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E201">
+        <v>46301.6104166667</v>
+      </c>
+      <c s="18" r="G201">
+        <v>46301.6208333333</v>
+      </c>
+      <c s="17" t="inlineStr" r="H201">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I201"/>
+      <c s="17" t="inlineStr" r="J201">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K201">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L201">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M201"/>
+      <c s="16" t="inlineStr" r="N201">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O201">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P201"/>
+      <c s="16" t="inlineStr" r="R201">
+        <is>
+          <t xml:space="preserve">eb5b2230-c1ac-11f1-a3eb-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S201">
+        <is>
+          <t xml:space="preserve">10048227    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U201">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V201"/>
+    </row>
+    <row r="202" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A202">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B202">
+        <is>
+          <t xml:space="preserve">TR05-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D202">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E202">
+        <v>46301.6131944444</v>
+      </c>
+      <c s="22" r="G202">
+        <v>46301.61875</v>
+      </c>
+      <c s="21" t="inlineStr" r="H202">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I202"/>
+      <c s="21" t="inlineStr" r="J202">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K202">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L202">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M202"/>
+      <c s="20" t="inlineStr" r="N202">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE FARDO</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O202">
+        <is>
+          <t xml:space="preserve">Passagem de fardo</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P202"/>
+      <c s="20" t="inlineStr" r="R202">
+        <is>
+          <t xml:space="preserve">7ace9d20-c1ad-11f1-cf35-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S202">
+        <is>
+          <t xml:space="preserve">10046767    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U202">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V202"/>
+    </row>
+    <row r="203" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A203">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B203"/>
+      <c s="17" t="inlineStr" r="D203">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E203">
+        <v>46301.6159722222</v>
+      </c>
+      <c s="18" r="G203">
+        <v>46301.6222222222</v>
+      </c>
+      <c s="17" t="inlineStr" r="H203">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I203"/>
+      <c s="17" t="inlineStr" r="J203">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K203">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L203">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M203"/>
+      <c s="16" t="inlineStr" r="N203">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O203">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 9 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P203"/>
+      <c s="16" t="inlineStr" r="R203">
+        <is>
+          <t xml:space="preserve">0dcbb400-c1ae-11f1-865f-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S203">
+        <is>
+          <t xml:space="preserve">10048039    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U203">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V203"/>
+    </row>
+    <row r="204" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A204">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B204">
+        <is>
+          <t xml:space="preserve">TR02-MESA TRANSPORTADORA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D204">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E204">
+        <v>46301.6215277778</v>
+      </c>
+      <c s="22" r="G204">
+        <v>46301.6229166667</v>
+      </c>
+      <c s="21" t="inlineStr" r="H204">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I204"/>
+      <c s="21" t="inlineStr" r="J204">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K204">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L204">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M204"/>
+      <c s="20" t="inlineStr" r="N204">
+        <is>
+          <t xml:space="preserve">RETIRADA DE PNC</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O204">
+        <is>
+          <t xml:space="preserve">RETIRADA DE PNC</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P204"/>
+      <c s="20" t="inlineStr" r="R204">
+        <is>
+          <t xml:space="preserve">5932e020-c1af-11f1-8123-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S204">
+        <is>
+          <t xml:space="preserve">10048227    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U204">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V204"/>
+    </row>
+    <row r="205" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A205">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B205">
+        <is>
+          <t xml:space="preserve">TR01-MESA TRANSPORTADORA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D205">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E205">
+        <v>46301.6229166667</v>
+      </c>
+      <c s="18" r="G205">
+        <v>46301.6270833333</v>
+      </c>
+      <c s="17" t="inlineStr" r="H205">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I205"/>
+      <c s="17" t="inlineStr" r="J205">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K205">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L205">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M205"/>
+      <c s="16" t="inlineStr" r="N205">
+        <is>
+          <t xml:space="preserve">PONTE ROLANTE INDISPONÍVEL</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O205">
+        <is>
+          <t xml:space="preserve">ponte ocupada</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P205"/>
+      <c s="16" t="inlineStr" r="R205">
+        <is>
+          <t xml:space="preserve">5c4d8da0-c1af-11f1-9e0f-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S205">
+        <is>
+          <t xml:space="preserve">10048039    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U205">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V205"/>
+    </row>
+    <row r="206" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A206">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B206">
+        <is>
+          <t xml:space="preserve">TR05-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D206">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E206">
+        <v>46301.6256944444</v>
+      </c>
+      <c s="22" r="G206">
+        <v>46301.6277777778</v>
+      </c>
+      <c s="21" t="inlineStr" r="H206">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I206"/>
+      <c s="21" t="inlineStr" r="J206">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K206">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L206">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M206"/>
+      <c s="20" t="inlineStr" r="N206">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE FARDO</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O206">
+        <is>
+          <t xml:space="preserve">Passagem de fardo</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P206"/>
+      <c s="20" t="inlineStr" r="R206">
+        <is>
+          <t xml:space="preserve">014ffc20-c1b0-11f1-86b7-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S206">
+        <is>
+          <t xml:space="preserve">10046767    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U206">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V206"/>
+    </row>
+    <row r="207" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A207">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B207">
+        <is>
+          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D207">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E207">
+        <v>46301.6291666667</v>
+      </c>
+      <c s="18" r="G207">
+        <v>46301.6361111111</v>
+      </c>
+      <c s="17" t="inlineStr" r="H207">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I207"/>
+      <c s="17" t="inlineStr" r="J207">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K207">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L207">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M207"/>
+      <c s="16" t="inlineStr" r="N207">
+        <is>
+          <t xml:space="preserve">QUALIDADE DA MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O207">
+        <is>
+          <t xml:space="preserve">Esperando a qualidade para verificar a bobina 2,65mm que esta com quebra de superfcie e ondulação nas bordas . OBS: UD 5012293779 FOI LIBERADO PARA PRODUZIR PELA  QUALIDADE .</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P207"/>
+      <c s="16" t="inlineStr" r="R207">
+        <is>
+          <t xml:space="preserve">9fde58f0-c1b0-11f1-90aa-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S207">
+        <is>
+          <t xml:space="preserve">10048227    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U207">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V207"/>
+    </row>
+    <row r="208" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A208">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B208">
+        <is>
+          <t xml:space="preserve">TR05-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D208">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E208">
+        <v>46301.6368055556</v>
+      </c>
+      <c s="22" r="G208">
+        <v>46301.6416666667</v>
+      </c>
+      <c s="21" t="inlineStr" r="H208">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I208"/>
+      <c s="21" t="inlineStr" r="J208">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K208">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L208">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M208"/>
+      <c s="20" t="inlineStr" r="N208">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE FARDO</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O208">
+        <is>
+          <t xml:space="preserve">Passagem de fardo</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P208"/>
+      <c s="20" t="inlineStr" r="R208">
+        <is>
+          <t xml:space="preserve">26169670-c1b2-11f1-8662-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S208">
+        <is>
+          <t xml:space="preserve">10046767    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U208">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V208"/>
+    </row>
+    <row r="209" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A209">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B209">
+        <is>
+          <t xml:space="preserve">TR01-MESA TRANSPORTADORA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D209">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E209">
+        <v>46301.6388888889</v>
+      </c>
+      <c s="18" r="G209">
+        <v>46301.6416666667</v>
+      </c>
+      <c s="17" t="inlineStr" r="H209">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I209"/>
+      <c s="17" t="inlineStr" r="J209">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K209">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L209">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M209"/>
+      <c s="16" t="inlineStr" r="N209">
+        <is>
+          <t xml:space="preserve">PESAGEM DE FARDO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O209">
+        <is>
+          <t xml:space="preserve">esperando op de ponte</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P209"/>
+      <c s="16" t="inlineStr" r="R209">
+        <is>
+          <t xml:space="preserve">98266ab0-c1b2-11f1-bf8b-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S209">
+        <is>
+          <t xml:space="preserve">10048039    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U209">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V209"/>
+    </row>
+    <row r="210" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A210">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B210">
+        <is>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D210">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E210">
+        <v>46301.6493055556</v>
+      </c>
+      <c s="22" r="G210">
+        <v>46302.2952486921</v>
+      </c>
+      <c s="21" t="inlineStr" r="H210">
+        <is>
+          <t xml:space="preserve">930</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I210"/>
+      <c s="21" t="inlineStr" r="J210">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K210">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L210">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M210"/>
+      <c s="20" t="inlineStr" r="N210">
+        <is>
+          <t xml:space="preserve">FALTA DEMANDA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O210">
+        <is>
+          <t xml:space="preserve">Falta de demanda</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P210"/>
+      <c s="20" t="inlineStr" r="R210">
+        <is>
+          <t xml:space="preserve">a80a7e10-c1b4-11f1-9b7d-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="S210"/>
+      <c s="20" t="inlineStr" r="U210">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V210"/>
+    </row>
+    <row r="211" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A211">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B211">
+        <is>
+          <t xml:space="preserve">TR05-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D211">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E211">
+        <v>46301.65</v>
+      </c>
+      <c s="18" r="G211">
+        <v>46301.6527777778</v>
+      </c>
+      <c s="17" t="inlineStr" r="H211">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I211"/>
+      <c s="17" t="inlineStr" r="J211">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K211">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L211">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M211"/>
+      <c s="16" t="inlineStr" r="N211">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE FARDO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O211">
+        <is>
+          <t xml:space="preserve">Passagem de fardo</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P211"/>
+      <c s="16" t="inlineStr" r="R211">
+        <is>
+          <t xml:space="preserve">e5ba9380-c1b4-11f1-a22c-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S211">
+        <is>
+          <t xml:space="preserve">10046767    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U211">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V211"/>
+    </row>
+    <row r="212" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A212">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B212">
+        <is>
+          <t xml:space="preserve">TR01-MESA TRANSPORTADORA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D212">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E212">
+        <v>46301.6534722222</v>
+      </c>
+      <c s="22" r="G212">
+        <v>46301.6569444444</v>
+      </c>
+      <c s="21" t="inlineStr" r="H212">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I212"/>
+      <c s="21" t="inlineStr" r="J212">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K212">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L212">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M212"/>
+      <c s="20" t="inlineStr" r="N212">
+        <is>
+          <t xml:space="preserve">PESAGEM DE FARDO</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O212">
+        <is>
+          <t xml:space="preserve">esperando op de ponte</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P212"/>
+      <c s="20" t="inlineStr" r="R212">
+        <is>
+          <t xml:space="preserve">97c6de30-c1b5-11f1-abf9-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S212">
+        <is>
+          <t xml:space="preserve">10048039    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U212">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V212"/>
+    </row>
+    <row r="213" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A213">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B213">
+        <is>
+          <t xml:space="preserve">TR05-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D213">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E213">
+        <v>46301.6576388889</v>
+      </c>
+      <c s="18" r="G213">
+        <v>46301.6680555556</v>
+      </c>
+      <c s="17" t="inlineStr" r="H213">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I213"/>
+      <c s="17" t="inlineStr" r="J213">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K213">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L213">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M213"/>
+      <c s="16" t="inlineStr" r="N213">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O213">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P213"/>
+      <c s="16" t="inlineStr" r="R213">
+        <is>
+          <t xml:space="preserve">65a1d7b4-c1b6-11f1-ca7f-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S213">
+        <is>
+          <t xml:space="preserve">10046773    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U213">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V213"/>
+    </row>
+    <row r="214" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A214">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B214">
+        <is>
+          <t xml:space="preserve">TR01-MESA TRANSPORTADORA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D214">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E214">
+        <v>46301.6618055556</v>
+      </c>
+      <c s="22" r="G214">
+        <v>46301.6638888889</v>
+      </c>
+      <c s="21" t="inlineStr" r="H214">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I214"/>
+      <c s="21" t="inlineStr" r="J214">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K214">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L214">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M214"/>
+      <c s="20" t="inlineStr" r="N214">
+        <is>
+          <t xml:space="preserve">RETIRADA DE INSUMOS</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O214">
+        <is>
+          <t xml:space="preserve">retirada de insumos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P214"/>
+      <c s="20" t="inlineStr" r="R214">
+        <is>
+          <t xml:space="preserve">40983990-c1b7-11f1-8891-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S214">
+        <is>
+          <t xml:space="preserve">10048039    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U214">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V214"/>
+    </row>
+    <row r="215" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A215">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B215">
+        <is>
+          <t xml:space="preserve">TR02-MESA TRANSPORTADORA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D215">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E215">
+        <v>46301.6673611111</v>
+      </c>
+      <c s="18" r="G215">
+        <v>46301.6722222222</v>
+      </c>
+      <c s="17" t="inlineStr" r="H215">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I215"/>
+      <c s="17" t="inlineStr" r="J215">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K215">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L215">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M215"/>
+      <c s="16" t="inlineStr" r="N215">
+        <is>
+          <t xml:space="preserve">RETIRADA DE PNC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O215">
+        <is>
+          <t xml:space="preserve">Retirada de sucata</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P215"/>
+      <c s="16" t="inlineStr" r="R215">
+        <is>
+          <t xml:space="preserve">4c716880-c1b8-11f1-9757-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S215">
+        <is>
+          <t xml:space="preserve">10048227    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U215">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V215"/>
+    </row>
+    <row r="216" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A216">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B216"/>
+      <c s="21" t="inlineStr" r="D216">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E216">
+        <v>46301.6743055556</v>
+      </c>
+      <c s="22" r="G216">
+        <v>46301.6791666667</v>
+      </c>
+      <c s="21" t="inlineStr" r="H216">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I216"/>
+      <c s="21" t="inlineStr" r="J216">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K216">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L216">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M216"/>
+      <c s="20" t="inlineStr" r="N216">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O216">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 7 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P216"/>
+      <c s="20" t="inlineStr" r="R216">
+        <is>
+          <t xml:space="preserve">bb3b9230-c1b9-11f1-9cdc-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S216">
+        <is>
+          <t xml:space="preserve">10048227    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U216">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V216"/>
+    </row>
+    <row r="217" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A217">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B217">
+        <is>
+          <t xml:space="preserve">TR01-MESA TRANSPORTADORA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D217">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E217">
+        <v>46301.6784722222</v>
+      </c>
+      <c s="18" r="G217">
+        <v>46301.6826388889</v>
+      </c>
+      <c s="17" t="inlineStr" r="H217">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I217"/>
+      <c s="17" t="inlineStr" r="J217">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K217">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L217">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M217"/>
+      <c s="16" t="inlineStr" r="N217">
+        <is>
+          <t xml:space="preserve">PESAGEM DE FARDO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O217">
+        <is>
+          <t xml:space="preserve">esperado op de ponte</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P217"/>
+      <c s="16" t="inlineStr" r="R217">
+        <is>
+          <t xml:space="preserve">9e4de960-c1ba-11f1-9d94-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S217">
+        <is>
+          <t xml:space="preserve">10048039    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U217">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V217"/>
+    </row>
+    <row r="218" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A218">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B218">
+        <is>
+          <t xml:space="preserve">TR05-MESA FIXA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D218">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E218">
+        <v>46301.68125</v>
+      </c>
+      <c s="22" r="G218">
+        <v>46301.6868055556</v>
+      </c>
+      <c s="21" t="inlineStr" r="H218">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I218"/>
+      <c s="21" t="inlineStr" r="J218">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K218">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L218">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M218"/>
+      <c s="20" t="inlineStr" r="N218">
+        <is>
+          <t xml:space="preserve">MESA CHEIA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O218">
+        <is>
+          <t xml:space="preserve">Aguardando retirada de material 6000x1200.</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P218"/>
+      <c s="20" t="inlineStr" r="R218">
+        <is>
+          <t xml:space="preserve">11045de0-c1bb-11f1-a963-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S218">
+        <is>
+          <t xml:space="preserve">10046774    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U218">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V218"/>
+    </row>
+    <row r="219" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A219">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B219">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D219">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E219">
+        <v>46301.6881944444</v>
+      </c>
+      <c s="18" r="G219">
+        <v>46301.6909722222</v>
+      </c>
+      <c s="17" t="inlineStr" r="H219">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I219"/>
+      <c s="17" t="inlineStr" r="J219">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K219">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L219">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M219"/>
+      <c s="16" t="inlineStr" r="N219">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE CHAPA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O219">
+        <is>
+          <t xml:space="preserve">ajustando chapa</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P219"/>
+      <c s="16" t="inlineStr" r="R219">
+        <is>
+          <t xml:space="preserve">82c72e20-c1bc-11f1-8665-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S219">
+        <is>
+          <t xml:space="preserve">10048039    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U219">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V219"/>
+    </row>
+    <row r="220" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A220">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B220"/>
+      <c s="21" t="inlineStr" r="D220">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E220">
+        <v>46301.6930555556</v>
+      </c>
+      <c s="22" r="G220">
+        <v>46302.2952486921</v>
+      </c>
+      <c s="21" t="inlineStr" r="H220">
+        <is>
+          <t xml:space="preserve">867</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I220"/>
+      <c s="21" t="inlineStr" r="J220">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K220">
+        <is>
+          <t xml:space="preserve">Integração Automática</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L220">
+        <is>
+          <t xml:space="preserve">Integração Automática</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M220"/>
+      <c s="20" t="inlineStr" r="N220">
+        <is>
+          <t xml:space="preserve">Parada Registrada via Integração</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O220">
+        <is>
+          <t xml:space="preserve">PARADA REGISTRADA VIA INTEGRAÇÃO AUTOMÁTICA.</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P220"/>
+      <c s="20" t="inlineStr" r="R220">
+        <is>
+          <t xml:space="preserve">8d4253b0-c1bd-11f1-8c3f-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S220">
+        <is>
+          <t xml:space="preserve">10046774    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U220">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V220"/>
+    </row>
+    <row r="221" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A221">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B221"/>
+      <c s="17" t="inlineStr" r="D221">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E221">
+        <v>46301.6986111111</v>
+      </c>
+      <c s="18" r="G221">
+        <v>46302.2952486921</v>
+      </c>
+      <c s="17" t="inlineStr" r="H221">
+        <is>
+          <t xml:space="preserve">859</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I221"/>
+      <c s="17" t="inlineStr" r="J221">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K221">
+        <is>
+          <t xml:space="preserve">Integração Automática</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L221">
+        <is>
+          <t xml:space="preserve">Integração Automática</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M221"/>
+      <c s="16" t="inlineStr" r="N221">
+        <is>
+          <t xml:space="preserve">Parada Registrada via Integração</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O221">
+        <is>
+          <t xml:space="preserve">PARADA REGISTRADA VIA INTEGRAÇÃO AUTOMÁTICA.</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P221"/>
+      <c s="16" t="inlineStr" r="R221">
+        <is>
+          <t xml:space="preserve">902077f0-c1be-11f1-9d7b-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S221">
+        <is>
+          <t xml:space="preserve">10048227    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U221">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V221"/>
+    </row>
+    <row r="222" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A222">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B222"/>
+      <c s="21" t="inlineStr" r="D222">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E222">
+        <v>46301.7013888889</v>
+      </c>
+      <c s="22" r="G222">
+        <v>46302.2840277778</v>
+      </c>
+      <c s="21" t="inlineStr" r="H222">
+        <is>
+          <t xml:space="preserve">839</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I222"/>
+      <c s="21" t="inlineStr" r="J222">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K222">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L222">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M222"/>
+      <c s="20" t="inlineStr" r="N222">
+        <is>
+          <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O222">
+        <is>
+          <t xml:space="preserve">Parada registrada automaticamente pelo sistema</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P222"/>
+      <c s="20" t="inlineStr" r="R222">
+        <is>
+          <t xml:space="preserve">1e40e600-c1bf-11f1-add1-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S222">
+        <is>
+          <t xml:space="preserve">10048039    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U222">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V222"/>
+    </row>
+    <row r="223" ht="15.55" customHeight="0">
+      <c s="23" t="inlineStr" r="A223">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 03</t>
+        </is>
+      </c>
+      <c s="24" t="str" r="B223"/>
+      <c s="10" t="str" r="C223"/>
+      <c s="25" t="inlineStr" r="D223">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="26" r="E223">
+        <v>46301.7013888889</v>
+      </c>
+      <c s="10" t="str" r="F223"/>
+      <c s="26" r="G223">
+        <v>46302.2840277778</v>
+      </c>
+      <c s="25" t="inlineStr" r="H223">
+        <is>
+          <t xml:space="preserve">839</t>
+        </is>
+      </c>
+      <c s="25" t="str" r="I223"/>
+      <c s="25" t="inlineStr" r="J223">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="K223">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="L223">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="24" t="str" r="M223"/>
+      <c s="24" t="inlineStr" r="N223">
+        <is>
+          <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="O223">
+        <is>
+          <t xml:space="preserve">Parada registrada automaticamente pelo sistema</t>
+        </is>
+      </c>
+      <c s="24" t="str" r="P223"/>
+      <c s="10" t="str" r="Q223"/>
+      <c s="24" t="inlineStr" r="R223">
+        <is>
+          <t xml:space="preserve">1e703360-c1bf-11f1-c100-f2050a003223</t>
+        </is>
+      </c>
+      <c s="24" t="str" r="S223"/>
+      <c s="10" t="str" r="T223"/>
+      <c s="24" t="inlineStr" r="U223">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="11" t="str" r="V223"/>
+    </row>
+    <row r="224" ht="0.05" customHeight="1"/>
   </sheetData>
   <mergeCells>
     <mergeCell ref="A3:B8"/>
@@ -11232,6 +16073,346 @@
     <mergeCell ref="P155:Q155"/>
     <mergeCell ref="S155:T155"/>
     <mergeCell ref="U155:V155"/>
+    <mergeCell ref="B156:C156"/>
+    <mergeCell ref="E156:F156"/>
+    <mergeCell ref="P156:Q156"/>
+    <mergeCell ref="S156:T156"/>
+    <mergeCell ref="U156:V156"/>
+    <mergeCell ref="B157:C157"/>
+    <mergeCell ref="E157:F157"/>
+    <mergeCell ref="P157:Q157"/>
+    <mergeCell ref="S157:T157"/>
+    <mergeCell ref="U157:V157"/>
+    <mergeCell ref="B158:C158"/>
+    <mergeCell ref="E158:F158"/>
+    <mergeCell ref="P158:Q158"/>
+    <mergeCell ref="S158:T158"/>
+    <mergeCell ref="U158:V158"/>
+    <mergeCell ref="B159:C159"/>
+    <mergeCell ref="E159:F159"/>
+    <mergeCell ref="P159:Q159"/>
+    <mergeCell ref="S159:T159"/>
+    <mergeCell ref="U159:V159"/>
+    <mergeCell ref="B160:C160"/>
+    <mergeCell ref="E160:F160"/>
+    <mergeCell ref="P160:Q160"/>
+    <mergeCell ref="S160:T160"/>
+    <mergeCell ref="U160:V160"/>
+    <mergeCell ref="B161:C161"/>
+    <mergeCell ref="E161:F161"/>
+    <mergeCell ref="P161:Q161"/>
+    <mergeCell ref="S161:T161"/>
+    <mergeCell ref="U161:V161"/>
+    <mergeCell ref="B162:C162"/>
+    <mergeCell ref="E162:F162"/>
+    <mergeCell ref="P162:Q162"/>
+    <mergeCell ref="S162:T162"/>
+    <mergeCell ref="U162:V162"/>
+    <mergeCell ref="B163:C163"/>
+    <mergeCell ref="E163:F163"/>
+    <mergeCell ref="P163:Q163"/>
+    <mergeCell ref="S163:T163"/>
+    <mergeCell ref="U163:V163"/>
+    <mergeCell ref="B164:C164"/>
+    <mergeCell ref="E164:F164"/>
+    <mergeCell ref="P164:Q164"/>
+    <mergeCell ref="S164:T164"/>
+    <mergeCell ref="U164:V164"/>
+    <mergeCell ref="B165:C165"/>
+    <mergeCell ref="E165:F165"/>
+    <mergeCell ref="P165:Q165"/>
+    <mergeCell ref="S165:T165"/>
+    <mergeCell ref="U165:V165"/>
+    <mergeCell ref="B166:C166"/>
+    <mergeCell ref="E166:F166"/>
+    <mergeCell ref="P166:Q166"/>
+    <mergeCell ref="S166:T166"/>
+    <mergeCell ref="U166:V166"/>
+    <mergeCell ref="B167:C167"/>
+    <mergeCell ref="E167:F167"/>
+    <mergeCell ref="P167:Q167"/>
+    <mergeCell ref="S167:T167"/>
+    <mergeCell ref="U167:V167"/>
+    <mergeCell ref="B168:C168"/>
+    <mergeCell ref="E168:F168"/>
+    <mergeCell ref="P168:Q168"/>
+    <mergeCell ref="S168:T168"/>
+    <mergeCell ref="U168:V168"/>
+    <mergeCell ref="B169:C169"/>
+    <mergeCell ref="E169:F169"/>
+    <mergeCell ref="P169:Q169"/>
+    <mergeCell ref="S169:T169"/>
+    <mergeCell ref="U169:V169"/>
+    <mergeCell ref="B170:C170"/>
+    <mergeCell ref="E170:F170"/>
+    <mergeCell ref="P170:Q170"/>
+    <mergeCell ref="S170:T170"/>
+    <mergeCell ref="U170:V170"/>
+    <mergeCell ref="B171:C171"/>
+    <mergeCell ref="E171:F171"/>
+    <mergeCell ref="P171:Q171"/>
+    <mergeCell ref="S171:T171"/>
+    <mergeCell ref="U171:V171"/>
+    <mergeCell ref="B172:C172"/>
+    <mergeCell ref="E172:F172"/>
+    <mergeCell ref="P172:Q172"/>
+    <mergeCell ref="S172:T172"/>
+    <mergeCell ref="U172:V172"/>
+    <mergeCell ref="B173:C173"/>
+    <mergeCell ref="E173:F173"/>
+    <mergeCell ref="P173:Q173"/>
+    <mergeCell ref="S173:T173"/>
+    <mergeCell ref="U173:V173"/>
+    <mergeCell ref="B174:C174"/>
+    <mergeCell ref="E174:F174"/>
+    <mergeCell ref="P174:Q174"/>
+    <mergeCell ref="S174:T174"/>
+    <mergeCell ref="U174:V174"/>
+    <mergeCell ref="B175:C175"/>
+    <mergeCell ref="E175:F175"/>
+    <mergeCell ref="P175:Q175"/>
+    <mergeCell ref="S175:T175"/>
+    <mergeCell ref="U175:V175"/>
+    <mergeCell ref="B176:C176"/>
+    <mergeCell ref="E176:F176"/>
+    <mergeCell ref="P176:Q176"/>
+    <mergeCell ref="S176:T176"/>
+    <mergeCell ref="U176:V176"/>
+    <mergeCell ref="B177:C177"/>
+    <mergeCell ref="E177:F177"/>
+    <mergeCell ref="P177:Q177"/>
+    <mergeCell ref="S177:T177"/>
+    <mergeCell ref="U177:V177"/>
+    <mergeCell ref="B178:C178"/>
+    <mergeCell ref="E178:F178"/>
+    <mergeCell ref="P178:Q178"/>
+    <mergeCell ref="S178:T178"/>
+    <mergeCell ref="U178:V178"/>
+    <mergeCell ref="B179:C179"/>
+    <mergeCell ref="E179:F179"/>
+    <mergeCell ref="P179:Q179"/>
+    <mergeCell ref="S179:T179"/>
+    <mergeCell ref="U179:V179"/>
+    <mergeCell ref="B180:C180"/>
+    <mergeCell ref="E180:F180"/>
+    <mergeCell ref="P180:Q180"/>
+    <mergeCell ref="S180:T180"/>
+    <mergeCell ref="U180:V180"/>
+    <mergeCell ref="B181:C181"/>
+    <mergeCell ref="E181:F181"/>
+    <mergeCell ref="P181:Q181"/>
+    <mergeCell ref="S181:T181"/>
+    <mergeCell ref="U181:V181"/>
+    <mergeCell ref="B182:C182"/>
+    <mergeCell ref="E182:F182"/>
+    <mergeCell ref="P182:Q182"/>
+    <mergeCell ref="S182:T182"/>
+    <mergeCell ref="U182:V182"/>
+    <mergeCell ref="B183:C183"/>
+    <mergeCell ref="E183:F183"/>
+    <mergeCell ref="P183:Q183"/>
+    <mergeCell ref="S183:T183"/>
+    <mergeCell ref="U183:V183"/>
+    <mergeCell ref="B184:C184"/>
+    <mergeCell ref="E184:F184"/>
+    <mergeCell ref="P184:Q184"/>
+    <mergeCell ref="S184:T184"/>
+    <mergeCell ref="U184:V184"/>
+    <mergeCell ref="B185:C185"/>
+    <mergeCell ref="E185:F185"/>
+    <mergeCell ref="P185:Q185"/>
+    <mergeCell ref="S185:T185"/>
+    <mergeCell ref="U185:V185"/>
+    <mergeCell ref="B186:C186"/>
+    <mergeCell ref="E186:F186"/>
+    <mergeCell ref="P186:Q186"/>
+    <mergeCell ref="S186:T186"/>
+    <mergeCell ref="U186:V186"/>
+    <mergeCell ref="B187:C187"/>
+    <mergeCell ref="E187:F187"/>
+    <mergeCell ref="P187:Q187"/>
+    <mergeCell ref="S187:T187"/>
+    <mergeCell ref="U187:V187"/>
+    <mergeCell ref="B188:C188"/>
+    <mergeCell ref="E188:F188"/>
+    <mergeCell ref="P188:Q188"/>
+    <mergeCell ref="S188:T188"/>
+    <mergeCell ref="U188:V188"/>
+    <mergeCell ref="B189:C189"/>
+    <mergeCell ref="E189:F189"/>
+    <mergeCell ref="P189:Q189"/>
+    <mergeCell ref="S189:T189"/>
+    <mergeCell ref="U189:V189"/>
+    <mergeCell ref="B190:C190"/>
+    <mergeCell ref="E190:F190"/>
+    <mergeCell ref="P190:Q190"/>
+    <mergeCell ref="S190:T190"/>
+    <mergeCell ref="U190:V190"/>
+    <mergeCell ref="B191:C191"/>
+    <mergeCell ref="E191:F191"/>
+    <mergeCell ref="P191:Q191"/>
+    <mergeCell ref="S191:T191"/>
+    <mergeCell ref="U191:V191"/>
+    <mergeCell ref="B192:C192"/>
+    <mergeCell ref="E192:F192"/>
+    <mergeCell ref="P192:Q192"/>
+    <mergeCell ref="S192:T192"/>
+    <mergeCell ref="U192:V192"/>
+    <mergeCell ref="B193:C193"/>
+    <mergeCell ref="E193:F193"/>
+    <mergeCell ref="P193:Q193"/>
+    <mergeCell ref="S193:T193"/>
+    <mergeCell ref="U193:V193"/>
+    <mergeCell ref="B194:C194"/>
+    <mergeCell ref="E194:F194"/>
+    <mergeCell ref="P194:Q194"/>
+    <mergeCell ref="S194:T194"/>
+    <mergeCell ref="U194:V194"/>
+    <mergeCell ref="B195:C195"/>
+    <mergeCell ref="E195:F195"/>
+    <mergeCell ref="P195:Q195"/>
+    <mergeCell ref="S195:T195"/>
+    <mergeCell ref="U195:V195"/>
+    <mergeCell ref="B196:C196"/>
+    <mergeCell ref="E196:F196"/>
+    <mergeCell ref="P196:Q196"/>
+    <mergeCell ref="S196:T196"/>
+    <mergeCell ref="U196:V196"/>
+    <mergeCell ref="B197:C197"/>
+    <mergeCell ref="E197:F197"/>
+    <mergeCell ref="P197:Q197"/>
+    <mergeCell ref="S197:T197"/>
+    <mergeCell ref="U197:V197"/>
+    <mergeCell ref="B198:C198"/>
+    <mergeCell ref="E198:F198"/>
+    <mergeCell ref="P198:Q198"/>
+    <mergeCell ref="S198:T198"/>
+    <mergeCell ref="U198:V198"/>
+    <mergeCell ref="B199:C199"/>
+    <mergeCell ref="E199:F199"/>
+    <mergeCell ref="P199:Q199"/>
+    <mergeCell ref="S199:T199"/>
+    <mergeCell ref="U199:V199"/>
+    <mergeCell ref="B200:C200"/>
+    <mergeCell ref="E200:F200"/>
+    <mergeCell ref="P200:Q200"/>
+    <mergeCell ref="S200:T200"/>
+    <mergeCell ref="U200:V200"/>
+    <mergeCell ref="B201:C201"/>
+    <mergeCell ref="E201:F201"/>
+    <mergeCell ref="P201:Q201"/>
+    <mergeCell ref="S201:T201"/>
+    <mergeCell ref="U201:V201"/>
+    <mergeCell ref="B202:C202"/>
+    <mergeCell ref="E202:F202"/>
+    <mergeCell ref="P202:Q202"/>
+    <mergeCell ref="S202:T202"/>
+    <mergeCell ref="U202:V202"/>
+    <mergeCell ref="B203:C203"/>
+    <mergeCell ref="E203:F203"/>
+    <mergeCell ref="P203:Q203"/>
+    <mergeCell ref="S203:T203"/>
+    <mergeCell ref="U203:V203"/>
+    <mergeCell ref="B204:C204"/>
+    <mergeCell ref="E204:F204"/>
+    <mergeCell ref="P204:Q204"/>
+    <mergeCell ref="S204:T204"/>
+    <mergeCell ref="U204:V204"/>
+    <mergeCell ref="B205:C205"/>
+    <mergeCell ref="E205:F205"/>
+    <mergeCell ref="P205:Q205"/>
+    <mergeCell ref="S205:T205"/>
+    <mergeCell ref="U205:V205"/>
+    <mergeCell ref="B206:C206"/>
+    <mergeCell ref="E206:F206"/>
+    <mergeCell ref="P206:Q206"/>
+    <mergeCell ref="S206:T206"/>
+    <mergeCell ref="U206:V206"/>
+    <mergeCell ref="B207:C207"/>
+    <mergeCell ref="E207:F207"/>
+    <mergeCell ref="P207:Q207"/>
+    <mergeCell ref="S207:T207"/>
+    <mergeCell ref="U207:V207"/>
+    <mergeCell ref="B208:C208"/>
+    <mergeCell ref="E208:F208"/>
+    <mergeCell ref="P208:Q208"/>
+    <mergeCell ref="S208:T208"/>
+    <mergeCell ref="U208:V208"/>
+    <mergeCell ref="B209:C209"/>
+    <mergeCell ref="E209:F209"/>
+    <mergeCell ref="P209:Q209"/>
+    <mergeCell ref="S209:T209"/>
+    <mergeCell ref="U209:V209"/>
+    <mergeCell ref="B210:C210"/>
+    <mergeCell ref="E210:F210"/>
+    <mergeCell ref="P210:Q210"/>
+    <mergeCell ref="S210:T210"/>
+    <mergeCell ref="U210:V210"/>
+    <mergeCell ref="B211:C211"/>
+    <mergeCell ref="E211:F211"/>
+    <mergeCell ref="P211:Q211"/>
+    <mergeCell ref="S211:T211"/>
+    <mergeCell ref="U211:V211"/>
+    <mergeCell ref="B212:C212"/>
+    <mergeCell ref="E212:F212"/>
+    <mergeCell ref="P212:Q212"/>
+    <mergeCell ref="S212:T212"/>
+    <mergeCell ref="U212:V212"/>
+    <mergeCell ref="B213:C213"/>
+    <mergeCell ref="E213:F213"/>
+    <mergeCell ref="P213:Q213"/>
+    <mergeCell ref="S213:T213"/>
+    <mergeCell ref="U213:V213"/>
+    <mergeCell ref="B214:C214"/>
+    <mergeCell ref="E214:F214"/>
+    <mergeCell ref="P214:Q214"/>
+    <mergeCell ref="S214:T214"/>
+    <mergeCell ref="U214:V214"/>
+    <mergeCell ref="B215:C215"/>
+    <mergeCell ref="E215:F215"/>
+    <mergeCell ref="P215:Q215"/>
+    <mergeCell ref="S215:T215"/>
+    <mergeCell ref="U215:V215"/>
+    <mergeCell ref="B216:C216"/>
+    <mergeCell ref="E216:F216"/>
+    <mergeCell ref="P216:Q216"/>
+    <mergeCell ref="S216:T216"/>
+    <mergeCell ref="U216:V216"/>
+    <mergeCell ref="B217:C217"/>
+    <mergeCell ref="E217:F217"/>
+    <mergeCell ref="P217:Q217"/>
+    <mergeCell ref="S217:T217"/>
+    <mergeCell ref="U217:V217"/>
+    <mergeCell ref="B218:C218"/>
+    <mergeCell ref="E218:F218"/>
+    <mergeCell ref="P218:Q218"/>
+    <mergeCell ref="S218:T218"/>
+    <mergeCell ref="U218:V218"/>
+    <mergeCell ref="B219:C219"/>
+    <mergeCell ref="E219:F219"/>
+    <mergeCell ref="P219:Q219"/>
+    <mergeCell ref="S219:T219"/>
+    <mergeCell ref="U219:V219"/>
+    <mergeCell ref="B220:C220"/>
+    <mergeCell ref="E220:F220"/>
+    <mergeCell ref="P220:Q220"/>
+    <mergeCell ref="S220:T220"/>
+    <mergeCell ref="U220:V220"/>
+    <mergeCell ref="B221:C221"/>
+    <mergeCell ref="E221:F221"/>
+    <mergeCell ref="P221:Q221"/>
+    <mergeCell ref="S221:T221"/>
+    <mergeCell ref="U221:V221"/>
+    <mergeCell ref="B222:C222"/>
+    <mergeCell ref="E222:F222"/>
+    <mergeCell ref="P222:Q222"/>
+    <mergeCell ref="S222:T222"/>
+    <mergeCell ref="U222:V222"/>
+    <mergeCell ref="B223:C223"/>
+    <mergeCell ref="E223:F223"/>
+    <mergeCell ref="P223:Q223"/>
+    <mergeCell ref="S223:T223"/>
+    <mergeCell ref="U223:V223"/>
   </mergeCells>
   <pageMargins left="0.0393700787401575" right="0.0393700787401575" top="0.0393700787401575" bottom="0.0393700787401575" header="0.0393700787401575" footer="0.0393700787401575"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>

--- a/Base_Interrupcoes.xlsx
+++ b/Base_Interrupcoes.xlsx
@@ -466,7 +466,7 @@
       <c s="4" t="str" r="A7"/>
       <c s="7" t="inlineStr" r="T7">
         <is>
-          <t xml:space="preserve">Emissão: 07/10/2026</t>
+          <t xml:space="preserve">Emissão: 08/10/2026</t>
         </is>
       </c>
       <c s="5" t="str" r="V7"/>
@@ -475,7 +475,7 @@
       <c s="4" t="str" r="A8"/>
       <c s="8" t="inlineStr" r="F8">
         <is>
-          <t xml:space="preserve">Período: 01/10/2026 até 06/10/2026; Turno: Todos; Tempo: Calendário</t>
+          <t xml:space="preserve">Período: 01/10/2026 até 07/10/2026; Turno: Todos; Tempo: Calendário</t>
         </is>
       </c>
       <c s="5" t="str" r="V8"/>
@@ -10595,12 +10595,12 @@
     <row r="157" ht="15.55" customHeight="0">
       <c s="15" t="inlineStr" r="A157">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 05</t>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="B157">
         <is>
-          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+          <t xml:space="preserve">TR01-MESA TRANSPORTADORA</t>
         </is>
       </c>
       <c s="17" t="inlineStr" r="D157">
@@ -10612,11 +10612,11 @@
         <v>46301.2916666667</v>
       </c>
       <c s="18" r="G157">
-        <v>46301.3055555556</v>
+        <v>46301.3020833333</v>
       </c>
       <c s="17" t="inlineStr" r="H157">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c s="17" t="str" r="I157"/>
@@ -10643,18 +10643,18 @@
       </c>
       <c s="16" t="inlineStr" r="O157">
         <is>
-          <t xml:space="preserve">dds</t>
+          <t xml:space="preserve">dds  e assinatura dos documentos</t>
         </is>
       </c>
       <c s="16" t="str" r="P157"/>
       <c s="16" t="inlineStr" r="R157">
         <is>
-          <t xml:space="preserve">4ed80b10-c172-11f1-84a1-f2050a003223</t>
+          <t xml:space="preserve">fa2e6070-c16f-11f1-a1bf-f2050a003223</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="S157">
         <is>
-          <t xml:space="preserve">10046766    </t>
+          <t xml:space="preserve">10047271    </t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="U157">
@@ -10667,12 +10667,12 @@
     <row r="158" ht="15.6" customHeight="0">
       <c s="19" t="inlineStr" r="A158">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 01</t>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="B158">
         <is>
-          <t xml:space="preserve">TR01-MESA TRANSPORTADORA</t>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
         </is>
       </c>
       <c s="21" t="inlineStr" r="D158">
@@ -10684,11 +10684,11 @@
         <v>46301.2916666667</v>
       </c>
       <c s="22" r="G158">
-        <v>46301.3020833333</v>
+        <v>46301.3055555556</v>
       </c>
       <c s="21" t="inlineStr" r="H158">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c s="21" t="str" r="I158"/>
@@ -10715,18 +10715,18 @@
       </c>
       <c s="20" t="inlineStr" r="O158">
         <is>
-          <t xml:space="preserve">dds  e assinatura dos documentos</t>
+          <t xml:space="preserve">dds</t>
         </is>
       </c>
       <c s="20" t="str" r="P158"/>
       <c s="20" t="inlineStr" r="R158">
         <is>
-          <t xml:space="preserve">fa2e6070-c16f-11f1-a1bf-f2050a003223</t>
+          <t xml:space="preserve">4ed80b10-c172-11f1-84a1-f2050a003223</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="S158">
         <is>
-          <t xml:space="preserve">10047271    </t>
+          <t xml:space="preserve">10046766    </t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="U158">
@@ -14400,11 +14400,11 @@
         <v>46301.6493055556</v>
       </c>
       <c s="22" r="G210">
-        <v>46302.2952486921</v>
+        <v>46302.3736111111</v>
       </c>
       <c s="21" t="inlineStr" r="H210">
         <is>
-          <t xml:space="preserve">930</t>
+          <t xml:space="preserve">1.043</t>
         </is>
       </c>
       <c s="21" t="str" r="I210"/>
@@ -15108,11 +15108,11 @@
         <v>46301.6930555556</v>
       </c>
       <c s="22" r="G220">
-        <v>46302.2952486921</v>
+        <v>46301.7034722222</v>
       </c>
       <c s="21" t="inlineStr" r="H220">
         <is>
-          <t xml:space="preserve">867</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c s="21" t="str" r="I220"/>
@@ -15123,23 +15123,23 @@
       </c>
       <c s="20" t="inlineStr" r="K220">
         <is>
-          <t xml:space="preserve">Integração Automática</t>
+          <t xml:space="preserve">Operacional</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="L220">
         <is>
-          <t xml:space="preserve">Integração Automática</t>
+          <t xml:space="preserve">Operacional</t>
         </is>
       </c>
       <c s="20" t="str" r="M220"/>
       <c s="20" t="inlineStr" r="N220">
         <is>
-          <t xml:space="preserve">Parada Registrada via Integração</t>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="O220">
         <is>
-          <t xml:space="preserve">PARADA REGISTRADA VIA INTEGRAÇÃO AUTOMÁTICA.</t>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
         </is>
       </c>
       <c s="20" t="str" r="P220"/>
@@ -15176,11 +15176,11 @@
         <v>46301.6986111111</v>
       </c>
       <c s="18" r="G221">
-        <v>46302.2952486921</v>
+        <v>46301.7090277778</v>
       </c>
       <c s="17" t="inlineStr" r="H221">
         <is>
-          <t xml:space="preserve">859</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c s="17" t="str" r="I221"/>
@@ -15191,23 +15191,23 @@
       </c>
       <c s="16" t="inlineStr" r="K221">
         <is>
-          <t xml:space="preserve">Integração Automática</t>
+          <t xml:space="preserve">Operacional</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="L221">
         <is>
-          <t xml:space="preserve">Integração Automática</t>
+          <t xml:space="preserve">Operacional</t>
         </is>
       </c>
       <c s="16" t="str" r="M221"/>
       <c s="16" t="inlineStr" r="N221">
         <is>
-          <t xml:space="preserve">Parada Registrada via Integração</t>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="O221">
         <is>
-          <t xml:space="preserve">PARADA REGISTRADA VIA INTEGRAÇÃO AUTOMÁTICA.</t>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
         </is>
       </c>
       <c s="16" t="str" r="P221"/>
@@ -15296,75 +15296,3179 @@
       </c>
       <c s="5" t="str" r="V222"/>
     </row>
-    <row r="223" ht="15.55" customHeight="0">
-      <c s="23" t="inlineStr" r="A223">
+    <row r="223" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A223">
         <is>
           <t xml:space="preserve">TRANSVERSAL 03</t>
         </is>
       </c>
-      <c s="24" t="str" r="B223"/>
-      <c s="10" t="str" r="C223"/>
-      <c s="25" t="inlineStr" r="D223">
+      <c s="16" t="str" r="B223"/>
+      <c s="17" t="inlineStr" r="D223">
         <is>
           <t xml:space="preserve">TURNO B</t>
         </is>
       </c>
-      <c s="26" r="E223">
+      <c s="18" r="E223">
         <v>46301.7013888889</v>
       </c>
-      <c s="10" t="str" r="F223"/>
-      <c s="26" r="G223">
+      <c s="18" r="G223">
         <v>46302.2840277778</v>
       </c>
-      <c s="25" t="inlineStr" r="H223">
+      <c s="17" t="inlineStr" r="H223">
         <is>
           <t xml:space="preserve">839</t>
         </is>
       </c>
-      <c s="25" t="str" r="I223"/>
-      <c s="25" t="inlineStr" r="J223">
-        <is>
-          <t xml:space="preserve">X</t>
-        </is>
-      </c>
-      <c s="24" t="inlineStr" r="K223">
+      <c s="17" t="str" r="I223"/>
+      <c s="17" t="inlineStr" r="J223">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K223">
         <is>
           <t xml:space="preserve">Tempo Livre</t>
         </is>
       </c>
-      <c s="24" t="inlineStr" r="L223">
+      <c s="16" t="inlineStr" r="L223">
         <is>
           <t xml:space="preserve">Tempo Livre</t>
         </is>
       </c>
-      <c s="24" t="str" r="M223"/>
-      <c s="24" t="inlineStr" r="N223">
+      <c s="16" t="str" r="M223"/>
+      <c s="16" t="inlineStr" r="N223">
         <is>
           <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
         </is>
       </c>
-      <c s="24" t="inlineStr" r="O223">
+      <c s="16" t="inlineStr" r="O223">
         <is>
           <t xml:space="preserve">Parada registrada automaticamente pelo sistema</t>
         </is>
       </c>
-      <c s="24" t="str" r="P223"/>
-      <c s="10" t="str" r="Q223"/>
-      <c s="24" t="inlineStr" r="R223">
+      <c s="16" t="str" r="P223"/>
+      <c s="16" t="inlineStr" r="R223">
         <is>
           <t xml:space="preserve">1e703360-c1bf-11f1-c100-f2050a003223</t>
         </is>
       </c>
-      <c s="24" t="str" r="S223"/>
-      <c s="10" t="str" r="T223"/>
-      <c s="24" t="inlineStr" r="U223">
-        <is>
-          <t xml:space="preserve">Sim</t>
-        </is>
-      </c>
-      <c s="11" t="str" r="V223"/>
-    </row>
-    <row r="224" ht="0.05" customHeight="1"/>
+      <c s="16" t="str" r="S223"/>
+      <c s="16" t="inlineStr" r="U223">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V223"/>
+    </row>
+    <row r="224" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A224">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B224">
+        <is>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D224">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E224">
+        <v>46301.7041666667</v>
+      </c>
+      <c s="22" r="G224">
+        <v>46302.2909722222</v>
+      </c>
+      <c s="21" t="inlineStr" r="H224">
+        <is>
+          <t xml:space="preserve">845</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I224"/>
+      <c s="21" t="inlineStr" r="J224">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K224">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L224">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M224"/>
+      <c s="20" t="inlineStr" r="N224">
+        <is>
+          <t xml:space="preserve">FALTA DEMANDA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O224">
+        <is>
+          <t xml:space="preserve">falta de demanda</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P224"/>
+      <c s="20" t="inlineStr" r="R224">
+        <is>
+          <t xml:space="preserve">b4bac720-c239-11f1-c26a-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S224">
+        <is>
+          <t xml:space="preserve">10046774    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U224">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V224"/>
+    </row>
+    <row r="225" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A225">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B225">
+        <is>
+          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D225">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E225">
+        <v>46301.7097222222</v>
+      </c>
+      <c s="18" r="G225">
+        <v>46302.2909722222</v>
+      </c>
+      <c s="17" t="inlineStr" r="H225">
+        <is>
+          <t xml:space="preserve">837</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I225"/>
+      <c s="17" t="inlineStr" r="J225">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K225">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L225">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M225"/>
+      <c s="16" t="inlineStr" r="N225">
+        <is>
+          <t xml:space="preserve">FALTA DEMANDA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O225">
+        <is>
+          <t xml:space="preserve">Tempo livre</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P225"/>
+      <c s="16" t="inlineStr" r="R225">
+        <is>
+          <t xml:space="preserve">b57bf440-c239-11f1-c1f5-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S225">
+        <is>
+          <t xml:space="preserve">10048227    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U225">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V225"/>
+    </row>
+    <row r="226" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A226">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B226">
+        <is>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D226">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E226">
+        <v>46302.2916666667</v>
+      </c>
+      <c s="22" r="G226">
+        <v>46302.3055555556</v>
+      </c>
+      <c s="21" t="inlineStr" r="H226">
+        <is>
+          <t xml:space="preserve">20</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I226"/>
+      <c s="21" t="inlineStr" r="J226">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K226">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L226">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M226"/>
+      <c s="20" t="inlineStr" r="N226">
+        <is>
+          <t xml:space="preserve">DDS</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O226">
+        <is>
+          <t xml:space="preserve">dds</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P226"/>
+      <c s="20" t="inlineStr" r="R226">
+        <is>
+          <t xml:space="preserve">0bb05300-c23b-11f1-bbbb-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S226">
+        <is>
+          <t xml:space="preserve">10046774    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U226">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V226"/>
+    </row>
+    <row r="227" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A227">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B227">
+        <is>
+          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D227">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E227">
+        <v>46302.2916666667</v>
+      </c>
+      <c s="18" r="G227">
+        <v>46302.2986111111</v>
+      </c>
+      <c s="17" t="inlineStr" r="H227">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I227"/>
+      <c s="17" t="inlineStr" r="J227">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K227">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L227">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M227"/>
+      <c s="16" t="inlineStr" r="N227">
+        <is>
+          <t xml:space="preserve">DDS</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O227">
+        <is>
+          <t xml:space="preserve">DDS</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P227"/>
+      <c s="16" t="inlineStr" r="R227">
+        <is>
+          <t xml:space="preserve">c3a92550-c23a-11f1-b331-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S227">
+        <is>
+          <t xml:space="preserve">10048227    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U227">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V227"/>
+    </row>
+    <row r="228" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A228">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B228">
+        <is>
+          <t xml:space="preserve">TR01-MESA TRANSPORTADORA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D228">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E228">
+        <v>46302.2916666667</v>
+      </c>
+      <c s="22" r="G228">
+        <v>46302.3020833333</v>
+      </c>
+      <c s="21" t="inlineStr" r="H228">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I228"/>
+      <c s="21" t="inlineStr" r="J228">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K228">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L228">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M228"/>
+      <c s="20" t="inlineStr" r="N228">
+        <is>
+          <t xml:space="preserve">DDS</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O228">
+        <is>
+          <t xml:space="preserve">dds e assinatura dos documentos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P228"/>
+      <c s="20" t="inlineStr" r="R228">
+        <is>
+          <t xml:space="preserve">e92b60c0-c237-11f1-ab7f-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S228">
+        <is>
+          <t xml:space="preserve">10048039    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U228">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V228"/>
+    </row>
+    <row r="229" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A229">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B229">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D229">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E229">
+        <v>46302.3111111111</v>
+      </c>
+      <c s="18" r="G229">
+        <v>46302.3152777778</v>
+      </c>
+      <c s="17" t="inlineStr" r="H229">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I229"/>
+      <c s="17" t="inlineStr" r="J229">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K229">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L229">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M229"/>
+      <c s="16" t="inlineStr" r="N229">
+        <is>
+          <t xml:space="preserve">PESAGEM DE FARDO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O229">
+        <is>
+          <t xml:space="preserve">esperando op da ponte retira material</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P229"/>
+      <c s="16" t="inlineStr" r="R229">
+        <is>
+          <t xml:space="preserve">e18dff62-c239-11f1-a43a-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S229">
+        <is>
+          <t xml:space="preserve">10048039    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U229">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V229"/>
+    </row>
+    <row r="230" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A230">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B230">
+        <is>
+          <t xml:space="preserve">TR05-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D230">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E230">
+        <v>46302.3173611111</v>
+      </c>
+      <c s="22" r="G230">
+        <v>46302.3291666667</v>
+      </c>
+      <c s="21" t="inlineStr" r="H230">
+        <is>
+          <t xml:space="preserve">17</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I230"/>
+      <c s="21" t="inlineStr" r="J230">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K230">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L230">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M230"/>
+      <c s="20" t="inlineStr" r="N230">
+        <is>
+          <t xml:space="preserve">MESA CHEIA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O230">
+        <is>
+          <t xml:space="preserve">Aguardando retirada de material 6000x1200.</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P230"/>
+      <c s="20" t="inlineStr" r="R230">
+        <is>
+          <t xml:space="preserve">11c83af0-c23b-11f1-9fa5-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S230">
+        <is>
+          <t xml:space="preserve">10046774    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U230">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V230"/>
+    </row>
+    <row r="231" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A231">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B231"/>
+      <c s="17" t="inlineStr" r="D231">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E231">
+        <v>46302.3208333333</v>
+      </c>
+      <c s="18" r="G231">
+        <v>46302.3305555556</v>
+      </c>
+      <c s="17" t="inlineStr" r="H231">
+        <is>
+          <t xml:space="preserve">14</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I231"/>
+      <c s="17" t="inlineStr" r="J231">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K231">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L231">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M231"/>
+      <c s="16" t="inlineStr" r="N231">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O231">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 14 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P231"/>
+      <c s="16" t="inlineStr" r="R231">
+        <is>
+          <t xml:space="preserve">ce1ca9c0-c23b-11f1-874d-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S231">
+        <is>
+          <t xml:space="preserve">10048039    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U231">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V231"/>
+    </row>
+    <row r="232" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A232">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B232"/>
+      <c s="21" t="inlineStr" r="D232">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E232">
+        <v>46302.3340277778</v>
+      </c>
+      <c s="22" r="G232">
+        <v>46302.3430555556</v>
+      </c>
+      <c s="21" t="inlineStr" r="H232">
+        <is>
+          <t xml:space="preserve">13</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I232"/>
+      <c s="21" t="inlineStr" r="J232">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K232">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L232">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M232"/>
+      <c s="20" t="inlineStr" r="N232">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O232">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 13 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P232"/>
+      <c s="20" t="inlineStr" r="R232">
+        <is>
+          <t xml:space="preserve">78aed280-c23e-11f1-b42c-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S232">
+        <is>
+          <t xml:space="preserve">10048227    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U232">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V232"/>
+    </row>
+    <row r="233" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A233">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B233">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D233">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E233">
+        <v>46302.3361111111</v>
+      </c>
+      <c s="18" r="G233">
+        <v>46302.3388888889</v>
+      </c>
+      <c s="17" t="inlineStr" r="H233">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I233"/>
+      <c s="17" t="inlineStr" r="J233">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K233">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L233">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M233"/>
+      <c s="16" t="inlineStr" r="N233">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE CHAPA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O233">
+        <is>
+          <t xml:space="preserve">ajustando chapa</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P233"/>
+      <c s="16" t="inlineStr" r="R233">
+        <is>
+          <t xml:space="preserve">d549f1f0-c23e-11f1-a80d-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S233">
+        <is>
+          <t xml:space="preserve">10048039    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U233">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V233"/>
+    </row>
+    <row r="234" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A234">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B234"/>
+      <c s="21" t="inlineStr" r="D234">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E234">
+        <v>46302.3833333333</v>
+      </c>
+      <c s="22" r="G234">
+        <v>46302.3902777778</v>
+      </c>
+      <c s="21" t="inlineStr" r="H234">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I234"/>
+      <c s="21" t="inlineStr" r="J234">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K234">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L234">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M234"/>
+      <c s="20" t="inlineStr" r="N234">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O234">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 10 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P234"/>
+      <c s="20" t="inlineStr" r="R234">
+        <is>
+          <t xml:space="preserve">5c249050-c248-11f1-9ded-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S234">
+        <is>
+          <t xml:space="preserve">10048043    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U234">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V234"/>
+    </row>
+    <row r="235" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A235">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B235">
+        <is>
+          <t xml:space="preserve">TR05-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D235">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E235">
+        <v>46302.3875</v>
+      </c>
+      <c s="18" r="G235">
+        <v>46302.4166666667</v>
+      </c>
+      <c s="17" t="inlineStr" r="H235">
+        <is>
+          <t xml:space="preserve">42</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I235"/>
+      <c s="17" t="inlineStr" r="J235">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K235">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L235">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M235"/>
+      <c s="16" t="inlineStr" r="N235">
+        <is>
+          <t xml:space="preserve">TROCA DAS CASTANHAS DO MANDRIL</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O235">
+        <is>
+          <t xml:space="preserve">fazendo APR MANUAL e colocando as castanhas</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P235"/>
+      <c s="16" t="inlineStr" r="R235">
+        <is>
+          <t xml:space="preserve">45e0af30-c249-11f1-cc3b-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S235">
+        <is>
+          <t xml:space="preserve">10046775    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U235">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V235"/>
+    </row>
+    <row r="236" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A236">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B236">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D236">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E236">
+        <v>46302.3951388889</v>
+      </c>
+      <c s="22" r="G236">
+        <v>46302.3979166667</v>
+      </c>
+      <c s="21" t="inlineStr" r="H236">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I236"/>
+      <c s="21" t="inlineStr" r="J236">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K236">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L236">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M236"/>
+      <c s="20" t="inlineStr" r="N236">
+        <is>
+          <t xml:space="preserve">AJUSTE DA MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O236">
+        <is>
+          <t xml:space="preserve">ajuste da mesa para tamanho de chapa</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P236"/>
+      <c s="20" t="inlineStr" r="R236">
+        <is>
+          <t xml:space="preserve">c2a77981-c24a-11f1-aaf1-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S236">
+        <is>
+          <t xml:space="preserve">10048043    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U236">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V236"/>
+    </row>
+    <row r="237" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A237">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B237">
+        <is>
+          <t xml:space="preserve">TR02-GUILHOTINA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D237">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E237">
+        <v>46302.3979166667</v>
+      </c>
+      <c s="18" r="G237">
+        <v>46302.4159722222</v>
+      </c>
+      <c s="17" t="inlineStr" r="H237">
+        <is>
+          <t xml:space="preserve">26</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I237"/>
+      <c s="17" t="inlineStr" r="J237">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K237">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L237">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M237"/>
+      <c s="16" t="inlineStr" r="N237">
+        <is>
+          <t xml:space="preserve">SETUP COMPLETO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O237">
+        <is>
+          <t xml:space="preserve">Setup completo, regulagem da guilhotina e endireitadeira</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P237"/>
+      <c s="16" t="inlineStr" r="R237">
+        <is>
+          <t xml:space="preserve">3df295c0-c24b-11f1-a9fd-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S237">
+        <is>
+          <t xml:space="preserve">10048227    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U237">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V237"/>
+    </row>
+    <row r="238" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A238">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B238">
+        <is>
+          <t xml:space="preserve">TR05-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D238">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E238">
+        <v>46302.4409722222</v>
+      </c>
+      <c s="22" r="G238">
+        <v>46302.45</v>
+      </c>
+      <c s="21" t="inlineStr" r="H238">
+        <is>
+          <t xml:space="preserve">13</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I238"/>
+      <c s="21" t="inlineStr" r="J238">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K238">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L238">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M238"/>
+      <c s="20" t="inlineStr" r="N238">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O238">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 3 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P238"/>
+      <c s="20" t="inlineStr" r="R238">
+        <is>
+          <t xml:space="preserve">0cec6bc0-c257-11f1-854a-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S238">
+        <is>
+          <t xml:space="preserve">10046781    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U238">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V238"/>
+    </row>
+    <row r="239" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A239">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B239"/>
+      <c s="17" t="inlineStr" r="D239">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E239">
+        <v>46302.4423611111</v>
+      </c>
+      <c s="18" r="G239">
+        <v>46302.4527777778</v>
+      </c>
+      <c s="17" t="inlineStr" r="H239">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I239"/>
+      <c s="17" t="inlineStr" r="J239">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K239">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L239">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M239"/>
+      <c s="16" t="inlineStr" r="N239">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O239">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P239"/>
+      <c s="16" t="inlineStr" r="R239">
+        <is>
+          <t xml:space="preserve">3df5b3f0-c254-11f1-96af-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S239">
+        <is>
+          <t xml:space="preserve">10048044    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U239">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V239"/>
+    </row>
+    <row r="240" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A240">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B240"/>
+      <c s="21" t="inlineStr" r="D240">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E240">
+        <v>46302.4479166667</v>
+      </c>
+      <c s="22" r="G240">
+        <v>46302.4555555556</v>
+      </c>
+      <c s="21" t="inlineStr" r="H240">
+        <is>
+          <t xml:space="preserve">11</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I240"/>
+      <c s="21" t="inlineStr" r="J240">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K240">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L240">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M240"/>
+      <c s="20" t="inlineStr" r="N240">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O240">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 11 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P240"/>
+      <c s="20" t="inlineStr" r="R240">
+        <is>
+          <t xml:space="preserve">5b0c7db0-c255-11f1-bb61-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S240">
+        <is>
+          <t xml:space="preserve">10048465    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U240">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V240"/>
+    </row>
+    <row r="241" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A241">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B241">
+        <is>
+          <t xml:space="preserve">TR01-MESA TRANSPORTADORA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D241">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E241">
+        <v>46302.4534722222</v>
+      </c>
+      <c s="18" r="G241">
+        <v>46302.4583333333</v>
+      </c>
+      <c s="17" t="inlineStr" r="H241">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I241"/>
+      <c s="17" t="inlineStr" r="J241">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K241">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L241">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M241"/>
+      <c s="16" t="inlineStr" r="N241">
+        <is>
+          <t xml:space="preserve">PESAGEM DE FARDO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O241">
+        <is>
+          <t xml:space="preserve">pesagem de fardo</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P241"/>
+      <c s="16" t="inlineStr" r="R241">
+        <is>
+          <t xml:space="preserve">d66124f0-c257-11f1-8dc9-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S241">
+        <is>
+          <t xml:space="preserve">10048044    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U241">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V241"/>
+    </row>
+    <row r="242" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A242">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B242">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D242">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E242">
+        <v>46302.4916666667</v>
+      </c>
+      <c s="22" r="G242">
+        <v>46302.4944444444</v>
+      </c>
+      <c s="21" t="inlineStr" r="H242">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I242"/>
+      <c s="21" t="inlineStr" r="J242">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K242">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L242">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M242"/>
+      <c s="20" t="inlineStr" r="N242">
+        <is>
+          <t xml:space="preserve">AJUSTE DE MESA GUIA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O242">
+        <is>
+          <t xml:space="preserve">ajuste da mesa</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P242"/>
+      <c s="20" t="inlineStr" r="R242">
+        <is>
+          <t xml:space="preserve">23752470-c25e-11f1-b8f5-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S242">
+        <is>
+          <t xml:space="preserve">10048232    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U242">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V242"/>
+    </row>
+    <row r="243" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A243">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B243">
+        <is>
+          <t xml:space="preserve">TR05-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D243">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E243">
+        <v>46302.4923611111</v>
+      </c>
+      <c s="18" r="G243">
+        <v>46302.4993055556</v>
+      </c>
+      <c s="17" t="inlineStr" r="H243">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I243"/>
+      <c s="17" t="inlineStr" r="J243">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K243">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L243">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M243"/>
+      <c s="16" t="inlineStr" r="N243">
+        <is>
+          <t xml:space="preserve">TROCA DAS CASTANHAS DO MANDRIL</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O243">
+        <is>
+          <t xml:space="preserve">retirada de castanha</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P243"/>
+      <c s="16" t="inlineStr" r="R243">
+        <is>
+          <t xml:space="preserve">5cf41350-c25e-11f1-cae1-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S243">
+        <is>
+          <t xml:space="preserve">10046782    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U243">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V243"/>
+    </row>
+    <row r="244" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A244">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B244"/>
+      <c s="21" t="inlineStr" r="D244">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E244">
+        <v>46302.4965277778</v>
+      </c>
+      <c s="22" r="G244">
+        <v>46302.5034722222</v>
+      </c>
+      <c s="21" t="inlineStr" r="H244">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I244"/>
+      <c s="21" t="inlineStr" r="J244">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K244">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L244">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M244"/>
+      <c s="20" t="inlineStr" r="N244">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O244">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 10 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P244"/>
+      <c s="20" t="inlineStr" r="R244">
+        <is>
+          <t xml:space="preserve">12b46550-c25f-11f1-b3a6-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S244">
+        <is>
+          <t xml:space="preserve">10048232    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U244">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V244"/>
+    </row>
+    <row r="245" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A245">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B245">
+        <is>
+          <t xml:space="preserve">TR05-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D245">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E245">
+        <v>46302.5013888889</v>
+      </c>
+      <c s="18" r="G245">
+        <v>46302.5319444444</v>
+      </c>
+      <c s="17" t="inlineStr" r="H245">
+        <is>
+          <t xml:space="preserve">44</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I245"/>
+      <c s="17" t="inlineStr" r="J245">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K245">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L245">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M245"/>
+      <c s="16" t="inlineStr" r="N245">
+        <is>
+          <t xml:space="preserve">SETUP COMPLETO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O245">
+        <is>
+          <t xml:space="preserve">Retirada das castanhas e  endireitadeira.</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P245"/>
+      <c s="16" t="inlineStr" r="R245">
+        <is>
+          <t xml:space="preserve">bc6412c0-c260-11f1-c749-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S245">
+        <is>
+          <t xml:space="preserve">10046782    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U245">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V245"/>
+    </row>
+    <row r="246" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A246">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B246">
+        <is>
+          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D246">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E246">
+        <v>46302.5027777778</v>
+      </c>
+      <c s="22" r="G246">
+        <v>46302.5444444444</v>
+      </c>
+      <c s="21" t="inlineStr" r="H246">
+        <is>
+          <t xml:space="preserve">60</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I246"/>
+      <c s="21" t="inlineStr" r="J246">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K246">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L246">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M246"/>
+      <c s="20" t="inlineStr" r="N246">
+        <is>
+          <t xml:space="preserve">ALMOÇO / JANTA / CEIA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O246">
+        <is>
+          <t xml:space="preserve">Refeição.</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P246"/>
+      <c s="20" t="inlineStr" r="R246">
+        <is>
+          <t xml:space="preserve">5eee4ac0-c260-11f1-b455-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S246">
+        <is>
+          <t xml:space="preserve">10048465    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U246">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V246"/>
+    </row>
+    <row r="247" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A247">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B247">
+        <is>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D247">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E247">
+        <v>46302.5138888889</v>
+      </c>
+      <c s="18" r="G247">
+        <v>46302.5555555556</v>
+      </c>
+      <c s="17" t="inlineStr" r="H247">
+        <is>
+          <t xml:space="preserve">60</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I247"/>
+      <c s="17" t="inlineStr" r="J247">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K247">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L247">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M247"/>
+      <c s="16" t="inlineStr" r="N247">
+        <is>
+          <t xml:space="preserve">ALMOÇO / JANTA / CEIA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O247">
+        <is>
+          <t xml:space="preserve">almoço</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P247"/>
+      <c s="16" t="inlineStr" r="R247">
+        <is>
+          <t xml:space="preserve">565610d0-c271-11f1-a923-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S247">
+        <is>
+          <t xml:space="preserve">10048415    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U247">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V247"/>
+    </row>
+    <row r="248" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A248">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B248">
+        <is>
+          <t xml:space="preserve">TR01-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D248">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E248">
+        <v>46302.5326388889</v>
+      </c>
+      <c s="22" r="G248">
+        <v>46302.5354166667</v>
+      </c>
+      <c s="21" t="inlineStr" r="H248">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I248"/>
+      <c s="21" t="inlineStr" r="J248">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K248">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L248">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M248"/>
+      <c s="20" t="inlineStr" r="N248">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O248">
+        <is>
+          <t xml:space="preserve">abastecendo</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P248"/>
+      <c s="20" t="inlineStr" r="R248">
+        <is>
+          <t xml:space="preserve">5986b850-c266-11f1-b303-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S248">
+        <is>
+          <t xml:space="preserve">10048232    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U248">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V248"/>
+    </row>
+    <row r="249" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A249">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B249"/>
+      <c s="17" t="inlineStr" r="D249">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E249">
+        <v>46302.5368055556</v>
+      </c>
+      <c s="18" r="G249">
+        <v>46302.5430555556</v>
+      </c>
+      <c s="17" t="inlineStr" r="H249">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I249"/>
+      <c s="17" t="inlineStr" r="J249">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K249">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L249">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M249"/>
+      <c s="16" t="inlineStr" r="N249">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O249">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 9 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P249"/>
+      <c s="16" t="inlineStr" r="R249">
+        <is>
+          <t xml:space="preserve">3681eae0-c267-11f1-8404-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S249">
+        <is>
+          <t xml:space="preserve">10048232    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U249">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V249"/>
+    </row>
+    <row r="250" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A250">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B250"/>
+      <c s="21" t="inlineStr" r="D250">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E250">
+        <v>46302.54375</v>
+      </c>
+      <c s="22" r="G250">
+        <v>46302.5458333333</v>
+      </c>
+      <c s="21" t="inlineStr" r="H250">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I250"/>
+      <c s="21" t="inlineStr" r="J250">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K250">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L250">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M250"/>
+      <c s="20" t="inlineStr" r="N250">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O250">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 3 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P250"/>
+      <c s="20" t="inlineStr" r="R250">
+        <is>
+          <t xml:space="preserve">9e47f7e0-c268-11f1-9499-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S250">
+        <is>
+          <t xml:space="preserve">10046782    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U250">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V250"/>
+    </row>
+    <row r="251" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A251">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B251">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D251">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E251">
+        <v>46302.5444444444</v>
+      </c>
+      <c s="18" r="G251">
+        <v>46302.5472222222</v>
+      </c>
+      <c s="17" t="inlineStr" r="H251">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I251"/>
+      <c s="17" t="inlineStr" r="J251">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K251">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L251">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M251"/>
+      <c s="16" t="inlineStr" r="N251">
+        <is>
+          <t xml:space="preserve">AJUSTE DA MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O251">
+        <is>
+          <t xml:space="preserve">ajuste da mesa para tamanho de chapa</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P251"/>
+      <c s="16" t="inlineStr" r="R251">
+        <is>
+          <t xml:space="preserve">cc168010-c268-11f1-9dbf-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S251">
+        <is>
+          <t xml:space="preserve">10048232    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U251">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V251"/>
+    </row>
+    <row r="252" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A252">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B252">
+        <is>
+          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D252">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E252">
+        <v>46302.5486111111</v>
+      </c>
+      <c s="22" r="G252">
+        <v>46302.5590277778</v>
+      </c>
+      <c s="21" t="inlineStr" r="H252">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I252"/>
+      <c s="21" t="inlineStr" r="J252">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K252">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L252">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M252"/>
+      <c s="20" t="inlineStr" r="N252">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O252">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P252"/>
+      <c s="20" t="inlineStr" r="R252">
+        <is>
+          <t xml:space="preserve">380a4650-c26c-11f1-aa46-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S252">
+        <is>
+          <t xml:space="preserve">10048465    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U252">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V252"/>
+    </row>
+    <row r="253" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A253">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B253"/>
+      <c s="17" t="inlineStr" r="D253">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E253">
+        <v>46302.5534722222</v>
+      </c>
+      <c s="18" r="G253">
+        <v>46302.5555555556</v>
+      </c>
+      <c s="17" t="inlineStr" r="H253">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I253"/>
+      <c s="17" t="inlineStr" r="J253">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K253">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L253">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M253"/>
+      <c s="16" t="inlineStr" r="N253">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O253">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 3 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P253"/>
+      <c s="16" t="inlineStr" r="R253">
+        <is>
+          <t xml:space="preserve">921fde40-c26a-11f1-c0f9-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S253">
+        <is>
+          <t xml:space="preserve">10046883    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U253">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V253"/>
+    </row>
+    <row r="254" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A254">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B254">
+        <is>
+          <t xml:space="preserve">TR05-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D254">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E254">
+        <v>46302.5625</v>
+      </c>
+      <c s="22" r="G254">
+        <v>46302.5708333333</v>
+      </c>
+      <c s="21" t="inlineStr" r="H254">
+        <is>
+          <t xml:space="preserve">12</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I254"/>
+      <c s="21" t="inlineStr" r="J254">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K254">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L254">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M254"/>
+      <c s="20" t="inlineStr" r="N254">
+        <is>
+          <t xml:space="preserve">MESA CHEIA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O254">
+        <is>
+          <t xml:space="preserve">aguardando a retirada do material de 5000x1200</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P254"/>
+      <c s="20" t="inlineStr" r="R254">
+        <is>
+          <t xml:space="preserve">620a1340-c26c-11f1-c470-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S254">
+        <is>
+          <t xml:space="preserve">10046883    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U254">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V254"/>
+    </row>
+    <row r="255" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A255">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B255">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D255">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E255">
+        <v>46302.5881944444</v>
+      </c>
+      <c s="18" r="G255">
+        <v>46302.5909722222</v>
+      </c>
+      <c s="17" t="inlineStr" r="H255">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I255"/>
+      <c s="17" t="inlineStr" r="J255">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K255">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L255">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M255"/>
+      <c s="16" t="inlineStr" r="N255">
+        <is>
+          <t xml:space="preserve">AJUSTE DA MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O255">
+        <is>
+          <t xml:space="preserve">ajustando chapa enganchada</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P255"/>
+      <c s="16" t="inlineStr" r="R255">
+        <is>
+          <t xml:space="preserve">87ea2c80-c271-11f1-aa20-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S255">
+        <is>
+          <t xml:space="preserve">10048233    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U255">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V255"/>
+    </row>
+    <row r="256" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A256">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B256"/>
+      <c s="21" t="inlineStr" r="D256">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E256">
+        <v>46302.5895833333</v>
+      </c>
+      <c s="22" r="G256">
+        <v>46302.5979166667</v>
+      </c>
+      <c s="21" t="inlineStr" r="H256">
+        <is>
+          <t xml:space="preserve">12</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I256"/>
+      <c s="21" t="inlineStr" r="J256">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K256">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L256">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M256"/>
+      <c s="20" t="inlineStr" r="N256">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O256">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 12 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P256"/>
+      <c s="20" t="inlineStr" r="R256">
+        <is>
+          <t xml:space="preserve">e9d3c960-c271-11f1-b9bf-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S256">
+        <is>
+          <t xml:space="preserve">10048465    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U256">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V256"/>
+    </row>
+    <row r="257" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A257">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B257">
+        <is>
+          <t xml:space="preserve">TR05-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D257">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E257">
+        <v>46302.6222222222</v>
+      </c>
+      <c s="18" r="G257">
+        <v>46302.6326388889</v>
+      </c>
+      <c s="17" t="inlineStr" r="H257">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I257"/>
+      <c s="17" t="inlineStr" r="J257">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K257">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L257">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M257"/>
+      <c s="16" t="inlineStr" r="N257">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O257">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P257"/>
+      <c s="16" t="inlineStr" r="R257">
+        <is>
+          <t xml:space="preserve">6c5fae70-c278-11f1-8ef5-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S257">
+        <is>
+          <t xml:space="preserve">10046886    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U257">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V257"/>
+    </row>
+    <row r="258" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A258">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B258"/>
+      <c s="21" t="inlineStr" r="D258">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E258">
+        <v>46302.6305555556</v>
+      </c>
+      <c s="22" r="G258">
+        <v>46302.6409722222</v>
+      </c>
+      <c s="21" t="inlineStr" r="H258">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I258"/>
+      <c s="21" t="inlineStr" r="J258">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K258">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L258">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M258"/>
+      <c s="20" t="inlineStr" r="N258">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O258">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P258"/>
+      <c s="20" t="inlineStr" r="R258">
+        <is>
+          <t xml:space="preserve">121af030-c27a-11f1-805d-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S258">
+        <is>
+          <t xml:space="preserve">10048465    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U258">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V258"/>
+    </row>
+    <row r="259" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A259">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B259">
+        <is>
+          <t xml:space="preserve">TR05-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D259">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E259">
+        <v>46302.6333333333</v>
+      </c>
+      <c s="18" r="G259">
+        <v>46302.6388888889</v>
+      </c>
+      <c s="17" t="inlineStr" r="H259">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I259"/>
+      <c s="17" t="inlineStr" r="J259">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K259">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L259">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M259"/>
+      <c s="16" t="inlineStr" r="N259">
+        <is>
+          <t xml:space="preserve">RETIRADA DE PNC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O259">
+        <is>
+          <t xml:space="preserve">retirada de pnc</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P259"/>
+      <c s="16" t="inlineStr" r="R259">
+        <is>
+          <t xml:space="preserve">ba1bdc30-c27b-11f1-8271-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S259">
+        <is>
+          <t xml:space="preserve">10046886    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U259">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V259"/>
+    </row>
+    <row r="260" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A260">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B260">
+        <is>
+          <t xml:space="preserve">TR05-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D260">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E260">
+        <v>46302.6493055556</v>
+      </c>
+      <c s="22" r="G260">
+        <v>46302.6513888889</v>
+      </c>
+      <c s="21" t="inlineStr" r="H260">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I260"/>
+      <c s="21" t="inlineStr" r="J260">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K260">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L260">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M260"/>
+      <c s="20" t="inlineStr" r="N260">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE FARDO</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O260">
+        <is>
+          <t xml:space="preserve">passagem de fardo</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P260"/>
+      <c s="20" t="inlineStr" r="R260">
+        <is>
+          <t xml:space="preserve">efb6c830-c27d-11f1-afe9-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S260">
+        <is>
+          <t xml:space="preserve">10047301    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U260">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V260"/>
+    </row>
+    <row r="261" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A261">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B261">
+        <is>
+          <t xml:space="preserve">TR02-MESA FIXA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D261">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E261">
+        <v>46302.6506944444</v>
+      </c>
+      <c s="18" r="G261">
+        <v>46302.6590277778</v>
+      </c>
+      <c s="17" t="inlineStr" r="H261">
+        <is>
+          <t xml:space="preserve">12</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I261"/>
+      <c s="17" t="inlineStr" r="J261">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K261">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L261">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M261"/>
+      <c s="16" t="inlineStr" r="N261">
+        <is>
+          <t xml:space="preserve">MESA CHEIA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O261">
+        <is>
+          <t xml:space="preserve">Mesa cheia.</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P261"/>
+      <c s="16" t="inlineStr" r="R261">
+        <is>
+          <t xml:space="preserve">280a2f60-c27e-11f1-8dce-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S261">
+        <is>
+          <t xml:space="preserve">10048465    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U261">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V261"/>
+    </row>
+    <row r="262" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A262">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B262">
+        <is>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D262">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E262">
+        <v>46302.6597222222</v>
+      </c>
+      <c s="22" r="G262">
+        <v>46303.2927896181</v>
+      </c>
+      <c s="21" t="inlineStr" r="H262">
+        <is>
+          <t xml:space="preserve">912</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I262"/>
+      <c s="21" t="inlineStr" r="J262">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K262">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L262">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M262"/>
+      <c s="20" t="inlineStr" r="N262">
+        <is>
+          <t xml:space="preserve">FALTA DEMANDA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O262">
+        <is>
+          <t xml:space="preserve">falta de demanda</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P262"/>
+      <c s="20" t="inlineStr" r="R262">
+        <is>
+          <t xml:space="preserve">33481340-c280-11f1-8f07-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="S262"/>
+      <c s="20" t="inlineStr" r="U262">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V262"/>
+    </row>
+    <row r="263" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A263">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B263"/>
+      <c s="17" t="inlineStr" r="D263">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E263">
+        <v>46302.6694444444</v>
+      </c>
+      <c s="18" r="G263">
+        <v>46302.6729166667</v>
+      </c>
+      <c s="17" t="inlineStr" r="H263">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I263"/>
+      <c s="17" t="inlineStr" r="J263">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K263">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L263">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M263"/>
+      <c s="16" t="inlineStr" r="N263">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O263">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 5 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P263"/>
+      <c s="16" t="inlineStr" r="R263">
+        <is>
+          <t xml:space="preserve">f63febb0-c281-11f1-af7c-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S263">
+        <is>
+          <t xml:space="preserve">10048465    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U263">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V263"/>
+    </row>
+    <row r="264" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A264">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B264"/>
+      <c s="21" t="inlineStr" r="D264">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E264">
+        <v>46302.6854166667</v>
+      </c>
+      <c s="22" r="G264">
+        <v>46303.2927896181</v>
+      </c>
+      <c s="21" t="inlineStr" r="H264">
+        <is>
+          <t xml:space="preserve">875</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I264"/>
+      <c s="21" t="inlineStr" r="J264">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K264">
+        <is>
+          <t xml:space="preserve">Integração Automática</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L264">
+        <is>
+          <t xml:space="preserve">Integração Automática</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M264"/>
+      <c s="20" t="inlineStr" r="N264">
+        <is>
+          <t xml:space="preserve">Parada Registrada via Integração</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O264">
+        <is>
+          <t xml:space="preserve">PARADA REGISTRADA VIA INTEGRAÇÃO AUTOMÁTICA.</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P264"/>
+      <c s="20" t="inlineStr" r="R264">
+        <is>
+          <t xml:space="preserve">275de5a0-c285-11f1-a307-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S264">
+        <is>
+          <t xml:space="preserve">10048465    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U264">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V264"/>
+    </row>
+    <row r="265" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A265">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B265">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D265">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E265">
+        <v>46302.6944444444</v>
+      </c>
+      <c s="18" r="G265">
+        <v>46303.2927896181</v>
+      </c>
+      <c s="17" t="inlineStr" r="H265">
+        <is>
+          <t xml:space="preserve">862</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I265"/>
+      <c s="17" t="inlineStr" r="J265">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K265">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L265">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M265"/>
+      <c s="16" t="inlineStr" r="N265">
+        <is>
+          <t xml:space="preserve">FALTA DEMANDA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O265">
+        <is>
+          <t xml:space="preserve">tempo livre</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P265"/>
+      <c s="16" t="inlineStr" r="R265">
+        <is>
+          <t xml:space="preserve">be49cd70-c286-11f1-b4a4-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S265">
+        <is>
+          <t xml:space="preserve">10048233    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U265">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V265"/>
+    </row>
+    <row r="266" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A266">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B266">
+        <is>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D266">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E266">
+        <v>46302.6993055556</v>
+      </c>
+      <c s="22" r="G266">
+        <v>46303.2927896181</v>
+      </c>
+      <c s="21" t="inlineStr" r="H266">
+        <is>
+          <t xml:space="preserve">855</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I266"/>
+      <c s="21" t="inlineStr" r="J266">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K266">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L266">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M266"/>
+      <c s="20" t="inlineStr" r="N266">
+        <is>
+          <t xml:space="preserve">FALTA DEMANDA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O266">
+        <is>
+          <t xml:space="preserve">FALTA DE DEMANDA</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P266"/>
+      <c s="20" t="inlineStr" r="R266">
+        <is>
+          <t xml:space="preserve">e66a84b0-c287-11f1-b888-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S266">
+        <is>
+          <t xml:space="preserve">10047305    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U266">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V266"/>
+    </row>
+    <row r="267" ht="15.55" customHeight="0">
+      <c s="23" t="inlineStr" r="A267">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 03</t>
+        </is>
+      </c>
+      <c s="24" t="str" r="B267"/>
+      <c s="10" t="str" r="C267"/>
+      <c s="25" t="inlineStr" r="D267">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="26" r="E267">
+        <v>46302.7013888889</v>
+      </c>
+      <c s="10" t="str" r="F267"/>
+      <c s="26" r="G267">
+        <v>46303.2840277778</v>
+      </c>
+      <c s="25" t="inlineStr" r="H267">
+        <is>
+          <t xml:space="preserve">839</t>
+        </is>
+      </c>
+      <c s="25" t="str" r="I267"/>
+      <c s="25" t="inlineStr" r="J267">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="K267">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="L267">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="24" t="str" r="M267"/>
+      <c s="24" t="inlineStr" r="N267">
+        <is>
+          <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="O267">
+        <is>
+          <t xml:space="preserve">Parada registrada automaticamente pelo sistema</t>
+        </is>
+      </c>
+      <c s="24" t="str" r="P267"/>
+      <c s="10" t="str" r="Q267"/>
+      <c s="24" t="inlineStr" r="R267">
+        <is>
+          <t xml:space="preserve">48564470-c288-11f1-94a6-f2050a003223</t>
+        </is>
+      </c>
+      <c s="24" t="str" r="S267"/>
+      <c s="10" t="str" r="T267"/>
+      <c s="24" t="inlineStr" r="U267">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="11" t="str" r="V267"/>
+    </row>
+    <row r="268" ht="0.05" customHeight="1"/>
   </sheetData>
   <mergeCells>
     <mergeCell ref="A3:B8"/>
@@ -16413,6 +19517,226 @@
     <mergeCell ref="P223:Q223"/>
     <mergeCell ref="S223:T223"/>
     <mergeCell ref="U223:V223"/>
+    <mergeCell ref="B224:C224"/>
+    <mergeCell ref="E224:F224"/>
+    <mergeCell ref="P224:Q224"/>
+    <mergeCell ref="S224:T224"/>
+    <mergeCell ref="U224:V224"/>
+    <mergeCell ref="B225:C225"/>
+    <mergeCell ref="E225:F225"/>
+    <mergeCell ref="P225:Q225"/>
+    <mergeCell ref="S225:T225"/>
+    <mergeCell ref="U225:V225"/>
+    <mergeCell ref="B226:C226"/>
+    <mergeCell ref="E226:F226"/>
+    <mergeCell ref="P226:Q226"/>
+    <mergeCell ref="S226:T226"/>
+    <mergeCell ref="U226:V226"/>
+    <mergeCell ref="B227:C227"/>
+    <mergeCell ref="E227:F227"/>
+    <mergeCell ref="P227:Q227"/>
+    <mergeCell ref="S227:T227"/>
+    <mergeCell ref="U227:V227"/>
+    <mergeCell ref="B228:C228"/>
+    <mergeCell ref="E228:F228"/>
+    <mergeCell ref="P228:Q228"/>
+    <mergeCell ref="S228:T228"/>
+    <mergeCell ref="U228:V228"/>
+    <mergeCell ref="B229:C229"/>
+    <mergeCell ref="E229:F229"/>
+    <mergeCell ref="P229:Q229"/>
+    <mergeCell ref="S229:T229"/>
+    <mergeCell ref="U229:V229"/>
+    <mergeCell ref="B230:C230"/>
+    <mergeCell ref="E230:F230"/>
+    <mergeCell ref="P230:Q230"/>
+    <mergeCell ref="S230:T230"/>
+    <mergeCell ref="U230:V230"/>
+    <mergeCell ref="B231:C231"/>
+    <mergeCell ref="E231:F231"/>
+    <mergeCell ref="P231:Q231"/>
+    <mergeCell ref="S231:T231"/>
+    <mergeCell ref="U231:V231"/>
+    <mergeCell ref="B232:C232"/>
+    <mergeCell ref="E232:F232"/>
+    <mergeCell ref="P232:Q232"/>
+    <mergeCell ref="S232:T232"/>
+    <mergeCell ref="U232:V232"/>
+    <mergeCell ref="B233:C233"/>
+    <mergeCell ref="E233:F233"/>
+    <mergeCell ref="P233:Q233"/>
+    <mergeCell ref="S233:T233"/>
+    <mergeCell ref="U233:V233"/>
+    <mergeCell ref="B234:C234"/>
+    <mergeCell ref="E234:F234"/>
+    <mergeCell ref="P234:Q234"/>
+    <mergeCell ref="S234:T234"/>
+    <mergeCell ref="U234:V234"/>
+    <mergeCell ref="B235:C235"/>
+    <mergeCell ref="E235:F235"/>
+    <mergeCell ref="P235:Q235"/>
+    <mergeCell ref="S235:T235"/>
+    <mergeCell ref="U235:V235"/>
+    <mergeCell ref="B236:C236"/>
+    <mergeCell ref="E236:F236"/>
+    <mergeCell ref="P236:Q236"/>
+    <mergeCell ref="S236:T236"/>
+    <mergeCell ref="U236:V236"/>
+    <mergeCell ref="B237:C237"/>
+    <mergeCell ref="E237:F237"/>
+    <mergeCell ref="P237:Q237"/>
+    <mergeCell ref="S237:T237"/>
+    <mergeCell ref="U237:V237"/>
+    <mergeCell ref="B238:C238"/>
+    <mergeCell ref="E238:F238"/>
+    <mergeCell ref="P238:Q238"/>
+    <mergeCell ref="S238:T238"/>
+    <mergeCell ref="U238:V238"/>
+    <mergeCell ref="B239:C239"/>
+    <mergeCell ref="E239:F239"/>
+    <mergeCell ref="P239:Q239"/>
+    <mergeCell ref="S239:T239"/>
+    <mergeCell ref="U239:V239"/>
+    <mergeCell ref="B240:C240"/>
+    <mergeCell ref="E240:F240"/>
+    <mergeCell ref="P240:Q240"/>
+    <mergeCell ref="S240:T240"/>
+    <mergeCell ref="U240:V240"/>
+    <mergeCell ref="B241:C241"/>
+    <mergeCell ref="E241:F241"/>
+    <mergeCell ref="P241:Q241"/>
+    <mergeCell ref="S241:T241"/>
+    <mergeCell ref="U241:V241"/>
+    <mergeCell ref="B242:C242"/>
+    <mergeCell ref="E242:F242"/>
+    <mergeCell ref="P242:Q242"/>
+    <mergeCell ref="S242:T242"/>
+    <mergeCell ref="U242:V242"/>
+    <mergeCell ref="B243:C243"/>
+    <mergeCell ref="E243:F243"/>
+    <mergeCell ref="P243:Q243"/>
+    <mergeCell ref="S243:T243"/>
+    <mergeCell ref="U243:V243"/>
+    <mergeCell ref="B244:C244"/>
+    <mergeCell ref="E244:F244"/>
+    <mergeCell ref="P244:Q244"/>
+    <mergeCell ref="S244:T244"/>
+    <mergeCell ref="U244:V244"/>
+    <mergeCell ref="B245:C245"/>
+    <mergeCell ref="E245:F245"/>
+    <mergeCell ref="P245:Q245"/>
+    <mergeCell ref="S245:T245"/>
+    <mergeCell ref="U245:V245"/>
+    <mergeCell ref="B246:C246"/>
+    <mergeCell ref="E246:F246"/>
+    <mergeCell ref="P246:Q246"/>
+    <mergeCell ref="S246:T246"/>
+    <mergeCell ref="U246:V246"/>
+    <mergeCell ref="B247:C247"/>
+    <mergeCell ref="E247:F247"/>
+    <mergeCell ref="P247:Q247"/>
+    <mergeCell ref="S247:T247"/>
+    <mergeCell ref="U247:V247"/>
+    <mergeCell ref="B248:C248"/>
+    <mergeCell ref="E248:F248"/>
+    <mergeCell ref="P248:Q248"/>
+    <mergeCell ref="S248:T248"/>
+    <mergeCell ref="U248:V248"/>
+    <mergeCell ref="B249:C249"/>
+    <mergeCell ref="E249:F249"/>
+    <mergeCell ref="P249:Q249"/>
+    <mergeCell ref="S249:T249"/>
+    <mergeCell ref="U249:V249"/>
+    <mergeCell ref="B250:C250"/>
+    <mergeCell ref="E250:F250"/>
+    <mergeCell ref="P250:Q250"/>
+    <mergeCell ref="S250:T250"/>
+    <mergeCell ref="U250:V250"/>
+    <mergeCell ref="B251:C251"/>
+    <mergeCell ref="E251:F251"/>
+    <mergeCell ref="P251:Q251"/>
+    <mergeCell ref="S251:T251"/>
+    <mergeCell ref="U251:V251"/>
+    <mergeCell ref="B252:C252"/>
+    <mergeCell ref="E252:F252"/>
+    <mergeCell ref="P252:Q252"/>
+    <mergeCell ref="S252:T252"/>
+    <mergeCell ref="U252:V252"/>
+    <mergeCell ref="B253:C253"/>
+    <mergeCell ref="E253:F253"/>
+    <mergeCell ref="P253:Q253"/>
+    <mergeCell ref="S253:T253"/>
+    <mergeCell ref="U253:V253"/>
+    <mergeCell ref="B254:C254"/>
+    <mergeCell ref="E254:F254"/>
+    <mergeCell ref="P254:Q254"/>
+    <mergeCell ref="S254:T254"/>
+    <mergeCell ref="U254:V254"/>
+    <mergeCell ref="B255:C255"/>
+    <mergeCell ref="E255:F255"/>
+    <mergeCell ref="P255:Q255"/>
+    <mergeCell ref="S255:T255"/>
+    <mergeCell ref="U255:V255"/>
+    <mergeCell ref="B256:C256"/>
+    <mergeCell ref="E256:F256"/>
+    <mergeCell ref="P256:Q256"/>
+    <mergeCell ref="S256:T256"/>
+    <mergeCell ref="U256:V256"/>
+    <mergeCell ref="B257:C257"/>
+    <mergeCell ref="E257:F257"/>
+    <mergeCell ref="P257:Q257"/>
+    <mergeCell ref="S257:T257"/>
+    <mergeCell ref="U257:V257"/>
+    <mergeCell ref="B258:C258"/>
+    <mergeCell ref="E258:F258"/>
+    <mergeCell ref="P258:Q258"/>
+    <mergeCell ref="S258:T258"/>
+    <mergeCell ref="U258:V258"/>
+    <mergeCell ref="B259:C259"/>
+    <mergeCell ref="E259:F259"/>
+    <mergeCell ref="P259:Q259"/>
+    <mergeCell ref="S259:T259"/>
+    <mergeCell ref="U259:V259"/>
+    <mergeCell ref="B260:C260"/>
+    <mergeCell ref="E260:F260"/>
+    <mergeCell ref="P260:Q260"/>
+    <mergeCell ref="S260:T260"/>
+    <mergeCell ref="U260:V260"/>
+    <mergeCell ref="B261:C261"/>
+    <mergeCell ref="E261:F261"/>
+    <mergeCell ref="P261:Q261"/>
+    <mergeCell ref="S261:T261"/>
+    <mergeCell ref="U261:V261"/>
+    <mergeCell ref="B262:C262"/>
+    <mergeCell ref="E262:F262"/>
+    <mergeCell ref="P262:Q262"/>
+    <mergeCell ref="S262:T262"/>
+    <mergeCell ref="U262:V262"/>
+    <mergeCell ref="B263:C263"/>
+    <mergeCell ref="E263:F263"/>
+    <mergeCell ref="P263:Q263"/>
+    <mergeCell ref="S263:T263"/>
+    <mergeCell ref="U263:V263"/>
+    <mergeCell ref="B264:C264"/>
+    <mergeCell ref="E264:F264"/>
+    <mergeCell ref="P264:Q264"/>
+    <mergeCell ref="S264:T264"/>
+    <mergeCell ref="U264:V264"/>
+    <mergeCell ref="B265:C265"/>
+    <mergeCell ref="E265:F265"/>
+    <mergeCell ref="P265:Q265"/>
+    <mergeCell ref="S265:T265"/>
+    <mergeCell ref="U265:V265"/>
+    <mergeCell ref="B266:C266"/>
+    <mergeCell ref="E266:F266"/>
+    <mergeCell ref="P266:Q266"/>
+    <mergeCell ref="S266:T266"/>
+    <mergeCell ref="U266:V266"/>
+    <mergeCell ref="B267:C267"/>
+    <mergeCell ref="E267:F267"/>
+    <mergeCell ref="P267:Q267"/>
+    <mergeCell ref="S267:T267"/>
+    <mergeCell ref="U267:V267"/>
   </mergeCells>
   <pageMargins left="0.0393700787401575" right="0.0393700787401575" top="0.0393700787401575" bottom="0.0393700787401575" header="0.0393700787401575" footer="0.0393700787401575"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>

--- a/Base_Interrupcoes.xlsx
+++ b/Base_Interrupcoes.xlsx
@@ -466,7 +466,7 @@
       <c s="4" t="str" r="A7"/>
       <c s="7" t="inlineStr" r="T7">
         <is>
-          <t xml:space="preserve">Emissão: 08/10/2026</t>
+          <t xml:space="preserve">Emissão: 09/10/2026</t>
         </is>
       </c>
       <c s="5" t="str" r="V7"/>
@@ -475,7 +475,7 @@
       <c s="4" t="str" r="A8"/>
       <c s="8" t="inlineStr" r="F8">
         <is>
-          <t xml:space="preserve">Período: 01/10/2026 até 07/10/2026; Turno: Todos; Tempo: Calendário</t>
+          <t xml:space="preserve">Período: 01/10/2026 até 08/10/2026; Turno: Todos; Tempo: Calendário</t>
         </is>
       </c>
       <c s="5" t="str" r="V8"/>
@@ -3110,12 +3110,12 @@
     <row r="52" ht="15.6" customHeight="0">
       <c s="19" t="inlineStr" r="A52">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 05</t>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="B52">
         <is>
-          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
         </is>
       </c>
       <c s="21" t="inlineStr" r="D52">
@@ -3127,11 +3127,11 @@
         <v>46297.2916666667</v>
       </c>
       <c s="22" r="G52">
-        <v>46297.3055555556</v>
+        <v>46297.2986111111</v>
       </c>
       <c s="21" t="inlineStr" r="H52">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c s="21" t="str" r="I52"/>
@@ -3158,18 +3158,18 @@
       </c>
       <c s="20" t="inlineStr" r="O52">
         <is>
-          <t xml:space="preserve">dds com supervisor QUEDA DE MATERIAIS</t>
+          <t xml:space="preserve">DDS</t>
         </is>
       </c>
       <c s="20" t="str" r="P52"/>
       <c s="20" t="inlineStr" r="R52">
         <is>
-          <t xml:space="preserve">167ccc00-be4e-11f1-cdcf-f2050a003223</t>
+          <t xml:space="preserve">942e4bd0-be4c-11f1-ca85-f2050a003223</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="S52">
         <is>
-          <t xml:space="preserve">10046135    </t>
+          <t xml:space="preserve">10047019    </t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="U52">
@@ -3182,12 +3182,12 @@
     <row r="53" ht="15.55" customHeight="0">
       <c s="15" t="inlineStr" r="A53">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 01</t>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="B53">
         <is>
-          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
         </is>
       </c>
       <c s="17" t="inlineStr" r="D53">
@@ -3199,11 +3199,11 @@
         <v>46297.2916666667</v>
       </c>
       <c s="18" r="G53">
-        <v>46297.3020833333</v>
+        <v>46297.3055555556</v>
       </c>
       <c s="17" t="inlineStr" r="H53">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c s="17" t="str" r="I53"/>
@@ -3230,18 +3230,18 @@
       </c>
       <c s="16" t="inlineStr" r="O53">
         <is>
-          <t xml:space="preserve">dds e assinatura dos documentos</t>
+          <t xml:space="preserve">dds com supervisor QUEDA DE MATERIAIS</t>
         </is>
       </c>
       <c s="16" t="str" r="P53"/>
       <c s="16" t="inlineStr" r="R53">
         <is>
-          <t xml:space="preserve">61a3b7a0-be4b-11f1-9cbf-f2050a003223</t>
+          <t xml:space="preserve">167ccc00-be4e-11f1-cdcf-f2050a003223</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="S53">
         <is>
-          <t xml:space="preserve">10046873    </t>
+          <t xml:space="preserve">10046135    </t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="U53">
@@ -3254,12 +3254,12 @@
     <row r="54" ht="15.6" customHeight="0">
       <c s="19" t="inlineStr" r="A54">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 04</t>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="B54">
         <is>
-          <t xml:space="preserve">TR04-DESENROLADOR</t>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
         </is>
       </c>
       <c s="21" t="inlineStr" r="D54">
@@ -3271,11 +3271,11 @@
         <v>46297.2916666667</v>
       </c>
       <c s="22" r="G54">
-        <v>46297.2986111111</v>
+        <v>46297.3020833333</v>
       </c>
       <c s="21" t="inlineStr" r="H54">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c s="21" t="str" r="I54"/>
@@ -3302,18 +3302,18 @@
       </c>
       <c s="20" t="inlineStr" r="O54">
         <is>
-          <t xml:space="preserve">DDS</t>
+          <t xml:space="preserve">dds e assinatura dos documentos</t>
         </is>
       </c>
       <c s="20" t="str" r="P54"/>
       <c s="20" t="inlineStr" r="R54">
         <is>
-          <t xml:space="preserve">942e4bd0-be4c-11f1-ca85-f2050a003223</t>
+          <t xml:space="preserve">61a3b7a0-be4b-11f1-9cbf-f2050a003223</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="S54">
         <is>
-          <t xml:space="preserve">10047019    </t>
+          <t xml:space="preserve">10046873    </t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="U54">
@@ -6238,12 +6238,12 @@
     <row r="96" ht="15.6" customHeight="0">
       <c s="19" t="inlineStr" r="A96">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 04</t>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="B96">
         <is>
-          <t xml:space="preserve">TR04-DESENROLADOR</t>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
         </is>
       </c>
       <c s="21" t="inlineStr" r="D96">
@@ -6286,18 +6286,18 @@
       </c>
       <c s="20" t="inlineStr" r="O96">
         <is>
-          <t xml:space="preserve">DDS</t>
+          <t xml:space="preserve">dds</t>
         </is>
       </c>
       <c s="20" t="str" r="P96"/>
       <c s="20" t="inlineStr" r="R96">
         <is>
-          <t xml:space="preserve">2a2a1a30-c0b2-11f1-9e79-f2050a003223</t>
+          <t xml:space="preserve">1176a761-c0ad-11f1-8444-f2050a003223</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="S96">
         <is>
-          <t xml:space="preserve">10046892    </t>
+          <t xml:space="preserve">10046136    </t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="U96">
@@ -6310,12 +6310,12 @@
     <row r="97" ht="15.6" customHeight="0">
       <c s="15" t="inlineStr" r="A97">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 05</t>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="B97">
         <is>
-          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
         </is>
       </c>
       <c s="17" t="inlineStr" r="D97">
@@ -6358,18 +6358,18 @@
       </c>
       <c s="16" t="inlineStr" r="O97">
         <is>
-          <t xml:space="preserve">dds</t>
+          <t xml:space="preserve">DDS</t>
         </is>
       </c>
       <c s="16" t="str" r="P97"/>
       <c s="16" t="inlineStr" r="R97">
         <is>
-          <t xml:space="preserve">1176a761-c0ad-11f1-8444-f2050a003223</t>
+          <t xml:space="preserve">2a2a1a30-c0b2-11f1-9e79-f2050a003223</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="S97">
         <is>
-          <t xml:space="preserve">10046136    </t>
+          <t xml:space="preserve">10046892    </t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="U97">
@@ -10386,7 +10386,11 @@
           <t xml:space="preserve">TRANSVERSAL 04</t>
         </is>
       </c>
-      <c s="20" t="str" r="B154"/>
+      <c s="20" t="inlineStr" r="B154">
+        <is>
+          <t xml:space="preserve">TR04-CARRO DE ENTRADA</t>
+        </is>
+      </c>
       <c s="21" t="inlineStr" r="D154">
         <is>
           <t xml:space="preserve">TURNO B</t>
@@ -10422,7 +10426,7 @@
       <c s="20" t="str" r="M154"/>
       <c s="20" t="inlineStr" r="N154">
         <is>
-          <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
+          <t xml:space="preserve">FALTA DEMANDA</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="O154">
@@ -10595,12 +10599,12 @@
     <row r="157" ht="15.55" customHeight="0">
       <c s="15" t="inlineStr" r="A157">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 01</t>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="B157">
         <is>
-          <t xml:space="preserve">TR01-MESA TRANSPORTADORA</t>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
         </is>
       </c>
       <c s="17" t="inlineStr" r="D157">
@@ -10612,11 +10616,11 @@
         <v>46301.2916666667</v>
       </c>
       <c s="18" r="G157">
-        <v>46301.3020833333</v>
+        <v>46301.2986111111</v>
       </c>
       <c s="17" t="inlineStr" r="H157">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c s="17" t="str" r="I157"/>
@@ -10643,18 +10647,18 @@
       </c>
       <c s="16" t="inlineStr" r="O157">
         <is>
-          <t xml:space="preserve">dds  e assinatura dos documentos</t>
+          <t xml:space="preserve">DDS</t>
         </is>
       </c>
       <c s="16" t="str" r="P157"/>
       <c s="16" t="inlineStr" r="R157">
         <is>
-          <t xml:space="preserve">fa2e6070-c16f-11f1-a1bf-f2050a003223</t>
+          <t xml:space="preserve">00542e40-c174-11f1-b395-f2050a003223</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="S157">
         <is>
-          <t xml:space="preserve">10047271    </t>
+          <t xml:space="preserve">10048032    </t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="U157">
@@ -10667,12 +10671,12 @@
     <row r="158" ht="15.6" customHeight="0">
       <c s="19" t="inlineStr" r="A158">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 05</t>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="B158">
         <is>
-          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+          <t xml:space="preserve">TR01-MESA TRANSPORTADORA</t>
         </is>
       </c>
       <c s="21" t="inlineStr" r="D158">
@@ -10684,11 +10688,11 @@
         <v>46301.2916666667</v>
       </c>
       <c s="22" r="G158">
-        <v>46301.3055555556</v>
+        <v>46301.3020833333</v>
       </c>
       <c s="21" t="inlineStr" r="H158">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c s="21" t="str" r="I158"/>
@@ -10715,18 +10719,18 @@
       </c>
       <c s="20" t="inlineStr" r="O158">
         <is>
-          <t xml:space="preserve">dds</t>
+          <t xml:space="preserve">dds  e assinatura dos documentos</t>
         </is>
       </c>
       <c s="20" t="str" r="P158"/>
       <c s="20" t="inlineStr" r="R158">
         <is>
-          <t xml:space="preserve">4ed80b10-c172-11f1-84a1-f2050a003223</t>
+          <t xml:space="preserve">fa2e6070-c16f-11f1-a1bf-f2050a003223</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="S158">
         <is>
-          <t xml:space="preserve">10046766    </t>
+          <t xml:space="preserve">10047271    </t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="U158">
@@ -10739,12 +10743,12 @@
     <row r="159" ht="15.55" customHeight="0">
       <c s="15" t="inlineStr" r="A159">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 04</t>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="B159">
         <is>
-          <t xml:space="preserve">TR04-DESENROLADOR</t>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
         </is>
       </c>
       <c s="17" t="inlineStr" r="D159">
@@ -10756,11 +10760,11 @@
         <v>46301.2916666667</v>
       </c>
       <c s="18" r="G159">
-        <v>46301.2986111111</v>
+        <v>46301.3055555556</v>
       </c>
       <c s="17" t="inlineStr" r="H159">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c s="17" t="str" r="I159"/>
@@ -10787,18 +10791,18 @@
       </c>
       <c s="16" t="inlineStr" r="O159">
         <is>
-          <t xml:space="preserve">DDS</t>
+          <t xml:space="preserve">dds</t>
         </is>
       </c>
       <c s="16" t="str" r="P159"/>
       <c s="16" t="inlineStr" r="R159">
         <is>
-          <t xml:space="preserve">00542e40-c174-11f1-b395-f2050a003223</t>
+          <t xml:space="preserve">4ed80b10-c172-11f1-84a1-f2050a003223</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="S159">
         <is>
-          <t xml:space="preserve">10048032    </t>
+          <t xml:space="preserve">10046766    </t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="U159">
@@ -15231,7 +15235,7 @@
     <row r="222" ht="15.6" customHeight="0">
       <c s="19" t="inlineStr" r="A222">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 01</t>
+          <t xml:space="preserve">TRANSVERSAL 03</t>
         </is>
       </c>
       <c s="20" t="str" r="B222"/>
@@ -15281,14 +15285,10 @@
       <c s="20" t="str" r="P222"/>
       <c s="20" t="inlineStr" r="R222">
         <is>
-          <t xml:space="preserve">1e40e600-c1bf-11f1-add1-f2050a003223</t>
-        </is>
-      </c>
-      <c s="20" t="inlineStr" r="S222">
-        <is>
-          <t xml:space="preserve">10048039    </t>
-        </is>
-      </c>
+          <t xml:space="preserve">1e703360-c1bf-11f1-c100-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="S222"/>
       <c s="20" t="inlineStr" r="U222">
         <is>
           <t xml:space="preserve">Sim</t>
@@ -15299,10 +15299,14 @@
     <row r="223" ht="15.6" customHeight="0">
       <c s="15" t="inlineStr" r="A223">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 03</t>
-        </is>
-      </c>
-      <c s="16" t="str" r="B223"/>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B223">
+        <is>
+          <t xml:space="preserve">TR01-CARRO DE ENTRADA</t>
+        </is>
+      </c>
       <c s="17" t="inlineStr" r="D223">
         <is>
           <t xml:space="preserve">TURNO B</t>
@@ -15338,7 +15342,7 @@
       <c s="16" t="str" r="M223"/>
       <c s="16" t="inlineStr" r="N223">
         <is>
-          <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
+          <t xml:space="preserve">FALTA DEMANDA</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="O223">
@@ -15349,10 +15353,14 @@
       <c s="16" t="str" r="P223"/>
       <c s="16" t="inlineStr" r="R223">
         <is>
-          <t xml:space="preserve">1e703360-c1bf-11f1-c100-f2050a003223</t>
-        </is>
-      </c>
-      <c s="16" t="str" r="S223"/>
+          <t xml:space="preserve">1e40e600-c1bf-11f1-add1-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S223">
+        <is>
+          <t xml:space="preserve">10048039    </t>
+        </is>
+      </c>
       <c s="16" t="inlineStr" r="U223">
         <is>
           <t xml:space="preserve">Sim</t>
@@ -15507,12 +15515,12 @@
     <row r="226" ht="15.55" customHeight="0">
       <c s="19" t="inlineStr" r="A226">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 05</t>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="B226">
         <is>
-          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
         </is>
       </c>
       <c s="21" t="inlineStr" r="D226">
@@ -15524,11 +15532,11 @@
         <v>46302.2916666667</v>
       </c>
       <c s="22" r="G226">
-        <v>46302.3055555556</v>
+        <v>46302.2986111111</v>
       </c>
       <c s="21" t="inlineStr" r="H226">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c s="21" t="str" r="I226"/>
@@ -15555,18 +15563,18 @@
       </c>
       <c s="20" t="inlineStr" r="O226">
         <is>
-          <t xml:space="preserve">dds</t>
+          <t xml:space="preserve">DDS</t>
         </is>
       </c>
       <c s="20" t="str" r="P226"/>
       <c s="20" t="inlineStr" r="R226">
         <is>
-          <t xml:space="preserve">0bb05300-c23b-11f1-bbbb-f2050a003223</t>
+          <t xml:space="preserve">c3a92550-c23a-11f1-b331-f2050a003223</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="S226">
         <is>
-          <t xml:space="preserve">10046774    </t>
+          <t xml:space="preserve">10048227    </t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="U226">
@@ -15579,12 +15587,12 @@
     <row r="227" ht="15.6" customHeight="0">
       <c s="15" t="inlineStr" r="A227">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 02</t>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="B227">
         <is>
-          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
+          <t xml:space="preserve">TR01-MESA TRANSPORTADORA</t>
         </is>
       </c>
       <c s="17" t="inlineStr" r="D227">
@@ -15596,11 +15604,11 @@
         <v>46302.2916666667</v>
       </c>
       <c s="18" r="G227">
-        <v>46302.2986111111</v>
+        <v>46302.3020833333</v>
       </c>
       <c s="17" t="inlineStr" r="H227">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c s="17" t="str" r="I227"/>
@@ -15627,18 +15635,18 @@
       </c>
       <c s="16" t="inlineStr" r="O227">
         <is>
-          <t xml:space="preserve">DDS</t>
+          <t xml:space="preserve">dds e assinatura dos documentos</t>
         </is>
       </c>
       <c s="16" t="str" r="P227"/>
       <c s="16" t="inlineStr" r="R227">
         <is>
-          <t xml:space="preserve">c3a92550-c23a-11f1-b331-f2050a003223</t>
+          <t xml:space="preserve">e92b60c0-c237-11f1-ab7f-f2050a003223</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="S227">
         <is>
-          <t xml:space="preserve">10048227    </t>
+          <t xml:space="preserve">10048039    </t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="U227">
@@ -15651,12 +15659,12 @@
     <row r="228" ht="15.6" customHeight="0">
       <c s="19" t="inlineStr" r="A228">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 01</t>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="B228">
         <is>
-          <t xml:space="preserve">TR01-MESA TRANSPORTADORA</t>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
         </is>
       </c>
       <c s="21" t="inlineStr" r="D228">
@@ -15668,11 +15676,11 @@
         <v>46302.2916666667</v>
       </c>
       <c s="22" r="G228">
-        <v>46302.3020833333</v>
+        <v>46302.3055555556</v>
       </c>
       <c s="21" t="inlineStr" r="H228">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c s="21" t="str" r="I228"/>
@@ -15699,18 +15707,18 @@
       </c>
       <c s="20" t="inlineStr" r="O228">
         <is>
-          <t xml:space="preserve">dds e assinatura dos documentos</t>
+          <t xml:space="preserve">dds</t>
         </is>
       </c>
       <c s="20" t="str" r="P228"/>
       <c s="20" t="inlineStr" r="R228">
         <is>
-          <t xml:space="preserve">e92b60c0-c237-11f1-ab7f-f2050a003223</t>
+          <t xml:space="preserve">0bb05300-c23b-11f1-bbbb-f2050a003223</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="S228">
         <is>
-          <t xml:space="preserve">10048039    </t>
+          <t xml:space="preserve">10046774    </t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="U228">
@@ -18072,11 +18080,11 @@
         <v>46302.6597222222</v>
       </c>
       <c s="22" r="G262">
-        <v>46303.2927896181</v>
+        <v>46303.5145833333</v>
       </c>
       <c s="21" t="inlineStr" r="H262">
         <is>
-          <t xml:space="preserve">912</t>
+          <t xml:space="preserve">1.231</t>
         </is>
       </c>
       <c s="21" t="str" r="I262"/>
@@ -18191,24 +18199,28 @@
     <row r="264" ht="15.6" customHeight="0">
       <c s="19" t="inlineStr" r="A264">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 02</t>
-        </is>
-      </c>
-      <c s="20" t="str" r="B264"/>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B264">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
       <c s="21" t="inlineStr" r="D264">
         <is>
           <t xml:space="preserve">TURNO B</t>
         </is>
       </c>
       <c s="22" r="E264">
-        <v>46302.6854166667</v>
+        <v>46302.6944444444</v>
       </c>
       <c s="22" r="G264">
-        <v>46303.2927896181</v>
+        <v>46302.7048611111</v>
       </c>
       <c s="21" t="inlineStr" r="H264">
         <is>
-          <t xml:space="preserve">875</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c s="21" t="str" r="I264"/>
@@ -18219,34 +18231,34 @@
       </c>
       <c s="20" t="inlineStr" r="K264">
         <is>
-          <t xml:space="preserve">Integração Automática</t>
+          <t xml:space="preserve">Operacional</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="L264">
         <is>
-          <t xml:space="preserve">Integração Automática</t>
+          <t xml:space="preserve">Operacional</t>
         </is>
       </c>
       <c s="20" t="str" r="M264"/>
       <c s="20" t="inlineStr" r="N264">
         <is>
-          <t xml:space="preserve">Parada Registrada via Integração</t>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="O264">
         <is>
-          <t xml:space="preserve">PARADA REGISTRADA VIA INTEGRAÇÃO AUTOMÁTICA.</t>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
         </is>
       </c>
       <c s="20" t="str" r="P264"/>
       <c s="20" t="inlineStr" r="R264">
         <is>
-          <t xml:space="preserve">275de5a0-c285-11f1-a307-f2050a003223</t>
+          <t xml:space="preserve">be49cd70-c286-11f1-b4a4-f2050a003223</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="S264">
         <is>
-          <t xml:space="preserve">10048465    </t>
+          <t xml:space="preserve">10048233    </t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="U264">
@@ -18259,12 +18271,12 @@
     <row r="265" ht="15.6" customHeight="0">
       <c s="15" t="inlineStr" r="A265">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 01</t>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="B265">
         <is>
-          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
         </is>
       </c>
       <c s="17" t="inlineStr" r="D265">
@@ -18273,14 +18285,14 @@
         </is>
       </c>
       <c s="18" r="E265">
-        <v>46302.6944444444</v>
+        <v>46302.6979166667</v>
       </c>
       <c s="18" r="G265">
-        <v>46303.2927896181</v>
+        <v>46303.2909722222</v>
       </c>
       <c s="17" t="inlineStr" r="H265">
         <is>
-          <t xml:space="preserve">862</t>
+          <t xml:space="preserve">854</t>
         </is>
       </c>
       <c s="17" t="str" r="I265"/>
@@ -18307,18 +18319,18 @@
       </c>
       <c s="16" t="inlineStr" r="O265">
         <is>
-          <t xml:space="preserve">tempo livre</t>
+          <t xml:space="preserve">Falta de demanda</t>
         </is>
       </c>
       <c s="16" t="str" r="P265"/>
       <c s="16" t="inlineStr" r="R265">
         <is>
-          <t xml:space="preserve">be49cd70-c286-11f1-b4a4-f2050a003223</t>
+          <t xml:space="preserve">275de5a0-c285-11f1-a307-f2050a003223</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="S265">
         <is>
-          <t xml:space="preserve">10048233    </t>
+          <t xml:space="preserve">10048465    </t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="U265">
@@ -18348,11 +18360,11 @@
         <v>46302.6993055556</v>
       </c>
       <c s="22" r="G266">
-        <v>46303.2927896181</v>
+        <v>46303.2909722222</v>
       </c>
       <c s="21" t="inlineStr" r="H266">
         <is>
-          <t xml:space="preserve">855</t>
+          <t xml:space="preserve">852</t>
         </is>
       </c>
       <c s="21" t="str" r="I266"/>
@@ -18400,75 +18412,2335 @@
       </c>
       <c s="5" t="str" r="V266"/>
     </row>
-    <row r="267" ht="15.55" customHeight="0">
-      <c s="23" t="inlineStr" r="A267">
+    <row r="267" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A267">
         <is>
           <t xml:space="preserve">TRANSVERSAL 03</t>
         </is>
       </c>
-      <c s="24" t="str" r="B267"/>
-      <c s="10" t="str" r="C267"/>
-      <c s="25" t="inlineStr" r="D267">
+      <c s="16" t="str" r="B267"/>
+      <c s="17" t="inlineStr" r="D267">
         <is>
           <t xml:space="preserve">TURNO B</t>
         </is>
       </c>
-      <c s="26" r="E267">
+      <c s="18" r="E267">
         <v>46302.7013888889</v>
       </c>
-      <c s="10" t="str" r="F267"/>
-      <c s="26" r="G267">
+      <c s="18" r="G267">
         <v>46303.2840277778</v>
       </c>
-      <c s="25" t="inlineStr" r="H267">
+      <c s="17" t="inlineStr" r="H267">
         <is>
           <t xml:space="preserve">839</t>
         </is>
       </c>
-      <c s="25" t="str" r="I267"/>
-      <c s="25" t="inlineStr" r="J267">
-        <is>
-          <t xml:space="preserve">X</t>
-        </is>
-      </c>
-      <c s="24" t="inlineStr" r="K267">
+      <c s="17" t="str" r="I267"/>
+      <c s="17" t="inlineStr" r="J267">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K267">
         <is>
           <t xml:space="preserve">Tempo Livre</t>
         </is>
       </c>
-      <c s="24" t="inlineStr" r="L267">
+      <c s="16" t="inlineStr" r="L267">
         <is>
           <t xml:space="preserve">Tempo Livre</t>
         </is>
       </c>
-      <c s="24" t="str" r="M267"/>
-      <c s="24" t="inlineStr" r="N267">
+      <c s="16" t="str" r="M267"/>
+      <c s="16" t="inlineStr" r="N267">
         <is>
           <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
         </is>
       </c>
-      <c s="24" t="inlineStr" r="O267">
+      <c s="16" t="inlineStr" r="O267">
         <is>
           <t xml:space="preserve">Parada registrada automaticamente pelo sistema</t>
         </is>
       </c>
-      <c s="24" t="str" r="P267"/>
-      <c s="10" t="str" r="Q267"/>
-      <c s="24" t="inlineStr" r="R267">
+      <c s="16" t="str" r="P267"/>
+      <c s="16" t="inlineStr" r="R267">
         <is>
           <t xml:space="preserve">48564470-c288-11f1-94a6-f2050a003223</t>
         </is>
       </c>
-      <c s="24" t="str" r="S267"/>
-      <c s="10" t="str" r="T267"/>
-      <c s="24" t="inlineStr" r="U267">
-        <is>
-          <t xml:space="preserve">Sim</t>
-        </is>
-      </c>
-      <c s="11" t="str" r="V267"/>
-    </row>
-    <row r="268" ht="0.05" customHeight="1"/>
+      <c s="16" t="str" r="S267"/>
+      <c s="16" t="inlineStr" r="U267">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V267"/>
+    </row>
+    <row r="268" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A268">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B268">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D268">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E268">
+        <v>46302.7055555556</v>
+      </c>
+      <c s="22" r="G268">
+        <v>46303.2909722222</v>
+      </c>
+      <c s="21" t="inlineStr" r="H268">
+        <is>
+          <t xml:space="preserve">843</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I268"/>
+      <c s="21" t="inlineStr" r="J268">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K268">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L268">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M268"/>
+      <c s="20" t="inlineStr" r="N268">
+        <is>
+          <t xml:space="preserve">FALTA DEMANDA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O268">
+        <is>
+          <t xml:space="preserve">tempo livre</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P268"/>
+      <c s="20" t="inlineStr" r="R268">
+        <is>
+          <t xml:space="preserve">ba264590-c301-11f1-b64a-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S268">
+        <is>
+          <t xml:space="preserve">10048233    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U268">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V268"/>
+    </row>
+    <row r="269" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A269">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B269">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D269">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E269">
+        <v>46303.2916666667</v>
+      </c>
+      <c s="18" r="G269">
+        <v>46303.3020833333</v>
+      </c>
+      <c s="17" t="inlineStr" r="H269">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I269"/>
+      <c s="17" t="inlineStr" r="J269">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K269">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L269">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M269"/>
+      <c s="16" t="inlineStr" r="N269">
+        <is>
+          <t xml:space="preserve">DDS</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O269">
+        <is>
+          <t xml:space="preserve">dds e assinatura dos documentos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P269"/>
+      <c s="16" t="inlineStr" r="R269">
+        <is>
+          <t xml:space="preserve">065f5d20-c302-11f1-8108-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S269">
+        <is>
+          <t xml:space="preserve">10048233    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U269">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V269"/>
+    </row>
+    <row r="270" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A270">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B270">
+        <is>
+          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D270">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E270">
+        <v>46303.2916666667</v>
+      </c>
+      <c s="22" r="G270">
+        <v>46303.2986111111</v>
+      </c>
+      <c s="21" t="inlineStr" r="H270">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I270"/>
+      <c s="21" t="inlineStr" r="J270">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K270">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L270">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M270"/>
+      <c s="20" t="inlineStr" r="N270">
+        <is>
+          <t xml:space="preserve">DDS</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O270">
+        <is>
+          <t xml:space="preserve">DDS</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P270"/>
+      <c s="20" t="inlineStr" r="R270">
+        <is>
+          <t xml:space="preserve">6e8883a0-c301-11f1-9a54-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S270">
+        <is>
+          <t xml:space="preserve">10048465    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U270">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V270"/>
+    </row>
+    <row r="271" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A271">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B271"/>
+      <c s="17" t="inlineStr" r="D271">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E271">
+        <v>46303.3034722222</v>
+      </c>
+      <c s="18" r="G271">
+        <v>46303.3111111111</v>
+      </c>
+      <c s="17" t="inlineStr" r="H271">
+        <is>
+          <t xml:space="preserve">11</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I271"/>
+      <c s="17" t="inlineStr" r="J271">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K271">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L271">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M271"/>
+      <c s="16" t="inlineStr" r="N271">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O271">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 11 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P271"/>
+      <c s="16" t="inlineStr" r="R271">
+        <is>
+          <t xml:space="preserve">750f32f0-c301-11f1-b481-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S271">
+        <is>
+          <t xml:space="preserve">10048465    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U271">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V271"/>
+    </row>
+    <row r="272" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A272">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B272">
+        <is>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D272">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E272">
+        <v>46303.3097222222</v>
+      </c>
+      <c s="22" r="G272">
+        <v>46304.4579892708</v>
+      </c>
+      <c s="21" t="inlineStr" r="H272">
+        <is>
+          <t xml:space="preserve">1.654</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I272"/>
+      <c s="21" t="inlineStr" r="J272">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K272">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L272">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M272"/>
+      <c s="20" t="inlineStr" r="N272">
+        <is>
+          <t xml:space="preserve">MANUTENÇÃO PREVENTIVA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O272">
+        <is>
+          <t xml:space="preserve">manutenção preventiva</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P272"/>
+      <c s="20" t="inlineStr" r="R272">
+        <is>
+          <t xml:space="preserve">c8f64650-c302-11f1-b750-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S272">
+        <is>
+          <t xml:space="preserve">10047305    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U272">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V272"/>
+    </row>
+    <row r="273" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A273">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B273">
+        <is>
+          <t xml:space="preserve">TR02-ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D273">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E273">
+        <v>46303.3118055556</v>
+      </c>
+      <c s="18" r="G273">
+        <v>46303.3145833333</v>
+      </c>
+      <c s="17" t="inlineStr" r="H273">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I273"/>
+      <c s="17" t="inlineStr" r="J273">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K273">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L273">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M273"/>
+      <c s="16" t="inlineStr" r="N273">
+        <is>
+          <t xml:space="preserve">AJUSTE DE ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O273">
+        <is>
+          <t xml:space="preserve">Regulagem da endireitadeira</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P273"/>
+      <c s="16" t="inlineStr" r="R273">
+        <is>
+          <t xml:space="preserve">3019ee40-c303-11f1-98c5-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S273">
+        <is>
+          <t xml:space="preserve">10048465    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U273">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V273"/>
+    </row>
+    <row r="274" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A274">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B274"/>
+      <c s="21" t="inlineStr" r="D274">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E274">
+        <v>46303.3263888889</v>
+      </c>
+      <c s="22" r="G274">
+        <v>46303.3354166667</v>
+      </c>
+      <c s="21" t="inlineStr" r="H274">
+        <is>
+          <t xml:space="preserve">13</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I274"/>
+      <c s="21" t="inlineStr" r="J274">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K274">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L274">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M274"/>
+      <c s="20" t="inlineStr" r="N274">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O274">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 13 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P274"/>
+      <c s="20" t="inlineStr" r="R274">
+        <is>
+          <t xml:space="preserve">22750330-c306-11f1-c07e-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S274">
+        <is>
+          <t xml:space="preserve">10048233    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U274">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V274"/>
+    </row>
+    <row r="275" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A275">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B275"/>
+      <c s="17" t="inlineStr" r="D275">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E275">
+        <v>46303.3305555556</v>
+      </c>
+      <c s="18" r="G275">
+        <v>46303.3333333333</v>
+      </c>
+      <c s="17" t="inlineStr" r="H275">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I275"/>
+      <c s="17" t="inlineStr" r="J275">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K275">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L275">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M275"/>
+      <c s="16" t="inlineStr" r="N275">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O275">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 4 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P275"/>
+      <c s="16" t="inlineStr" r="R275">
+        <is>
+          <t xml:space="preserve">f6970af0-c306-11f1-8bae-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S275">
+        <is>
+          <t xml:space="preserve">10048465    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U275">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V275"/>
+    </row>
+    <row r="276" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A276">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B276"/>
+      <c s="21" t="inlineStr" r="D276">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E276">
+        <v>46303.3375</v>
+      </c>
+      <c s="22" r="G276">
+        <v>46303.3402777778</v>
+      </c>
+      <c s="21" t="inlineStr" r="H276">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I276"/>
+      <c s="21" t="inlineStr" r="J276">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K276">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L276">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M276"/>
+      <c s="20" t="inlineStr" r="N276">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O276">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 4 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P276"/>
+      <c s="20" t="inlineStr" r="R276">
+        <is>
+          <t xml:space="preserve">4d383540-c308-11f1-b339-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S276">
+        <is>
+          <t xml:space="preserve">10048465    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U276">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V276"/>
+    </row>
+    <row r="277" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A277">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B277"/>
+      <c s="17" t="inlineStr" r="D277">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E277">
+        <v>46303.3430555556</v>
+      </c>
+      <c s="18" r="G277">
+        <v>46303.3451388889</v>
+      </c>
+      <c s="17" t="inlineStr" r="H277">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I277"/>
+      <c s="17" t="inlineStr" r="J277">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K277">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L277">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M277"/>
+      <c s="16" t="inlineStr" r="N277">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O277">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 3 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P277"/>
+      <c s="16" t="inlineStr" r="R277">
+        <is>
+          <t xml:space="preserve">69518c30-c309-11f1-9e08-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S277">
+        <is>
+          <t xml:space="preserve">10048465    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U277">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V277"/>
+    </row>
+    <row r="278" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A278">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B278">
+        <is>
+          <t xml:space="preserve">TR01-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D278">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E278">
+        <v>46303.34375</v>
+      </c>
+      <c s="22" r="G278">
+        <v>46303.3444444444</v>
+      </c>
+      <c s="21" t="inlineStr" r="H278">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I278"/>
+      <c s="21" t="inlineStr" r="J278">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K278">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L278">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M278"/>
+      <c s="20" t="inlineStr" r="N278">
+        <is>
+          <t xml:space="preserve">AGUARDANDO INSPEÇÃO DE  QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O278">
+        <is>
+          <t xml:space="preserve">material com num leve amassado na borda material foi liberado como bom UD:2003984577</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P278"/>
+      <c s="20" t="inlineStr" r="R278">
+        <is>
+          <t xml:space="preserve">bb36d190-c309-11f1-ab2b-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S278">
+        <is>
+          <t xml:space="preserve">10048233    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U278">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V278"/>
+    </row>
+    <row r="279" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A279">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B279">
+        <is>
+          <t xml:space="preserve">TR02-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D279">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E279">
+        <v>46303.3534722222</v>
+      </c>
+      <c s="18" r="G279">
+        <v>46303.4166666667</v>
+      </c>
+      <c s="17" t="inlineStr" r="H279">
+        <is>
+          <t xml:space="preserve">91</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I279"/>
+      <c s="17" t="inlineStr" r="J279">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K279">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L279">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M279"/>
+      <c s="16" t="inlineStr" r="N279">
+        <is>
+          <t xml:space="preserve">FALTA DEMANDA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O279">
+        <is>
+          <t xml:space="preserve">Falta de demanda</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P279"/>
+      <c s="16" t="inlineStr" r="R279">
+        <is>
+          <t xml:space="preserve">a225aa30-c30b-11f1-93d4-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S279">
+        <is>
+          <t xml:space="preserve">10048466    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U279">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V279"/>
+    </row>
+    <row r="280" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A280">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B280"/>
+      <c s="21" t="inlineStr" r="D280">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E280">
+        <v>46303.4138888889</v>
+      </c>
+      <c s="22" r="G280">
+        <v>46303.4208333333</v>
+      </c>
+      <c s="21" t="inlineStr" r="H280">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I280"/>
+      <c s="21" t="inlineStr" r="J280">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K280">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L280">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M280"/>
+      <c s="20" t="inlineStr" r="N280">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O280">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 10 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P280"/>
+      <c s="20" t="inlineStr" r="R280">
+        <is>
+          <t xml:space="preserve">b681cca0-c317-11f1-a724-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S280">
+        <is>
+          <t xml:space="preserve">10048233    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U280">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V280"/>
+    </row>
+    <row r="281" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A281">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B281">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D281">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E281">
+        <v>46303.4243055556</v>
+      </c>
+      <c s="18" r="G281">
+        <v>46303.4270833333</v>
+      </c>
+      <c s="17" t="inlineStr" r="H281">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I281"/>
+      <c s="17" t="inlineStr" r="J281">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K281">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L281">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M281"/>
+      <c s="16" t="inlineStr" r="N281">
+        <is>
+          <t xml:space="preserve">QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O281">
+        <is>
+          <t xml:space="preserve">vaiando material</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P281"/>
+      <c s="16" t="inlineStr" r="R281">
+        <is>
+          <t xml:space="preserve">d4386360-c319-11f1-c8a3-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S281">
+        <is>
+          <t xml:space="preserve">10048233    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U281">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V281"/>
+    </row>
+    <row r="282" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A282">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B282">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D282">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E282">
+        <v>46303.4333333333</v>
+      </c>
+      <c s="22" r="G282">
+        <v>46303.4375</v>
+      </c>
+      <c s="21" t="inlineStr" r="H282">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I282"/>
+      <c s="21" t="inlineStr" r="J282">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K282">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L282">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M282"/>
+      <c s="20" t="inlineStr" r="N282">
+        <is>
+          <t xml:space="preserve">QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O282">
+        <is>
+          <t xml:space="preserve">avaliando material material com oxidação na borda UD:2003984078 material foi liberado como bom</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P282"/>
+      <c s="20" t="inlineStr" r="R282">
+        <is>
+          <t xml:space="preserve">902e4200-c31b-11f1-ca5c-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S282">
+        <is>
+          <t xml:space="preserve">10048233    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U282">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V282"/>
+    </row>
+    <row r="283" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A283">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B283">
+        <is>
+          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D283">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E283">
+        <v>46303.4583333333</v>
+      </c>
+      <c s="18" r="G283">
+        <v>46303.5</v>
+      </c>
+      <c s="17" t="inlineStr" r="H283">
+        <is>
+          <t xml:space="preserve">60</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I283"/>
+      <c s="17" t="inlineStr" r="J283">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K283">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L283">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M283"/>
+      <c s="16" t="inlineStr" r="N283">
+        <is>
+          <t xml:space="preserve">ALMOÇO / JANTA / CEIA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O283">
+        <is>
+          <t xml:space="preserve">Almoço.</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P283"/>
+      <c s="16" t="inlineStr" r="R283">
+        <is>
+          <t xml:space="preserve">d85a37f0-c32a-11f1-bd6c-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S283">
+        <is>
+          <t xml:space="preserve">10048466    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U283">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V283"/>
+    </row>
+    <row r="284" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A284">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B284">
+        <is>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D284">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E284">
+        <v>46303.5194444444</v>
+      </c>
+      <c s="22" r="G284">
+        <v>46303.5215277778</v>
+      </c>
+      <c s="21" t="inlineStr" r="H284">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I284"/>
+      <c s="21" t="inlineStr" r="J284">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K284">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L284">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M284"/>
+      <c s="20" t="inlineStr" r="N284">
+        <is>
+          <t xml:space="preserve">QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O284">
+        <is>
+          <t xml:space="preserve">Bobina 0.60x1.000 de UD.2003627070 com oxidação OBS. Inspetor  de qualidade Luis Gustavo autorizou cortar como material bom.</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P284"/>
+      <c s="20" t="inlineStr" r="R284">
+        <is>
+          <t xml:space="preserve">565dab80-c32d-11f1-bc13-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S284">
+        <is>
+          <t xml:space="preserve">10048747    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U284">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V284"/>
+    </row>
+    <row r="285" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A285">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B285"/>
+      <c s="17" t="inlineStr" r="D285">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E285">
+        <v>46303.5215277778</v>
+      </c>
+      <c s="18" r="G285">
+        <v>46303.5284722222</v>
+      </c>
+      <c s="17" t="inlineStr" r="H285">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I285"/>
+      <c s="17" t="inlineStr" r="J285">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K285">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L285">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M285"/>
+      <c s="16" t="inlineStr" r="N285">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O285">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 10 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P285"/>
+      <c s="16" t="inlineStr" r="R285">
+        <is>
+          <t xml:space="preserve">528c5830-c32d-11f1-ca64-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S285">
+        <is>
+          <t xml:space="preserve">10048233    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U285">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V285"/>
+    </row>
+    <row r="286" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A286">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B286">
+        <is>
+          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D286">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E286">
+        <v>46303.5555555556</v>
+      </c>
+      <c s="22" r="G286">
+        <v>46303.575</v>
+      </c>
+      <c s="21" t="inlineStr" r="H286">
+        <is>
+          <t xml:space="preserve">28</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I286"/>
+      <c s="21" t="inlineStr" r="J286">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K286">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L286">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M286"/>
+      <c s="20" t="inlineStr" r="N286">
+        <is>
+          <t xml:space="preserve">SETUP COMPLETO</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O286">
+        <is>
+          <t xml:space="preserve">Regulagem da endireitadeira e guilhotina.</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P286"/>
+      <c s="20" t="inlineStr" r="R286">
+        <is>
+          <t xml:space="preserve">20bceac0-c339-11f1-8cf3-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S286">
+        <is>
+          <t xml:space="preserve">10048466    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U286">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V286"/>
+    </row>
+    <row r="287" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A287">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B287">
+        <is>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D287">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E287">
+        <v>46303.5583333333</v>
+      </c>
+      <c s="18" r="G287">
+        <v>46303.5631944444</v>
+      </c>
+      <c s="17" t="inlineStr" r="H287">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I287"/>
+      <c s="17" t="inlineStr" r="J287">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K287">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L287">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M287"/>
+      <c s="16" t="inlineStr" r="N287">
+        <is>
+          <t xml:space="preserve">AGUARDANDO INSPEÇÃO DE  QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O287">
+        <is>
+          <t xml:space="preserve">Bobina 0.60x1.000 de UD.2003627070 com oxidação. (observação liberado pela a qualidade para fazer material especial)</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P287"/>
+      <c s="16" t="inlineStr" r="R287">
+        <is>
+          <t xml:space="preserve">c3253fb0-c334-11f1-b6c8-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S287">
+        <is>
+          <t xml:space="preserve">10048747    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U287">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V287"/>
+    </row>
+    <row r="288" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A288">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B288">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D288">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E288">
+        <v>46303.60625</v>
+      </c>
+      <c s="22" r="G288">
+        <v>46303.6263888889</v>
+      </c>
+      <c s="21" t="inlineStr" r="H288">
+        <is>
+          <t xml:space="preserve">29</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I288"/>
+      <c s="21" t="inlineStr" r="J288">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K288">
+        <is>
+          <t xml:space="preserve">Utilidades</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L288">
+        <is>
+          <t xml:space="preserve">Utilidades</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M288"/>
+      <c s="20" t="inlineStr" r="N288">
+        <is>
+          <t xml:space="preserve">INSTALAÇÕES ELÉTRICAS</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O288">
+        <is>
+          <t xml:space="preserve">queda de energia</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="P288">
+        <is>
+          <t xml:space="preserve">000010034678</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="R288">
+        <is>
+          <t xml:space="preserve">5f6ec680-c33e-11f1-b1ee-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S288">
+        <is>
+          <t xml:space="preserve">10048233    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U288">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V288"/>
+    </row>
+    <row r="289" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A289">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B289"/>
+      <c s="17" t="inlineStr" r="D289">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E289">
+        <v>46303.6270833333</v>
+      </c>
+      <c s="18" r="G289">
+        <v>46303.6375</v>
+      </c>
+      <c s="17" t="inlineStr" r="H289">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I289"/>
+      <c s="17" t="inlineStr" r="J289">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K289">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L289">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M289"/>
+      <c s="16" t="inlineStr" r="N289">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O289">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P289"/>
+      <c s="16" t="inlineStr" r="R289">
+        <is>
+          <t xml:space="preserve">93c93150-c342-11f1-a743-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S289">
+        <is>
+          <t xml:space="preserve">10048233    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U289">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V289"/>
+    </row>
+    <row r="290" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A290">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B290">
+        <is>
+          <t xml:space="preserve">TR01-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D290">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E290">
+        <v>46303.6381944444</v>
+      </c>
+      <c s="22" r="G290">
+        <v>46303.6458333333</v>
+      </c>
+      <c s="21" t="inlineStr" r="H290">
+        <is>
+          <t xml:space="preserve">11</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I290"/>
+      <c s="21" t="inlineStr" r="J290">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K290">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L290">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M290"/>
+      <c s="20" t="inlineStr" r="N290">
+        <is>
+          <t xml:space="preserve">TROCA DAS CASTANHAS DO MANDRIL</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O290">
+        <is>
+          <t xml:space="preserve">troca das castanhas</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P290"/>
+      <c s="20" t="inlineStr" r="R290">
+        <is>
+          <t xml:space="preserve">6c8b3c20-c345-11f1-a501-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S290">
+        <is>
+          <t xml:space="preserve">10048233    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U290">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V290"/>
+    </row>
+    <row r="291" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A291">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B291"/>
+      <c s="17" t="inlineStr" r="D291">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E291">
+        <v>46303.6409722222</v>
+      </c>
+      <c s="18" r="G291">
+        <v>46303.6430555556</v>
+      </c>
+      <c s="17" t="inlineStr" r="H291">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I291"/>
+      <c s="17" t="inlineStr" r="J291">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K291">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L291">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M291"/>
+      <c s="16" t="inlineStr" r="N291">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O291">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 3 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P291"/>
+      <c s="16" t="inlineStr" r="R291">
+        <is>
+          <t xml:space="preserve">4cff3730-c345-11f1-bf7e-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S291">
+        <is>
+          <t xml:space="preserve">10048737    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U291">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V291"/>
+    </row>
+    <row r="292" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A292">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B292">
+        <is>
+          <t xml:space="preserve">TR02-GUILHOTINA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D292">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E292">
+        <v>46303.6444444444</v>
+      </c>
+      <c s="22" r="G292">
+        <v>46303.6583333333</v>
+      </c>
+      <c s="21" t="inlineStr" r="H292">
+        <is>
+          <t xml:space="preserve">20</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I292"/>
+      <c s="21" t="inlineStr" r="J292">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K292">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L292">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M292"/>
+      <c s="20" t="inlineStr" r="N292">
+        <is>
+          <t xml:space="preserve">SETUP COMPLETO</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O292">
+        <is>
+          <t xml:space="preserve">Setup completo</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P292"/>
+      <c s="20" t="inlineStr" r="R292">
+        <is>
+          <t xml:space="preserve">145b97b0-c346-11f1-c820-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S292">
+        <is>
+          <t xml:space="preserve">10048737    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U292">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V292"/>
+    </row>
+    <row r="293" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A293">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B293">
+        <is>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D293">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E293">
+        <v>46303.6541666667</v>
+      </c>
+      <c s="18" r="G293">
+        <v>46304.4579892708</v>
+      </c>
+      <c s="17" t="inlineStr" r="H293">
+        <is>
+          <t xml:space="preserve">1.158</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I293"/>
+      <c s="17" t="inlineStr" r="J293">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K293">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L293">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M293"/>
+      <c s="16" t="inlineStr" r="N293">
+        <is>
+          <t xml:space="preserve">FALTA DEMANDA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O293">
+        <is>
+          <t xml:space="preserve">Falta de demanda</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P293"/>
+      <c s="16" t="inlineStr" r="R293">
+        <is>
+          <t xml:space="preserve">3b6914c0-c348-11f1-8e13-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="S293"/>
+      <c s="16" t="inlineStr" r="U293">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V293"/>
+    </row>
+    <row r="294" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A294">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B294">
+        <is>
+          <t xml:space="preserve">TR01-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D294">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E294">
+        <v>46303.6583333333</v>
+      </c>
+      <c s="22" r="G294">
+        <v>46303.6590277778</v>
+      </c>
+      <c s="21" t="inlineStr" r="H294">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I294"/>
+      <c s="21" t="inlineStr" r="J294">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K294">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L294">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M294"/>
+      <c s="20" t="inlineStr" r="N294">
+        <is>
+          <t xml:space="preserve">QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O294">
+        <is>
+          <t xml:space="preserve">material com marcação na superfície da chapa material foi liberado como boa</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P294"/>
+      <c s="20" t="inlineStr" r="R294">
+        <is>
+          <t xml:space="preserve">92642210-c34d-11f1-85b6-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S294">
+        <is>
+          <t xml:space="preserve">10048417    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U294">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V294"/>
+    </row>
+    <row r="295" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A295">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B295">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D295">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E295">
+        <v>46303.6881944444</v>
+      </c>
+      <c s="18" r="G295">
+        <v>46303.6909722222</v>
+      </c>
+      <c s="17" t="inlineStr" r="H295">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I295"/>
+      <c s="17" t="inlineStr" r="J295">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K295">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L295">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M295"/>
+      <c s="16" t="inlineStr" r="N295">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE CHAPA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O295">
+        <is>
+          <t xml:space="preserve">ajuste da chapa</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P295"/>
+      <c s="16" t="inlineStr" r="R295">
+        <is>
+          <t xml:space="preserve">cd78d6b0-c34e-11f1-b4a0-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S295">
+        <is>
+          <t xml:space="preserve">10048417    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U295">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V295"/>
+    </row>
+    <row r="296" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A296">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B296">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D296">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E296">
+        <v>46303.6951388889</v>
+      </c>
+      <c s="22" r="G296">
+        <v>46303.7055555556</v>
+      </c>
+      <c s="21" t="inlineStr" r="H296">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I296"/>
+      <c s="21" t="inlineStr" r="J296">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K296">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L296">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M296"/>
+      <c s="20" t="inlineStr" r="N296">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O296">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P296"/>
+      <c s="20" t="inlineStr" r="R296">
+        <is>
+          <t xml:space="preserve">3a183120-c350-11f1-a73c-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S296">
+        <is>
+          <t xml:space="preserve">10048417    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U296">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V296"/>
+    </row>
+    <row r="297" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A297">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B297">
+        <is>
+          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D297">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E297">
+        <v>46303.6993055556</v>
+      </c>
+      <c s="18" r="G297">
+        <v>46304.2909722222</v>
+      </c>
+      <c s="17" t="inlineStr" r="H297">
+        <is>
+          <t xml:space="preserve">852</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I297"/>
+      <c s="17" t="inlineStr" r="J297">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K297">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L297">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M297"/>
+      <c s="16" t="inlineStr" r="N297">
+        <is>
+          <t xml:space="preserve">FALTA DEMANDA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O297">
+        <is>
+          <t xml:space="preserve">Tempo livre.</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P297"/>
+      <c s="16" t="inlineStr" r="R297">
+        <is>
+          <t xml:space="preserve">1ed419a0-c351-11f1-c6d1-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S297">
+        <is>
+          <t xml:space="preserve">10048738    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U297">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V297"/>
+    </row>
+    <row r="298" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A298">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 03</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B298"/>
+      <c s="21" t="inlineStr" r="D298">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E298">
+        <v>46303.7013888889</v>
+      </c>
+      <c s="22" r="G298">
+        <v>46304.2840277778</v>
+      </c>
+      <c s="21" t="inlineStr" r="H298">
+        <is>
+          <t xml:space="preserve">839</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I298"/>
+      <c s="21" t="inlineStr" r="J298">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K298">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L298">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M298"/>
+      <c s="20" t="inlineStr" r="N298">
+        <is>
+          <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O298">
+        <is>
+          <t xml:space="preserve">Parada registrada automaticamente pelo sistema</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P298"/>
+      <c s="20" t="inlineStr" r="R298">
+        <is>
+          <t xml:space="preserve">72aca380-c351-11f1-ad18-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="S298"/>
+      <c s="20" t="inlineStr" r="U298">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V298"/>
+    </row>
+    <row r="299" ht="15.55" customHeight="0">
+      <c s="23" t="inlineStr" r="A299">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="B299">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="10" t="str" r="C299"/>
+      <c s="25" t="inlineStr" r="D299">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="26" r="E299">
+        <v>46303.70625</v>
+      </c>
+      <c s="10" t="str" r="F299"/>
+      <c s="26" r="G299">
+        <v>46304.2909722222</v>
+      </c>
+      <c s="25" t="inlineStr" r="H299">
+        <is>
+          <t xml:space="preserve">842</t>
+        </is>
+      </c>
+      <c s="25" t="str" r="I299"/>
+      <c s="25" t="inlineStr" r="J299">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="K299">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="L299">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="24" t="str" r="M299"/>
+      <c s="24" t="inlineStr" r="N299">
+        <is>
+          <t xml:space="preserve">FALTA DEMANDA</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="O299">
+        <is>
+          <t xml:space="preserve">tempo livre</t>
+        </is>
+      </c>
+      <c s="24" t="str" r="P299"/>
+      <c s="10" t="str" r="Q299"/>
+      <c s="24" t="inlineStr" r="R299">
+        <is>
+          <t xml:space="preserve">c1e92c10-c3ca-11f1-ca8c-f2050a003223</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="S299">
+        <is>
+          <t xml:space="preserve">10048417    </t>
+        </is>
+      </c>
+      <c s="10" t="str" r="T299"/>
+      <c s="24" t="inlineStr" r="U299">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="11" t="str" r="V299"/>
+    </row>
+    <row r="300" ht="0.05" customHeight="1"/>
   </sheetData>
   <mergeCells>
     <mergeCell ref="A3:B8"/>
@@ -19737,6 +22009,166 @@
     <mergeCell ref="P267:Q267"/>
     <mergeCell ref="S267:T267"/>
     <mergeCell ref="U267:V267"/>
+    <mergeCell ref="B268:C268"/>
+    <mergeCell ref="E268:F268"/>
+    <mergeCell ref="P268:Q268"/>
+    <mergeCell ref="S268:T268"/>
+    <mergeCell ref="U268:V268"/>
+    <mergeCell ref="B269:C269"/>
+    <mergeCell ref="E269:F269"/>
+    <mergeCell ref="P269:Q269"/>
+    <mergeCell ref="S269:T269"/>
+    <mergeCell ref="U269:V269"/>
+    <mergeCell ref="B270:C270"/>
+    <mergeCell ref="E270:F270"/>
+    <mergeCell ref="P270:Q270"/>
+    <mergeCell ref="S270:T270"/>
+    <mergeCell ref="U270:V270"/>
+    <mergeCell ref="B271:C271"/>
+    <mergeCell ref="E271:F271"/>
+    <mergeCell ref="P271:Q271"/>
+    <mergeCell ref="S271:T271"/>
+    <mergeCell ref="U271:V271"/>
+    <mergeCell ref="B272:C272"/>
+    <mergeCell ref="E272:F272"/>
+    <mergeCell ref="P272:Q272"/>
+    <mergeCell ref="S272:T272"/>
+    <mergeCell ref="U272:V272"/>
+    <mergeCell ref="B273:C273"/>
+    <mergeCell ref="E273:F273"/>
+    <mergeCell ref="P273:Q273"/>
+    <mergeCell ref="S273:T273"/>
+    <mergeCell ref="U273:V273"/>
+    <mergeCell ref="B274:C274"/>
+    <mergeCell ref="E274:F274"/>
+    <mergeCell ref="P274:Q274"/>
+    <mergeCell ref="S274:T274"/>
+    <mergeCell ref="U274:V274"/>
+    <mergeCell ref="B275:C275"/>
+    <mergeCell ref="E275:F275"/>
+    <mergeCell ref="P275:Q275"/>
+    <mergeCell ref="S275:T275"/>
+    <mergeCell ref="U275:V275"/>
+    <mergeCell ref="B276:C276"/>
+    <mergeCell ref="E276:F276"/>
+    <mergeCell ref="P276:Q276"/>
+    <mergeCell ref="S276:T276"/>
+    <mergeCell ref="U276:V276"/>
+    <mergeCell ref="B277:C277"/>
+    <mergeCell ref="E277:F277"/>
+    <mergeCell ref="P277:Q277"/>
+    <mergeCell ref="S277:T277"/>
+    <mergeCell ref="U277:V277"/>
+    <mergeCell ref="B278:C278"/>
+    <mergeCell ref="E278:F278"/>
+    <mergeCell ref="P278:Q278"/>
+    <mergeCell ref="S278:T278"/>
+    <mergeCell ref="U278:V278"/>
+    <mergeCell ref="B279:C279"/>
+    <mergeCell ref="E279:F279"/>
+    <mergeCell ref="P279:Q279"/>
+    <mergeCell ref="S279:T279"/>
+    <mergeCell ref="U279:V279"/>
+    <mergeCell ref="B280:C280"/>
+    <mergeCell ref="E280:F280"/>
+    <mergeCell ref="P280:Q280"/>
+    <mergeCell ref="S280:T280"/>
+    <mergeCell ref="U280:V280"/>
+    <mergeCell ref="B281:C281"/>
+    <mergeCell ref="E281:F281"/>
+    <mergeCell ref="P281:Q281"/>
+    <mergeCell ref="S281:T281"/>
+    <mergeCell ref="U281:V281"/>
+    <mergeCell ref="B282:C282"/>
+    <mergeCell ref="E282:F282"/>
+    <mergeCell ref="P282:Q282"/>
+    <mergeCell ref="S282:T282"/>
+    <mergeCell ref="U282:V282"/>
+    <mergeCell ref="B283:C283"/>
+    <mergeCell ref="E283:F283"/>
+    <mergeCell ref="P283:Q283"/>
+    <mergeCell ref="S283:T283"/>
+    <mergeCell ref="U283:V283"/>
+    <mergeCell ref="B284:C284"/>
+    <mergeCell ref="E284:F284"/>
+    <mergeCell ref="P284:Q284"/>
+    <mergeCell ref="S284:T284"/>
+    <mergeCell ref="U284:V284"/>
+    <mergeCell ref="B285:C285"/>
+    <mergeCell ref="E285:F285"/>
+    <mergeCell ref="P285:Q285"/>
+    <mergeCell ref="S285:T285"/>
+    <mergeCell ref="U285:V285"/>
+    <mergeCell ref="B286:C286"/>
+    <mergeCell ref="E286:F286"/>
+    <mergeCell ref="P286:Q286"/>
+    <mergeCell ref="S286:T286"/>
+    <mergeCell ref="U286:V286"/>
+    <mergeCell ref="B287:C287"/>
+    <mergeCell ref="E287:F287"/>
+    <mergeCell ref="P287:Q287"/>
+    <mergeCell ref="S287:T287"/>
+    <mergeCell ref="U287:V287"/>
+    <mergeCell ref="B288:C288"/>
+    <mergeCell ref="E288:F288"/>
+    <mergeCell ref="P288:Q288"/>
+    <mergeCell ref="S288:T288"/>
+    <mergeCell ref="U288:V288"/>
+    <mergeCell ref="B289:C289"/>
+    <mergeCell ref="E289:F289"/>
+    <mergeCell ref="P289:Q289"/>
+    <mergeCell ref="S289:T289"/>
+    <mergeCell ref="U289:V289"/>
+    <mergeCell ref="B290:C290"/>
+    <mergeCell ref="E290:F290"/>
+    <mergeCell ref="P290:Q290"/>
+    <mergeCell ref="S290:T290"/>
+    <mergeCell ref="U290:V290"/>
+    <mergeCell ref="B291:C291"/>
+    <mergeCell ref="E291:F291"/>
+    <mergeCell ref="P291:Q291"/>
+    <mergeCell ref="S291:T291"/>
+    <mergeCell ref="U291:V291"/>
+    <mergeCell ref="B292:C292"/>
+    <mergeCell ref="E292:F292"/>
+    <mergeCell ref="P292:Q292"/>
+    <mergeCell ref="S292:T292"/>
+    <mergeCell ref="U292:V292"/>
+    <mergeCell ref="B293:C293"/>
+    <mergeCell ref="E293:F293"/>
+    <mergeCell ref="P293:Q293"/>
+    <mergeCell ref="S293:T293"/>
+    <mergeCell ref="U293:V293"/>
+    <mergeCell ref="B294:C294"/>
+    <mergeCell ref="E294:F294"/>
+    <mergeCell ref="P294:Q294"/>
+    <mergeCell ref="S294:T294"/>
+    <mergeCell ref="U294:V294"/>
+    <mergeCell ref="B295:C295"/>
+    <mergeCell ref="E295:F295"/>
+    <mergeCell ref="P295:Q295"/>
+    <mergeCell ref="S295:T295"/>
+    <mergeCell ref="U295:V295"/>
+    <mergeCell ref="B296:C296"/>
+    <mergeCell ref="E296:F296"/>
+    <mergeCell ref="P296:Q296"/>
+    <mergeCell ref="S296:T296"/>
+    <mergeCell ref="U296:V296"/>
+    <mergeCell ref="B297:C297"/>
+    <mergeCell ref="E297:F297"/>
+    <mergeCell ref="P297:Q297"/>
+    <mergeCell ref="S297:T297"/>
+    <mergeCell ref="U297:V297"/>
+    <mergeCell ref="B298:C298"/>
+    <mergeCell ref="E298:F298"/>
+    <mergeCell ref="P298:Q298"/>
+    <mergeCell ref="S298:T298"/>
+    <mergeCell ref="U298:V298"/>
+    <mergeCell ref="B299:C299"/>
+    <mergeCell ref="E299:F299"/>
+    <mergeCell ref="P299:Q299"/>
+    <mergeCell ref="S299:T299"/>
+    <mergeCell ref="U299:V299"/>
   </mergeCells>
   <pageMargins left="0.0393700787401575" right="0.0393700787401575" top="0.0393700787401575" bottom="0.0393700787401575" header="0.0393700787401575" footer="0.0393700787401575"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>

--- a/Base_Interrupcoes.xlsx
+++ b/Base_Interrupcoes.xlsx
@@ -466,7 +466,7 @@
       <c s="4" t="str" r="A7"/>
       <c s="7" t="inlineStr" r="T7">
         <is>
-          <t xml:space="preserve">Emissão: 09/10/2026</t>
+          <t xml:space="preserve">Emissão: 13/10/2026</t>
         </is>
       </c>
       <c s="5" t="str" r="V7"/>
@@ -475,7 +475,7 @@
       <c s="4" t="str" r="A8"/>
       <c s="8" t="inlineStr" r="F8">
         <is>
-          <t xml:space="preserve">Período: 01/10/2026 até 08/10/2026; Turno: Todos; Tempo: Calendário</t>
+          <t xml:space="preserve">Período: 01/10/2026 até 12/10/2026; Turno: Todos; Tempo: Calendário</t>
         </is>
       </c>
       <c s="5" t="str" r="V8"/>
@@ -2838,10 +2838,14 @@
     <row r="48" ht="15.55" customHeight="0">
       <c s="19" t="inlineStr" r="A48">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 02</t>
-        </is>
-      </c>
-      <c s="20" t="str" r="B48"/>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B48">
+        <is>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
       <c s="21" t="inlineStr" r="D48">
         <is>
           <t xml:space="preserve">TURNO B</t>
@@ -2877,21 +2881,25 @@
       <c s="20" t="str" r="M48"/>
       <c s="20" t="inlineStr" r="N48">
         <is>
-          <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
+          <t xml:space="preserve">FALTA DEMANDA</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="O48">
         <is>
-          <t xml:space="preserve">Parada registrada automaticamente pelo sistema</t>
+          <t xml:space="preserve">falta de demanda</t>
         </is>
       </c>
       <c s="20" t="str" r="P48"/>
       <c s="20" t="inlineStr" r="R48">
         <is>
-          <t xml:space="preserve">49cef330-bdd1-11f1-8f07-f2050a003223</t>
-        </is>
-      </c>
-      <c s="20" t="str" r="S48"/>
+          <t xml:space="preserve">4a25c5c0-bdd1-11f1-86c2-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S48">
+        <is>
+          <t xml:space="preserve">10046135    </t>
+        </is>
+      </c>
       <c s="20" t="inlineStr" r="U48">
         <is>
           <t xml:space="preserve">Sim</t>
@@ -2902,7 +2910,7 @@
     <row r="49" ht="15.6" customHeight="0">
       <c s="15" t="inlineStr" r="A49">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 03</t>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
         </is>
       </c>
       <c s="16" t="str" r="B49"/>
@@ -2952,7 +2960,7 @@
       <c s="16" t="str" r="P49"/>
       <c s="16" t="inlineStr" r="R49">
         <is>
-          <t xml:space="preserve">49efe8b0-bdd1-11f1-cb5a-f2050a003223</t>
+          <t xml:space="preserve">49cef330-bdd1-11f1-8f07-f2050a003223</t>
         </is>
       </c>
       <c s="16" t="str" r="S49"/>
@@ -2966,14 +2974,10 @@
     <row r="50" ht="15.6" customHeight="0">
       <c s="19" t="inlineStr" r="A50">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 05</t>
-        </is>
-      </c>
-      <c s="20" t="inlineStr" r="B50">
-        <is>
-          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
-        </is>
-      </c>
+          <t xml:space="preserve">TRANSVERSAL 03</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B50"/>
       <c s="21" t="inlineStr" r="D50">
         <is>
           <t xml:space="preserve">TURNO B</t>
@@ -3009,25 +3013,21 @@
       <c s="20" t="str" r="M50"/>
       <c s="20" t="inlineStr" r="N50">
         <is>
-          <t xml:space="preserve">FALTA DEMANDA</t>
+          <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="O50">
         <is>
-          <t xml:space="preserve">falta de demanda</t>
+          <t xml:space="preserve">Parada registrada automaticamente pelo sistema</t>
         </is>
       </c>
       <c s="20" t="str" r="P50"/>
       <c s="20" t="inlineStr" r="R50">
         <is>
-          <t xml:space="preserve">4a25c5c0-bdd1-11f1-86c2-f2050a003223</t>
-        </is>
-      </c>
-      <c s="20" t="inlineStr" r="S50">
-        <is>
-          <t xml:space="preserve">10046135    </t>
-        </is>
-      </c>
+          <t xml:space="preserve">49efe8b0-bdd1-11f1-cb5a-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="S50"/>
       <c s="20" t="inlineStr" r="U50">
         <is>
           <t xml:space="preserve">Sim</t>
@@ -3110,12 +3110,12 @@
     <row r="52" ht="15.6" customHeight="0">
       <c s="19" t="inlineStr" r="A52">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 04</t>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="B52">
         <is>
-          <t xml:space="preserve">TR04-DESENROLADOR</t>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
         </is>
       </c>
       <c s="21" t="inlineStr" r="D52">
@@ -3127,11 +3127,11 @@
         <v>46297.2916666667</v>
       </c>
       <c s="22" r="G52">
-        <v>46297.2986111111</v>
+        <v>46297.3020833333</v>
       </c>
       <c s="21" t="inlineStr" r="H52">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c s="21" t="str" r="I52"/>
@@ -3158,18 +3158,18 @@
       </c>
       <c s="20" t="inlineStr" r="O52">
         <is>
-          <t xml:space="preserve">DDS</t>
+          <t xml:space="preserve">dds e assinatura dos documentos</t>
         </is>
       </c>
       <c s="20" t="str" r="P52"/>
       <c s="20" t="inlineStr" r="R52">
         <is>
-          <t xml:space="preserve">942e4bd0-be4c-11f1-ca85-f2050a003223</t>
+          <t xml:space="preserve">61a3b7a0-be4b-11f1-9cbf-f2050a003223</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="S52">
         <is>
-          <t xml:space="preserve">10047019    </t>
+          <t xml:space="preserve">10046873    </t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="U52">
@@ -3182,12 +3182,12 @@
     <row r="53" ht="15.55" customHeight="0">
       <c s="15" t="inlineStr" r="A53">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 05</t>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="B53">
         <is>
-          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
         </is>
       </c>
       <c s="17" t="inlineStr" r="D53">
@@ -3199,11 +3199,11 @@
         <v>46297.2916666667</v>
       </c>
       <c s="18" r="G53">
-        <v>46297.3055555556</v>
+        <v>46297.2986111111</v>
       </c>
       <c s="17" t="inlineStr" r="H53">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c s="17" t="str" r="I53"/>
@@ -3230,18 +3230,18 @@
       </c>
       <c s="16" t="inlineStr" r="O53">
         <is>
-          <t xml:space="preserve">dds com supervisor QUEDA DE MATERIAIS</t>
+          <t xml:space="preserve">DDS</t>
         </is>
       </c>
       <c s="16" t="str" r="P53"/>
       <c s="16" t="inlineStr" r="R53">
         <is>
-          <t xml:space="preserve">167ccc00-be4e-11f1-cdcf-f2050a003223</t>
+          <t xml:space="preserve">942e4bd0-be4c-11f1-ca85-f2050a003223</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="S53">
         <is>
-          <t xml:space="preserve">10046135    </t>
+          <t xml:space="preserve">10047019    </t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="U53">
@@ -3254,12 +3254,12 @@
     <row r="54" ht="15.6" customHeight="0">
       <c s="19" t="inlineStr" r="A54">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 01</t>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="B54">
         <is>
-          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
         </is>
       </c>
       <c s="21" t="inlineStr" r="D54">
@@ -3271,11 +3271,11 @@
         <v>46297.2916666667</v>
       </c>
       <c s="22" r="G54">
-        <v>46297.3020833333</v>
+        <v>46297.3055555556</v>
       </c>
       <c s="21" t="inlineStr" r="H54">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c s="21" t="str" r="I54"/>
@@ -3302,18 +3302,18 @@
       </c>
       <c s="20" t="inlineStr" r="O54">
         <is>
-          <t xml:space="preserve">dds e assinatura dos documentos</t>
+          <t xml:space="preserve">dds com supervisor QUEDA DE MATERIAIS</t>
         </is>
       </c>
       <c s="20" t="str" r="P54"/>
       <c s="20" t="inlineStr" r="R54">
         <is>
-          <t xml:space="preserve">61a3b7a0-be4b-11f1-9cbf-f2050a003223</t>
+          <t xml:space="preserve">167ccc00-be4e-11f1-cdcf-f2050a003223</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="S54">
         <is>
-          <t xml:space="preserve">10046873    </t>
+          <t xml:space="preserve">10046135    </t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="U54">
@@ -10319,10 +10319,14 @@
     <row r="153" ht="15.6" customHeight="0">
       <c s="15" t="inlineStr" r="A153">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 03</t>
-        </is>
-      </c>
-      <c s="16" t="str" r="B153"/>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B153">
+        <is>
+          <t xml:space="preserve">TR04-CARRO DE ENTRADA</t>
+        </is>
+      </c>
       <c s="17" t="inlineStr" r="D153">
         <is>
           <t xml:space="preserve">TURNO B</t>
@@ -10358,7 +10362,7 @@
       <c s="16" t="str" r="M153"/>
       <c s="16" t="inlineStr" r="N153">
         <is>
-          <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
+          <t xml:space="preserve">FALTA DEMANDA</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="O153">
@@ -10369,10 +10373,14 @@
       <c s="16" t="str" r="P153"/>
       <c s="16" t="inlineStr" r="R153">
         <is>
-          <t xml:space="preserve">f4dfe370-c0f5-11f1-c191-f2050a003223</t>
-        </is>
-      </c>
-      <c s="16" t="str" r="S153"/>
+          <t xml:space="preserve">f4fe8f00-c0f5-11f1-ad1e-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S153">
+        <is>
+          <t xml:space="preserve">10048032    </t>
+        </is>
+      </c>
       <c s="16" t="inlineStr" r="U153">
         <is>
           <t xml:space="preserve">Sim</t>
@@ -10383,14 +10391,10 @@
     <row r="154" ht="15.55" customHeight="0">
       <c s="19" t="inlineStr" r="A154">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 04</t>
-        </is>
-      </c>
-      <c s="20" t="inlineStr" r="B154">
-        <is>
-          <t xml:space="preserve">TR04-CARRO DE ENTRADA</t>
-        </is>
-      </c>
+          <t xml:space="preserve">TRANSVERSAL 03</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B154"/>
       <c s="21" t="inlineStr" r="D154">
         <is>
           <t xml:space="preserve">TURNO B</t>
@@ -10426,7 +10430,7 @@
       <c s="20" t="str" r="M154"/>
       <c s="20" t="inlineStr" r="N154">
         <is>
-          <t xml:space="preserve">FALTA DEMANDA</t>
+          <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="O154">
@@ -10437,14 +10441,10 @@
       <c s="20" t="str" r="P154"/>
       <c s="20" t="inlineStr" r="R154">
         <is>
-          <t xml:space="preserve">f4fe8f00-c0f5-11f1-ad1e-f2050a003223</t>
-        </is>
-      </c>
-      <c s="20" t="inlineStr" r="S154">
-        <is>
-          <t xml:space="preserve">10048032    </t>
-        </is>
-      </c>
+          <t xml:space="preserve">f4dfe370-c0f5-11f1-c191-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="S154"/>
       <c s="20" t="inlineStr" r="U154">
         <is>
           <t xml:space="preserve">Sim</t>
@@ -10599,12 +10599,12 @@
     <row r="157" ht="15.55" customHeight="0">
       <c s="15" t="inlineStr" r="A157">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 04</t>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="B157">
         <is>
-          <t xml:space="preserve">TR04-DESENROLADOR</t>
+          <t xml:space="preserve">TR01-MESA TRANSPORTADORA</t>
         </is>
       </c>
       <c s="17" t="inlineStr" r="D157">
@@ -10616,11 +10616,11 @@
         <v>46301.2916666667</v>
       </c>
       <c s="18" r="G157">
-        <v>46301.2986111111</v>
+        <v>46301.3020833333</v>
       </c>
       <c s="17" t="inlineStr" r="H157">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c s="17" t="str" r="I157"/>
@@ -10647,18 +10647,18 @@
       </c>
       <c s="16" t="inlineStr" r="O157">
         <is>
-          <t xml:space="preserve">DDS</t>
+          <t xml:space="preserve">dds  e assinatura dos documentos</t>
         </is>
       </c>
       <c s="16" t="str" r="P157"/>
       <c s="16" t="inlineStr" r="R157">
         <is>
-          <t xml:space="preserve">00542e40-c174-11f1-b395-f2050a003223</t>
+          <t xml:space="preserve">fa2e6070-c16f-11f1-a1bf-f2050a003223</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="S157">
         <is>
-          <t xml:space="preserve">10048032    </t>
+          <t xml:space="preserve">10047271    </t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="U157">
@@ -10671,12 +10671,12 @@
     <row r="158" ht="15.6" customHeight="0">
       <c s="19" t="inlineStr" r="A158">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 01</t>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="B158">
         <is>
-          <t xml:space="preserve">TR01-MESA TRANSPORTADORA</t>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
         </is>
       </c>
       <c s="21" t="inlineStr" r="D158">
@@ -10688,11 +10688,11 @@
         <v>46301.2916666667</v>
       </c>
       <c s="22" r="G158">
-        <v>46301.3020833333</v>
+        <v>46301.3055555556</v>
       </c>
       <c s="21" t="inlineStr" r="H158">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c s="21" t="str" r="I158"/>
@@ -10719,18 +10719,18 @@
       </c>
       <c s="20" t="inlineStr" r="O158">
         <is>
-          <t xml:space="preserve">dds  e assinatura dos documentos</t>
+          <t xml:space="preserve">dds</t>
         </is>
       </c>
       <c s="20" t="str" r="P158"/>
       <c s="20" t="inlineStr" r="R158">
         <is>
-          <t xml:space="preserve">fa2e6070-c16f-11f1-a1bf-f2050a003223</t>
+          <t xml:space="preserve">4ed80b10-c172-11f1-84a1-f2050a003223</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="S158">
         <is>
-          <t xml:space="preserve">10047271    </t>
+          <t xml:space="preserve">10046766    </t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="U158">
@@ -10743,12 +10743,12 @@
     <row r="159" ht="15.55" customHeight="0">
       <c s="15" t="inlineStr" r="A159">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 05</t>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="B159">
         <is>
-          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
         </is>
       </c>
       <c s="17" t="inlineStr" r="D159">
@@ -10760,11 +10760,11 @@
         <v>46301.2916666667</v>
       </c>
       <c s="18" r="G159">
-        <v>46301.3055555556</v>
+        <v>46301.2986111111</v>
       </c>
       <c s="17" t="inlineStr" r="H159">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c s="17" t="str" r="I159"/>
@@ -10791,18 +10791,18 @@
       </c>
       <c s="16" t="inlineStr" r="O159">
         <is>
-          <t xml:space="preserve">dds</t>
+          <t xml:space="preserve">DDS</t>
         </is>
       </c>
       <c s="16" t="str" r="P159"/>
       <c s="16" t="inlineStr" r="R159">
         <is>
-          <t xml:space="preserve">4ed80b10-c172-11f1-84a1-f2050a003223</t>
+          <t xml:space="preserve">00542e40-c174-11f1-b395-f2050a003223</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="S159">
         <is>
-          <t xml:space="preserve">10046766    </t>
+          <t xml:space="preserve">10048032    </t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="U159">
@@ -15515,12 +15515,12 @@
     <row r="226" ht="15.55" customHeight="0">
       <c s="19" t="inlineStr" r="A226">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 02</t>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="B226">
         <is>
-          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
+          <t xml:space="preserve">TR01-MESA TRANSPORTADORA</t>
         </is>
       </c>
       <c s="21" t="inlineStr" r="D226">
@@ -15532,11 +15532,11 @@
         <v>46302.2916666667</v>
       </c>
       <c s="22" r="G226">
-        <v>46302.2986111111</v>
+        <v>46302.3020833333</v>
       </c>
       <c s="21" t="inlineStr" r="H226">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c s="21" t="str" r="I226"/>
@@ -15563,18 +15563,18 @@
       </c>
       <c s="20" t="inlineStr" r="O226">
         <is>
-          <t xml:space="preserve">DDS</t>
+          <t xml:space="preserve">dds e assinatura dos documentos</t>
         </is>
       </c>
       <c s="20" t="str" r="P226"/>
       <c s="20" t="inlineStr" r="R226">
         <is>
-          <t xml:space="preserve">c3a92550-c23a-11f1-b331-f2050a003223</t>
+          <t xml:space="preserve">e92b60c0-c237-11f1-ab7f-f2050a003223</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="S226">
         <is>
-          <t xml:space="preserve">10048227    </t>
+          <t xml:space="preserve">10048039    </t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="U226">
@@ -15587,12 +15587,12 @@
     <row r="227" ht="15.6" customHeight="0">
       <c s="15" t="inlineStr" r="A227">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 01</t>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="B227">
         <is>
-          <t xml:space="preserve">TR01-MESA TRANSPORTADORA</t>
+          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
         </is>
       </c>
       <c s="17" t="inlineStr" r="D227">
@@ -15604,11 +15604,11 @@
         <v>46302.2916666667</v>
       </c>
       <c s="18" r="G227">
-        <v>46302.3020833333</v>
+        <v>46302.2986111111</v>
       </c>
       <c s="17" t="inlineStr" r="H227">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c s="17" t="str" r="I227"/>
@@ -15635,18 +15635,18 @@
       </c>
       <c s="16" t="inlineStr" r="O227">
         <is>
-          <t xml:space="preserve">dds e assinatura dos documentos</t>
+          <t xml:space="preserve">DDS</t>
         </is>
       </c>
       <c s="16" t="str" r="P227"/>
       <c s="16" t="inlineStr" r="R227">
         <is>
-          <t xml:space="preserve">e92b60c0-c237-11f1-ab7f-f2050a003223</t>
+          <t xml:space="preserve">c3a92550-c23a-11f1-b331-f2050a003223</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="S227">
         <is>
-          <t xml:space="preserve">10048039    </t>
+          <t xml:space="preserve">10048227    </t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="U227">
@@ -18551,12 +18551,12 @@
     <row r="269" ht="15.6" customHeight="0">
       <c s="15" t="inlineStr" r="A269">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 01</t>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="B269">
         <is>
-          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
         </is>
       </c>
       <c s="17" t="inlineStr" r="D269">
@@ -18568,11 +18568,11 @@
         <v>46303.2916666667</v>
       </c>
       <c s="18" r="G269">
-        <v>46303.3020833333</v>
+        <v>46303.2986111111</v>
       </c>
       <c s="17" t="inlineStr" r="H269">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c s="17" t="str" r="I269"/>
@@ -18599,18 +18599,18 @@
       </c>
       <c s="16" t="inlineStr" r="O269">
         <is>
-          <t xml:space="preserve">dds e assinatura dos documentos</t>
+          <t xml:space="preserve">DDS</t>
         </is>
       </c>
       <c s="16" t="str" r="P269"/>
       <c s="16" t="inlineStr" r="R269">
         <is>
-          <t xml:space="preserve">065f5d20-c302-11f1-8108-f2050a003223</t>
+          <t xml:space="preserve">6e8883a0-c301-11f1-9a54-f2050a003223</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="S269">
         <is>
-          <t xml:space="preserve">10048233    </t>
+          <t xml:space="preserve">10048465    </t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="U269">
@@ -18623,12 +18623,12 @@
     <row r="270" ht="15.6" customHeight="0">
       <c s="19" t="inlineStr" r="A270">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 02</t>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="B270">
         <is>
-          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
         </is>
       </c>
       <c s="21" t="inlineStr" r="D270">
@@ -18640,11 +18640,11 @@
         <v>46303.2916666667</v>
       </c>
       <c s="22" r="G270">
-        <v>46303.2986111111</v>
+        <v>46303.3020833333</v>
       </c>
       <c s="21" t="inlineStr" r="H270">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c s="21" t="str" r="I270"/>
@@ -18671,18 +18671,18 @@
       </c>
       <c s="20" t="inlineStr" r="O270">
         <is>
-          <t xml:space="preserve">DDS</t>
+          <t xml:space="preserve">dds e assinatura dos documentos</t>
         </is>
       </c>
       <c s="20" t="str" r="P270"/>
       <c s="20" t="inlineStr" r="R270">
         <is>
-          <t xml:space="preserve">6e8883a0-c301-11f1-9a54-f2050a003223</t>
+          <t xml:space="preserve">065f5d20-c302-11f1-8108-f2050a003223</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="S270">
         <is>
-          <t xml:space="preserve">10048465    </t>
+          <t xml:space="preserve">10048233    </t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="U270">
@@ -18780,11 +18780,11 @@
         <v>46303.3097222222</v>
       </c>
       <c s="22" r="G272">
-        <v>46304.4579892708</v>
+        <v>46303.3201388889</v>
       </c>
       <c s="21" t="inlineStr" r="H272">
         <is>
-          <t xml:space="preserve">1.654</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c s="21" t="str" r="I272"/>
@@ -18795,23 +18795,23 @@
       </c>
       <c s="20" t="inlineStr" r="K272">
         <is>
-          <t xml:space="preserve">Paradas Programadas</t>
+          <t xml:space="preserve">Operacional</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="L272">
         <is>
-          <t xml:space="preserve">Paradas Programadas</t>
+          <t xml:space="preserve">Operacional</t>
         </is>
       </c>
       <c s="20" t="str" r="M272"/>
       <c s="20" t="inlineStr" r="N272">
         <is>
-          <t xml:space="preserve">MANUTENÇÃO PREVENTIVA</t>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="O272">
         <is>
-          <t xml:space="preserve">manutenção preventiva</t>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
         </is>
       </c>
       <c s="20" t="str" r="P272"/>
@@ -20264,11 +20264,11 @@
         <v>46303.6541666667</v>
       </c>
       <c s="18" r="G293">
-        <v>46304.4579892708</v>
+        <v>46308.2950509606</v>
       </c>
       <c s="17" t="inlineStr" r="H293">
         <is>
-          <t xml:space="preserve">1.158</t>
+          <t xml:space="preserve">6.683</t>
         </is>
       </c>
       <c s="17" t="str" r="I293"/>
@@ -20664,83 +20664,1914 @@
       </c>
       <c s="5" t="str" r="V298"/>
     </row>
-    <row r="299" ht="15.55" customHeight="0">
-      <c s="23" t="inlineStr" r="A299">
+    <row r="299" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A299">
         <is>
           <t xml:space="preserve">TRANSVERSAL 01</t>
         </is>
       </c>
-      <c s="24" t="inlineStr" r="B299">
+      <c s="16" t="inlineStr" r="B299">
         <is>
           <t xml:space="preserve">TR01-MESA MÓVEL</t>
         </is>
       </c>
-      <c s="10" t="str" r="C299"/>
-      <c s="25" t="inlineStr" r="D299">
+      <c s="17" t="inlineStr" r="D299">
         <is>
           <t xml:space="preserve">TURNO B</t>
         </is>
       </c>
-      <c s="26" r="E299">
+      <c s="18" r="E299">
         <v>46303.70625</v>
       </c>
-      <c s="10" t="str" r="F299"/>
-      <c s="26" r="G299">
+      <c s="18" r="G299">
         <v>46304.2909722222</v>
       </c>
-      <c s="25" t="inlineStr" r="H299">
+      <c s="17" t="inlineStr" r="H299">
         <is>
           <t xml:space="preserve">842</t>
         </is>
       </c>
-      <c s="25" t="str" r="I299"/>
-      <c s="25" t="inlineStr" r="J299">
-        <is>
-          <t xml:space="preserve">X</t>
-        </is>
-      </c>
-      <c s="24" t="inlineStr" r="K299">
+      <c s="17" t="str" r="I299"/>
+      <c s="17" t="inlineStr" r="J299">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K299">
         <is>
           <t xml:space="preserve">Tempo Livre</t>
         </is>
       </c>
-      <c s="24" t="inlineStr" r="L299">
+      <c s="16" t="inlineStr" r="L299">
         <is>
           <t xml:space="preserve">Tempo Livre</t>
         </is>
       </c>
-      <c s="24" t="str" r="M299"/>
-      <c s="24" t="inlineStr" r="N299">
+      <c s="16" t="str" r="M299"/>
+      <c s="16" t="inlineStr" r="N299">
         <is>
           <t xml:space="preserve">FALTA DEMANDA</t>
         </is>
       </c>
-      <c s="24" t="inlineStr" r="O299">
+      <c s="16" t="inlineStr" r="O299">
         <is>
           <t xml:space="preserve">tempo livre</t>
         </is>
       </c>
-      <c s="24" t="str" r="P299"/>
-      <c s="10" t="str" r="Q299"/>
-      <c s="24" t="inlineStr" r="R299">
+      <c s="16" t="str" r="P299"/>
+      <c s="16" t="inlineStr" r="R299">
         <is>
           <t xml:space="preserve">c1e92c10-c3ca-11f1-ca8c-f2050a003223</t>
         </is>
       </c>
-      <c s="24" t="inlineStr" r="S299">
+      <c s="16" t="inlineStr" r="S299">
         <is>
           <t xml:space="preserve">10048417    </t>
         </is>
       </c>
-      <c s="10" t="str" r="T299"/>
-      <c s="24" t="inlineStr" r="U299">
-        <is>
-          <t xml:space="preserve">Sim</t>
-        </is>
-      </c>
-      <c s="11" t="str" r="V299"/>
-    </row>
-    <row r="300" ht="0.05" customHeight="1"/>
+      <c s="16" t="inlineStr" r="U299">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V299"/>
+    </row>
+    <row r="300" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A300">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B300">
+        <is>
+          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D300">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E300">
+        <v>46304.2916666667</v>
+      </c>
+      <c s="22" r="G300">
+        <v>46304.2986111111</v>
+      </c>
+      <c s="21" t="inlineStr" r="H300">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I300"/>
+      <c s="21" t="inlineStr" r="J300">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K300">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L300">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M300"/>
+      <c s="20" t="inlineStr" r="N300">
+        <is>
+          <t xml:space="preserve">DDS</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O300">
+        <is>
+          <t xml:space="preserve">DDS</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P300"/>
+      <c s="20" t="inlineStr" r="R300">
+        <is>
+          <t xml:space="preserve">8328c2a0-c3cb-11f1-c59b-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S300">
+        <is>
+          <t xml:space="preserve">10048738    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U300">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V300"/>
+    </row>
+    <row r="301" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A301">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B301">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D301">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E301">
+        <v>46304.2916666667</v>
+      </c>
+      <c s="18" r="G301">
+        <v>46304.3020833333</v>
+      </c>
+      <c s="17" t="inlineStr" r="H301">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I301"/>
+      <c s="17" t="inlineStr" r="J301">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K301">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L301">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M301"/>
+      <c s="16" t="inlineStr" r="N301">
+        <is>
+          <t xml:space="preserve">DDS</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O301">
+        <is>
+          <t xml:space="preserve">dds e assinatura dos documentos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P301"/>
+      <c s="16" t="inlineStr" r="R301">
+        <is>
+          <t xml:space="preserve">c7659750-c3ca-11f1-b424-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S301">
+        <is>
+          <t xml:space="preserve">10048417    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U301">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V301"/>
+    </row>
+    <row r="302" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A302">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B302">
+        <is>
+          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D302">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E302">
+        <v>46304.3152777778</v>
+      </c>
+      <c s="22" r="G302">
+        <v>46304.3305555556</v>
+      </c>
+      <c s="21" t="inlineStr" r="H302">
+        <is>
+          <t xml:space="preserve">22</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I302"/>
+      <c s="21" t="inlineStr" r="J302">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K302">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L302">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M302"/>
+      <c s="20" t="inlineStr" r="N302">
+        <is>
+          <t xml:space="preserve">QUALIDADE DA MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O302">
+        <is>
+          <t xml:space="preserve">Material 2.00mm 6000x1200 UD 5012312960 OP 10048738 está com quebra de superfície qualidade pediu pra cortar o material de 3000x1200 e apontar pnc.</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P302"/>
+      <c s="20" t="inlineStr" r="R302">
+        <is>
+          <t xml:space="preserve">024822f0-c3cd-11f1-8ed5-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S302">
+        <is>
+          <t xml:space="preserve">10048738    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U302">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V302"/>
+    </row>
+    <row r="303" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A303">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B303">
+        <is>
+          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D303">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E303">
+        <v>46304.3645833333</v>
+      </c>
+      <c s="18" r="G303">
+        <v>46308.2950509606</v>
+      </c>
+      <c s="17" t="inlineStr" r="H303">
+        <is>
+          <t xml:space="preserve">5.660</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I303"/>
+      <c s="17" t="inlineStr" r="J303">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K303">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L303">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M303"/>
+      <c s="16" t="inlineStr" r="N303">
+        <is>
+          <t xml:space="preserve">FALTA DEMANDA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O303">
+        <is>
+          <t xml:space="preserve">Falta demanda.</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P303"/>
+      <c s="16" t="inlineStr" r="R303">
+        <is>
+          <t xml:space="preserve">d26b48a0-c3d6-11f1-a941-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="S303"/>
+      <c s="16" t="inlineStr" r="U303">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V303"/>
+    </row>
+    <row r="304" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A304">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B304">
+        <is>
+          <t xml:space="preserve">TR01-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D304">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E304">
+        <v>46304.3916666667</v>
+      </c>
+      <c s="22" r="G304">
+        <v>46304.3923611111</v>
+      </c>
+      <c s="21" t="inlineStr" r="H304">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I304"/>
+      <c s="21" t="inlineStr" r="J304">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K304">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L304">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M304"/>
+      <c s="20" t="inlineStr" r="N304">
+        <is>
+          <t xml:space="preserve">QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O304">
+        <is>
+          <t xml:space="preserve">material com mancha na superfície material foi liberada com bom UD:2003643869</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P304"/>
+      <c s="20" t="inlineStr" r="R304">
+        <is>
+          <t xml:space="preserve">a0791fb0-c3dc-11f1-8c5e-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S304">
+        <is>
+          <t xml:space="preserve">10048418    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U304">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V304"/>
+    </row>
+    <row r="305" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A305">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B305">
+        <is>
+          <t xml:space="preserve">TR01-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D305">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E305">
+        <v>46304.4388888889</v>
+      </c>
+      <c s="18" r="G305">
+        <v>46304.4458333333</v>
+      </c>
+      <c s="17" t="inlineStr" r="H305">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I305"/>
+      <c s="17" t="inlineStr" r="J305">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K305">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L305">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M305"/>
+      <c s="16" t="inlineStr" r="N305">
+        <is>
+          <t xml:space="preserve">TROCA DAS CASTANHAS DO MANDRIL</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O305">
+        <is>
+          <t xml:space="preserve">troca das castanhas</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P305"/>
+      <c s="16" t="inlineStr" r="R305">
+        <is>
+          <t xml:space="preserve">d0e79100-c3e5-11f1-a44c-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S305">
+        <is>
+          <t xml:space="preserve">10048418    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U305">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V305"/>
+    </row>
+    <row r="306" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A306">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B306">
+        <is>
+          <t xml:space="preserve">TR01-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D306">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E306">
+        <v>46304.4583333333</v>
+      </c>
+      <c s="22" r="G306">
+        <v>46304.5</v>
+      </c>
+      <c s="21" t="inlineStr" r="H306">
+        <is>
+          <t xml:space="preserve">60</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I306"/>
+      <c s="21" t="inlineStr" r="J306">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K306">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L306">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M306"/>
+      <c s="20" t="inlineStr" r="N306">
+        <is>
+          <t xml:space="preserve">ALMOÇO / JANTA / CEIA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O306">
+        <is>
+          <t xml:space="preserve">almoço</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P306"/>
+      <c s="20" t="inlineStr" r="R306">
+        <is>
+          <t xml:space="preserve">66cb8c70-c3ec-11f1-a704-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S306">
+        <is>
+          <t xml:space="preserve">10048939    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U306">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V306"/>
+    </row>
+    <row r="307" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A307">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B307">
+        <is>
+          <t xml:space="preserve">TR01-GUILHOTINA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D307">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E307">
+        <v>46304.5006944444</v>
+      </c>
+      <c s="18" r="G307">
+        <v>46304.5194444444</v>
+      </c>
+      <c s="17" t="inlineStr" r="H307">
+        <is>
+          <t xml:space="preserve">27</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I307"/>
+      <c s="17" t="inlineStr" r="J307">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K307">
+        <is>
+          <t xml:space="preserve">Manutenção Corretiva Mecânica</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L307">
+        <is>
+          <t xml:space="preserve">Manutenção Corretiva Mecânica</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M307"/>
+      <c s="16" t="inlineStr" r="N307">
+        <is>
+          <t xml:space="preserve">BAIXA PRESSÃO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O307">
+        <is>
+          <t xml:space="preserve">guilhotina travando</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="P307">
+        <is>
+          <t xml:space="preserve">000010034844</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="R307">
+        <is>
+          <t xml:space="preserve">c8d302d0-c3f2-11f1-9142-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S307">
+        <is>
+          <t xml:space="preserve">10048939    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U307">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V307"/>
+    </row>
+    <row r="308" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A308">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B308"/>
+      <c s="21" t="inlineStr" r="D308">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E308">
+        <v>46304.5381944444</v>
+      </c>
+      <c s="22" r="G308">
+        <v>46304.5416666667</v>
+      </c>
+      <c s="21" t="inlineStr" r="H308">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I308"/>
+      <c s="21" t="inlineStr" r="J308">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K308">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L308">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M308"/>
+      <c s="20" t="inlineStr" r="N308">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O308">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 5 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P308"/>
+      <c s="20" t="inlineStr" r="R308">
+        <is>
+          <t xml:space="preserve">e45ab960-c3f9-11f1-b9a0-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S308">
+        <is>
+          <t xml:space="preserve">10048939    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U308">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V308"/>
+    </row>
+    <row r="309" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A309">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B309"/>
+      <c s="17" t="inlineStr" r="D309">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E309">
+        <v>46304.5416666667</v>
+      </c>
+      <c s="18" r="G309">
+        <v>46304.5472222222</v>
+      </c>
+      <c s="17" t="inlineStr" r="H309">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I309"/>
+      <c s="17" t="inlineStr" r="J309">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K309">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L309">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M309"/>
+      <c s="16" t="inlineStr" r="N309">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O309">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 8 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P309"/>
+      <c s="16" t="inlineStr" r="R309">
+        <is>
+          <t xml:space="preserve">9979e960-c3fa-11f1-af2c-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S309">
+        <is>
+          <t xml:space="preserve">10048939    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U309">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V309"/>
+    </row>
+    <row r="310" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A310">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B310">
+        <is>
+          <t xml:space="preserve">TR01-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D310">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E310">
+        <v>46304.5493055556</v>
+      </c>
+      <c s="22" r="G310">
+        <v>46304.5520833333</v>
+      </c>
+      <c s="21" t="inlineStr" r="H310">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I310"/>
+      <c s="21" t="inlineStr" r="J310">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K310">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L310">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M310"/>
+      <c s="20" t="inlineStr" r="N310">
+        <is>
+          <t xml:space="preserve">MEP - ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O310">
+        <is>
+          <t xml:space="preserve">abastecimento</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P310"/>
+      <c s="20" t="inlineStr" r="R310">
+        <is>
+          <t xml:space="preserve">a8a2c310-c3fc-11f1-cf6d-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S310">
+        <is>
+          <t xml:space="preserve">10048939    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U310">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V310"/>
+    </row>
+    <row r="311" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A311">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B311"/>
+      <c s="17" t="inlineStr" r="D311">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E311">
+        <v>46304.5798611111</v>
+      </c>
+      <c s="18" r="G311">
+        <v>46304.5875</v>
+      </c>
+      <c s="17" t="inlineStr" r="H311">
+        <is>
+          <t xml:space="preserve">11</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I311"/>
+      <c s="17" t="inlineStr" r="J311">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K311">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L311">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M311"/>
+      <c s="16" t="inlineStr" r="N311">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O311">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 11 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P311"/>
+      <c s="16" t="inlineStr" r="R311">
+        <is>
+          <t xml:space="preserve">37617ab0-c402-11f1-a7b1-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S311">
+        <is>
+          <t xml:space="preserve">10048941    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U311">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V311"/>
+    </row>
+    <row r="312" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A312">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B312">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D312">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E312">
+        <v>46304.5916666667</v>
+      </c>
+      <c s="22" r="G312">
+        <v>46304.5951388889</v>
+      </c>
+      <c s="21" t="inlineStr" r="H312">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I312"/>
+      <c s="21" t="inlineStr" r="J312">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K312">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L312">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M312"/>
+      <c s="20" t="inlineStr" r="N312">
+        <is>
+          <t xml:space="preserve">AJUSTE DA MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O312">
+        <is>
+          <t xml:space="preserve">ajuste da mesa pra tamanho de chapa</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P312"/>
+      <c s="20" t="inlineStr" r="R312">
+        <is>
+          <t xml:space="preserve">a3e56870-c404-11f1-bf29-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S312">
+        <is>
+          <t xml:space="preserve">10048954    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U312">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V312"/>
+    </row>
+    <row r="313" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A313">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B313">
+        <is>
+          <t xml:space="preserve">TR01-MESA TRANSPORTADORA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D313">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E313">
+        <v>46304.6097222222</v>
+      </c>
+      <c s="18" r="G313">
+        <v>46304.6118055556</v>
+      </c>
+      <c s="17" t="inlineStr" r="H313">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I313"/>
+      <c s="17" t="inlineStr" r="J313">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K313">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L313">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M313"/>
+      <c s="16" t="inlineStr" r="N313">
+        <is>
+          <t xml:space="preserve">PESAGEM DE FARDO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O313">
+        <is>
+          <t xml:space="preserve">esperando op de ponte</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P313"/>
+      <c s="16" t="inlineStr" r="R313">
+        <is>
+          <t xml:space="preserve">331395a0-c408-11f1-9a76-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S313">
+        <is>
+          <t xml:space="preserve">10048954    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U313">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V313"/>
+    </row>
+    <row r="314" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A314">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B314"/>
+      <c s="21" t="inlineStr" r="D314">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E314">
+        <v>46304.6125</v>
+      </c>
+      <c s="22" r="G314">
+        <v>46304.61875</v>
+      </c>
+      <c s="21" t="inlineStr" r="H314">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I314"/>
+      <c s="21" t="inlineStr" r="J314">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K314">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L314">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M314"/>
+      <c s="20" t="inlineStr" r="N314">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O314">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 9 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P314"/>
+      <c s="20" t="inlineStr" r="R314">
+        <is>
+          <t xml:space="preserve">c3036c80-c408-11f1-c0c6-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S314">
+        <is>
+          <t xml:space="preserve">10048954    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U314">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V314"/>
+    </row>
+    <row r="315" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A315">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B315">
+        <is>
+          <t xml:space="preserve">TR01-MESA TRANSPORTADORA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D315">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E315">
+        <v>46304.6368055556</v>
+      </c>
+      <c s="18" r="G315">
+        <v>46304.6395833333</v>
+      </c>
+      <c s="17" t="inlineStr" r="H315">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I315"/>
+      <c s="17" t="inlineStr" r="J315">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K315">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L315">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M315"/>
+      <c s="16" t="inlineStr" r="N315">
+        <is>
+          <t xml:space="preserve">PESAGEM DE FARDO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O315">
+        <is>
+          <t xml:space="preserve">esperando op: de ponte retira material</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P315"/>
+      <c s="16" t="inlineStr" r="R315">
+        <is>
+          <t xml:space="preserve">be86a4b0-c40d-11f1-a8db-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S315">
+        <is>
+          <t xml:space="preserve">10048954    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U315">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V315"/>
+    </row>
+    <row r="316" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A316">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B316"/>
+      <c s="21" t="inlineStr" r="D316">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E316">
+        <v>46304.6416666667</v>
+      </c>
+      <c s="22" r="G316">
+        <v>46304.6479166667</v>
+      </c>
+      <c s="21" t="inlineStr" r="H316">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I316"/>
+      <c s="21" t="inlineStr" r="J316">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K316">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L316">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M316"/>
+      <c s="20" t="inlineStr" r="N316">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O316">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 9 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P316"/>
+      <c s="20" t="inlineStr" r="R316">
+        <is>
+          <t xml:space="preserve">9a754940-c40e-11f1-8680-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S316">
+        <is>
+          <t xml:space="preserve">10048954    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U316">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V316"/>
+    </row>
+    <row r="317" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A317">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B317">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D317">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E317">
+        <v>46304.6486111111</v>
+      </c>
+      <c s="18" r="G317">
+        <v>46304.6506944444</v>
+      </c>
+      <c s="17" t="inlineStr" r="H317">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I317"/>
+      <c s="17" t="inlineStr" r="J317">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K317">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L317">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M317"/>
+      <c s="16" t="inlineStr" r="N317">
+        <is>
+          <t xml:space="preserve">AJUSTE DA MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O317">
+        <is>
+          <t xml:space="preserve">ajuste da mesa pra tamanho de chapa</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P317"/>
+      <c s="16" t="inlineStr" r="R317">
+        <is>
+          <t xml:space="preserve">1cbe7240-c410-11f1-9d69-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S317">
+        <is>
+          <t xml:space="preserve">10048954    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U317">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V317"/>
+    </row>
+    <row r="318" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A318">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B318">
+        <is>
+          <t xml:space="preserve">TR01-MESA FIXA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D318">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E318">
+        <v>46304.6597222222</v>
+      </c>
+      <c s="22" r="G318">
+        <v>46304.6645833333</v>
+      </c>
+      <c s="21" t="inlineStr" r="H318">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I318"/>
+      <c s="21" t="inlineStr" r="J318">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K318">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L318">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M318"/>
+      <c s="20" t="inlineStr" r="N318">
+        <is>
+          <t xml:space="preserve">PESAGEM DE FARDO</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O318">
+        <is>
+          <t xml:space="preserve">esperando op:de ponte retiras material</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P318"/>
+      <c s="20" t="inlineStr" r="R318">
+        <is>
+          <t xml:space="preserve">3e945540-c412-11f1-903d-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S318">
+        <is>
+          <t xml:space="preserve">10048955    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U318">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V318"/>
+    </row>
+    <row r="319" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A319">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B319">
+        <is>
+          <t xml:space="preserve">TR01-MESA FIXA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D319">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E319">
+        <v>46304.6680555556</v>
+      </c>
+      <c s="18" r="G319">
+        <v>46304.6701388889</v>
+      </c>
+      <c s="17" t="inlineStr" r="H319">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I319"/>
+      <c s="17" t="inlineStr" r="J319">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K319">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L319">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M319"/>
+      <c s="16" t="inlineStr" r="N319">
+        <is>
+          <t xml:space="preserve">PESAGEM DE FARDO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O319">
+        <is>
+          <t xml:space="preserve">aguardando op:de ponte retira material</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P319"/>
+      <c s="16" t="inlineStr" r="R319">
+        <is>
+          <t xml:space="preserve">051be420-c414-11f1-920b-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S319">
+        <is>
+          <t xml:space="preserve">10048955    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U319">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V319"/>
+    </row>
+    <row r="320" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A320">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B320"/>
+      <c s="21" t="inlineStr" r="D320">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E320">
+        <v>46304.6729166667</v>
+      </c>
+      <c s="22" r="G320">
+        <v>46304.6798611111</v>
+      </c>
+      <c s="21" t="inlineStr" r="H320">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I320"/>
+      <c s="21" t="inlineStr" r="J320">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K320">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L320">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M320"/>
+      <c s="20" t="inlineStr" r="N320">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O320">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 10 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P320"/>
+      <c s="20" t="inlineStr" r="R320">
+        <is>
+          <t xml:space="preserve">e8ebbef0-c414-11f1-8590-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S320">
+        <is>
+          <t xml:space="preserve">10048955    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U320">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V320"/>
+    </row>
+    <row r="321" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A321">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B321">
+        <is>
+          <t xml:space="preserve">TR01-MESA TRANSPORTADORA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D321">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E321">
+        <v>46304.6805555556</v>
+      </c>
+      <c s="18" r="G321">
+        <v>46304.6854166667</v>
+      </c>
+      <c s="17" t="inlineStr" r="H321">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I321"/>
+      <c s="17" t="inlineStr" r="J321">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K321">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L321">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M321"/>
+      <c s="16" t="inlineStr" r="N321">
+        <is>
+          <t xml:space="preserve">AGUARDANDO INSPEÇÃO DE  QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O321">
+        <is>
+          <t xml:space="preserve">material com oxidação galvânica UD:2003908530</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P321"/>
+      <c s="16" t="inlineStr" r="R321">
+        <is>
+          <t xml:space="preserve">73f35ed0-c416-11f1-a9e4-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S321">
+        <is>
+          <t xml:space="preserve">10048955    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U321">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V321"/>
+    </row>
+    <row r="322" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A322">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B322">
+        <is>
+          <t xml:space="preserve">TR01-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D322">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E322">
+        <v>46304.6944444444</v>
+      </c>
+      <c s="22" r="G322">
+        <v>46308.2950509606</v>
+      </c>
+      <c s="21" t="inlineStr" r="H322">
+        <is>
+          <t xml:space="preserve">5.185</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I322"/>
+      <c s="21" t="inlineStr" r="J322">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K322">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L322">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M322"/>
+      <c s="20" t="inlineStr" r="N322">
+        <is>
+          <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O322">
+        <is>
+          <t xml:space="preserve">tempo livre</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P322"/>
+      <c s="20" t="inlineStr" r="R322">
+        <is>
+          <t xml:space="preserve">4f1ad0e1-c419-11f1-86aa-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S322">
+        <is>
+          <t xml:space="preserve">10048955    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U322">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V322"/>
+    </row>
+    <row r="323" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A323">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B323">
+        <is>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D323">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E323">
+        <v>46304.6958333333</v>
+      </c>
+      <c s="18" r="G323">
+        <v>46308.2950509606</v>
+      </c>
+      <c s="17" t="inlineStr" r="H323">
+        <is>
+          <t xml:space="preserve">5.183</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I323"/>
+      <c s="17" t="inlineStr" r="J323">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K323">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L323">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M323"/>
+      <c s="16" t="inlineStr" r="N323">
+        <is>
+          <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O323">
+        <is>
+          <t xml:space="preserve">espera fim de semana</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P323"/>
+      <c s="16" t="inlineStr" r="R323">
+        <is>
+          <t xml:space="preserve">22153e00-c419-11f1-9944-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S323">
+        <is>
+          <t xml:space="preserve">10048445    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U323">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V323"/>
+    </row>
+    <row r="324" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A324">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 03</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B324"/>
+      <c s="21" t="inlineStr" r="D324">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E324">
+        <v>46304.7013888889</v>
+      </c>
+      <c s="22" r="G324">
+        <v>46307.2840277778</v>
+      </c>
+      <c s="21" t="inlineStr" r="H324">
+        <is>
+          <t xml:space="preserve">3.719</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I324"/>
+      <c s="21" t="inlineStr" r="J324">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K324">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L324">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M324"/>
+      <c s="20" t="inlineStr" r="N324">
+        <is>
+          <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O324">
+        <is>
+          <t xml:space="preserve">Parada registrada automaticamente pelo sistema</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P324"/>
+      <c s="20" t="inlineStr" r="R324">
+        <is>
+          <t xml:space="preserve">9d358440-c41a-11f1-a2a1-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="S324"/>
+      <c s="20" t="inlineStr" r="U324">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V324"/>
+    </row>
+    <row r="325" ht="15.55" customHeight="0">
+      <c s="23" t="inlineStr" r="A325">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 03</t>
+        </is>
+      </c>
+      <c s="24" t="str" r="B325"/>
+      <c s="10" t="str" r="C325"/>
+      <c s="25" t="inlineStr" r="D325">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="26" r="E325">
+        <v>46307.7013888889</v>
+      </c>
+      <c s="10" t="str" r="F325"/>
+      <c s="26" r="G325">
+        <v>46308.2840277778</v>
+      </c>
+      <c s="25" t="inlineStr" r="H325">
+        <is>
+          <t xml:space="preserve">839</t>
+        </is>
+      </c>
+      <c s="25" t="str" r="I325"/>
+      <c s="25" t="inlineStr" r="J325">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="K325">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="L325">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="24" t="str" r="M325"/>
+      <c s="24" t="inlineStr" r="N325">
+        <is>
+          <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="O325">
+        <is>
+          <t xml:space="preserve">Parada registrada automaticamente pelo sistema</t>
+        </is>
+      </c>
+      <c s="24" t="str" r="P325"/>
+      <c s="10" t="str" r="Q325"/>
+      <c s="24" t="inlineStr" r="R325">
+        <is>
+          <t xml:space="preserve">1cbee870-c676-11f1-8d02-f2050a003223</t>
+        </is>
+      </c>
+      <c s="24" t="str" r="S325"/>
+      <c s="10" t="str" r="T325"/>
+      <c s="24" t="inlineStr" r="U325">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="11" t="str" r="V325"/>
+    </row>
   </sheetData>
   <mergeCells>
     <mergeCell ref="A3:B8"/>
@@ -22169,6 +24000,136 @@
     <mergeCell ref="P299:Q299"/>
     <mergeCell ref="S299:T299"/>
     <mergeCell ref="U299:V299"/>
+    <mergeCell ref="B300:C300"/>
+    <mergeCell ref="E300:F300"/>
+    <mergeCell ref="P300:Q300"/>
+    <mergeCell ref="S300:T300"/>
+    <mergeCell ref="U300:V300"/>
+    <mergeCell ref="B301:C301"/>
+    <mergeCell ref="E301:F301"/>
+    <mergeCell ref="P301:Q301"/>
+    <mergeCell ref="S301:T301"/>
+    <mergeCell ref="U301:V301"/>
+    <mergeCell ref="B302:C302"/>
+    <mergeCell ref="E302:F302"/>
+    <mergeCell ref="P302:Q302"/>
+    <mergeCell ref="S302:T302"/>
+    <mergeCell ref="U302:V302"/>
+    <mergeCell ref="B303:C303"/>
+    <mergeCell ref="E303:F303"/>
+    <mergeCell ref="P303:Q303"/>
+    <mergeCell ref="S303:T303"/>
+    <mergeCell ref="U303:V303"/>
+    <mergeCell ref="B304:C304"/>
+    <mergeCell ref="E304:F304"/>
+    <mergeCell ref="P304:Q304"/>
+    <mergeCell ref="S304:T304"/>
+    <mergeCell ref="U304:V304"/>
+    <mergeCell ref="B305:C305"/>
+    <mergeCell ref="E305:F305"/>
+    <mergeCell ref="P305:Q305"/>
+    <mergeCell ref="S305:T305"/>
+    <mergeCell ref="U305:V305"/>
+    <mergeCell ref="B306:C306"/>
+    <mergeCell ref="E306:F306"/>
+    <mergeCell ref="P306:Q306"/>
+    <mergeCell ref="S306:T306"/>
+    <mergeCell ref="U306:V306"/>
+    <mergeCell ref="B307:C307"/>
+    <mergeCell ref="E307:F307"/>
+    <mergeCell ref="P307:Q307"/>
+    <mergeCell ref="S307:T307"/>
+    <mergeCell ref="U307:V307"/>
+    <mergeCell ref="B308:C308"/>
+    <mergeCell ref="E308:F308"/>
+    <mergeCell ref="P308:Q308"/>
+    <mergeCell ref="S308:T308"/>
+    <mergeCell ref="U308:V308"/>
+    <mergeCell ref="B309:C309"/>
+    <mergeCell ref="E309:F309"/>
+    <mergeCell ref="P309:Q309"/>
+    <mergeCell ref="S309:T309"/>
+    <mergeCell ref="U309:V309"/>
+    <mergeCell ref="B310:C310"/>
+    <mergeCell ref="E310:F310"/>
+    <mergeCell ref="P310:Q310"/>
+    <mergeCell ref="S310:T310"/>
+    <mergeCell ref="U310:V310"/>
+    <mergeCell ref="B311:C311"/>
+    <mergeCell ref="E311:F311"/>
+    <mergeCell ref="P311:Q311"/>
+    <mergeCell ref="S311:T311"/>
+    <mergeCell ref="U311:V311"/>
+    <mergeCell ref="B312:C312"/>
+    <mergeCell ref="E312:F312"/>
+    <mergeCell ref="P312:Q312"/>
+    <mergeCell ref="S312:T312"/>
+    <mergeCell ref="U312:V312"/>
+    <mergeCell ref="B313:C313"/>
+    <mergeCell ref="E313:F313"/>
+    <mergeCell ref="P313:Q313"/>
+    <mergeCell ref="S313:T313"/>
+    <mergeCell ref="U313:V313"/>
+    <mergeCell ref="B314:C314"/>
+    <mergeCell ref="E314:F314"/>
+    <mergeCell ref="P314:Q314"/>
+    <mergeCell ref="S314:T314"/>
+    <mergeCell ref="U314:V314"/>
+    <mergeCell ref="B315:C315"/>
+    <mergeCell ref="E315:F315"/>
+    <mergeCell ref="P315:Q315"/>
+    <mergeCell ref="S315:T315"/>
+    <mergeCell ref="U315:V315"/>
+    <mergeCell ref="B316:C316"/>
+    <mergeCell ref="E316:F316"/>
+    <mergeCell ref="P316:Q316"/>
+    <mergeCell ref="S316:T316"/>
+    <mergeCell ref="U316:V316"/>
+    <mergeCell ref="B317:C317"/>
+    <mergeCell ref="E317:F317"/>
+    <mergeCell ref="P317:Q317"/>
+    <mergeCell ref="S317:T317"/>
+    <mergeCell ref="U317:V317"/>
+    <mergeCell ref="B318:C318"/>
+    <mergeCell ref="E318:F318"/>
+    <mergeCell ref="P318:Q318"/>
+    <mergeCell ref="S318:T318"/>
+    <mergeCell ref="U318:V318"/>
+    <mergeCell ref="B319:C319"/>
+    <mergeCell ref="E319:F319"/>
+    <mergeCell ref="P319:Q319"/>
+    <mergeCell ref="S319:T319"/>
+    <mergeCell ref="U319:V319"/>
+    <mergeCell ref="B320:C320"/>
+    <mergeCell ref="E320:F320"/>
+    <mergeCell ref="P320:Q320"/>
+    <mergeCell ref="S320:T320"/>
+    <mergeCell ref="U320:V320"/>
+    <mergeCell ref="B321:C321"/>
+    <mergeCell ref="E321:F321"/>
+    <mergeCell ref="P321:Q321"/>
+    <mergeCell ref="S321:T321"/>
+    <mergeCell ref="U321:V321"/>
+    <mergeCell ref="B322:C322"/>
+    <mergeCell ref="E322:F322"/>
+    <mergeCell ref="P322:Q322"/>
+    <mergeCell ref="S322:T322"/>
+    <mergeCell ref="U322:V322"/>
+    <mergeCell ref="B323:C323"/>
+    <mergeCell ref="E323:F323"/>
+    <mergeCell ref="P323:Q323"/>
+    <mergeCell ref="S323:T323"/>
+    <mergeCell ref="U323:V323"/>
+    <mergeCell ref="B324:C324"/>
+    <mergeCell ref="E324:F324"/>
+    <mergeCell ref="P324:Q324"/>
+    <mergeCell ref="S324:T324"/>
+    <mergeCell ref="U324:V324"/>
+    <mergeCell ref="B325:C325"/>
+    <mergeCell ref="E325:F325"/>
+    <mergeCell ref="P325:Q325"/>
+    <mergeCell ref="S325:T325"/>
+    <mergeCell ref="U325:V325"/>
   </mergeCells>
   <pageMargins left="0.0393700787401575" right="0.0393700787401575" top="0.0393700787401575" bottom="0.0393700787401575" header="0.0393700787401575" footer="0.0393700787401575"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>

--- a/Base_Interrupcoes.xlsx
+++ b/Base_Interrupcoes.xlsx
@@ -253,16 +253,16 @@
     <xf applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" numFmtId="82" fontId="5" fillId="4" borderId="0">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" numFmtId="0" fontId="5" fillId="3" borderId="6">
+    <xf applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" numFmtId="0" fontId="5" fillId="4" borderId="6">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" numFmtId="0" fontId="5" fillId="3" borderId="7">
+    <xf applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" numFmtId="0" fontId="5" fillId="4" borderId="7">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" numFmtId="0" fontId="5" fillId="3" borderId="7">
+    <xf applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" numFmtId="0" fontId="5" fillId="4" borderId="7">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" numFmtId="82" fontId="5" fillId="3" borderId="7">
+    <xf applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" numFmtId="82" fontId="5" fillId="4" borderId="7">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -466,7 +466,7 @@
       <c s="4" t="str" r="A7"/>
       <c s="7" t="inlineStr" r="T7">
         <is>
-          <t xml:space="preserve">Emissão: 13/10/2026</t>
+          <t xml:space="preserve">Emissão: 15/10/2026</t>
         </is>
       </c>
       <c s="5" t="str" r="V7"/>
@@ -475,7 +475,7 @@
       <c s="4" t="str" r="A8"/>
       <c s="8" t="inlineStr" r="F8">
         <is>
-          <t xml:space="preserve">Período: 01/10/2026 até 12/10/2026; Turno: Todos; Tempo: Calendário</t>
+          <t xml:space="preserve">Período: 01/10/2026 até 14/10/2026; Turno: Todos; Tempo: Calendário</t>
         </is>
       </c>
       <c s="5" t="str" r="V8"/>
@@ -2910,7 +2910,7 @@
     <row r="49" ht="15.6" customHeight="0">
       <c s="15" t="inlineStr" r="A49">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 02</t>
+          <t xml:space="preserve">TRANSVERSAL 03</t>
         </is>
       </c>
       <c s="16" t="str" r="B49"/>
@@ -2960,7 +2960,7 @@
       <c s="16" t="str" r="P49"/>
       <c s="16" t="inlineStr" r="R49">
         <is>
-          <t xml:space="preserve">49cef330-bdd1-11f1-8f07-f2050a003223</t>
+          <t xml:space="preserve">49efe8b0-bdd1-11f1-cb5a-f2050a003223</t>
         </is>
       </c>
       <c s="16" t="str" r="S49"/>
@@ -2974,7 +2974,7 @@
     <row r="50" ht="15.6" customHeight="0">
       <c s="19" t="inlineStr" r="A50">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 03</t>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
         </is>
       </c>
       <c s="20" t="str" r="B50"/>
@@ -3024,7 +3024,7 @@
       <c s="20" t="str" r="P50"/>
       <c s="20" t="inlineStr" r="R50">
         <is>
-          <t xml:space="preserve">49efe8b0-bdd1-11f1-cb5a-f2050a003223</t>
+          <t xml:space="preserve">49cef330-bdd1-11f1-8f07-f2050a003223</t>
         </is>
       </c>
       <c s="20" t="str" r="S50"/>
@@ -3110,12 +3110,12 @@
     <row r="52" ht="15.6" customHeight="0">
       <c s="19" t="inlineStr" r="A52">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 01</t>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="B52">
         <is>
-          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
         </is>
       </c>
       <c s="21" t="inlineStr" r="D52">
@@ -3127,11 +3127,11 @@
         <v>46297.2916666667</v>
       </c>
       <c s="22" r="G52">
-        <v>46297.3020833333</v>
+        <v>46297.2986111111</v>
       </c>
       <c s="21" t="inlineStr" r="H52">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c s="21" t="str" r="I52"/>
@@ -3158,18 +3158,18 @@
       </c>
       <c s="20" t="inlineStr" r="O52">
         <is>
-          <t xml:space="preserve">dds e assinatura dos documentos</t>
+          <t xml:space="preserve">DDS</t>
         </is>
       </c>
       <c s="20" t="str" r="P52"/>
       <c s="20" t="inlineStr" r="R52">
         <is>
-          <t xml:space="preserve">61a3b7a0-be4b-11f1-9cbf-f2050a003223</t>
+          <t xml:space="preserve">942e4bd0-be4c-11f1-ca85-f2050a003223</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="S52">
         <is>
-          <t xml:space="preserve">10046873    </t>
+          <t xml:space="preserve">10047019    </t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="U52">
@@ -3182,12 +3182,12 @@
     <row r="53" ht="15.55" customHeight="0">
       <c s="15" t="inlineStr" r="A53">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 04</t>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="B53">
         <is>
-          <t xml:space="preserve">TR04-DESENROLADOR</t>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
         </is>
       </c>
       <c s="17" t="inlineStr" r="D53">
@@ -3199,11 +3199,11 @@
         <v>46297.2916666667</v>
       </c>
       <c s="18" r="G53">
-        <v>46297.2986111111</v>
+        <v>46297.3020833333</v>
       </c>
       <c s="17" t="inlineStr" r="H53">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c s="17" t="str" r="I53"/>
@@ -3230,18 +3230,18 @@
       </c>
       <c s="16" t="inlineStr" r="O53">
         <is>
-          <t xml:space="preserve">DDS</t>
+          <t xml:space="preserve">dds e assinatura dos documentos</t>
         </is>
       </c>
       <c s="16" t="str" r="P53"/>
       <c s="16" t="inlineStr" r="R53">
         <is>
-          <t xml:space="preserve">942e4bd0-be4c-11f1-ca85-f2050a003223</t>
+          <t xml:space="preserve">61a3b7a0-be4b-11f1-9cbf-f2050a003223</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="S53">
         <is>
-          <t xml:space="preserve">10047019    </t>
+          <t xml:space="preserve">10046873    </t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="U53">
@@ -10319,14 +10319,10 @@
     <row r="153" ht="15.6" customHeight="0">
       <c s="15" t="inlineStr" r="A153">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 04</t>
-        </is>
-      </c>
-      <c s="16" t="inlineStr" r="B153">
-        <is>
-          <t xml:space="preserve">TR04-CARRO DE ENTRADA</t>
-        </is>
-      </c>
+          <t xml:space="preserve">TRANSVERSAL 03</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B153"/>
       <c s="17" t="inlineStr" r="D153">
         <is>
           <t xml:space="preserve">TURNO B</t>
@@ -10362,7 +10358,7 @@
       <c s="16" t="str" r="M153"/>
       <c s="16" t="inlineStr" r="N153">
         <is>
-          <t xml:space="preserve">FALTA DEMANDA</t>
+          <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="O153">
@@ -10373,14 +10369,10 @@
       <c s="16" t="str" r="P153"/>
       <c s="16" t="inlineStr" r="R153">
         <is>
-          <t xml:space="preserve">f4fe8f00-c0f5-11f1-ad1e-f2050a003223</t>
-        </is>
-      </c>
-      <c s="16" t="inlineStr" r="S153">
-        <is>
-          <t xml:space="preserve">10048032    </t>
-        </is>
-      </c>
+          <t xml:space="preserve">f4dfe370-c0f5-11f1-c191-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="S153"/>
       <c s="16" t="inlineStr" r="U153">
         <is>
           <t xml:space="preserve">Sim</t>
@@ -10391,10 +10383,14 @@
     <row r="154" ht="15.55" customHeight="0">
       <c s="19" t="inlineStr" r="A154">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 03</t>
-        </is>
-      </c>
-      <c s="20" t="str" r="B154"/>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B154">
+        <is>
+          <t xml:space="preserve">TR04-CARRO DE ENTRADA</t>
+        </is>
+      </c>
       <c s="21" t="inlineStr" r="D154">
         <is>
           <t xml:space="preserve">TURNO B</t>
@@ -10430,7 +10426,7 @@
       <c s="20" t="str" r="M154"/>
       <c s="20" t="inlineStr" r="N154">
         <is>
-          <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
+          <t xml:space="preserve">FALTA DEMANDA</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="O154">
@@ -10441,10 +10437,14 @@
       <c s="20" t="str" r="P154"/>
       <c s="20" t="inlineStr" r="R154">
         <is>
-          <t xml:space="preserve">f4dfe370-c0f5-11f1-c191-f2050a003223</t>
-        </is>
-      </c>
-      <c s="20" t="str" r="S154"/>
+          <t xml:space="preserve">f4fe8f00-c0f5-11f1-ad1e-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S154">
+        <is>
+          <t xml:space="preserve">10048032    </t>
+        </is>
+      </c>
       <c s="20" t="inlineStr" r="U154">
         <is>
           <t xml:space="preserve">Sim</t>
@@ -10671,12 +10671,12 @@
     <row r="158" ht="15.6" customHeight="0">
       <c s="19" t="inlineStr" r="A158">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 05</t>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="B158">
         <is>
-          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
         </is>
       </c>
       <c s="21" t="inlineStr" r="D158">
@@ -10688,11 +10688,11 @@
         <v>46301.2916666667</v>
       </c>
       <c s="22" r="G158">
-        <v>46301.3055555556</v>
+        <v>46301.2986111111</v>
       </c>
       <c s="21" t="inlineStr" r="H158">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c s="21" t="str" r="I158"/>
@@ -10719,18 +10719,18 @@
       </c>
       <c s="20" t="inlineStr" r="O158">
         <is>
-          <t xml:space="preserve">dds</t>
+          <t xml:space="preserve">DDS</t>
         </is>
       </c>
       <c s="20" t="str" r="P158"/>
       <c s="20" t="inlineStr" r="R158">
         <is>
-          <t xml:space="preserve">4ed80b10-c172-11f1-84a1-f2050a003223</t>
+          <t xml:space="preserve">00542e40-c174-11f1-b395-f2050a003223</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="S158">
         <is>
-          <t xml:space="preserve">10046766    </t>
+          <t xml:space="preserve">10048032    </t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="U158">
@@ -10743,12 +10743,12 @@
     <row r="159" ht="15.55" customHeight="0">
       <c s="15" t="inlineStr" r="A159">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 04</t>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="B159">
         <is>
-          <t xml:space="preserve">TR04-DESENROLADOR</t>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
         </is>
       </c>
       <c s="17" t="inlineStr" r="D159">
@@ -10760,11 +10760,11 @@
         <v>46301.2916666667</v>
       </c>
       <c s="18" r="G159">
-        <v>46301.2986111111</v>
+        <v>46301.3055555556</v>
       </c>
       <c s="17" t="inlineStr" r="H159">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c s="17" t="str" r="I159"/>
@@ -10791,18 +10791,18 @@
       </c>
       <c s="16" t="inlineStr" r="O159">
         <is>
-          <t xml:space="preserve">DDS</t>
+          <t xml:space="preserve">dds</t>
         </is>
       </c>
       <c s="16" t="str" r="P159"/>
       <c s="16" t="inlineStr" r="R159">
         <is>
-          <t xml:space="preserve">00542e40-c174-11f1-b395-f2050a003223</t>
+          <t xml:space="preserve">4ed80b10-c172-11f1-84a1-f2050a003223</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="S159">
         <is>
-          <t xml:space="preserve">10048032    </t>
+          <t xml:space="preserve">10046766    </t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="U159">
@@ -15235,10 +15235,14 @@
     <row r="222" ht="15.6" customHeight="0">
       <c s="19" t="inlineStr" r="A222">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 03</t>
-        </is>
-      </c>
-      <c s="20" t="str" r="B222"/>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B222">
+        <is>
+          <t xml:space="preserve">TR01-CARRO DE ENTRADA</t>
+        </is>
+      </c>
       <c s="21" t="inlineStr" r="D222">
         <is>
           <t xml:space="preserve">TURNO B</t>
@@ -15274,7 +15278,7 @@
       <c s="20" t="str" r="M222"/>
       <c s="20" t="inlineStr" r="N222">
         <is>
-          <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
+          <t xml:space="preserve">FALTA DEMANDA</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="O222">
@@ -15285,10 +15289,14 @@
       <c s="20" t="str" r="P222"/>
       <c s="20" t="inlineStr" r="R222">
         <is>
-          <t xml:space="preserve">1e703360-c1bf-11f1-c100-f2050a003223</t>
-        </is>
-      </c>
-      <c s="20" t="str" r="S222"/>
+          <t xml:space="preserve">1e40e600-c1bf-11f1-add1-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S222">
+        <is>
+          <t xml:space="preserve">10048039    </t>
+        </is>
+      </c>
       <c s="20" t="inlineStr" r="U222">
         <is>
           <t xml:space="preserve">Sim</t>
@@ -15299,14 +15307,10 @@
     <row r="223" ht="15.6" customHeight="0">
       <c s="15" t="inlineStr" r="A223">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 01</t>
-        </is>
-      </c>
-      <c s="16" t="inlineStr" r="B223">
-        <is>
-          <t xml:space="preserve">TR01-CARRO DE ENTRADA</t>
-        </is>
-      </c>
+          <t xml:space="preserve">TRANSVERSAL 03</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B223"/>
       <c s="17" t="inlineStr" r="D223">
         <is>
           <t xml:space="preserve">TURNO B</t>
@@ -15342,7 +15346,7 @@
       <c s="16" t="str" r="M223"/>
       <c s="16" t="inlineStr" r="N223">
         <is>
-          <t xml:space="preserve">FALTA DEMANDA</t>
+          <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="O223">
@@ -15353,14 +15357,10 @@
       <c s="16" t="str" r="P223"/>
       <c s="16" t="inlineStr" r="R223">
         <is>
-          <t xml:space="preserve">1e40e600-c1bf-11f1-add1-f2050a003223</t>
-        </is>
-      </c>
-      <c s="16" t="inlineStr" r="S223">
-        <is>
-          <t xml:space="preserve">10048039    </t>
-        </is>
-      </c>
+          <t xml:space="preserve">1e703360-c1bf-11f1-c100-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="S223"/>
       <c s="16" t="inlineStr" r="U223">
         <is>
           <t xml:space="preserve">Sim</t>
@@ -17112,7 +17112,7 @@
       </c>
       <c s="20" t="inlineStr" r="L248">
         <is>
-          <t xml:space="preserve">MEP/QUALIDADE</t>
+          <t xml:space="preserve">Operacional</t>
         </is>
       </c>
       <c s="20" t="str" r="M248"/>
@@ -18375,23 +18375,23 @@
       </c>
       <c s="20" t="inlineStr" r="K266">
         <is>
-          <t xml:space="preserve">Tempo Livre</t>
+          <t xml:space="preserve">Paradas Programadas</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="L266">
         <is>
-          <t xml:space="preserve">Tempo Livre</t>
+          <t xml:space="preserve">Paradas Programadas</t>
         </is>
       </c>
       <c s="20" t="str" r="M266"/>
       <c s="20" t="inlineStr" r="N266">
         <is>
-          <t xml:space="preserve">FALTA DEMANDA</t>
+          <t xml:space="preserve">MANUTENÇÃO PREVENTIVA</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="O266">
         <is>
-          <t xml:space="preserve">FALTA DE DEMANDA</t>
+          <t xml:space="preserve">preventiva</t>
         </is>
       </c>
       <c s="20" t="str" r="P266"/>
@@ -18551,12 +18551,12 @@
     <row r="269" ht="15.6" customHeight="0">
       <c s="15" t="inlineStr" r="A269">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 02</t>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="B269">
         <is>
-          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
         </is>
       </c>
       <c s="17" t="inlineStr" r="D269">
@@ -18568,11 +18568,11 @@
         <v>46303.2916666667</v>
       </c>
       <c s="18" r="G269">
-        <v>46303.2986111111</v>
+        <v>46303.3020833333</v>
       </c>
       <c s="17" t="inlineStr" r="H269">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c s="17" t="str" r="I269"/>
@@ -18599,18 +18599,18 @@
       </c>
       <c s="16" t="inlineStr" r="O269">
         <is>
-          <t xml:space="preserve">DDS</t>
+          <t xml:space="preserve">dds e assinatura dos documentos</t>
         </is>
       </c>
       <c s="16" t="str" r="P269"/>
       <c s="16" t="inlineStr" r="R269">
         <is>
-          <t xml:space="preserve">6e8883a0-c301-11f1-9a54-f2050a003223</t>
+          <t xml:space="preserve">065f5d20-c302-11f1-8108-f2050a003223</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="S269">
         <is>
-          <t xml:space="preserve">10048465    </t>
+          <t xml:space="preserve">10048233    </t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="U269">
@@ -18623,12 +18623,12 @@
     <row r="270" ht="15.6" customHeight="0">
       <c s="19" t="inlineStr" r="A270">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 01</t>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="B270">
         <is>
-          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
         </is>
       </c>
       <c s="21" t="inlineStr" r="D270">
@@ -18640,11 +18640,11 @@
         <v>46303.2916666667</v>
       </c>
       <c s="22" r="G270">
-        <v>46303.3020833333</v>
+        <v>46303.2986111111</v>
       </c>
       <c s="21" t="inlineStr" r="H270">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c s="21" t="str" r="I270"/>
@@ -18671,18 +18671,18 @@
       </c>
       <c s="20" t="inlineStr" r="O270">
         <is>
-          <t xml:space="preserve">dds e assinatura dos documentos</t>
+          <t xml:space="preserve">DDS</t>
         </is>
       </c>
       <c s="20" t="str" r="P270"/>
       <c s="20" t="inlineStr" r="R270">
         <is>
-          <t xml:space="preserve">065f5d20-c302-11f1-8108-f2050a003223</t>
+          <t xml:space="preserve">6e8883a0-c301-11f1-9a54-f2050a003223</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="S270">
         <is>
-          <t xml:space="preserve">10048233    </t>
+          <t xml:space="preserve">10048465    </t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="U270">
@@ -20264,11 +20264,11 @@
         <v>46303.6541666667</v>
       </c>
       <c s="18" r="G293">
-        <v>46308.2950509606</v>
+        <v>46308.3743055556</v>
       </c>
       <c s="17" t="inlineStr" r="H293">
         <is>
-          <t xml:space="preserve">6.683</t>
+          <t xml:space="preserve">6.797</t>
         </is>
       </c>
       <c s="17" t="str" r="I293"/>
@@ -20972,11 +20972,11 @@
         <v>46304.3645833333</v>
       </c>
       <c s="18" r="G303">
-        <v>46308.2950509606</v>
+        <v>46308.3972222222</v>
       </c>
       <c s="17" t="inlineStr" r="H303">
         <is>
-          <t xml:space="preserve">5.660</t>
+          <t xml:space="preserve">5.807</t>
         </is>
       </c>
       <c s="17" t="str" r="I303"/>
@@ -22316,11 +22316,11 @@
         <v>46304.6944444444</v>
       </c>
       <c s="22" r="G322">
-        <v>46308.2950509606</v>
+        <v>46308.2909722222</v>
       </c>
       <c s="21" t="inlineStr" r="H322">
         <is>
-          <t xml:space="preserve">5.185</t>
+          <t xml:space="preserve">5.179</t>
         </is>
       </c>
       <c s="21" t="str" r="I322"/>
@@ -22388,11 +22388,11 @@
         <v>46304.6958333333</v>
       </c>
       <c s="18" r="G323">
-        <v>46308.2950509606</v>
+        <v>46304.70625</v>
       </c>
       <c s="17" t="inlineStr" r="H323">
         <is>
-          <t xml:space="preserve">5.183</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c s="17" t="str" r="I323"/>
@@ -22403,23 +22403,23 @@
       </c>
       <c s="16" t="inlineStr" r="K323">
         <is>
-          <t xml:space="preserve">Tempo Livre</t>
+          <t xml:space="preserve">Operacional</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="L323">
         <is>
-          <t xml:space="preserve">Tempo Livre</t>
+          <t xml:space="preserve">Operacional</t>
         </is>
       </c>
       <c s="16" t="str" r="M323"/>
       <c s="16" t="inlineStr" r="N323">
         <is>
-          <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="O323">
         <is>
-          <t xml:space="preserve">espera fim de semana</t>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
         </is>
       </c>
       <c s="16" t="str" r="P323"/>
@@ -22505,73 +22505,8075 @@
       <c s="5" t="str" r="V324"/>
     </row>
     <row r="325" ht="15.55" customHeight="0">
-      <c s="23" t="inlineStr" r="A325">
+      <c s="15" t="inlineStr" r="A325">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B325">
+        <is>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D325">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E325">
+        <v>46304.7069444444</v>
+      </c>
+      <c s="18" r="G325">
+        <v>46308.2909722222</v>
+      </c>
+      <c s="17" t="inlineStr" r="H325">
+        <is>
+          <t xml:space="preserve">5.161</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I325"/>
+      <c s="17" t="inlineStr" r="J325">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K325">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L325">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M325"/>
+      <c s="16" t="inlineStr" r="N325">
+        <is>
+          <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O325">
+        <is>
+          <t xml:space="preserve">espera fim de semana</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P325"/>
+      <c s="16" t="inlineStr" r="R325">
+        <is>
+          <t xml:space="preserve">769cc6c0-c6f1-11f1-96cc-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S325">
+        <is>
+          <t xml:space="preserve">10048445    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U325">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V325"/>
+    </row>
+    <row r="326" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A326">
         <is>
           <t xml:space="preserve">TRANSVERSAL 03</t>
         </is>
       </c>
-      <c s="24" t="str" r="B325"/>
-      <c s="10" t="str" r="C325"/>
-      <c s="25" t="inlineStr" r="D325">
+      <c s="20" t="str" r="B326"/>
+      <c s="21" t="inlineStr" r="D326">
         <is>
           <t xml:space="preserve">TURNO B</t>
         </is>
       </c>
-      <c s="26" r="E325">
+      <c s="22" r="E326">
         <v>46307.7013888889</v>
       </c>
-      <c s="10" t="str" r="F325"/>
-      <c s="26" r="G325">
+      <c s="22" r="G326">
         <v>46308.2840277778</v>
       </c>
-      <c s="25" t="inlineStr" r="H325">
+      <c s="21" t="inlineStr" r="H326">
         <is>
           <t xml:space="preserve">839</t>
         </is>
       </c>
-      <c s="25" t="str" r="I325"/>
-      <c s="25" t="inlineStr" r="J325">
-        <is>
-          <t xml:space="preserve">X</t>
-        </is>
-      </c>
-      <c s="24" t="inlineStr" r="K325">
+      <c s="21" t="str" r="I326"/>
+      <c s="21" t="inlineStr" r="J326">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K326">
         <is>
           <t xml:space="preserve">Tempo Livre</t>
         </is>
       </c>
-      <c s="24" t="inlineStr" r="L325">
+      <c s="20" t="inlineStr" r="L326">
         <is>
           <t xml:space="preserve">Tempo Livre</t>
         </is>
       </c>
-      <c s="24" t="str" r="M325"/>
-      <c s="24" t="inlineStr" r="N325">
+      <c s="20" t="str" r="M326"/>
+      <c s="20" t="inlineStr" r="N326">
         <is>
           <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
         </is>
       </c>
-      <c s="24" t="inlineStr" r="O325">
+      <c s="20" t="inlineStr" r="O326">
         <is>
           <t xml:space="preserve">Parada registrada automaticamente pelo sistema</t>
         </is>
       </c>
-      <c s="24" t="str" r="P325"/>
-      <c s="10" t="str" r="Q325"/>
-      <c s="24" t="inlineStr" r="R325">
+      <c s="20" t="str" r="P326"/>
+      <c s="20" t="inlineStr" r="R326">
         <is>
           <t xml:space="preserve">1cbee870-c676-11f1-8d02-f2050a003223</t>
         </is>
       </c>
-      <c s="24" t="str" r="S325"/>
-      <c s="10" t="str" r="T325"/>
-      <c s="24" t="inlineStr" r="U325">
-        <is>
-          <t xml:space="preserve">Sim</t>
-        </is>
-      </c>
-      <c s="11" t="str" r="V325"/>
-    </row>
+      <c s="20" t="str" r="S326"/>
+      <c s="20" t="inlineStr" r="U326">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V326"/>
+    </row>
+    <row r="327" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A327">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B327">
+        <is>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D327">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E327">
+        <v>46308.2916666667</v>
+      </c>
+      <c s="18" r="G327">
+        <v>46308.2986111111</v>
+      </c>
+      <c s="17" t="inlineStr" r="H327">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I327"/>
+      <c s="17" t="inlineStr" r="J327">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K327">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L327">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M327"/>
+      <c s="16" t="inlineStr" r="N327">
+        <is>
+          <t xml:space="preserve">DDS</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O327">
+        <is>
+          <t xml:space="preserve">dds</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P327"/>
+      <c s="16" t="inlineStr" r="R327">
+        <is>
+          <t xml:space="preserve">90a4c9e0-c6f2-11f1-c266-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S327">
+        <is>
+          <t xml:space="preserve">10048445    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U327">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V327"/>
+    </row>
+    <row r="328" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A328">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B328">
+        <is>
+          <t xml:space="preserve">TR01-MESA TRANSPORTADORA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D328">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E328">
+        <v>46308.2916666667</v>
+      </c>
+      <c s="22" r="G328">
+        <v>46308.3020833333</v>
+      </c>
+      <c s="21" t="inlineStr" r="H328">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I328"/>
+      <c s="21" t="inlineStr" r="J328">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K328">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L328">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M328"/>
+      <c s="20" t="inlineStr" r="N328">
+        <is>
+          <t xml:space="preserve">DDS</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O328">
+        <is>
+          <t xml:space="preserve">dds e assinatura dos documentos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P328"/>
+      <c s="20" t="inlineStr" r="R328">
+        <is>
+          <t xml:space="preserve">49ee6680-c6ef-11f1-b32a-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S328">
+        <is>
+          <t xml:space="preserve">10048955    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U328">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V328"/>
+    </row>
+    <row r="329" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A329">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B329">
+        <is>
+          <t xml:space="preserve">TR01-MESA FIXA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D329">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E329">
+        <v>46308.3159722222</v>
+      </c>
+      <c s="18" r="G329">
+        <v>46308.3201388889</v>
+      </c>
+      <c s="17" t="inlineStr" r="H329">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I329"/>
+      <c s="17" t="inlineStr" r="J329">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K329">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L329">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M329"/>
+      <c s="16" t="inlineStr" r="N329">
+        <is>
+          <t xml:space="preserve">PESAGEM DE FARDO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O329">
+        <is>
+          <t xml:space="preserve">aguardando op: de ponte retira material</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P329"/>
+      <c s="16" t="inlineStr" r="R329">
+        <is>
+          <t xml:space="preserve">c2121920-c6f1-11f1-8d5c-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S329">
+        <is>
+          <t xml:space="preserve">10048955    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U329">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V329"/>
+    </row>
+    <row r="330" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A330">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B330">
+        <is>
+          <t xml:space="preserve">TR01-MESA FIXA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D330">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E330">
+        <v>46308.3236111111</v>
+      </c>
+      <c s="22" r="G330">
+        <v>46308.3263888889</v>
+      </c>
+      <c s="21" t="inlineStr" r="H330">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I330"/>
+      <c s="21" t="inlineStr" r="J330">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K330">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L330">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M330"/>
+      <c s="20" t="inlineStr" r="N330">
+        <is>
+          <t xml:space="preserve">PESAGEM DE FARDO</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O330">
+        <is>
+          <t xml:space="preserve">aguardando op:de ponte retira material</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P330"/>
+      <c s="20" t="inlineStr" r="R330">
+        <is>
+          <t xml:space="preserve">687ad8f0-c6f3-11f1-c2e1-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S330">
+        <is>
+          <t xml:space="preserve">10048955    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U330">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V330"/>
+    </row>
+    <row r="331" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A331">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B331">
+        <is>
+          <t xml:space="preserve">TR01-MESA FIXA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D331">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E331">
+        <v>46308.3298611111</v>
+      </c>
+      <c s="18" r="G331">
+        <v>46308.3319444444</v>
+      </c>
+      <c s="17" t="inlineStr" r="H331">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I331"/>
+      <c s="17" t="inlineStr" r="J331">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K331">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L331">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M331"/>
+      <c s="16" t="inlineStr" r="N331">
+        <is>
+          <t xml:space="preserve">PESAGEM DE FARDO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O331">
+        <is>
+          <t xml:space="preserve">aguardando op:de ponte retira material</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P331"/>
+      <c s="16" t="inlineStr" r="R331">
+        <is>
+          <t xml:space="preserve">aba7d960-c6f4-11f1-b78e-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S331">
+        <is>
+          <t xml:space="preserve">10048955    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U331">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V331"/>
+    </row>
+    <row r="332" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A332">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B332"/>
+      <c s="21" t="inlineStr" r="D332">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E332">
+        <v>46308.3326388889</v>
+      </c>
+      <c s="22" r="G332">
+        <v>46308.3416666667</v>
+      </c>
+      <c s="21" t="inlineStr" r="H332">
+        <is>
+          <t xml:space="preserve">13</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I332"/>
+      <c s="21" t="inlineStr" r="J332">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K332">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L332">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M332"/>
+      <c s="20" t="inlineStr" r="N332">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O332">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 13 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P332"/>
+      <c s="20" t="inlineStr" r="R332">
+        <is>
+          <t xml:space="preserve">355ef9e0-c6f5-11f1-a691-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S332">
+        <is>
+          <t xml:space="preserve">10048955    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U332">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V332"/>
+    </row>
+    <row r="333" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A333">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B333">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D333">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E333">
+        <v>46308.3555555556</v>
+      </c>
+      <c s="18" r="G333">
+        <v>46308.3576388889</v>
+      </c>
+      <c s="17" t="inlineStr" r="H333">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I333"/>
+      <c s="17" t="inlineStr" r="J333">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K333">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L333">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M333"/>
+      <c s="16" t="inlineStr" r="N333">
+        <is>
+          <t xml:space="preserve">AJUSTE DA MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O333">
+        <is>
+          <t xml:space="preserve">ajuste da mesa para tamanho de chapa</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P333"/>
+      <c s="16" t="inlineStr" r="R333">
+        <is>
+          <t xml:space="preserve">d4f4b7c0-c6f9-11f1-aefc-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S333">
+        <is>
+          <t xml:space="preserve">10048955    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U333">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V333"/>
+    </row>
+    <row r="334" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A334">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B334">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D334">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E334">
+        <v>46308.3708333333</v>
+      </c>
+      <c s="22" r="G334">
+        <v>46308.3736111111</v>
+      </c>
+      <c s="21" t="inlineStr" r="H334">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I334"/>
+      <c s="21" t="inlineStr" r="J334">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K334">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L334">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M334"/>
+      <c s="20" t="inlineStr" r="N334">
+        <is>
+          <t xml:space="preserve">AJUSTE DA MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O334">
+        <is>
+          <t xml:space="preserve">ajuste da mesa para tamanho de chapa</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P334"/>
+      <c s="20" t="inlineStr" r="R334">
+        <is>
+          <t xml:space="preserve">d6b37760-c6fc-11f1-be63-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S334">
+        <is>
+          <t xml:space="preserve">10048646    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U334">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V334"/>
+    </row>
+    <row r="335" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A335">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B335">
+        <is>
+          <t xml:space="preserve">TR04-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D335">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E335">
+        <v>46308.375</v>
+      </c>
+      <c s="18" r="G335">
+        <v>46308.3861111111</v>
+      </c>
+      <c s="17" t="inlineStr" r="H335">
+        <is>
+          <t xml:space="preserve">16</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I335"/>
+      <c s="17" t="inlineStr" r="J335">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K335">
+        <is>
+          <t xml:space="preserve">Manutenção Corretiva Mecânica</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L335">
+        <is>
+          <t xml:space="preserve">Manutenção Corretiva Mecânica</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M335"/>
+      <c s="16" t="inlineStr" r="N335">
+        <is>
+          <t xml:space="preserve">FALHA NA TRANSMISSÃO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O335">
+        <is>
+          <t xml:space="preserve">mesa móvel não atua</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="P335">
+        <is>
+          <t xml:space="preserve">000010035093</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="R335">
+        <is>
+          <t xml:space="preserve">c5429ef0-c6f9-11f1-8823-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S335">
+        <is>
+          <t xml:space="preserve">10049282    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U335">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V335"/>
+    </row>
+    <row r="336" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A336">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B336">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D336">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E336">
+        <v>46308.3791666667</v>
+      </c>
+      <c s="22" r="G336">
+        <v>46308.38125</v>
+      </c>
+      <c s="21" t="inlineStr" r="H336">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I336"/>
+      <c s="21" t="inlineStr" r="J336">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K336">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L336">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M336"/>
+      <c s="20" t="inlineStr" r="N336">
+        <is>
+          <t xml:space="preserve">AJUSTE DA MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O336">
+        <is>
+          <t xml:space="preserve">ajuste da mesa para tamanho de chapa</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P336"/>
+      <c s="20" t="inlineStr" r="R336">
+        <is>
+          <t xml:space="preserve">848900c0-c6fe-11f1-c37b-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S336">
+        <is>
+          <t xml:space="preserve">10049152    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U336">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V336"/>
+    </row>
+    <row r="337" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A337">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B337">
+        <is>
+          <t xml:space="preserve">TR05-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D337">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E337">
+        <v>46308.3868055556</v>
+      </c>
+      <c s="18" r="G337">
+        <v>46308.3951388889</v>
+      </c>
+      <c s="17" t="inlineStr" r="H337">
+        <is>
+          <t xml:space="preserve">12</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I337"/>
+      <c s="17" t="inlineStr" r="J337">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K337">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L337">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M337"/>
+      <c s="16" t="inlineStr" r="N337">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O337">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 12 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P337"/>
+      <c s="16" t="inlineStr" r="R337">
+        <is>
+          <t xml:space="preserve">211137e0-c700-11f1-8064-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S337">
+        <is>
+          <t xml:space="preserve">10048449    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U337">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V337"/>
+    </row>
+    <row r="338" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A338">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B338"/>
+      <c s="21" t="inlineStr" r="D338">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E338">
+        <v>46308.3881944444</v>
+      </c>
+      <c s="22" r="G338">
+        <v>46308.3958333333</v>
+      </c>
+      <c s="21" t="inlineStr" r="H338">
+        <is>
+          <t xml:space="preserve">11</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I338"/>
+      <c s="21" t="inlineStr" r="J338">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K338">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L338">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M338"/>
+      <c s="20" t="inlineStr" r="N338">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O338">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 11 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P338"/>
+      <c s="20" t="inlineStr" r="R338">
+        <is>
+          <t xml:space="preserve">509e38f0-c700-11f1-a3f7-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S338">
+        <is>
+          <t xml:space="preserve">10049152    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U338">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V338"/>
+    </row>
+    <row r="339" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A339">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B339">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D339">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E339">
+        <v>46308.3972222222</v>
+      </c>
+      <c s="18" r="G339">
+        <v>46308.4</v>
+      </c>
+      <c s="17" t="inlineStr" r="H339">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I339"/>
+      <c s="17" t="inlineStr" r="J339">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K339">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L339">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M339"/>
+      <c s="16" t="inlineStr" r="N339">
+        <is>
+          <t xml:space="preserve">AJUSTE DA MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O339">
+        <is>
+          <t xml:space="preserve">ajuste da mesa para tamanho de chapa</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P339"/>
+      <c s="16" t="inlineStr" r="R339">
+        <is>
+          <t xml:space="preserve">34065bd0-c702-11f1-c576-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S339">
+        <is>
+          <t xml:space="preserve">10049152    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U339">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V339"/>
+    </row>
+    <row r="340" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A340">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B340">
+        <is>
+          <t xml:space="preserve">TR05-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D340">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E340">
+        <v>46308.4034722222</v>
+      </c>
+      <c s="22" r="G340">
+        <v>46308.40625</v>
+      </c>
+      <c s="21" t="inlineStr" r="H340">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I340"/>
+      <c s="21" t="inlineStr" r="J340">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K340">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L340">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M340"/>
+      <c s="20" t="inlineStr" r="N340">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE FARDO</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O340">
+        <is>
+          <t xml:space="preserve">passagem de fardo</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P340"/>
+      <c s="20" t="inlineStr" r="R340">
+        <is>
+          <t xml:space="preserve">7151c690-c703-11f1-cf4b-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S340">
+        <is>
+          <t xml:space="preserve">10047516    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U340">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V340"/>
+    </row>
+    <row r="341" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A341">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B341">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D341">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E341">
+        <v>46308.4319444444</v>
+      </c>
+      <c s="18" r="G341">
+        <v>46308.4347222222</v>
+      </c>
+      <c s="17" t="inlineStr" r="H341">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I341"/>
+      <c s="17" t="inlineStr" r="J341">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K341">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L341">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M341"/>
+      <c s="16" t="inlineStr" r="N341">
+        <is>
+          <t xml:space="preserve">AJUSTE DA MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O341">
+        <is>
+          <t xml:space="preserve">ajustando chapa enganchada</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P341"/>
+      <c s="16" t="inlineStr" r="R341">
+        <is>
+          <t xml:space="preserve">24fbc970-c709-11f1-8402-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S341">
+        <is>
+          <t xml:space="preserve">10049152    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U341">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V341"/>
+    </row>
+    <row r="342" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A342">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B342">
+        <is>
+          <t xml:space="preserve">TR04-ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D342">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E342">
+        <v>46308.4375</v>
+      </c>
+      <c s="22" r="G342">
+        <v>46308.4444444444</v>
+      </c>
+      <c s="21" t="inlineStr" r="H342">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I342"/>
+      <c s="21" t="inlineStr" r="J342">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K342">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L342">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M342"/>
+      <c s="20" t="inlineStr" r="N342">
+        <is>
+          <t xml:space="preserve">SETUP COMPLETO</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O342">
+        <is>
+          <t xml:space="preserve">trocar 1.25x1.000 para 0.60x1.000 e fazer regulagem</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P342"/>
+      <c s="20" t="inlineStr" r="R342">
+        <is>
+          <t xml:space="preserve">f833df00-c70c-11f1-9345-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S342">
+        <is>
+          <t xml:space="preserve">10049287    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U342">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V342"/>
+    </row>
+    <row r="343" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A343">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B343">
+        <is>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D343">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E343">
+        <v>46308.4451388889</v>
+      </c>
+      <c s="18" r="G343">
+        <v>46308.4486111111</v>
+      </c>
+      <c s="17" t="inlineStr" r="H343">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I343"/>
+      <c s="17" t="inlineStr" r="J343">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K343">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L343">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M343"/>
+      <c s="16" t="inlineStr" r="N343">
+        <is>
+          <t xml:space="preserve">QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O343">
+        <is>
+          <t xml:space="preserve">Bobina 0.60x1.000 de UD.2003627062 com oxidação OBS. Inspetor de qualidade Alisson autorizou cortar</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P343"/>
+      <c s="16" t="inlineStr" r="R343">
+        <is>
+          <t xml:space="preserve">3d4943f0-c70d-11f1-a757-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S343">
+        <is>
+          <t xml:space="preserve">10049287    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U343">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V343"/>
+    </row>
+    <row r="344" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A344">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B344">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D344">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E344">
+        <v>46308.4451388889</v>
+      </c>
+      <c s="22" r="G344">
+        <v>46308.4493055556</v>
+      </c>
+      <c s="21" t="inlineStr" r="H344">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I344"/>
+      <c s="21" t="inlineStr" r="J344">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K344">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L344">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M344"/>
+      <c s="20" t="inlineStr" r="N344">
+        <is>
+          <t xml:space="preserve">AJUSTE DA MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O344">
+        <is>
+          <t xml:space="preserve">ajuste da mesa</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P344"/>
+      <c s="20" t="inlineStr" r="R344">
+        <is>
+          <t xml:space="preserve">d32cc3d0-c70b-11f1-a48c-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S344">
+        <is>
+          <t xml:space="preserve">10048479    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U344">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V344"/>
+    </row>
+    <row r="345" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A345">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B345">
+        <is>
+          <t xml:space="preserve">TR05-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D345">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E345">
+        <v>46308.4458333333</v>
+      </c>
+      <c s="18" r="G345">
+        <v>46308.4534722222</v>
+      </c>
+      <c s="17" t="inlineStr" r="H345">
+        <is>
+          <t xml:space="preserve">11</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I345"/>
+      <c s="17" t="inlineStr" r="J345">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K345">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L345">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M345"/>
+      <c s="16" t="inlineStr" r="N345">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O345">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 11 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P345"/>
+      <c s="16" t="inlineStr" r="R345">
+        <is>
+          <t xml:space="preserve">ef996050-c70b-11f1-8656-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S345">
+        <is>
+          <t xml:space="preserve">10047516    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U345">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V345"/>
+    </row>
+    <row r="346" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A346">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B346">
+        <is>
+          <t xml:space="preserve">TR02-GUILHOTINA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D346">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E346">
+        <v>46308.46875</v>
+      </c>
+      <c s="22" r="G346">
+        <v>46308.4847222222</v>
+      </c>
+      <c s="21" t="inlineStr" r="H346">
+        <is>
+          <t xml:space="preserve">23</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I346"/>
+      <c s="21" t="inlineStr" r="J346">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K346">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L346">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M346"/>
+      <c s="20" t="inlineStr" r="N346">
+        <is>
+          <t xml:space="preserve">SETUP COMPLETO</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O346">
+        <is>
+          <t xml:space="preserve">Setup completo</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P346"/>
+      <c s="20" t="inlineStr" r="R346">
+        <is>
+          <t xml:space="preserve">9b5c07e0-c710-11f1-c525-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S346">
+        <is>
+          <t xml:space="preserve">10049316    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U346">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V346"/>
+    </row>
+    <row r="347" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A347">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B347">
+        <is>
+          <t xml:space="preserve">TR05-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D347">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E347">
+        <v>46308.4743055556</v>
+      </c>
+      <c s="18" r="G347">
+        <v>46308.4763888889</v>
+      </c>
+      <c s="17" t="inlineStr" r="H347">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I347"/>
+      <c s="17" t="inlineStr" r="J347">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K347">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L347">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M347"/>
+      <c s="16" t="inlineStr" r="N347">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE FARDO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O347">
+        <is>
+          <t xml:space="preserve">passagem de fardo</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P347"/>
+      <c s="16" t="inlineStr" r="R347">
+        <is>
+          <t xml:space="preserve">ba273860-c711-11f1-922c-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S347">
+        <is>
+          <t xml:space="preserve">10047449    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U347">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V347"/>
+    </row>
+    <row r="348" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A348">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B348"/>
+      <c s="21" t="inlineStr" r="D348">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E348">
+        <v>46308.4854166667</v>
+      </c>
+      <c s="22" r="G348">
+        <v>46308.4875</v>
+      </c>
+      <c s="21" t="inlineStr" r="H348">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I348"/>
+      <c s="21" t="inlineStr" r="J348">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K348">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L348">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M348"/>
+      <c s="20" t="inlineStr" r="N348">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O348">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 3 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P348"/>
+      <c s="20" t="inlineStr" r="R348">
+        <is>
+          <t xml:space="preserve">e055c720-c713-11f1-b537-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S348">
+        <is>
+          <t xml:space="preserve">10049316    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U348">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V348"/>
+    </row>
+    <row r="349" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A349">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B349"/>
+      <c s="17" t="inlineStr" r="D349">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E349">
+        <v>46308.5013888889</v>
+      </c>
+      <c s="18" r="G349">
+        <v>46308.5041666667</v>
+      </c>
+      <c s="17" t="inlineStr" r="H349">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I349"/>
+      <c s="17" t="inlineStr" r="J349">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K349">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L349">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M349"/>
+      <c s="16" t="inlineStr" r="N349">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O349">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 4 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P349"/>
+      <c s="16" t="inlineStr" r="R349">
+        <is>
+          <t xml:space="preserve">12ea8290-c717-11f1-b800-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S349">
+        <is>
+          <t xml:space="preserve">10048479    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U349">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V349"/>
+    </row>
+    <row r="350" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A350">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B350">
+        <is>
+          <t xml:space="preserve">TR05-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D350">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E350">
+        <v>46308.5104166667</v>
+      </c>
+      <c s="22" r="G350">
+        <v>46308.51875</v>
+      </c>
+      <c s="21" t="inlineStr" r="H350">
+        <is>
+          <t xml:space="preserve">12</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I350"/>
+      <c s="21" t="inlineStr" r="J350">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K350">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L350">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M350"/>
+      <c s="20" t="inlineStr" r="N350">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O350">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO.</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P350"/>
+      <c s="20" t="inlineStr" r="R350">
+        <is>
+          <t xml:space="preserve">e445fad0-c718-11f1-a219-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S350">
+        <is>
+          <t xml:space="preserve">10047449    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U350">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V350"/>
+    </row>
+    <row r="351" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A351">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B351"/>
+      <c s="17" t="inlineStr" r="D351">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E351">
+        <v>46308.5173611111</v>
+      </c>
+      <c s="18" r="G351">
+        <v>46308.5236111111</v>
+      </c>
+      <c s="17" t="inlineStr" r="H351">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I351"/>
+      <c s="17" t="inlineStr" r="J351">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K351">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L351">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M351"/>
+      <c s="16" t="inlineStr" r="N351">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O351">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 9 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P351"/>
+      <c s="16" t="inlineStr" r="R351">
+        <is>
+          <t xml:space="preserve">5be13900-c71a-11f1-94ca-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S351">
+        <is>
+          <t xml:space="preserve">10049316    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U351">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V351"/>
+    </row>
+    <row r="352" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A352">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B352">
+        <is>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D352">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E352">
+        <v>46308.5208333333</v>
+      </c>
+      <c s="22" r="G352">
+        <v>46308.5243055556</v>
+      </c>
+      <c s="21" t="inlineStr" r="H352">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I352"/>
+      <c s="21" t="inlineStr" r="J352">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K352">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L352">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M352"/>
+      <c s="20" t="inlineStr" r="N352">
+        <is>
+          <t xml:space="preserve">QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O352">
+        <is>
+          <t xml:space="preserve">Bobina 0.60x1.000 com oxidação OBS. Inspetor de qualidade Alisson autorizou cortar como material bom.</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P352"/>
+      <c s="20" t="inlineStr" r="R352">
+        <is>
+          <t xml:space="preserve">1a61fdb0-c71b-11f1-c006-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S352">
+        <is>
+          <t xml:space="preserve">10049287    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U352">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V352"/>
+    </row>
+    <row r="353" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A353">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B353">
+        <is>
+          <t xml:space="preserve">TR05-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D353">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E353">
+        <v>46308.5215277778</v>
+      </c>
+      <c s="18" r="G353">
+        <v>46308.5277777778</v>
+      </c>
+      <c s="17" t="inlineStr" r="H353">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I353"/>
+      <c s="17" t="inlineStr" r="J353">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K353">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L353">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M353"/>
+      <c s="16" t="inlineStr" r="N353">
+        <is>
+          <t xml:space="preserve">RETIRADA DE PNC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O353">
+        <is>
+          <t xml:space="preserve">retirada de pnc</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P353"/>
+      <c s="16" t="inlineStr" r="R353">
+        <is>
+          <t xml:space="preserve">e74a6460-c71c-11f1-aba2-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S353">
+        <is>
+          <t xml:space="preserve">10047449    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U353">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V353"/>
+    </row>
+    <row r="354" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A354">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B354"/>
+      <c s="21" t="inlineStr" r="D354">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E354">
+        <v>46308.525</v>
+      </c>
+      <c s="22" r="G354">
+        <v>46308.5284722222</v>
+      </c>
+      <c s="21" t="inlineStr" r="H354">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I354"/>
+      <c s="21" t="inlineStr" r="J354">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K354">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L354">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M354"/>
+      <c s="20" t="inlineStr" r="N354">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O354">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 5 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P354"/>
+      <c s="20" t="inlineStr" r="R354">
+        <is>
+          <t xml:space="preserve">e9567d80-c71b-11f1-a5e7-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S354">
+        <is>
+          <t xml:space="preserve">10049316    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U354">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V354"/>
+    </row>
+    <row r="355" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A355">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B355"/>
+      <c s="17" t="inlineStr" r="D355">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E355">
+        <v>46308.5430555556</v>
+      </c>
+      <c s="18" r="G355">
+        <v>46308.5513888889</v>
+      </c>
+      <c s="17" t="inlineStr" r="H355">
+        <is>
+          <t xml:space="preserve">12</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I355"/>
+      <c s="17" t="inlineStr" r="J355">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K355">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L355">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M355"/>
+      <c s="16" t="inlineStr" r="N355">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O355">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 12 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P355"/>
+      <c s="16" t="inlineStr" r="R355">
+        <is>
+          <t xml:space="preserve">7cd58e40-c71f-11f1-c8d2-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S355">
+        <is>
+          <t xml:space="preserve">10048480    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U355">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V355"/>
+    </row>
+    <row r="356" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A356">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B356"/>
+      <c s="21" t="inlineStr" r="D356">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E356">
+        <v>46308.5666666667</v>
+      </c>
+      <c s="22" r="G356">
+        <v>46308.5763888889</v>
+      </c>
+      <c s="21" t="inlineStr" r="H356">
+        <is>
+          <t xml:space="preserve">14</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I356"/>
+      <c s="21" t="inlineStr" r="J356">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K356">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L356">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M356"/>
+      <c s="20" t="inlineStr" r="N356">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O356">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 14 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P356"/>
+      <c s="20" t="inlineStr" r="R356">
+        <is>
+          <t xml:space="preserve">4b8b3380-c724-11f1-8300-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S356">
+        <is>
+          <t xml:space="preserve">10049316    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U356">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V356"/>
+    </row>
+    <row r="357" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A357">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B357">
+        <is>
+          <t xml:space="preserve">TR05-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D357">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E357">
+        <v>46308.5881944444</v>
+      </c>
+      <c s="18" r="G357">
+        <v>46308.5972106481</v>
+      </c>
+      <c s="17" t="inlineStr" r="H357">
+        <is>
+          <t xml:space="preserve">13</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I357"/>
+      <c s="17" t="inlineStr" r="J357">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K357">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L357">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M357"/>
+      <c s="16" t="inlineStr" r="N357">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O357">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 13 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P357"/>
+      <c s="16" t="inlineStr" r="R357">
+        <is>
+          <t xml:space="preserve">975511b0-c728-11f1-9e62-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S357">
+        <is>
+          <t xml:space="preserve">10047449    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U357">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V357"/>
+    </row>
+    <row r="358" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A358">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B358"/>
+      <c s="21" t="inlineStr" r="D358">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E358">
+        <v>46308.5909722222</v>
+      </c>
+      <c s="22" r="G358">
+        <v>46308.6</v>
+      </c>
+      <c s="21" t="inlineStr" r="H358">
+        <is>
+          <t xml:space="preserve">13</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I358"/>
+      <c s="21" t="inlineStr" r="J358">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K358">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L358">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M358"/>
+      <c s="20" t="inlineStr" r="N358">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O358">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 13 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P358"/>
+      <c s="20" t="inlineStr" r="R358">
+        <is>
+          <t xml:space="preserve">179abf00-c729-11f1-86ad-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S358">
+        <is>
+          <t xml:space="preserve">10048480    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U358">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V358"/>
+    </row>
+    <row r="359" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A359">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B359">
+        <is>
+          <t xml:space="preserve">TR04-ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D359">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E359">
+        <v>46308.59375</v>
+      </c>
+      <c s="18" r="G359">
+        <v>46308.6006944444</v>
+      </c>
+      <c s="17" t="inlineStr" r="H359">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I359"/>
+      <c s="17" t="inlineStr" r="J359">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K359">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L359">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M359"/>
+      <c s="16" t="inlineStr" r="N359">
+        <is>
+          <t xml:space="preserve">SETUP COMPLETO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O359">
+        <is>
+          <t xml:space="preserve">trocar 0.60x1.000 para 0.95x1000 e fazer regulagem</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P359"/>
+      <c s="16" t="inlineStr" r="R359">
+        <is>
+          <t xml:space="preserve">de9a5cb0-c72d-11f1-8965-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S359">
+        <is>
+          <t xml:space="preserve">10049287    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U359">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V359"/>
+    </row>
+    <row r="360" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A360">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B360"/>
+      <c s="21" t="inlineStr" r="D360">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E360">
+        <v>46308.6034722222</v>
+      </c>
+      <c s="22" r="G360">
+        <v>46308.6118055556</v>
+      </c>
+      <c s="21" t="inlineStr" r="H360">
+        <is>
+          <t xml:space="preserve">12</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I360"/>
+      <c s="21" t="inlineStr" r="J360">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K360">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L360">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M360"/>
+      <c s="20" t="inlineStr" r="N360">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O360">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 12 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P360"/>
+      <c s="20" t="inlineStr" r="R360">
+        <is>
+          <t xml:space="preserve">98d25b80-c72b-11f1-84cb-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S360">
+        <is>
+          <t xml:space="preserve">10049316    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U360">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V360"/>
+    </row>
+    <row r="361" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A361">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B361">
+        <is>
+          <t xml:space="preserve">TR01-UNIDADE DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D361">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E361">
+        <v>46308.6069444444</v>
+      </c>
+      <c s="18" r="G361">
+        <v>46308.6111111111</v>
+      </c>
+      <c s="17" t="inlineStr" r="H361">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I361"/>
+      <c s="17" t="inlineStr" r="J361">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K361">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L361">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M361"/>
+      <c s="16" t="inlineStr" r="N361">
+        <is>
+          <t xml:space="preserve">AJUSTE NO ROLO ALIMENTADOR</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O361">
+        <is>
+          <t xml:space="preserve">ajuste no rolo alimentador</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P361"/>
+      <c s="16" t="inlineStr" r="R361">
+        <is>
+          <t xml:space="preserve">5d494f50-c72c-11f1-843f-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S361">
+        <is>
+          <t xml:space="preserve">10048480    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U361">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V361"/>
+    </row>
+    <row r="362" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A362">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B362">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D362">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E362">
+        <v>46308.6263888889</v>
+      </c>
+      <c s="22" r="G362">
+        <v>46308.6291666667</v>
+      </c>
+      <c s="21" t="inlineStr" r="H362">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I362"/>
+      <c s="21" t="inlineStr" r="J362">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K362">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L362">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M362"/>
+      <c s="20" t="inlineStr" r="N362">
+        <is>
+          <t xml:space="preserve">AJUSTE DA MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O362">
+        <is>
+          <t xml:space="preserve">ajuste da mesa para tamanho de chapa</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P362"/>
+      <c s="20" t="inlineStr" r="R362">
+        <is>
+          <t xml:space="preserve">4cccbdc0-c730-11f1-92a5-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S362">
+        <is>
+          <t xml:space="preserve">10048769    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U362">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V362"/>
+    </row>
+    <row r="363" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A363">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B363"/>
+      <c s="17" t="inlineStr" r="D363">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E363">
+        <v>46308.6409722222</v>
+      </c>
+      <c s="18" r="G363">
+        <v>46308.6486111111</v>
+      </c>
+      <c s="17" t="inlineStr" r="H363">
+        <is>
+          <t xml:space="preserve">11</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I363"/>
+      <c s="17" t="inlineStr" r="J363">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K363">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L363">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M363"/>
+      <c s="16" t="inlineStr" r="N363">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O363">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 11 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P363"/>
+      <c s="16" t="inlineStr" r="R363">
+        <is>
+          <t xml:space="preserve">34ab0a00-c733-11f1-a26d-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S363">
+        <is>
+          <t xml:space="preserve">10049316    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U363">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V363"/>
+    </row>
+    <row r="364" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A364">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B364"/>
+      <c s="21" t="inlineStr" r="D364">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E364">
+        <v>46308.6423611111</v>
+      </c>
+      <c s="22" r="G364">
+        <v>46308.6527777778</v>
+      </c>
+      <c s="21" t="inlineStr" r="H364">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I364"/>
+      <c s="21" t="inlineStr" r="J364">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K364">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L364">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M364"/>
+      <c s="20" t="inlineStr" r="N364">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O364">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P364"/>
+      <c s="20" t="inlineStr" r="R364">
+        <is>
+          <t xml:space="preserve">83c1ed20-c733-11f1-c611-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S364">
+        <is>
+          <t xml:space="preserve">10048770    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U364">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V364"/>
+    </row>
+    <row r="365" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A365">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B365">
+        <is>
+          <t xml:space="preserve">TR05-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D365">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E365">
+        <v>46308.6451388889</v>
+      </c>
+      <c s="18" r="G365">
+        <v>46308.6680555556</v>
+      </c>
+      <c s="17" t="inlineStr" r="H365">
+        <is>
+          <t xml:space="preserve">33</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I365"/>
+      <c s="17" t="inlineStr" r="J365">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K365">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L365">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M365"/>
+      <c s="16" t="inlineStr" r="N365">
+        <is>
+          <t xml:space="preserve">MEP - FALTA MATÉRIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O365">
+        <is>
+          <t xml:space="preserve">falta de matéria prima</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P365"/>
+      <c s="16" t="inlineStr" r="R365">
+        <is>
+          <t xml:space="preserve">0ddfa230-c735-11f1-9266-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S365">
+        <is>
+          <t xml:space="preserve">10048459    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U365">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V365"/>
+    </row>
+    <row r="366" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A366">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B366">
+        <is>
+          <t xml:space="preserve">TR05-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D366">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E366">
+        <v>46308.66875</v>
+      </c>
+      <c s="22" r="G366">
+        <v>46308.6777777778</v>
+      </c>
+      <c s="21" t="inlineStr" r="H366">
+        <is>
+          <t xml:space="preserve">13</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I366"/>
+      <c s="21" t="inlineStr" r="J366">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K366">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L366">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M366"/>
+      <c s="20" t="inlineStr" r="N366">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O366">
+        <is>
+          <t xml:space="preserve">abastecimento de matéria prima</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P366"/>
+      <c s="20" t="inlineStr" r="R366">
+        <is>
+          <t xml:space="preserve">d68a2630-c738-11f1-b920-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S366">
+        <is>
+          <t xml:space="preserve">10048459    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U366">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V366"/>
+    </row>
+    <row r="367" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A367">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B367"/>
+      <c s="17" t="inlineStr" r="D367">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E367">
+        <v>46308.6743055556</v>
+      </c>
+      <c s="18" r="G367">
+        <v>46308.6763888889</v>
+      </c>
+      <c s="17" t="inlineStr" r="H367">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I367"/>
+      <c s="17" t="inlineStr" r="J367">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K367">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L367">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M367"/>
+      <c s="16" t="inlineStr" r="N367">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O367">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 3 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P367"/>
+      <c s="16" t="inlineStr" r="R367">
+        <is>
+          <t xml:space="preserve">d86929f0-c739-11f1-8c65-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S367">
+        <is>
+          <t xml:space="preserve">10049316    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U367">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V367"/>
+    </row>
+    <row r="368" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A368">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B368">
+        <is>
+          <t xml:space="preserve">TR05-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D368">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E368">
+        <v>46308.6861111111</v>
+      </c>
+      <c s="22" r="G368">
+        <v>46308.6881944444</v>
+      </c>
+      <c s="21" t="inlineStr" r="H368">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I368"/>
+      <c s="21" t="inlineStr" r="J368">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K368">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L368">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M368"/>
+      <c s="20" t="inlineStr" r="N368">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE FARDO</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O368">
+        <is>
+          <t xml:space="preserve">passagem de fardo</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P368"/>
+      <c s="20" t="inlineStr" r="R368">
+        <is>
+          <t xml:space="preserve">52d17560-c73c-11f1-b035-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S368">
+        <is>
+          <t xml:space="preserve">10048460    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U368">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V368"/>
+    </row>
+    <row r="369" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A369">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B369">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D369">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E369">
+        <v>46308.6958333333</v>
+      </c>
+      <c s="18" r="G369">
+        <v>46308.70625</v>
+      </c>
+      <c s="17" t="inlineStr" r="H369">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I369"/>
+      <c s="17" t="inlineStr" r="J369">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K369">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L369">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M369"/>
+      <c s="16" t="inlineStr" r="N369">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O369">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P369"/>
+      <c s="16" t="inlineStr" r="R369">
+        <is>
+          <t xml:space="preserve">e2f474c0-c73d-11f1-a003-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S369">
+        <is>
+          <t xml:space="preserve">10048771    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U369">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V369"/>
+    </row>
+    <row r="370" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A370">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B370">
+        <is>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D370">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E370">
+        <v>46308.6958333333</v>
+      </c>
+      <c s="22" r="G370">
+        <v>46309.2909722222</v>
+      </c>
+      <c s="21" t="inlineStr" r="H370">
+        <is>
+          <t xml:space="preserve">857</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I370"/>
+      <c s="21" t="inlineStr" r="J370">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K370">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L370">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M370"/>
+      <c s="20" t="inlineStr" r="N370">
+        <is>
+          <t xml:space="preserve">FALTA DEMANDA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O370">
+        <is>
+          <t xml:space="preserve">falta de demanda</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P370"/>
+      <c s="20" t="inlineStr" r="R370">
+        <is>
+          <t xml:space="preserve">4f550df0-c73e-11f1-918f-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S370">
+        <is>
+          <t xml:space="preserve">10048460    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U370">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V370"/>
+    </row>
+    <row r="371" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A371">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B371">
+        <is>
+          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D371">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E371">
+        <v>46308.6979166667</v>
+      </c>
+      <c s="18" r="G371">
+        <v>46309.2493055556</v>
+      </c>
+      <c s="17" t="inlineStr" r="H371">
+        <is>
+          <t xml:space="preserve">794</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I371"/>
+      <c s="17" t="inlineStr" r="J371">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K371">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L371">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M371"/>
+      <c s="16" t="inlineStr" r="N371">
+        <is>
+          <t xml:space="preserve">FALTA DEMANDA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O371">
+        <is>
+          <t xml:space="preserve">Tempo livre.</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P371"/>
+      <c s="16" t="inlineStr" r="R371">
+        <is>
+          <t xml:space="preserve">a38d1cf0-c73e-11f1-8261-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S371">
+        <is>
+          <t xml:space="preserve">10049316    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U371">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V371"/>
+    </row>
+    <row r="372" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A372">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 03</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B372"/>
+      <c s="21" t="inlineStr" r="D372">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E372">
+        <v>46308.7013888889</v>
+      </c>
+      <c s="22" r="G372">
+        <v>46309.2840277778</v>
+      </c>
+      <c s="21" t="inlineStr" r="H372">
+        <is>
+          <t xml:space="preserve">839</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I372"/>
+      <c s="21" t="inlineStr" r="J372">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K372">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L372">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M372"/>
+      <c s="20" t="inlineStr" r="N372">
+        <is>
+          <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O372">
+        <is>
+          <t xml:space="preserve">Parada registrada automaticamente pelo sistema</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P372"/>
+      <c s="20" t="inlineStr" r="R372">
+        <is>
+          <t xml:space="preserve">471c2550-c73f-11f1-9b2c-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="S372"/>
+      <c s="20" t="inlineStr" r="U372">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V372"/>
+    </row>
+    <row r="373" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A373">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B373"/>
+      <c s="17" t="inlineStr" r="D373">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E373">
+        <v>46308.7013888889</v>
+      </c>
+      <c s="18" r="G373">
+        <v>46309.2840277778</v>
+      </c>
+      <c s="17" t="inlineStr" r="H373">
+        <is>
+          <t xml:space="preserve">839</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I373"/>
+      <c s="17" t="inlineStr" r="J373">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K373">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L373">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M373"/>
+      <c s="16" t="inlineStr" r="N373">
+        <is>
+          <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O373">
+        <is>
+          <t xml:space="preserve">Parada registrada automaticamente pelo sistema</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P373"/>
+      <c s="16" t="inlineStr" r="R373">
+        <is>
+          <t xml:space="preserve">473aa9d0-c73f-11f1-caf1-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S373">
+        <is>
+          <t xml:space="preserve">10049290    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U373">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V373"/>
+    </row>
+    <row r="374" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A374">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B374">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D374">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E374">
+        <v>46308.7069444444</v>
+      </c>
+      <c s="22" r="G374">
+        <v>46309.2909722222</v>
+      </c>
+      <c s="21" t="inlineStr" r="H374">
+        <is>
+          <t xml:space="preserve">841</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I374"/>
+      <c s="21" t="inlineStr" r="J374">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K374">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L374">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M374"/>
+      <c s="20" t="inlineStr" r="N374">
+        <is>
+          <t xml:space="preserve">FALTA DEMANDA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O374">
+        <is>
+          <t xml:space="preserve">tempo livre</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P374"/>
+      <c s="20" t="inlineStr" r="R374">
+        <is>
+          <t xml:space="preserve">46875460-c7b8-11f1-89de-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S374">
+        <is>
+          <t xml:space="preserve">10048771    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U374">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V374"/>
+    </row>
+    <row r="375" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A375">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B375">
+        <is>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D375">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E375">
+        <v>46309.2847222222</v>
+      </c>
+      <c s="18" r="G375">
+        <v>46309.2916666667</v>
+      </c>
+      <c s="17" t="inlineStr" r="H375">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I375"/>
+      <c s="17" t="inlineStr" r="J375">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K375">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L375">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M375"/>
+      <c s="16" t="inlineStr" r="N375">
+        <is>
+          <t xml:space="preserve">DDS</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O375">
+        <is>
+          <t xml:space="preserve">DDS</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P375"/>
+      <c s="16" t="inlineStr" r="R375">
+        <is>
+          <t xml:space="preserve">df4312d0-c7bc-11f1-b3e6-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S375">
+        <is>
+          <t xml:space="preserve">10049290    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U375">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V375"/>
+    </row>
+    <row r="376" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A376">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B376">
+        <is>
+          <t xml:space="preserve">TR01-INTRODUTOR</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D376">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E376">
+        <v>46309.2916666667</v>
+      </c>
+      <c s="22" r="G376">
+        <v>46309.3020833333</v>
+      </c>
+      <c s="21" t="inlineStr" r="H376">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I376"/>
+      <c s="21" t="inlineStr" r="J376">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K376">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L376">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M376"/>
+      <c s="20" t="inlineStr" r="N376">
+        <is>
+          <t xml:space="preserve">DDS</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O376">
+        <is>
+          <t xml:space="preserve">dds e assinatura dos documentos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P376"/>
+      <c s="20" t="inlineStr" r="R376">
+        <is>
+          <t xml:space="preserve">93690800-c7b8-11f1-8505-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S376">
+        <is>
+          <t xml:space="preserve">10048771    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U376">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V376"/>
+    </row>
+    <row r="377" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A377">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B377">
+        <is>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D377">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E377">
+        <v>46309.2916666667</v>
+      </c>
+      <c s="18" r="G377">
+        <v>46309.2986111111</v>
+      </c>
+      <c s="17" t="inlineStr" r="H377">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I377"/>
+      <c s="17" t="inlineStr" r="J377">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K377">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L377">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M377"/>
+      <c s="16" t="inlineStr" r="N377">
+        <is>
+          <t xml:space="preserve">DDS</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O377">
+        <is>
+          <t xml:space="preserve">dds</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P377"/>
+      <c s="16" t="inlineStr" r="R377">
+        <is>
+          <t xml:space="preserve">732e6900-c7b7-11f1-c550-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S377">
+        <is>
+          <t xml:space="preserve">10048460    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U377">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V377"/>
+    </row>
+    <row r="378" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A378">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B378">
+        <is>
+          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D378">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E378">
+        <v>46309.2916666667</v>
+      </c>
+      <c s="22" r="G378">
+        <v>46309.2986111111</v>
+      </c>
+      <c s="21" t="inlineStr" r="H378">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I378"/>
+      <c s="21" t="inlineStr" r="J378">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K378">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L378">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M378"/>
+      <c s="20" t="inlineStr" r="N378">
+        <is>
+          <t xml:space="preserve">DDS</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O378">
+        <is>
+          <t xml:space="preserve">DDS</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P378"/>
+      <c s="20" t="inlineStr" r="R378">
+        <is>
+          <t xml:space="preserve">7fd8f910-c7b5-11f1-a842-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S378">
+        <is>
+          <t xml:space="preserve">10049316    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U378">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V378"/>
+    </row>
+    <row r="379" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A379">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B379">
+        <is>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D379">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E379">
+        <v>46309.2923611111</v>
+      </c>
+      <c s="18" r="G379">
+        <v>46309.2993055556</v>
+      </c>
+      <c s="17" t="inlineStr" r="H379">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I379"/>
+      <c s="17" t="inlineStr" r="J379">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K379">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L379">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M379"/>
+      <c s="16" t="inlineStr" r="N379">
+        <is>
+          <t xml:space="preserve">ASSINATURA DE DOCUMENTOS</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O379">
+        <is>
+          <t xml:space="preserve">Assinatura de documentos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P379"/>
+      <c s="16" t="inlineStr" r="R379">
+        <is>
+          <t xml:space="preserve">1c4cd620-c7bd-11f1-bd8d-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S379">
+        <is>
+          <t xml:space="preserve">10049290    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U379">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V379"/>
+    </row>
+    <row r="380" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A380">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B380"/>
+      <c s="21" t="inlineStr" r="D380">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E380">
+        <v>46309.3097222222</v>
+      </c>
+      <c s="22" r="G380">
+        <v>46309.3201388889</v>
+      </c>
+      <c s="21" t="inlineStr" r="H380">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I380"/>
+      <c s="21" t="inlineStr" r="J380">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K380">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L380">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M380"/>
+      <c s="20" t="inlineStr" r="N380">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O380">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P380"/>
+      <c s="20" t="inlineStr" r="R380">
+        <is>
+          <t xml:space="preserve">ae71d951-c7b9-11f1-b991-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S380">
+        <is>
+          <t xml:space="preserve">10049316    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U380">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V380"/>
+    </row>
+    <row r="381" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A381">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B381"/>
+      <c s="17" t="inlineStr" r="D381">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E381">
+        <v>46309.3104166667</v>
+      </c>
+      <c s="18" r="G381">
+        <v>46309.3208333333</v>
+      </c>
+      <c s="17" t="inlineStr" r="H381">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I381"/>
+      <c s="17" t="inlineStr" r="J381">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K381">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L381">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M381"/>
+      <c s="16" t="inlineStr" r="N381">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O381">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P381"/>
+      <c s="16" t="inlineStr" r="R381">
+        <is>
+          <t xml:space="preserve">dabafa00-c7b9-11f1-a325-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S381">
+        <is>
+          <t xml:space="preserve">10048771    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U381">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V381"/>
+    </row>
+    <row r="382" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A382">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B382">
+        <is>
+          <t xml:space="preserve">TR05-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D382">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E382">
+        <v>46309.3125</v>
+      </c>
+      <c s="22" r="G382">
+        <v>46309.3215277778</v>
+      </c>
+      <c s="21" t="inlineStr" r="H382">
+        <is>
+          <t xml:space="preserve">13</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I382"/>
+      <c s="21" t="inlineStr" r="J382">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K382">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L382">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M382"/>
+      <c s="20" t="inlineStr" r="N382">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O382">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 13 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P382"/>
+      <c s="20" t="inlineStr" r="R382">
+        <is>
+          <t xml:space="preserve">4fec0b70-c7ba-11f1-9fd7-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S382">
+        <is>
+          <t xml:space="preserve">10048460    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U382">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V382"/>
+    </row>
+    <row r="383" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A383">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B383">
+        <is>
+          <t xml:space="preserve">TR02-MESA TRANSPORTADORA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D383">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E383">
+        <v>46309.3208333333</v>
+      </c>
+      <c s="18" r="G383">
+        <v>46309.3229166667</v>
+      </c>
+      <c s="17" t="inlineStr" r="H383">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I383"/>
+      <c s="17" t="inlineStr" r="J383">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K383">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L383">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M383"/>
+      <c s="16" t="inlineStr" r="N383">
+        <is>
+          <t xml:space="preserve">RETIRADA DE PNC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O383">
+        <is>
+          <t xml:space="preserve">Retirada de pnc</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P383"/>
+      <c s="16" t="inlineStr" r="R383">
+        <is>
+          <t xml:space="preserve">68499d70-c7bc-11f1-bdec-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S383">
+        <is>
+          <t xml:space="preserve">10049316    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U383">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V383"/>
+    </row>
+    <row r="384" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A384">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B384">
+        <is>
+          <t xml:space="preserve">TR01-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D384">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E384">
+        <v>46309.3215277778</v>
+      </c>
+      <c s="22" r="G384">
+        <v>46309.3305555556</v>
+      </c>
+      <c s="21" t="inlineStr" r="H384">
+        <is>
+          <t xml:space="preserve">13</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I384"/>
+      <c s="21" t="inlineStr" r="J384">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K384">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L384">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M384"/>
+      <c s="20" t="inlineStr" r="N384">
+        <is>
+          <t xml:space="preserve">TROCA DAS CASTANHAS DO MANDRIL</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O384">
+        <is>
+          <t xml:space="preserve">troca de castanhas</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P384"/>
+      <c s="20" t="inlineStr" r="R384">
+        <is>
+          <t xml:space="preserve">de146160-c7bd-11f1-add9-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S384">
+        <is>
+          <t xml:space="preserve">10048771    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U384">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V384"/>
+    </row>
+    <row r="385" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A385">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B385"/>
+      <c s="17" t="inlineStr" r="D385">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E385">
+        <v>46309.3243055556</v>
+      </c>
+      <c s="18" r="G385">
+        <v>46309.3277777778</v>
+      </c>
+      <c s="17" t="inlineStr" r="H385">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I385"/>
+      <c s="17" t="inlineStr" r="J385">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K385">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L385">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M385"/>
+      <c s="16" t="inlineStr" r="N385">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O385">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 5 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P385"/>
+      <c s="16" t="inlineStr" r="R385">
+        <is>
+          <t xml:space="preserve">b49d68f0-c7bc-11f1-bd1c-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S385">
+        <is>
+          <t xml:space="preserve">10049316    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U385">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V385"/>
+    </row>
+    <row r="386" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A386">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B386"/>
+      <c s="21" t="inlineStr" r="D386">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E386">
+        <v>46309.3284722222</v>
+      </c>
+      <c s="22" r="G386">
+        <v>46309.33125</v>
+      </c>
+      <c s="21" t="inlineStr" r="H386">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I386"/>
+      <c s="21" t="inlineStr" r="J386">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K386">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L386">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M386"/>
+      <c s="20" t="inlineStr" r="N386">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O386">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 4 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P386"/>
+      <c s="20" t="inlineStr" r="R386">
+        <is>
+          <t xml:space="preserve">8ea65d90-c7bd-11f1-ad94-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S386">
+        <is>
+          <t xml:space="preserve">10049316    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U386">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V386"/>
+    </row>
+    <row r="387" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A387">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B387"/>
+      <c s="17" t="inlineStr" r="D387">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E387">
+        <v>46309.33125</v>
+      </c>
+      <c s="18" r="G387">
+        <v>46309.3361111111</v>
+      </c>
+      <c s="17" t="inlineStr" r="H387">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I387"/>
+      <c s="17" t="inlineStr" r="J387">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K387">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L387">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M387"/>
+      <c s="16" t="inlineStr" r="N387">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O387">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 7 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P387"/>
+      <c s="16" t="inlineStr" r="R387">
+        <is>
+          <t xml:space="preserve">1d1f4be0-c7be-11f1-9013-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S387">
+        <is>
+          <t xml:space="preserve">10049316    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U387">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V387"/>
+    </row>
+    <row r="388" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A388">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B388">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D388">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E388">
+        <v>46309.33125</v>
+      </c>
+      <c s="22" r="G388">
+        <v>46309.3375</v>
+      </c>
+      <c s="21" t="inlineStr" r="H388">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I388"/>
+      <c s="21" t="inlineStr" r="J388">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K388">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L388">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M388"/>
+      <c s="20" t="inlineStr" r="N388">
+        <is>
+          <t xml:space="preserve">AGUARDANDO INSPEÇÃO DE  QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O388">
+        <is>
+          <t xml:space="preserve">material com ponto de pressão liberado como [PNC ] UD 2003983292</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P388"/>
+      <c s="20" t="inlineStr" r="R388">
+        <is>
+          <t xml:space="preserve">deb02c30-c7bd-11f1-c196-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S388">
+        <is>
+          <t xml:space="preserve">10048771    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U388">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V388"/>
+    </row>
+    <row r="389" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A389">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B389">
+        <is>
+          <t xml:space="preserve">TR05-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D389">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E389">
+        <v>46309.3458333333</v>
+      </c>
+      <c s="18" r="G389">
+        <v>46309.3486111111</v>
+      </c>
+      <c s="17" t="inlineStr" r="H389">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I389"/>
+      <c s="17" t="inlineStr" r="J389">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K389">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L389">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M389"/>
+      <c s="16" t="inlineStr" r="N389">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE FARDO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O389">
+        <is>
+          <t xml:space="preserve">passagem de fardo</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P389"/>
+      <c s="16" t="inlineStr" r="R389">
+        <is>
+          <t xml:space="preserve">0ad23580-c7c1-11f1-cd83-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S389">
+        <is>
+          <t xml:space="preserve">10048461    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U389">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V389"/>
+    </row>
+    <row r="390" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A390">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B390">
+        <is>
+          <t xml:space="preserve">TR05-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D390">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E390">
+        <v>46309.3493055556</v>
+      </c>
+      <c s="22" r="G390">
+        <v>46309.35625</v>
+      </c>
+      <c s="21" t="inlineStr" r="H390">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I390"/>
+      <c s="21" t="inlineStr" r="J390">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K390">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L390">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M390"/>
+      <c s="20" t="inlineStr" r="N390">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O390">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 10 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P390"/>
+      <c s="20" t="inlineStr" r="R390">
+        <is>
+          <t xml:space="preserve">aade7fc0-c7c1-11f1-bec8-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S390">
+        <is>
+          <t xml:space="preserve">10048461    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U390">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V390"/>
+    </row>
+    <row r="391" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A391">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B391">
+        <is>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D391">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E391">
+        <v>46309.3583333333</v>
+      </c>
+      <c s="18" r="G391">
+        <v>46309.3694444444</v>
+      </c>
+      <c s="17" t="inlineStr" r="H391">
+        <is>
+          <t xml:space="preserve">16</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I391"/>
+      <c s="17" t="inlineStr" r="J391">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K391">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L391">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M391"/>
+      <c s="16" t="inlineStr" r="N391">
+        <is>
+          <t xml:space="preserve">QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O391">
+        <is>
+          <t xml:space="preserve">Bobina 0.43x1.000 de UD.5012476005 apresentando OBS. Só gerou um fardo bom o restante gerou PNC com autorização Inspetor de qualidade Alisson.</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P391"/>
+      <c s="16" t="inlineStr" r="R391">
+        <is>
+          <t xml:space="preserve">d97c05d0-c7c3-11f1-abc2-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S391">
+        <is>
+          <t xml:space="preserve">10049289    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U391">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V391"/>
+    </row>
+    <row r="392" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A392">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B392">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D392">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E392">
+        <v>46309.3666666667</v>
+      </c>
+      <c s="22" r="G392">
+        <v>46309.36875</v>
+      </c>
+      <c s="21" t="inlineStr" r="H392">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I392"/>
+      <c s="21" t="inlineStr" r="J392">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K392">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L392">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M392"/>
+      <c s="20" t="inlineStr" r="N392">
+        <is>
+          <t xml:space="preserve">AJUSTE DA MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O392">
+        <is>
+          <t xml:space="preserve">AJUSTE DA MESA PARA TAMANHO DE CHAPA</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P392"/>
+      <c s="20" t="inlineStr" r="R392">
+        <is>
+          <t xml:space="preserve">2e42cad1-c7c5-11f1-cfb0-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S392">
+        <is>
+          <t xml:space="preserve">10049156    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U392">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V392"/>
+    </row>
+    <row r="393" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A393">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B393"/>
+      <c s="17" t="inlineStr" r="D393">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E393">
+        <v>46309.36875</v>
+      </c>
+      <c s="18" r="G393">
+        <v>46309.3777777778</v>
+      </c>
+      <c s="17" t="inlineStr" r="H393">
+        <is>
+          <t xml:space="preserve">13</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I393"/>
+      <c s="17" t="inlineStr" r="J393">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K393">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L393">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M393"/>
+      <c s="16" t="inlineStr" r="N393">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O393">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 13 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P393"/>
+      <c s="16" t="inlineStr" r="R393">
+        <is>
+          <t xml:space="preserve">9409f000-c7c5-11f1-89a2-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S393">
+        <is>
+          <t xml:space="preserve">10049316    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U393">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V393"/>
+    </row>
+    <row r="394" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A394">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B394">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D394">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E394">
+        <v>46309.3715277778</v>
+      </c>
+      <c s="22" r="G394">
+        <v>46309.375</v>
+      </c>
+      <c s="21" t="inlineStr" r="H394">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I394"/>
+      <c s="21" t="inlineStr" r="J394">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K394">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L394">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M394"/>
+      <c s="20" t="inlineStr" r="N394">
+        <is>
+          <t xml:space="preserve">AJUSTE DA MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O394">
+        <is>
+          <t xml:space="preserve">AJUSTANDO CHAPA ENGANCHADA</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P394"/>
+      <c s="20" t="inlineStr" r="R394">
+        <is>
+          <t xml:space="preserve">2d6546a0-c7c6-11f1-8351-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S394">
+        <is>
+          <t xml:space="preserve">10049156    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U394">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V394"/>
+    </row>
+    <row r="395" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A395">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B395">
+        <is>
+          <t xml:space="preserve">TR02-MESA FIXA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D395">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E395">
+        <v>46309.3784722222</v>
+      </c>
+      <c s="18" r="G395">
+        <v>46309.3826388889</v>
+      </c>
+      <c s="17" t="inlineStr" r="H395">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I395"/>
+      <c s="17" t="inlineStr" r="J395">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K395">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L395">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M395"/>
+      <c s="16" t="inlineStr" r="N395">
+        <is>
+          <t xml:space="preserve">PESAGEM DE FARDO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O395">
+        <is>
+          <t xml:space="preserve">Pesagem de pnc</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P395"/>
+      <c s="16" t="inlineStr" r="R395">
+        <is>
+          <t xml:space="preserve">75423a90-c7c7-11f1-a8be-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S395">
+        <is>
+          <t xml:space="preserve">10049316    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U395">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V395"/>
+    </row>
+    <row r="396" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A396">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B396">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D396">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E396">
+        <v>46309.3833333333</v>
+      </c>
+      <c s="22" r="G396">
+        <v>46309.3854166667</v>
+      </c>
+      <c s="21" t="inlineStr" r="H396">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I396"/>
+      <c s="21" t="inlineStr" r="J396">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K396">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L396">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M396"/>
+      <c s="20" t="inlineStr" r="N396">
+        <is>
+          <t xml:space="preserve">AJUSTE DA MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O396">
+        <is>
+          <t xml:space="preserve">AJUSTANDO CHAPA</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P396"/>
+      <c s="20" t="inlineStr" r="R396">
+        <is>
+          <t xml:space="preserve">7728df70-c7c8-11f1-cccc-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S396">
+        <is>
+          <t xml:space="preserve">10048772    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U396">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V396"/>
+    </row>
+    <row r="397" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A397">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B397">
+        <is>
+          <t xml:space="preserve">TR05-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D397">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E397">
+        <v>46309.3847222222</v>
+      </c>
+      <c s="18" r="G397">
+        <v>46309.3923611111</v>
+      </c>
+      <c s="17" t="inlineStr" r="H397">
+        <is>
+          <t xml:space="preserve">11</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I397"/>
+      <c s="17" t="inlineStr" r="J397">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K397">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L397">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M397"/>
+      <c s="16" t="inlineStr" r="N397">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O397">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 11 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P397"/>
+      <c s="16" t="inlineStr" r="R397">
+        <is>
+          <t xml:space="preserve">c2aadc00-c7c8-11f1-830f-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S397">
+        <is>
+          <t xml:space="preserve">10048461    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U397">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V397"/>
+    </row>
+    <row r="398" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A398">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B398"/>
+      <c s="21" t="inlineStr" r="D398">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E398">
+        <v>46309.3868055556</v>
+      </c>
+      <c s="22" r="G398">
+        <v>46309.3895833333</v>
+      </c>
+      <c s="21" t="inlineStr" r="H398">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I398"/>
+      <c s="21" t="inlineStr" r="J398">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K398">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L398">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M398"/>
+      <c s="20" t="inlineStr" r="N398">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O398">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 4 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P398"/>
+      <c s="20" t="inlineStr" r="R398">
+        <is>
+          <t xml:space="preserve">44813b70-c7c9-11f1-848a-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S398">
+        <is>
+          <t xml:space="preserve">10049327    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U398">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V398"/>
+    </row>
+    <row r="399" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A399">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B399"/>
+      <c s="17" t="inlineStr" r="D399">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E399">
+        <v>46309.3881944444</v>
+      </c>
+      <c s="18" r="G399">
+        <v>46309.3930555556</v>
+      </c>
+      <c s="17" t="inlineStr" r="H399">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I399"/>
+      <c s="17" t="inlineStr" r="J399">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K399">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L399">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M399"/>
+      <c s="16" t="inlineStr" r="N399">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O399">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 7 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P399"/>
+      <c s="16" t="inlineStr" r="R399">
+        <is>
+          <t xml:space="preserve">8982ca40-c7c9-11f1-b8d6-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S399">
+        <is>
+          <t xml:space="preserve">10048772    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U399">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V399"/>
+    </row>
+    <row r="400" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A400">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B400">
+        <is>
+          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D400">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E400">
+        <v>46309.3916666667</v>
+      </c>
+      <c s="22" r="G400">
+        <v>46309.4027777778</v>
+      </c>
+      <c s="21" t="inlineStr" r="H400">
+        <is>
+          <t xml:space="preserve">16</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I400"/>
+      <c s="21" t="inlineStr" r="J400">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K400">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L400">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M400"/>
+      <c s="20" t="inlineStr" r="N400">
+        <is>
+          <t xml:space="preserve">QUALIDADE DA MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O400">
+        <is>
+          <t xml:space="preserve">Material 3.75mm 6000x1200 UD 5012424119 com leve ondulação.
+obs: material liberado pela qualidade para consumo.</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P400"/>
+      <c s="20" t="inlineStr" r="R400">
+        <is>
+          <t xml:space="preserve">619a0100-c7ca-11f1-a5d7-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S400">
+        <is>
+          <t xml:space="preserve">10049327    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U400">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V400"/>
+    </row>
+    <row r="401" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A401">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B401">
+        <is>
+          <t xml:space="preserve">TR01-ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D401">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E401">
+        <v>46309.3965277778</v>
+      </c>
+      <c s="18" r="G401">
+        <v>46309.3993055556</v>
+      </c>
+      <c s="17" t="inlineStr" r="H401">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I401"/>
+      <c s="17" t="inlineStr" r="J401">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K401">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L401">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M401"/>
+      <c s="16" t="inlineStr" r="N401">
+        <is>
+          <t xml:space="preserve">TROCA DE ESPESSURA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O401">
+        <is>
+          <t xml:space="preserve">REGULAGEM</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P401"/>
+      <c s="16" t="inlineStr" r="R401">
+        <is>
+          <t xml:space="preserve">2566f930-c7cb-11f1-85eb-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S401">
+        <is>
+          <t xml:space="preserve">10048772    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U401">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V401"/>
+    </row>
+    <row r="402" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A402">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B402">
+        <is>
+          <t xml:space="preserve">TR01-ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D402">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E402">
+        <v>46309.4013888889</v>
+      </c>
+      <c s="22" r="G402">
+        <v>46309.4034722222</v>
+      </c>
+      <c s="21" t="inlineStr" r="H402">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I402"/>
+      <c s="21" t="inlineStr" r="J402">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K402">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L402">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M402"/>
+      <c s="20" t="inlineStr" r="N402">
+        <is>
+          <t xml:space="preserve">TROCA DE ESPESSURA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O402">
+        <is>
+          <t xml:space="preserve">REGULAGEM</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P402"/>
+      <c s="20" t="inlineStr" r="R402">
+        <is>
+          <t xml:space="preserve">20acfe20-c7cc-11f1-aed1-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S402">
+        <is>
+          <t xml:space="preserve">10048772    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U402">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V402"/>
+    </row>
+    <row r="403" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A403">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B403"/>
+      <c s="17" t="inlineStr" r="D403">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E403">
+        <v>46309.4125</v>
+      </c>
+      <c s="18" r="G403">
+        <v>46309.4145833333</v>
+      </c>
+      <c s="17" t="inlineStr" r="H403">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I403"/>
+      <c s="17" t="inlineStr" r="J403">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K403">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L403">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M403"/>
+      <c s="16" t="inlineStr" r="N403">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O403">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 3 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P403"/>
+      <c s="16" t="inlineStr" r="R403">
+        <is>
+          <t xml:space="preserve">650cbcc0-c7ce-11f1-c075-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S403">
+        <is>
+          <t xml:space="preserve">10049327    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U403">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V403"/>
+    </row>
+    <row r="404" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A404">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B404">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D404">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E404">
+        <v>46309.4159722222</v>
+      </c>
+      <c s="22" r="G404">
+        <v>46309.41875</v>
+      </c>
+      <c s="21" t="inlineStr" r="H404">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I404"/>
+      <c s="21" t="inlineStr" r="J404">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K404">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L404">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M404"/>
+      <c s="20" t="inlineStr" r="N404">
+        <is>
+          <t xml:space="preserve">AJUSTE DA MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O404">
+        <is>
+          <t xml:space="preserve">AJUSTE DA MESA PRA TAMANHO DEW CHAPA</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P404"/>
+      <c s="20" t="inlineStr" r="R404">
+        <is>
+          <t xml:space="preserve">1b9519b0-c7cf-11f1-889b-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S404">
+        <is>
+          <t xml:space="preserve">10048772    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U404">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V404"/>
+    </row>
+    <row r="405" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A405">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B405">
+        <is>
+          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D405">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E405">
+        <v>46309.4166666667</v>
+      </c>
+      <c s="18" r="G405">
+        <v>46309.4388888889</v>
+      </c>
+      <c s="17" t="inlineStr" r="H405">
+        <is>
+          <t xml:space="preserve">32</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I405"/>
+      <c s="17" t="inlineStr" r="J405">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K405">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L405">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M405"/>
+      <c s="16" t="inlineStr" r="N405">
+        <is>
+          <t xml:space="preserve">SETUP COMPLETO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O405">
+        <is>
+          <t xml:space="preserve">Regulagem da endireitadeira e guilhotina.</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P405"/>
+      <c s="16" t="inlineStr" r="R405">
+        <is>
+          <t xml:space="preserve">8ea25200-c7d5-11f1-c53c-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S405">
+        <is>
+          <t xml:space="preserve">10049327    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U405">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V405"/>
+    </row>
+    <row r="406" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A406">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B406">
+        <is>
+          <t xml:space="preserve">TR05-GUILHOTINA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D406">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E406">
+        <v>46309.4270833333</v>
+      </c>
+      <c s="22" r="G406">
+        <v>46309.4347222222</v>
+      </c>
+      <c s="21" t="inlineStr" r="H406">
+        <is>
+          <t xml:space="preserve">11</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I406"/>
+      <c s="21" t="inlineStr" r="J406">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K406">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L406">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M406"/>
+      <c s="20" t="inlineStr" r="N406">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE CHAPA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O406">
+        <is>
+          <t xml:space="preserve">chapa amassou tivemos que voltar e passar novamente</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P406"/>
+      <c s="20" t="inlineStr" r="R406">
+        <is>
+          <t xml:space="preserve">6384b5d0-c7d1-11f1-9ff7-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S406">
+        <is>
+          <t xml:space="preserve">10048450    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U406">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V406"/>
+    </row>
+    <row r="407" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A407">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B407">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D407">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E407">
+        <v>46309.4409722222</v>
+      </c>
+      <c s="18" r="G407">
+        <v>46309.4479166667</v>
+      </c>
+      <c s="17" t="inlineStr" r="H407">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I407"/>
+      <c s="17" t="inlineStr" r="J407">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K407">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L407">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M407"/>
+      <c s="16" t="inlineStr" r="N407">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE CHAPA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O407">
+        <is>
+          <t xml:space="preserve">chapa amassada</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P407"/>
+      <c s="16" t="inlineStr" r="R407">
+        <is>
+          <t xml:space="preserve">1cc039f0-c7d4-11f1-864e-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S407">
+        <is>
+          <t xml:space="preserve">10048914    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U407">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V407"/>
+    </row>
+    <row r="408" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A408">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B408"/>
+      <c s="21" t="inlineStr" r="D408">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E408">
+        <v>46309.4479166667</v>
+      </c>
+      <c s="22" r="G408">
+        <v>46309.4583333333</v>
+      </c>
+      <c s="21" t="inlineStr" r="H408">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I408"/>
+      <c s="21" t="inlineStr" r="J408">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K408">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L408">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M408"/>
+      <c s="20" t="inlineStr" r="N408">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O408">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P408"/>
+      <c s="20" t="inlineStr" r="R408">
+        <is>
+          <t xml:space="preserve">80797140-c7d5-11f1-bc78-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S408">
+        <is>
+          <t xml:space="preserve">10048914    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U408">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V408"/>
+    </row>
+    <row r="409" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A409">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B409">
+        <is>
+          <t xml:space="preserve">TR05-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D409">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E409">
+        <v>46309.4486111111</v>
+      </c>
+      <c s="18" r="G409">
+        <v>46309.4541666667</v>
+      </c>
+      <c s="17" t="inlineStr" r="H409">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I409"/>
+      <c s="17" t="inlineStr" r="J409">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K409">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L409">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M409"/>
+      <c s="16" t="inlineStr" r="N409">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O409">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 8 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P409"/>
+      <c s="16" t="inlineStr" r="R409">
+        <is>
+          <t xml:space="preserve">a280d670-c7d5-11f1-afd0-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S409">
+        <is>
+          <t xml:space="preserve">10048450    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U409">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V409"/>
+    </row>
+    <row r="410" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A410">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B410">
+        <is>
+          <t xml:space="preserve">TR05-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D410">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E410">
+        <v>46309.4715277778</v>
+      </c>
+      <c s="22" r="G410">
+        <v>46309.4736111111</v>
+      </c>
+      <c s="21" t="inlineStr" r="H410">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I410"/>
+      <c s="21" t="inlineStr" r="J410">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K410">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L410">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M410"/>
+      <c s="20" t="inlineStr" r="N410">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE FARDO</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O410">
+        <is>
+          <t xml:space="preserve">passagem de fardo</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P410"/>
+      <c s="20" t="inlineStr" r="R410">
+        <is>
+          <t xml:space="preserve">55808500-c7da-11f1-a43d-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S410">
+        <is>
+          <t xml:space="preserve">10048452    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U410">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V410"/>
+    </row>
+    <row r="411" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A411">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B411"/>
+      <c s="17" t="inlineStr" r="D411">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E411">
+        <v>46309.4722222222</v>
+      </c>
+      <c s="18" r="G411">
+        <v>46309.4826388889</v>
+      </c>
+      <c s="17" t="inlineStr" r="H411">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I411"/>
+      <c s="17" t="inlineStr" r="J411">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K411">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L411">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M411"/>
+      <c s="16" t="inlineStr" r="N411">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O411">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P411"/>
+      <c s="16" t="inlineStr" r="R411">
+        <is>
+          <t xml:space="preserve">733f1cf0-c7da-11f1-9604-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S411">
+        <is>
+          <t xml:space="preserve">10049334    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U411">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V411"/>
+    </row>
+    <row r="412" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A412">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B412">
+        <is>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D412">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E412">
+        <v>46309.4756944444</v>
+      </c>
+      <c s="22" r="G412">
+        <v>46309.4888888889</v>
+      </c>
+      <c s="21" t="inlineStr" r="H412">
+        <is>
+          <t xml:space="preserve">19</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I412"/>
+      <c s="21" t="inlineStr" r="J412">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K412">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L412">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M412"/>
+      <c s="20" t="inlineStr" r="N412">
+        <is>
+          <t xml:space="preserve">QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O412">
+        <is>
+          <t xml:space="preserve">Bobina 0.43x1000 de UD.5012476132 apresentando oxidação ,(observação qualidade liberou o material para produzir como bom).</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P412"/>
+      <c s="20" t="inlineStr" r="R412">
+        <is>
+          <t xml:space="preserve">54eba290-c7db-11f1-acc1-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S412">
+        <is>
+          <t xml:space="preserve">10049289    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U412">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V412"/>
+    </row>
+    <row r="413" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A413">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B413">
+        <is>
+          <t xml:space="preserve">TR05-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D413">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E413">
+        <v>46309.4895833333</v>
+      </c>
+      <c s="18" r="G413">
+        <v>46309.5</v>
+      </c>
+      <c s="17" t="inlineStr" r="H413">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I413"/>
+      <c s="17" t="inlineStr" r="J413">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K413">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L413">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M413"/>
+      <c s="16" t="inlineStr" r="N413">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O413">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P413"/>
+      <c s="16" t="inlineStr" r="R413">
+        <is>
+          <t xml:space="preserve">e49e8590-c7dd-11f1-901a-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S413">
+        <is>
+          <t xml:space="preserve">10048452    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U413">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V413"/>
+    </row>
+    <row r="414" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A414">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B414">
+        <is>
+          <t xml:space="preserve">TR05-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D414">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E414">
+        <v>46309.5020833333</v>
+      </c>
+      <c s="22" r="G414">
+        <v>46309.50625</v>
+      </c>
+      <c s="21" t="inlineStr" r="H414">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I414"/>
+      <c s="21" t="inlineStr" r="J414">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K414">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L414">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M414"/>
+      <c s="20" t="inlineStr" r="N414">
+        <is>
+          <t xml:space="preserve">AGUARDANDO INSPEÇÃO DE  QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O414">
+        <is>
+          <t xml:space="preserve">aguardando inspeção de matéria prima, matéria prima dando variação no comprimento ud 2003908515</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P414"/>
+      <c s="20" t="inlineStr" r="R414">
+        <is>
+          <t xml:space="preserve">6c94aa40-c7e0-11f1-a7e5-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S414">
+        <is>
+          <t xml:space="preserve">10048452    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U414">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V414"/>
+    </row>
+    <row r="415" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A415">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B415"/>
+      <c s="17" t="inlineStr" r="D415">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E415">
+        <v>46309.5034722222</v>
+      </c>
+      <c s="18" r="G415">
+        <v>46309.5138888889</v>
+      </c>
+      <c s="17" t="inlineStr" r="H415">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I415"/>
+      <c s="17" t="inlineStr" r="J415">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K415">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L415">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M415"/>
+      <c s="16" t="inlineStr" r="N415">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O415">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P415"/>
+      <c s="16" t="inlineStr" r="R415">
+        <is>
+          <t xml:space="preserve">ae65b9a0-c7e0-11f1-84ea-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S415">
+        <is>
+          <t xml:space="preserve">10048914    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U415">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V415"/>
+    </row>
+    <row r="416" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A416">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B416">
+        <is>
+          <t xml:space="preserve">TR05-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D416">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E416">
+        <v>46309.5069444444</v>
+      </c>
+      <c s="22" r="G416">
+        <v>46309.5097222222</v>
+      </c>
+      <c s="21" t="inlineStr" r="H416">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I416"/>
+      <c s="21" t="inlineStr" r="J416">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K416">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L416">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M416"/>
+      <c s="20" t="inlineStr" r="N416">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE FARDO</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O416">
+        <is>
+          <t xml:space="preserve">passagem de fardo</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P416"/>
+      <c s="20" t="inlineStr" r="R416">
+        <is>
+          <t xml:space="preserve">75b2d7e0-c7e1-11f1-ac06-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S416">
+        <is>
+          <t xml:space="preserve">10048452    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U416">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V416"/>
+    </row>
+    <row r="417" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A417">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B417">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D417">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E417">
+        <v>46309.5145833333</v>
+      </c>
+      <c s="18" r="G417">
+        <v>46309.5208333333</v>
+      </c>
+      <c s="17" t="inlineStr" r="H417">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I417"/>
+      <c s="17" t="inlineStr" r="J417">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K417">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L417">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M417"/>
+      <c s="16" t="inlineStr" r="N417">
+        <is>
+          <t xml:space="preserve">AJUSTE DA MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O417">
+        <is>
+          <t xml:space="preserve">AJUSTE DA MESA PARA TAMANHO DE CHAPA</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P417"/>
+      <c s="16" t="inlineStr" r="R417">
+        <is>
+          <t xml:space="preserve">2007f7a0-c7e4-11f1-8f4e-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S417">
+        <is>
+          <t xml:space="preserve">10048914    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U417">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V417"/>
+    </row>
+    <row r="418" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A418">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B418"/>
+      <c s="21" t="inlineStr" r="D418">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E418">
+        <v>46309.5159722222</v>
+      </c>
+      <c s="22" r="G418">
+        <v>46309.5256944444</v>
+      </c>
+      <c s="21" t="inlineStr" r="H418">
+        <is>
+          <t xml:space="preserve">14</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I418"/>
+      <c s="21" t="inlineStr" r="J418">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K418">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L418">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M418"/>
+      <c s="20" t="inlineStr" r="N418">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O418">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 14 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P418"/>
+      <c s="20" t="inlineStr" r="R418">
+        <is>
+          <t xml:space="preserve">2631d660-c7e3-11f1-cf48-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S418">
+        <is>
+          <t xml:space="preserve">10049334    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U418">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V418"/>
+    </row>
+    <row r="419" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A419">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B419">
+        <is>
+          <t xml:space="preserve">TR01-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D419">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E419">
+        <v>46309.5243055556</v>
+      </c>
+      <c s="18" r="G419">
+        <v>46309.5381944444</v>
+      </c>
+      <c s="17" t="inlineStr" r="H419">
+        <is>
+          <t xml:space="preserve">20</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I419"/>
+      <c s="17" t="inlineStr" r="J419">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K419">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L419">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M419"/>
+      <c s="16" t="inlineStr" r="N419">
+        <is>
+          <t xml:space="preserve">AGUARDANDO INSPEÇÃO DE  QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O419">
+        <is>
+          <t xml:space="preserve">MATERIAL COM PONTO DE PRESSÃO</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P419"/>
+      <c s="16" t="inlineStr" r="R419">
+        <is>
+          <t xml:space="preserve">00bbc560-c7e5-11f1-ab4e-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S419">
+        <is>
+          <t xml:space="preserve">10048914    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U419">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V419"/>
+    </row>
+    <row r="420" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A420">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B420">
+        <is>
+          <t xml:space="preserve">TR05-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D420">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E420">
+        <v>46309.5277777778</v>
+      </c>
+      <c s="22" r="G420">
+        <v>46309.5298611111</v>
+      </c>
+      <c s="21" t="inlineStr" r="H420">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I420"/>
+      <c s="21" t="inlineStr" r="J420">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K420">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L420">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M420"/>
+      <c s="20" t="inlineStr" r="N420">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE FARDO</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O420">
+        <is>
+          <t xml:space="preserve">passagem de fardo</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P420"/>
+      <c s="20" t="inlineStr" r="R420">
+        <is>
+          <t xml:space="preserve">984409b0-c7e5-11f1-8a85-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S420">
+        <is>
+          <t xml:space="preserve">10048448    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U420">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V420"/>
+    </row>
+    <row r="421" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A421">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B421">
+        <is>
+          <t xml:space="preserve">TR05-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D421">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E421">
+        <v>46309.5326388889</v>
+      </c>
+      <c s="18" r="G421">
+        <v>46309.5423611111</v>
+      </c>
+      <c s="17" t="inlineStr" r="H421">
+        <is>
+          <t xml:space="preserve">14</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I421"/>
+      <c s="17" t="inlineStr" r="J421">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K421">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L421">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M421"/>
+      <c s="16" t="inlineStr" r="N421">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE CHAPA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O421">
+        <is>
+          <t xml:space="preserve">chapa caiu no fosso</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P421"/>
+      <c s="16" t="inlineStr" r="R421">
+        <is>
+          <t xml:space="preserve">87aacfc0-c7e6-11f1-c6bc-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S421">
+        <is>
+          <t xml:space="preserve">10048448    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U421">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V421"/>
+    </row>
+    <row r="422" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A422">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B422">
+        <is>
+          <t xml:space="preserve">TR05-ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D422">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E422">
+        <v>46309.5430555556</v>
+      </c>
+      <c s="22" r="G422">
+        <v>46309.55</v>
+      </c>
+      <c s="21" t="inlineStr" r="H422">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I422"/>
+      <c s="21" t="inlineStr" r="J422">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K422">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L422">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M422"/>
+      <c s="20" t="inlineStr" r="N422">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE CHAPA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O422">
+        <is>
+          <t xml:space="preserve">chapa caiu no fosso</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P422"/>
+      <c s="20" t="inlineStr" r="R422">
+        <is>
+          <t xml:space="preserve">59bc9fb0-c7e8-11f1-cbff-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S422">
+        <is>
+          <t xml:space="preserve">10048448    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U422">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V422"/>
+    </row>
+    <row r="423" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A423">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B423"/>
+      <c s="17" t="inlineStr" r="D423">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E423">
+        <v>46309.5430555556</v>
+      </c>
+      <c s="18" r="G423">
+        <v>46309.5451388889</v>
+      </c>
+      <c s="17" t="inlineStr" r="H423">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I423"/>
+      <c s="17" t="inlineStr" r="J423">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K423">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L423">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M423"/>
+      <c s="16" t="inlineStr" r="N423">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O423">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 3 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P423"/>
+      <c s="16" t="inlineStr" r="R423">
+        <is>
+          <t xml:space="preserve">b76166f0-c7e8-11f1-bb38-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S423">
+        <is>
+          <t xml:space="preserve">10049334    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U423">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V423"/>
+    </row>
+    <row r="424" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A424">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B424"/>
+      <c s="21" t="inlineStr" r="D424">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E424">
+        <v>46309.5597222222</v>
+      </c>
+      <c s="22" r="G424">
+        <v>46309.5694444444</v>
+      </c>
+      <c s="21" t="inlineStr" r="H424">
+        <is>
+          <t xml:space="preserve">14</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I424"/>
+      <c s="21" t="inlineStr" r="J424">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K424">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L424">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M424"/>
+      <c s="20" t="inlineStr" r="N424">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O424">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 14 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P424"/>
+      <c s="20" t="inlineStr" r="R424">
+        <is>
+          <t xml:space="preserve">0056e4e0-c7ec-11f1-9906-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S424">
+        <is>
+          <t xml:space="preserve">10049340    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U424">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V424"/>
+    </row>
+    <row r="425" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A425">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B425">
+        <is>
+          <t xml:space="preserve">TR05-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D425">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E425">
+        <v>46309.5791666667</v>
+      </c>
+      <c s="18" r="G425">
+        <v>46309.5888888889</v>
+      </c>
+      <c s="17" t="inlineStr" r="H425">
+        <is>
+          <t xml:space="preserve">14</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I425"/>
+      <c s="17" t="inlineStr" r="J425">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K425">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L425">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M425"/>
+      <c s="16" t="inlineStr" r="N425">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O425">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 14 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P425"/>
+      <c s="16" t="inlineStr" r="R425">
+        <is>
+          <t xml:space="preserve">db588a00-c7ef-11f1-b27a-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S425">
+        <is>
+          <t xml:space="preserve">10048448    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U425">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V425"/>
+    </row>
+    <row r="426" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A426">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B426"/>
+      <c s="21" t="inlineStr" r="D426">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E426">
+        <v>46309.5875</v>
+      </c>
+      <c s="22" r="G426">
+        <v>46309.5979166667</v>
+      </c>
+      <c s="21" t="inlineStr" r="H426">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I426"/>
+      <c s="21" t="inlineStr" r="J426">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K426">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L426">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M426"/>
+      <c s="20" t="inlineStr" r="N426">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O426">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P426"/>
+      <c s="20" t="inlineStr" r="R426">
+        <is>
+          <t xml:space="preserve">8f1d64b0-c7f1-11f1-c25c-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S426">
+        <is>
+          <t xml:space="preserve">10048916    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U426">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V426"/>
+    </row>
+    <row r="427" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A427">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B427">
+        <is>
+          <t xml:space="preserve">TR02-GUILHOTINA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D427">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E427">
+        <v>46309.5993055556</v>
+      </c>
+      <c s="18" r="G427">
+        <v>46309.6125</v>
+      </c>
+      <c s="17" t="inlineStr" r="H427">
+        <is>
+          <t xml:space="preserve">19</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I427"/>
+      <c s="17" t="inlineStr" r="J427">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K427">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L427">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M427"/>
+      <c s="16" t="inlineStr" r="N427">
+        <is>
+          <t xml:space="preserve">SETUP COMPLETO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O427">
+        <is>
+          <t xml:space="preserve">Setup completo</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P427"/>
+      <c s="16" t="inlineStr" r="R427">
+        <is>
+          <t xml:space="preserve">044f0070-c7f4-11f1-b52f-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S427">
+        <is>
+          <t xml:space="preserve">10049340    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U427">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V427"/>
+    </row>
+    <row r="428" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A428">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B428"/>
+      <c s="21" t="inlineStr" r="D428">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E428">
+        <v>46309.6020833333</v>
+      </c>
+      <c s="22" r="G428">
+        <v>46309.60625</v>
+      </c>
+      <c s="21" t="inlineStr" r="H428">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I428"/>
+      <c s="21" t="inlineStr" r="J428">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K428">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L428">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M428"/>
+      <c s="20" t="inlineStr" r="N428">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O428">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 6 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P428"/>
+      <c s="20" t="inlineStr" r="R428">
+        <is>
+          <t xml:space="preserve">81afdd50-c7f4-11f1-98d2-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S428">
+        <is>
+          <t xml:space="preserve">10048916    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U428">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V428"/>
+    </row>
+    <row r="429" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A429">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B429">
+        <is>
+          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D429">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E429">
+        <v>46309.6152777778</v>
+      </c>
+      <c s="18" r="G429">
+        <v>46309.6986111111</v>
+      </c>
+      <c s="17" t="inlineStr" r="H429">
+        <is>
+          <t xml:space="preserve">120</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I429"/>
+      <c s="17" t="inlineStr" r="J429">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K429">
+        <is>
+          <t xml:space="preserve">Manutenção Corretiva Elétrica</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L429">
+        <is>
+          <t xml:space="preserve">Manutenção Corretiva Elétrica</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M429"/>
+      <c s="16" t="inlineStr" r="N429">
+        <is>
+          <t xml:space="preserve">FALHA NO ACIONAMENTO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O429">
+        <is>
+          <t xml:space="preserve">Falha no convesor da endireitadeira.</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="P429">
+        <is>
+          <t xml:space="preserve">000010035324</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="R429">
+        <is>
+          <t xml:space="preserve">4183c400-c7f7-11f1-90dc-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S429">
+        <is>
+          <t xml:space="preserve">10049342    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U429">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V429"/>
+    </row>
+    <row r="430" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A430">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B430">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D430">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E430">
+        <v>46309.6347222222</v>
+      </c>
+      <c s="22" r="G430">
+        <v>46309.6368055556</v>
+      </c>
+      <c s="21" t="inlineStr" r="H430">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I430"/>
+      <c s="21" t="inlineStr" r="J430">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K430">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L430">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M430"/>
+      <c s="20" t="inlineStr" r="N430">
+        <is>
+          <t xml:space="preserve">AJUSTE DA MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O430">
+        <is>
+          <t xml:space="preserve">AJUSTE NA CHAPA</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P430"/>
+      <c s="20" t="inlineStr" r="R430">
+        <is>
+          <t xml:space="preserve">11e36530-c7fb-11f1-c48e-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S430">
+        <is>
+          <t xml:space="preserve">10049603    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U430">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V430"/>
+    </row>
+    <row r="431" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A431">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B431">
+        <is>
+          <t xml:space="preserve">TR05-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D431">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E431">
+        <v>46309.6541666667</v>
+      </c>
+      <c s="18" r="G431">
+        <v>46309.6597222222</v>
+      </c>
+      <c s="17" t="inlineStr" r="H431">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I431"/>
+      <c s="17" t="inlineStr" r="J431">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K431">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L431">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M431"/>
+      <c s="16" t="inlineStr" r="N431">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O431">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 8 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P431"/>
+      <c s="16" t="inlineStr" r="R431">
+        <is>
+          <t xml:space="preserve">f8547060-c7fe-11f1-be45-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S431">
+        <is>
+          <t xml:space="preserve">10048448    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U431">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V431"/>
+    </row>
+    <row r="432" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A432">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B432">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D432">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E432">
+        <v>46309.6763888889</v>
+      </c>
+      <c s="22" r="G432">
+        <v>46309.6784722222</v>
+      </c>
+      <c s="21" t="inlineStr" r="H432">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I432"/>
+      <c s="21" t="inlineStr" r="J432">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K432">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L432">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M432"/>
+      <c s="20" t="inlineStr" r="N432">
+        <is>
+          <t xml:space="preserve">AJUSTE DA MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O432">
+        <is>
+          <t xml:space="preserve">AJUSTE NA CHAPA</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P432"/>
+      <c s="20" t="inlineStr" r="R432">
+        <is>
+          <t xml:space="preserve">8b28f3d0-c803-11f1-968f-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S432">
+        <is>
+          <t xml:space="preserve">10049745    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U432">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V432"/>
+    </row>
+    <row r="433" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A433">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B433">
+        <is>
+          <t xml:space="preserve">TR01-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D433">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E433">
+        <v>46309.6958333333</v>
+      </c>
+      <c s="18" r="G433">
+        <v>46309.70625</v>
+      </c>
+      <c s="17" t="inlineStr" r="H433">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I433"/>
+      <c s="17" t="inlineStr" r="J433">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K433">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L433">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M433"/>
+      <c s="16" t="inlineStr" r="N433">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O433">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P433"/>
+      <c s="16" t="inlineStr" r="R433">
+        <is>
+          <t xml:space="preserve">8c073e80-c806-11f1-9501-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S433">
+        <is>
+          <t xml:space="preserve">10049745    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U433">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V433"/>
+    </row>
+    <row r="434" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A434">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B434">
+        <is>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D434">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E434">
+        <v>46309.6993055556</v>
+      </c>
+      <c s="22" r="G434">
+        <v>46310.2909722222</v>
+      </c>
+      <c s="21" t="inlineStr" r="H434">
+        <is>
+          <t xml:space="preserve">852</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I434"/>
+      <c s="21" t="inlineStr" r="J434">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K434">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L434">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M434"/>
+      <c s="20" t="inlineStr" r="N434">
+        <is>
+          <t xml:space="preserve">FALTA DEMANDA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O434">
+        <is>
+          <t xml:space="preserve">falta de demanda</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P434"/>
+      <c s="20" t="inlineStr" r="R434">
+        <is>
+          <t xml:space="preserve">0aabc980-c808-11f1-987a-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S434">
+        <is>
+          <t xml:space="preserve">10048447    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U434">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V434"/>
+    </row>
+    <row r="435" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A435">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B435">
+        <is>
+          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D435">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E435">
+        <v>46309.6993055556</v>
+      </c>
+      <c s="18" r="G435">
+        <v>46310.2909722222</v>
+      </c>
+      <c s="17" t="inlineStr" r="H435">
+        <is>
+          <t xml:space="preserve">852</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I435"/>
+      <c s="17" t="inlineStr" r="J435">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K435">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L435">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M435"/>
+      <c s="16" t="inlineStr" r="N435">
+        <is>
+          <t xml:space="preserve">FALTA DEMANDA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O435">
+        <is>
+          <t xml:space="preserve">Tempo livre.</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P435"/>
+      <c s="16" t="inlineStr" r="R435">
+        <is>
+          <t xml:space="preserve">27757a20-c808-11f1-b1c6-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S435">
+        <is>
+          <t xml:space="preserve">10049342    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U435">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V435"/>
+    </row>
+    <row r="436" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A436">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 03</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B436"/>
+      <c s="21" t="inlineStr" r="D436">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E436">
+        <v>46309.7013888889</v>
+      </c>
+      <c s="22" r="G436">
+        <v>46310.2840277778</v>
+      </c>
+      <c s="21" t="inlineStr" r="H436">
+        <is>
+          <t xml:space="preserve">839</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I436"/>
+      <c s="21" t="inlineStr" r="J436">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K436">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L436">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M436"/>
+      <c s="20" t="inlineStr" r="N436">
+        <is>
+          <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O436">
+        <is>
+          <t xml:space="preserve">Parada registrada automaticamente pelo sistema</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P436"/>
+      <c s="20" t="inlineStr" r="R436">
+        <is>
+          <t xml:space="preserve">735a0910-c808-11f1-ad2c-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="S436"/>
+      <c s="20" t="inlineStr" r="U436">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V436"/>
+    </row>
+    <row r="437" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A437">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B437"/>
+      <c s="17" t="inlineStr" r="D437">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E437">
+        <v>46309.7013888889</v>
+      </c>
+      <c s="18" r="G437">
+        <v>46310.2840277778</v>
+      </c>
+      <c s="17" t="inlineStr" r="H437">
+        <is>
+          <t xml:space="preserve">839</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I437"/>
+      <c s="17" t="inlineStr" r="J437">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K437">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L437">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M437"/>
+      <c s="16" t="inlineStr" r="N437">
+        <is>
+          <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O437">
+        <is>
+          <t xml:space="preserve">Parada registrada automaticamente pelo sistema</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P437"/>
+      <c s="16" t="inlineStr" r="R437">
+        <is>
+          <t xml:space="preserve">73727310-c808-11f1-9a96-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S437">
+        <is>
+          <t xml:space="preserve">10049635    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U437">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V437"/>
+    </row>
+    <row r="438" ht="15.55" customHeight="0">
+      <c s="23" t="inlineStr" r="A438">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="B438">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="10" t="str" r="C438"/>
+      <c s="25" t="inlineStr" r="D438">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="26" r="E438">
+        <v>46309.7069444444</v>
+      </c>
+      <c s="10" t="str" r="F438"/>
+      <c s="26" r="G438">
+        <v>46310.2909722222</v>
+      </c>
+      <c s="25" t="inlineStr" r="H438">
+        <is>
+          <t xml:space="preserve">841</t>
+        </is>
+      </c>
+      <c s="25" t="str" r="I438"/>
+      <c s="25" t="inlineStr" r="J438">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="K438">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="L438">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="24" t="str" r="M438"/>
+      <c s="24" t="inlineStr" r="N438">
+        <is>
+          <t xml:space="preserve">FALTA DEMANDA</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="O438">
+        <is>
+          <t xml:space="preserve">tempo livre</t>
+        </is>
+      </c>
+      <c s="24" t="str" r="P438"/>
+      <c s="10" t="str" r="Q438"/>
+      <c s="24" t="inlineStr" r="R438">
+        <is>
+          <t xml:space="preserve">1b4c3980-c882-11f1-b0f1-f2050a003223</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="S438">
+        <is>
+          <t xml:space="preserve">10049745    </t>
+        </is>
+      </c>
+      <c s="10" t="str" r="T438"/>
+      <c s="24" t="inlineStr" r="U438">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="11" t="str" r="V438"/>
+    </row>
+    <row r="439" ht="0.05" customHeight="1"/>
   </sheetData>
   <mergeCells>
     <mergeCell ref="A3:B8"/>
@@ -24130,6 +32132,571 @@
     <mergeCell ref="P325:Q325"/>
     <mergeCell ref="S325:T325"/>
     <mergeCell ref="U325:V325"/>
+    <mergeCell ref="B326:C326"/>
+    <mergeCell ref="E326:F326"/>
+    <mergeCell ref="P326:Q326"/>
+    <mergeCell ref="S326:T326"/>
+    <mergeCell ref="U326:V326"/>
+    <mergeCell ref="B327:C327"/>
+    <mergeCell ref="E327:F327"/>
+    <mergeCell ref="P327:Q327"/>
+    <mergeCell ref="S327:T327"/>
+    <mergeCell ref="U327:V327"/>
+    <mergeCell ref="B328:C328"/>
+    <mergeCell ref="E328:F328"/>
+    <mergeCell ref="P328:Q328"/>
+    <mergeCell ref="S328:T328"/>
+    <mergeCell ref="U328:V328"/>
+    <mergeCell ref="B329:C329"/>
+    <mergeCell ref="E329:F329"/>
+    <mergeCell ref="P329:Q329"/>
+    <mergeCell ref="S329:T329"/>
+    <mergeCell ref="U329:V329"/>
+    <mergeCell ref="B330:C330"/>
+    <mergeCell ref="E330:F330"/>
+    <mergeCell ref="P330:Q330"/>
+    <mergeCell ref="S330:T330"/>
+    <mergeCell ref="U330:V330"/>
+    <mergeCell ref="B331:C331"/>
+    <mergeCell ref="E331:F331"/>
+    <mergeCell ref="P331:Q331"/>
+    <mergeCell ref="S331:T331"/>
+    <mergeCell ref="U331:V331"/>
+    <mergeCell ref="B332:C332"/>
+    <mergeCell ref="E332:F332"/>
+    <mergeCell ref="P332:Q332"/>
+    <mergeCell ref="S332:T332"/>
+    <mergeCell ref="U332:V332"/>
+    <mergeCell ref="B333:C333"/>
+    <mergeCell ref="E333:F333"/>
+    <mergeCell ref="P333:Q333"/>
+    <mergeCell ref="S333:T333"/>
+    <mergeCell ref="U333:V333"/>
+    <mergeCell ref="B334:C334"/>
+    <mergeCell ref="E334:F334"/>
+    <mergeCell ref="P334:Q334"/>
+    <mergeCell ref="S334:T334"/>
+    <mergeCell ref="U334:V334"/>
+    <mergeCell ref="B335:C335"/>
+    <mergeCell ref="E335:F335"/>
+    <mergeCell ref="P335:Q335"/>
+    <mergeCell ref="S335:T335"/>
+    <mergeCell ref="U335:V335"/>
+    <mergeCell ref="B336:C336"/>
+    <mergeCell ref="E336:F336"/>
+    <mergeCell ref="P336:Q336"/>
+    <mergeCell ref="S336:T336"/>
+    <mergeCell ref="U336:V336"/>
+    <mergeCell ref="B337:C337"/>
+    <mergeCell ref="E337:F337"/>
+    <mergeCell ref="P337:Q337"/>
+    <mergeCell ref="S337:T337"/>
+    <mergeCell ref="U337:V337"/>
+    <mergeCell ref="B338:C338"/>
+    <mergeCell ref="E338:F338"/>
+    <mergeCell ref="P338:Q338"/>
+    <mergeCell ref="S338:T338"/>
+    <mergeCell ref="U338:V338"/>
+    <mergeCell ref="B339:C339"/>
+    <mergeCell ref="E339:F339"/>
+    <mergeCell ref="P339:Q339"/>
+    <mergeCell ref="S339:T339"/>
+    <mergeCell ref="U339:V339"/>
+    <mergeCell ref="B340:C340"/>
+    <mergeCell ref="E340:F340"/>
+    <mergeCell ref="P340:Q340"/>
+    <mergeCell ref="S340:T340"/>
+    <mergeCell ref="U340:V340"/>
+    <mergeCell ref="B341:C341"/>
+    <mergeCell ref="E341:F341"/>
+    <mergeCell ref="P341:Q341"/>
+    <mergeCell ref="S341:T341"/>
+    <mergeCell ref="U341:V341"/>
+    <mergeCell ref="B342:C342"/>
+    <mergeCell ref="E342:F342"/>
+    <mergeCell ref="P342:Q342"/>
+    <mergeCell ref="S342:T342"/>
+    <mergeCell ref="U342:V342"/>
+    <mergeCell ref="B343:C343"/>
+    <mergeCell ref="E343:F343"/>
+    <mergeCell ref="P343:Q343"/>
+    <mergeCell ref="S343:T343"/>
+    <mergeCell ref="U343:V343"/>
+    <mergeCell ref="B344:C344"/>
+    <mergeCell ref="E344:F344"/>
+    <mergeCell ref="P344:Q344"/>
+    <mergeCell ref="S344:T344"/>
+    <mergeCell ref="U344:V344"/>
+    <mergeCell ref="B345:C345"/>
+    <mergeCell ref="E345:F345"/>
+    <mergeCell ref="P345:Q345"/>
+    <mergeCell ref="S345:T345"/>
+    <mergeCell ref="U345:V345"/>
+    <mergeCell ref="B346:C346"/>
+    <mergeCell ref="E346:F346"/>
+    <mergeCell ref="P346:Q346"/>
+    <mergeCell ref="S346:T346"/>
+    <mergeCell ref="U346:V346"/>
+    <mergeCell ref="B347:C347"/>
+    <mergeCell ref="E347:F347"/>
+    <mergeCell ref="P347:Q347"/>
+    <mergeCell ref="S347:T347"/>
+    <mergeCell ref="U347:V347"/>
+    <mergeCell ref="B348:C348"/>
+    <mergeCell ref="E348:F348"/>
+    <mergeCell ref="P348:Q348"/>
+    <mergeCell ref="S348:T348"/>
+    <mergeCell ref="U348:V348"/>
+    <mergeCell ref="B349:C349"/>
+    <mergeCell ref="E349:F349"/>
+    <mergeCell ref="P349:Q349"/>
+    <mergeCell ref="S349:T349"/>
+    <mergeCell ref="U349:V349"/>
+    <mergeCell ref="B350:C350"/>
+    <mergeCell ref="E350:F350"/>
+    <mergeCell ref="P350:Q350"/>
+    <mergeCell ref="S350:T350"/>
+    <mergeCell ref="U350:V350"/>
+    <mergeCell ref="B351:C351"/>
+    <mergeCell ref="E351:F351"/>
+    <mergeCell ref="P351:Q351"/>
+    <mergeCell ref="S351:T351"/>
+    <mergeCell ref="U351:V351"/>
+    <mergeCell ref="B352:C352"/>
+    <mergeCell ref="E352:F352"/>
+    <mergeCell ref="P352:Q352"/>
+    <mergeCell ref="S352:T352"/>
+    <mergeCell ref="U352:V352"/>
+    <mergeCell ref="B353:C353"/>
+    <mergeCell ref="E353:F353"/>
+    <mergeCell ref="P353:Q353"/>
+    <mergeCell ref="S353:T353"/>
+    <mergeCell ref="U353:V353"/>
+    <mergeCell ref="B354:C354"/>
+    <mergeCell ref="E354:F354"/>
+    <mergeCell ref="P354:Q354"/>
+    <mergeCell ref="S354:T354"/>
+    <mergeCell ref="U354:V354"/>
+    <mergeCell ref="B355:C355"/>
+    <mergeCell ref="E355:F355"/>
+    <mergeCell ref="P355:Q355"/>
+    <mergeCell ref="S355:T355"/>
+    <mergeCell ref="U355:V355"/>
+    <mergeCell ref="B356:C356"/>
+    <mergeCell ref="E356:F356"/>
+    <mergeCell ref="P356:Q356"/>
+    <mergeCell ref="S356:T356"/>
+    <mergeCell ref="U356:V356"/>
+    <mergeCell ref="B357:C357"/>
+    <mergeCell ref="E357:F357"/>
+    <mergeCell ref="P357:Q357"/>
+    <mergeCell ref="S357:T357"/>
+    <mergeCell ref="U357:V357"/>
+    <mergeCell ref="B358:C358"/>
+    <mergeCell ref="E358:F358"/>
+    <mergeCell ref="P358:Q358"/>
+    <mergeCell ref="S358:T358"/>
+    <mergeCell ref="U358:V358"/>
+    <mergeCell ref="B359:C359"/>
+    <mergeCell ref="E359:F359"/>
+    <mergeCell ref="P359:Q359"/>
+    <mergeCell ref="S359:T359"/>
+    <mergeCell ref="U359:V359"/>
+    <mergeCell ref="B360:C360"/>
+    <mergeCell ref="E360:F360"/>
+    <mergeCell ref="P360:Q360"/>
+    <mergeCell ref="S360:T360"/>
+    <mergeCell ref="U360:V360"/>
+    <mergeCell ref="B361:C361"/>
+    <mergeCell ref="E361:F361"/>
+    <mergeCell ref="P361:Q361"/>
+    <mergeCell ref="S361:T361"/>
+    <mergeCell ref="U361:V361"/>
+    <mergeCell ref="B362:C362"/>
+    <mergeCell ref="E362:F362"/>
+    <mergeCell ref="P362:Q362"/>
+    <mergeCell ref="S362:T362"/>
+    <mergeCell ref="U362:V362"/>
+    <mergeCell ref="B363:C363"/>
+    <mergeCell ref="E363:F363"/>
+    <mergeCell ref="P363:Q363"/>
+    <mergeCell ref="S363:T363"/>
+    <mergeCell ref="U363:V363"/>
+    <mergeCell ref="B364:C364"/>
+    <mergeCell ref="E364:F364"/>
+    <mergeCell ref="P364:Q364"/>
+    <mergeCell ref="S364:T364"/>
+    <mergeCell ref="U364:V364"/>
+    <mergeCell ref="B365:C365"/>
+    <mergeCell ref="E365:F365"/>
+    <mergeCell ref="P365:Q365"/>
+    <mergeCell ref="S365:T365"/>
+    <mergeCell ref="U365:V365"/>
+    <mergeCell ref="B366:C366"/>
+    <mergeCell ref="E366:F366"/>
+    <mergeCell ref="P366:Q366"/>
+    <mergeCell ref="S366:T366"/>
+    <mergeCell ref="U366:V366"/>
+    <mergeCell ref="B367:C367"/>
+    <mergeCell ref="E367:F367"/>
+    <mergeCell ref="P367:Q367"/>
+    <mergeCell ref="S367:T367"/>
+    <mergeCell ref="U367:V367"/>
+    <mergeCell ref="B368:C368"/>
+    <mergeCell ref="E368:F368"/>
+    <mergeCell ref="P368:Q368"/>
+    <mergeCell ref="S368:T368"/>
+    <mergeCell ref="U368:V368"/>
+    <mergeCell ref="B369:C369"/>
+    <mergeCell ref="E369:F369"/>
+    <mergeCell ref="P369:Q369"/>
+    <mergeCell ref="S369:T369"/>
+    <mergeCell ref="U369:V369"/>
+    <mergeCell ref="B370:C370"/>
+    <mergeCell ref="E370:F370"/>
+    <mergeCell ref="P370:Q370"/>
+    <mergeCell ref="S370:T370"/>
+    <mergeCell ref="U370:V370"/>
+    <mergeCell ref="B371:C371"/>
+    <mergeCell ref="E371:F371"/>
+    <mergeCell ref="P371:Q371"/>
+    <mergeCell ref="S371:T371"/>
+    <mergeCell ref="U371:V371"/>
+    <mergeCell ref="B372:C372"/>
+    <mergeCell ref="E372:F372"/>
+    <mergeCell ref="P372:Q372"/>
+    <mergeCell ref="S372:T372"/>
+    <mergeCell ref="U372:V372"/>
+    <mergeCell ref="B373:C373"/>
+    <mergeCell ref="E373:F373"/>
+    <mergeCell ref="P373:Q373"/>
+    <mergeCell ref="S373:T373"/>
+    <mergeCell ref="U373:V373"/>
+    <mergeCell ref="B374:C374"/>
+    <mergeCell ref="E374:F374"/>
+    <mergeCell ref="P374:Q374"/>
+    <mergeCell ref="S374:T374"/>
+    <mergeCell ref="U374:V374"/>
+    <mergeCell ref="B375:C375"/>
+    <mergeCell ref="E375:F375"/>
+    <mergeCell ref="P375:Q375"/>
+    <mergeCell ref="S375:T375"/>
+    <mergeCell ref="U375:V375"/>
+    <mergeCell ref="B376:C376"/>
+    <mergeCell ref="E376:F376"/>
+    <mergeCell ref="P376:Q376"/>
+    <mergeCell ref="S376:T376"/>
+    <mergeCell ref="U376:V376"/>
+    <mergeCell ref="B377:C377"/>
+    <mergeCell ref="E377:F377"/>
+    <mergeCell ref="P377:Q377"/>
+    <mergeCell ref="S377:T377"/>
+    <mergeCell ref="U377:V377"/>
+    <mergeCell ref="B378:C378"/>
+    <mergeCell ref="E378:F378"/>
+    <mergeCell ref="P378:Q378"/>
+    <mergeCell ref="S378:T378"/>
+    <mergeCell ref="U378:V378"/>
+    <mergeCell ref="B379:C379"/>
+    <mergeCell ref="E379:F379"/>
+    <mergeCell ref="P379:Q379"/>
+    <mergeCell ref="S379:T379"/>
+    <mergeCell ref="U379:V379"/>
+    <mergeCell ref="B380:C380"/>
+    <mergeCell ref="E380:F380"/>
+    <mergeCell ref="P380:Q380"/>
+    <mergeCell ref="S380:T380"/>
+    <mergeCell ref="U380:V380"/>
+    <mergeCell ref="B381:C381"/>
+    <mergeCell ref="E381:F381"/>
+    <mergeCell ref="P381:Q381"/>
+    <mergeCell ref="S381:T381"/>
+    <mergeCell ref="U381:V381"/>
+    <mergeCell ref="B382:C382"/>
+    <mergeCell ref="E382:F382"/>
+    <mergeCell ref="P382:Q382"/>
+    <mergeCell ref="S382:T382"/>
+    <mergeCell ref="U382:V382"/>
+    <mergeCell ref="B383:C383"/>
+    <mergeCell ref="E383:F383"/>
+    <mergeCell ref="P383:Q383"/>
+    <mergeCell ref="S383:T383"/>
+    <mergeCell ref="U383:V383"/>
+    <mergeCell ref="B384:C384"/>
+    <mergeCell ref="E384:F384"/>
+    <mergeCell ref="P384:Q384"/>
+    <mergeCell ref="S384:T384"/>
+    <mergeCell ref="U384:V384"/>
+    <mergeCell ref="B385:C385"/>
+    <mergeCell ref="E385:F385"/>
+    <mergeCell ref="P385:Q385"/>
+    <mergeCell ref="S385:T385"/>
+    <mergeCell ref="U385:V385"/>
+    <mergeCell ref="B386:C386"/>
+    <mergeCell ref="E386:F386"/>
+    <mergeCell ref="P386:Q386"/>
+    <mergeCell ref="S386:T386"/>
+    <mergeCell ref="U386:V386"/>
+    <mergeCell ref="B387:C387"/>
+    <mergeCell ref="E387:F387"/>
+    <mergeCell ref="P387:Q387"/>
+    <mergeCell ref="S387:T387"/>
+    <mergeCell ref="U387:V387"/>
+    <mergeCell ref="B388:C388"/>
+    <mergeCell ref="E388:F388"/>
+    <mergeCell ref="P388:Q388"/>
+    <mergeCell ref="S388:T388"/>
+    <mergeCell ref="U388:V388"/>
+    <mergeCell ref="B389:C389"/>
+    <mergeCell ref="E389:F389"/>
+    <mergeCell ref="P389:Q389"/>
+    <mergeCell ref="S389:T389"/>
+    <mergeCell ref="U389:V389"/>
+    <mergeCell ref="B390:C390"/>
+    <mergeCell ref="E390:F390"/>
+    <mergeCell ref="P390:Q390"/>
+    <mergeCell ref="S390:T390"/>
+    <mergeCell ref="U390:V390"/>
+    <mergeCell ref="B391:C391"/>
+    <mergeCell ref="E391:F391"/>
+    <mergeCell ref="P391:Q391"/>
+    <mergeCell ref="S391:T391"/>
+    <mergeCell ref="U391:V391"/>
+    <mergeCell ref="B392:C392"/>
+    <mergeCell ref="E392:F392"/>
+    <mergeCell ref="P392:Q392"/>
+    <mergeCell ref="S392:T392"/>
+    <mergeCell ref="U392:V392"/>
+    <mergeCell ref="B393:C393"/>
+    <mergeCell ref="E393:F393"/>
+    <mergeCell ref="P393:Q393"/>
+    <mergeCell ref="S393:T393"/>
+    <mergeCell ref="U393:V393"/>
+    <mergeCell ref="B394:C394"/>
+    <mergeCell ref="E394:F394"/>
+    <mergeCell ref="P394:Q394"/>
+    <mergeCell ref="S394:T394"/>
+    <mergeCell ref="U394:V394"/>
+    <mergeCell ref="B395:C395"/>
+    <mergeCell ref="E395:F395"/>
+    <mergeCell ref="P395:Q395"/>
+    <mergeCell ref="S395:T395"/>
+    <mergeCell ref="U395:V395"/>
+    <mergeCell ref="B396:C396"/>
+    <mergeCell ref="E396:F396"/>
+    <mergeCell ref="P396:Q396"/>
+    <mergeCell ref="S396:T396"/>
+    <mergeCell ref="U396:V396"/>
+    <mergeCell ref="B397:C397"/>
+    <mergeCell ref="E397:F397"/>
+    <mergeCell ref="P397:Q397"/>
+    <mergeCell ref="S397:T397"/>
+    <mergeCell ref="U397:V397"/>
+    <mergeCell ref="B398:C398"/>
+    <mergeCell ref="E398:F398"/>
+    <mergeCell ref="P398:Q398"/>
+    <mergeCell ref="S398:T398"/>
+    <mergeCell ref="U398:V398"/>
+    <mergeCell ref="B399:C399"/>
+    <mergeCell ref="E399:F399"/>
+    <mergeCell ref="P399:Q399"/>
+    <mergeCell ref="S399:T399"/>
+    <mergeCell ref="U399:V399"/>
+    <mergeCell ref="B400:C400"/>
+    <mergeCell ref="E400:F400"/>
+    <mergeCell ref="P400:Q400"/>
+    <mergeCell ref="S400:T400"/>
+    <mergeCell ref="U400:V400"/>
+    <mergeCell ref="B401:C401"/>
+    <mergeCell ref="E401:F401"/>
+    <mergeCell ref="P401:Q401"/>
+    <mergeCell ref="S401:T401"/>
+    <mergeCell ref="U401:V401"/>
+    <mergeCell ref="B402:C402"/>
+    <mergeCell ref="E402:F402"/>
+    <mergeCell ref="P402:Q402"/>
+    <mergeCell ref="S402:T402"/>
+    <mergeCell ref="U402:V402"/>
+    <mergeCell ref="B403:C403"/>
+    <mergeCell ref="E403:F403"/>
+    <mergeCell ref="P403:Q403"/>
+    <mergeCell ref="S403:T403"/>
+    <mergeCell ref="U403:V403"/>
+    <mergeCell ref="B404:C404"/>
+    <mergeCell ref="E404:F404"/>
+    <mergeCell ref="P404:Q404"/>
+    <mergeCell ref="S404:T404"/>
+    <mergeCell ref="U404:V404"/>
+    <mergeCell ref="B405:C405"/>
+    <mergeCell ref="E405:F405"/>
+    <mergeCell ref="P405:Q405"/>
+    <mergeCell ref="S405:T405"/>
+    <mergeCell ref="U405:V405"/>
+    <mergeCell ref="B406:C406"/>
+    <mergeCell ref="E406:F406"/>
+    <mergeCell ref="P406:Q406"/>
+    <mergeCell ref="S406:T406"/>
+    <mergeCell ref="U406:V406"/>
+    <mergeCell ref="B407:C407"/>
+    <mergeCell ref="E407:F407"/>
+    <mergeCell ref="P407:Q407"/>
+    <mergeCell ref="S407:T407"/>
+    <mergeCell ref="U407:V407"/>
+    <mergeCell ref="B408:C408"/>
+    <mergeCell ref="E408:F408"/>
+    <mergeCell ref="P408:Q408"/>
+    <mergeCell ref="S408:T408"/>
+    <mergeCell ref="U408:V408"/>
+    <mergeCell ref="B409:C409"/>
+    <mergeCell ref="E409:F409"/>
+    <mergeCell ref="P409:Q409"/>
+    <mergeCell ref="S409:T409"/>
+    <mergeCell ref="U409:V409"/>
+    <mergeCell ref="B410:C410"/>
+    <mergeCell ref="E410:F410"/>
+    <mergeCell ref="P410:Q410"/>
+    <mergeCell ref="S410:T410"/>
+    <mergeCell ref="U410:V410"/>
+    <mergeCell ref="B411:C411"/>
+    <mergeCell ref="E411:F411"/>
+    <mergeCell ref="P411:Q411"/>
+    <mergeCell ref="S411:T411"/>
+    <mergeCell ref="U411:V411"/>
+    <mergeCell ref="B412:C412"/>
+    <mergeCell ref="E412:F412"/>
+    <mergeCell ref="P412:Q412"/>
+    <mergeCell ref="S412:T412"/>
+    <mergeCell ref="U412:V412"/>
+    <mergeCell ref="B413:C413"/>
+    <mergeCell ref="E413:F413"/>
+    <mergeCell ref="P413:Q413"/>
+    <mergeCell ref="S413:T413"/>
+    <mergeCell ref="U413:V413"/>
+    <mergeCell ref="B414:C414"/>
+    <mergeCell ref="E414:F414"/>
+    <mergeCell ref="P414:Q414"/>
+    <mergeCell ref="S414:T414"/>
+    <mergeCell ref="U414:V414"/>
+    <mergeCell ref="B415:C415"/>
+    <mergeCell ref="E415:F415"/>
+    <mergeCell ref="P415:Q415"/>
+    <mergeCell ref="S415:T415"/>
+    <mergeCell ref="U415:V415"/>
+    <mergeCell ref="B416:C416"/>
+    <mergeCell ref="E416:F416"/>
+    <mergeCell ref="P416:Q416"/>
+    <mergeCell ref="S416:T416"/>
+    <mergeCell ref="U416:V416"/>
+    <mergeCell ref="B417:C417"/>
+    <mergeCell ref="E417:F417"/>
+    <mergeCell ref="P417:Q417"/>
+    <mergeCell ref="S417:T417"/>
+    <mergeCell ref="U417:V417"/>
+    <mergeCell ref="B418:C418"/>
+    <mergeCell ref="E418:F418"/>
+    <mergeCell ref="P418:Q418"/>
+    <mergeCell ref="S418:T418"/>
+    <mergeCell ref="U418:V418"/>
+    <mergeCell ref="B419:C419"/>
+    <mergeCell ref="E419:F419"/>
+    <mergeCell ref="P419:Q419"/>
+    <mergeCell ref="S419:T419"/>
+    <mergeCell ref="U419:V419"/>
+    <mergeCell ref="B420:C420"/>
+    <mergeCell ref="E420:F420"/>
+    <mergeCell ref="P420:Q420"/>
+    <mergeCell ref="S420:T420"/>
+    <mergeCell ref="U420:V420"/>
+    <mergeCell ref="B421:C421"/>
+    <mergeCell ref="E421:F421"/>
+    <mergeCell ref="P421:Q421"/>
+    <mergeCell ref="S421:T421"/>
+    <mergeCell ref="U421:V421"/>
+    <mergeCell ref="B422:C422"/>
+    <mergeCell ref="E422:F422"/>
+    <mergeCell ref="P422:Q422"/>
+    <mergeCell ref="S422:T422"/>
+    <mergeCell ref="U422:V422"/>
+    <mergeCell ref="B423:C423"/>
+    <mergeCell ref="E423:F423"/>
+    <mergeCell ref="P423:Q423"/>
+    <mergeCell ref="S423:T423"/>
+    <mergeCell ref="U423:V423"/>
+    <mergeCell ref="B424:C424"/>
+    <mergeCell ref="E424:F424"/>
+    <mergeCell ref="P424:Q424"/>
+    <mergeCell ref="S424:T424"/>
+    <mergeCell ref="U424:V424"/>
+    <mergeCell ref="B425:C425"/>
+    <mergeCell ref="E425:F425"/>
+    <mergeCell ref="P425:Q425"/>
+    <mergeCell ref="S425:T425"/>
+    <mergeCell ref="U425:V425"/>
+    <mergeCell ref="B426:C426"/>
+    <mergeCell ref="E426:F426"/>
+    <mergeCell ref="P426:Q426"/>
+    <mergeCell ref="S426:T426"/>
+    <mergeCell ref="U426:V426"/>
+    <mergeCell ref="B427:C427"/>
+    <mergeCell ref="E427:F427"/>
+    <mergeCell ref="P427:Q427"/>
+    <mergeCell ref="S427:T427"/>
+    <mergeCell ref="U427:V427"/>
+    <mergeCell ref="B428:C428"/>
+    <mergeCell ref="E428:F428"/>
+    <mergeCell ref="P428:Q428"/>
+    <mergeCell ref="S428:T428"/>
+    <mergeCell ref="U428:V428"/>
+    <mergeCell ref="B429:C429"/>
+    <mergeCell ref="E429:F429"/>
+    <mergeCell ref="P429:Q429"/>
+    <mergeCell ref="S429:T429"/>
+    <mergeCell ref="U429:V429"/>
+    <mergeCell ref="B430:C430"/>
+    <mergeCell ref="E430:F430"/>
+    <mergeCell ref="P430:Q430"/>
+    <mergeCell ref="S430:T430"/>
+    <mergeCell ref="U430:V430"/>
+    <mergeCell ref="B431:C431"/>
+    <mergeCell ref="E431:F431"/>
+    <mergeCell ref="P431:Q431"/>
+    <mergeCell ref="S431:T431"/>
+    <mergeCell ref="U431:V431"/>
+    <mergeCell ref="B432:C432"/>
+    <mergeCell ref="E432:F432"/>
+    <mergeCell ref="P432:Q432"/>
+    <mergeCell ref="S432:T432"/>
+    <mergeCell ref="U432:V432"/>
+    <mergeCell ref="B433:C433"/>
+    <mergeCell ref="E433:F433"/>
+    <mergeCell ref="P433:Q433"/>
+    <mergeCell ref="S433:T433"/>
+    <mergeCell ref="U433:V433"/>
+    <mergeCell ref="B434:C434"/>
+    <mergeCell ref="E434:F434"/>
+    <mergeCell ref="P434:Q434"/>
+    <mergeCell ref="S434:T434"/>
+    <mergeCell ref="U434:V434"/>
+    <mergeCell ref="B435:C435"/>
+    <mergeCell ref="E435:F435"/>
+    <mergeCell ref="P435:Q435"/>
+    <mergeCell ref="S435:T435"/>
+    <mergeCell ref="U435:V435"/>
+    <mergeCell ref="B436:C436"/>
+    <mergeCell ref="E436:F436"/>
+    <mergeCell ref="P436:Q436"/>
+    <mergeCell ref="S436:T436"/>
+    <mergeCell ref="U436:V436"/>
+    <mergeCell ref="B437:C437"/>
+    <mergeCell ref="E437:F437"/>
+    <mergeCell ref="P437:Q437"/>
+    <mergeCell ref="S437:T437"/>
+    <mergeCell ref="U437:V437"/>
+    <mergeCell ref="B438:C438"/>
+    <mergeCell ref="E438:F438"/>
+    <mergeCell ref="P438:Q438"/>
+    <mergeCell ref="S438:T438"/>
+    <mergeCell ref="U438:V438"/>
   </mergeCells>
   <pageMargins left="0.0393700787401575" right="0.0393700787401575" top="0.0393700787401575" bottom="0.0393700787401575" header="0.0393700787401575" footer="0.0393700787401575"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>

--- a/Base_Interrupcoes.xlsx
+++ b/Base_Interrupcoes.xlsx
@@ -253,16 +253,16 @@
     <xf applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" numFmtId="82" fontId="5" fillId="4" borderId="0">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" numFmtId="0" fontId="5" fillId="3" borderId="6">
+    <xf applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" numFmtId="0" fontId="5" fillId="4" borderId="6">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" numFmtId="0" fontId="5" fillId="3" borderId="7">
+    <xf applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" numFmtId="0" fontId="5" fillId="4" borderId="7">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" numFmtId="0" fontId="5" fillId="3" borderId="7">
+    <xf applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" numFmtId="0" fontId="5" fillId="4" borderId="7">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" numFmtId="82" fontId="5" fillId="3" borderId="7">
+    <xf applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" numFmtId="82" fontId="5" fillId="4" borderId="7">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -466,7 +466,7 @@
       <c s="4" t="str" r="A7"/>
       <c s="7" t="inlineStr" r="T7">
         <is>
-          <t xml:space="preserve">Emissão: 19/10/2026</t>
+          <t xml:space="preserve">Emissão: 20/10/2026</t>
         </is>
       </c>
       <c s="5" t="str" r="V7"/>
@@ -475,7 +475,7 @@
       <c s="4" t="str" r="A8"/>
       <c s="8" t="inlineStr" r="F8">
         <is>
-          <t xml:space="preserve">Período: 01/10/2026 até 18/10/2026; Turno: Todos; Tempo: Calendário</t>
+          <t xml:space="preserve">Período: 01/10/2026 até 19/10/2026; Turno: Todos; Tempo: Calendário</t>
         </is>
       </c>
       <c s="5" t="str" r="V8"/>
@@ -2910,7 +2910,7 @@
     <row r="49" ht="15.6" customHeight="0">
       <c s="15" t="inlineStr" r="A49">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 03</t>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
         </is>
       </c>
       <c s="16" t="str" r="B49"/>
@@ -2960,7 +2960,7 @@
       <c s="16" t="str" r="P49"/>
       <c s="16" t="inlineStr" r="R49">
         <is>
-          <t xml:space="preserve">49efe8b0-bdd1-11f1-cb5a-f2050a003223</t>
+          <t xml:space="preserve">49cef330-bdd1-11f1-8f07-f2050a003223</t>
         </is>
       </c>
       <c s="16" t="str" r="S49"/>
@@ -2974,7 +2974,7 @@
     <row r="50" ht="15.6" customHeight="0">
       <c s="19" t="inlineStr" r="A50">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 02</t>
+          <t xml:space="preserve">TRANSVERSAL 03</t>
         </is>
       </c>
       <c s="20" t="str" r="B50"/>
@@ -3024,7 +3024,7 @@
       <c s="20" t="str" r="P50"/>
       <c s="20" t="inlineStr" r="R50">
         <is>
-          <t xml:space="preserve">49cef330-bdd1-11f1-8f07-f2050a003223</t>
+          <t xml:space="preserve">49efe8b0-bdd1-11f1-cb5a-f2050a003223</t>
         </is>
       </c>
       <c s="20" t="str" r="S50"/>
@@ -3110,12 +3110,12 @@
     <row r="52" ht="15.6" customHeight="0">
       <c s="19" t="inlineStr" r="A52">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 01</t>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="B52">
         <is>
-          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
         </is>
       </c>
       <c s="21" t="inlineStr" r="D52">
@@ -3127,11 +3127,11 @@
         <v>46297.2916666667</v>
       </c>
       <c s="22" r="G52">
-        <v>46297.3020833333</v>
+        <v>46297.2986111111</v>
       </c>
       <c s="21" t="inlineStr" r="H52">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c s="21" t="str" r="I52"/>
@@ -3158,18 +3158,18 @@
       </c>
       <c s="20" t="inlineStr" r="O52">
         <is>
-          <t xml:space="preserve">dds e assinatura dos documentos</t>
+          <t xml:space="preserve">DDS</t>
         </is>
       </c>
       <c s="20" t="str" r="P52"/>
       <c s="20" t="inlineStr" r="R52">
         <is>
-          <t xml:space="preserve">61a3b7a0-be4b-11f1-9cbf-f2050a003223</t>
+          <t xml:space="preserve">942e4bd0-be4c-11f1-ca85-f2050a003223</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="S52">
         <is>
-          <t xml:space="preserve">10046873    </t>
+          <t xml:space="preserve">10047019    </t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="U52">
@@ -3182,12 +3182,12 @@
     <row r="53" ht="15.55" customHeight="0">
       <c s="15" t="inlineStr" r="A53">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 05</t>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="B53">
         <is>
-          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
         </is>
       </c>
       <c s="17" t="inlineStr" r="D53">
@@ -3199,11 +3199,11 @@
         <v>46297.2916666667</v>
       </c>
       <c s="18" r="G53">
-        <v>46297.3055555556</v>
+        <v>46297.3020833333</v>
       </c>
       <c s="17" t="inlineStr" r="H53">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c s="17" t="str" r="I53"/>
@@ -3230,18 +3230,18 @@
       </c>
       <c s="16" t="inlineStr" r="O53">
         <is>
-          <t xml:space="preserve">dds com supervisor QUEDA DE MATERIAIS</t>
+          <t xml:space="preserve">dds e assinatura dos documentos</t>
         </is>
       </c>
       <c s="16" t="str" r="P53"/>
       <c s="16" t="inlineStr" r="R53">
         <is>
-          <t xml:space="preserve">167ccc00-be4e-11f1-cdcf-f2050a003223</t>
+          <t xml:space="preserve">61a3b7a0-be4b-11f1-9cbf-f2050a003223</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="S53">
         <is>
-          <t xml:space="preserve">10046135    </t>
+          <t xml:space="preserve">10046873    </t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="U53">
@@ -3254,12 +3254,12 @@
     <row r="54" ht="15.6" customHeight="0">
       <c s="19" t="inlineStr" r="A54">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 04</t>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="B54">
         <is>
-          <t xml:space="preserve">TR04-DESENROLADOR</t>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
         </is>
       </c>
       <c s="21" t="inlineStr" r="D54">
@@ -3271,11 +3271,11 @@
         <v>46297.2916666667</v>
       </c>
       <c s="22" r="G54">
-        <v>46297.2986111111</v>
+        <v>46297.3055555556</v>
       </c>
       <c s="21" t="inlineStr" r="H54">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c s="21" t="str" r="I54"/>
@@ -3302,18 +3302,18 @@
       </c>
       <c s="20" t="inlineStr" r="O54">
         <is>
-          <t xml:space="preserve">DDS</t>
+          <t xml:space="preserve">dds com supervisor QUEDA DE MATERIAIS</t>
         </is>
       </c>
       <c s="20" t="str" r="P54"/>
       <c s="20" t="inlineStr" r="R54">
         <is>
-          <t xml:space="preserve">942e4bd0-be4c-11f1-ca85-f2050a003223</t>
+          <t xml:space="preserve">167ccc00-be4e-11f1-cdcf-f2050a003223</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="S54">
         <is>
-          <t xml:space="preserve">10047019    </t>
+          <t xml:space="preserve">10046135    </t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="U54">
@@ -10319,10 +10319,14 @@
     <row r="153" ht="15.6" customHeight="0">
       <c s="15" t="inlineStr" r="A153">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 03</t>
-        </is>
-      </c>
-      <c s="16" t="str" r="B153"/>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B153">
+        <is>
+          <t xml:space="preserve">TR04-CARRO DE ENTRADA</t>
+        </is>
+      </c>
       <c s="17" t="inlineStr" r="D153">
         <is>
           <t xml:space="preserve">TURNO B</t>
@@ -10358,7 +10362,7 @@
       <c s="16" t="str" r="M153"/>
       <c s="16" t="inlineStr" r="N153">
         <is>
-          <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
+          <t xml:space="preserve">FALTA DEMANDA</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="O153">
@@ -10369,10 +10373,14 @@
       <c s="16" t="str" r="P153"/>
       <c s="16" t="inlineStr" r="R153">
         <is>
-          <t xml:space="preserve">f4dfe370-c0f5-11f1-c191-f2050a003223</t>
-        </is>
-      </c>
-      <c s="16" t="str" r="S153"/>
+          <t xml:space="preserve">f4fe8f00-c0f5-11f1-ad1e-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S153">
+        <is>
+          <t xml:space="preserve">10048032    </t>
+        </is>
+      </c>
       <c s="16" t="inlineStr" r="U153">
         <is>
           <t xml:space="preserve">Sim</t>
@@ -10383,14 +10391,10 @@
     <row r="154" ht="15.55" customHeight="0">
       <c s="19" t="inlineStr" r="A154">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 04</t>
-        </is>
-      </c>
-      <c s="20" t="inlineStr" r="B154">
-        <is>
-          <t xml:space="preserve">TR04-CARRO DE ENTRADA</t>
-        </is>
-      </c>
+          <t xml:space="preserve">TRANSVERSAL 03</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B154"/>
       <c s="21" t="inlineStr" r="D154">
         <is>
           <t xml:space="preserve">TURNO B</t>
@@ -10426,7 +10430,7 @@
       <c s="20" t="str" r="M154"/>
       <c s="20" t="inlineStr" r="N154">
         <is>
-          <t xml:space="preserve">FALTA DEMANDA</t>
+          <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="O154">
@@ -10437,14 +10441,10 @@
       <c s="20" t="str" r="P154"/>
       <c s="20" t="inlineStr" r="R154">
         <is>
-          <t xml:space="preserve">f4fe8f00-c0f5-11f1-ad1e-f2050a003223</t>
-        </is>
-      </c>
-      <c s="20" t="inlineStr" r="S154">
-        <is>
-          <t xml:space="preserve">10048032    </t>
-        </is>
-      </c>
+          <t xml:space="preserve">f4dfe370-c0f5-11f1-c191-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="S154"/>
       <c s="20" t="inlineStr" r="U154">
         <is>
           <t xml:space="preserve">Sim</t>
@@ -10671,12 +10671,12 @@
     <row r="158" ht="15.6" customHeight="0">
       <c s="19" t="inlineStr" r="A158">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 04</t>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="B158">
         <is>
-          <t xml:space="preserve">TR04-DESENROLADOR</t>
+          <t xml:space="preserve">TR01-MESA TRANSPORTADORA</t>
         </is>
       </c>
       <c s="21" t="inlineStr" r="D158">
@@ -10688,11 +10688,11 @@
         <v>46301.2916666667</v>
       </c>
       <c s="22" r="G158">
-        <v>46301.2986111111</v>
+        <v>46301.3020833333</v>
       </c>
       <c s="21" t="inlineStr" r="H158">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c s="21" t="str" r="I158"/>
@@ -10719,18 +10719,18 @@
       </c>
       <c s="20" t="inlineStr" r="O158">
         <is>
-          <t xml:space="preserve">DDS</t>
+          <t xml:space="preserve">dds  e assinatura dos documentos</t>
         </is>
       </c>
       <c s="20" t="str" r="P158"/>
       <c s="20" t="inlineStr" r="R158">
         <is>
-          <t xml:space="preserve">00542e40-c174-11f1-b395-f2050a003223</t>
+          <t xml:space="preserve">fa2e6070-c16f-11f1-a1bf-f2050a003223</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="S158">
         <is>
-          <t xml:space="preserve">10048032    </t>
+          <t xml:space="preserve">10047271    </t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="U158">
@@ -10743,12 +10743,12 @@
     <row r="159" ht="15.55" customHeight="0">
       <c s="15" t="inlineStr" r="A159">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 01</t>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="B159">
         <is>
-          <t xml:space="preserve">TR01-MESA TRANSPORTADORA</t>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
         </is>
       </c>
       <c s="17" t="inlineStr" r="D159">
@@ -10760,11 +10760,11 @@
         <v>46301.2916666667</v>
       </c>
       <c s="18" r="G159">
-        <v>46301.3020833333</v>
+        <v>46301.2986111111</v>
       </c>
       <c s="17" t="inlineStr" r="H159">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c s="17" t="str" r="I159"/>
@@ -10791,18 +10791,18 @@
       </c>
       <c s="16" t="inlineStr" r="O159">
         <is>
-          <t xml:space="preserve">dds  e assinatura dos documentos</t>
+          <t xml:space="preserve">DDS</t>
         </is>
       </c>
       <c s="16" t="str" r="P159"/>
       <c s="16" t="inlineStr" r="R159">
         <is>
-          <t xml:space="preserve">fa2e6070-c16f-11f1-a1bf-f2050a003223</t>
+          <t xml:space="preserve">00542e40-c174-11f1-b395-f2050a003223</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="S159">
         <is>
-          <t xml:space="preserve">10047271    </t>
+          <t xml:space="preserve">10048032    </t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="U159">
@@ -15587,12 +15587,12 @@
     <row r="227" ht="15.6" customHeight="0">
       <c s="15" t="inlineStr" r="A227">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 01</t>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="B227">
         <is>
-          <t xml:space="preserve">TR01-MESA TRANSPORTADORA</t>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
         </is>
       </c>
       <c s="17" t="inlineStr" r="D227">
@@ -15604,11 +15604,11 @@
         <v>46302.2916666667</v>
       </c>
       <c s="18" r="G227">
-        <v>46302.3020833333</v>
+        <v>46302.3055555556</v>
       </c>
       <c s="17" t="inlineStr" r="H227">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c s="17" t="str" r="I227"/>
@@ -15635,18 +15635,18 @@
       </c>
       <c s="16" t="inlineStr" r="O227">
         <is>
-          <t xml:space="preserve">dds e assinatura dos documentos</t>
+          <t xml:space="preserve">dds</t>
         </is>
       </c>
       <c s="16" t="str" r="P227"/>
       <c s="16" t="inlineStr" r="R227">
         <is>
-          <t xml:space="preserve">e92b60c0-c237-11f1-ab7f-f2050a003223</t>
+          <t xml:space="preserve">0bb05300-c23b-11f1-bbbb-f2050a003223</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="S227">
         <is>
-          <t xml:space="preserve">10048039    </t>
+          <t xml:space="preserve">10046774    </t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="U227">
@@ -15659,12 +15659,12 @@
     <row r="228" ht="15.6" customHeight="0">
       <c s="19" t="inlineStr" r="A228">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 05</t>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="B228">
         <is>
-          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+          <t xml:space="preserve">TR01-MESA TRANSPORTADORA</t>
         </is>
       </c>
       <c s="21" t="inlineStr" r="D228">
@@ -15676,11 +15676,11 @@
         <v>46302.2916666667</v>
       </c>
       <c s="22" r="G228">
-        <v>46302.3055555556</v>
+        <v>46302.3020833333</v>
       </c>
       <c s="21" t="inlineStr" r="H228">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c s="21" t="str" r="I228"/>
@@ -15707,18 +15707,18 @@
       </c>
       <c s="20" t="inlineStr" r="O228">
         <is>
-          <t xml:space="preserve">dds</t>
+          <t xml:space="preserve">dds e assinatura dos documentos</t>
         </is>
       </c>
       <c s="20" t="str" r="P228"/>
       <c s="20" t="inlineStr" r="R228">
         <is>
-          <t xml:space="preserve">0bb05300-c23b-11f1-bbbb-f2050a003223</t>
+          <t xml:space="preserve">e92b60c0-c237-11f1-ab7f-f2050a003223</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="S228">
         <is>
-          <t xml:space="preserve">10046774    </t>
+          <t xml:space="preserve">10048039    </t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="U228">
@@ -18551,12 +18551,12 @@
     <row r="269" ht="15.6" customHeight="0">
       <c s="15" t="inlineStr" r="A269">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 01</t>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="B269">
         <is>
-          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
         </is>
       </c>
       <c s="17" t="inlineStr" r="D269">
@@ -18568,11 +18568,11 @@
         <v>46303.2916666667</v>
       </c>
       <c s="18" r="G269">
-        <v>46303.3020833333</v>
+        <v>46303.2986111111</v>
       </c>
       <c s="17" t="inlineStr" r="H269">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c s="17" t="str" r="I269"/>
@@ -18599,18 +18599,18 @@
       </c>
       <c s="16" t="inlineStr" r="O269">
         <is>
-          <t xml:space="preserve">dds e assinatura dos documentos</t>
+          <t xml:space="preserve">DDS</t>
         </is>
       </c>
       <c s="16" t="str" r="P269"/>
       <c s="16" t="inlineStr" r="R269">
         <is>
-          <t xml:space="preserve">065f5d20-c302-11f1-8108-f2050a003223</t>
+          <t xml:space="preserve">6e8883a0-c301-11f1-9a54-f2050a003223</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="S269">
         <is>
-          <t xml:space="preserve">10048233    </t>
+          <t xml:space="preserve">10048465    </t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="U269">
@@ -18623,12 +18623,12 @@
     <row r="270" ht="15.6" customHeight="0">
       <c s="19" t="inlineStr" r="A270">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 02</t>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="B270">
         <is>
-          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
         </is>
       </c>
       <c s="21" t="inlineStr" r="D270">
@@ -18640,11 +18640,11 @@
         <v>46303.2916666667</v>
       </c>
       <c s="22" r="G270">
-        <v>46303.2986111111</v>
+        <v>46303.3020833333</v>
       </c>
       <c s="21" t="inlineStr" r="H270">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c s="21" t="str" r="I270"/>
@@ -18671,18 +18671,18 @@
       </c>
       <c s="20" t="inlineStr" r="O270">
         <is>
-          <t xml:space="preserve">DDS</t>
+          <t xml:space="preserve">dds e assinatura dos documentos</t>
         </is>
       </c>
       <c s="20" t="str" r="P270"/>
       <c s="20" t="inlineStr" r="R270">
         <is>
-          <t xml:space="preserve">6e8883a0-c301-11f1-9a54-f2050a003223</t>
+          <t xml:space="preserve">065f5d20-c302-11f1-8108-f2050a003223</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="S270">
         <is>
-          <t xml:space="preserve">10048465    </t>
+          <t xml:space="preserve">10048233    </t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="U270">
@@ -20811,12 +20811,12 @@
     <row r="301" ht="15.6" customHeight="0">
       <c s="15" t="inlineStr" r="A301">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 01</t>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="B301">
         <is>
-          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
         </is>
       </c>
       <c s="17" t="inlineStr" r="D301">
@@ -20828,11 +20828,11 @@
         <v>46304.2916666667</v>
       </c>
       <c s="18" r="G301">
-        <v>46304.3020833333</v>
+        <v>46304.2986111111</v>
       </c>
       <c s="17" t="inlineStr" r="H301">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c s="17" t="str" r="I301"/>
@@ -20859,18 +20859,18 @@
       </c>
       <c s="16" t="inlineStr" r="O301">
         <is>
-          <t xml:space="preserve">dds e assinatura dos documentos</t>
+          <t xml:space="preserve">DDS</t>
         </is>
       </c>
       <c s="16" t="str" r="P301"/>
       <c s="16" t="inlineStr" r="R301">
         <is>
-          <t xml:space="preserve">c7659750-c3ca-11f1-b424-f2050a003223</t>
+          <t xml:space="preserve">8328c2a0-c3cb-11f1-c59b-f2050a003223</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="S301">
         <is>
-          <t xml:space="preserve">10048417    </t>
+          <t xml:space="preserve">10048738    </t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="U301">
@@ -20883,12 +20883,12 @@
     <row r="302" ht="15.6" customHeight="0">
       <c s="19" t="inlineStr" r="A302">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 02</t>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="B302">
         <is>
-          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
         </is>
       </c>
       <c s="21" t="inlineStr" r="D302">
@@ -20900,11 +20900,11 @@
         <v>46304.2916666667</v>
       </c>
       <c s="22" r="G302">
-        <v>46304.2986111111</v>
+        <v>46304.3020833333</v>
       </c>
       <c s="21" t="inlineStr" r="H302">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c s="21" t="str" r="I302"/>
@@ -20931,18 +20931,18 @@
       </c>
       <c s="20" t="inlineStr" r="O302">
         <is>
-          <t xml:space="preserve">DDS</t>
+          <t xml:space="preserve">dds e assinatura dos documentos</t>
         </is>
       </c>
       <c s="20" t="str" r="P302"/>
       <c s="20" t="inlineStr" r="R302">
         <is>
-          <t xml:space="preserve">8328c2a0-c3cb-11f1-c59b-f2050a003223</t>
+          <t xml:space="preserve">c7659750-c3ca-11f1-b424-f2050a003223</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="S302">
         <is>
-          <t xml:space="preserve">10048738    </t>
+          <t xml:space="preserve">10048417    </t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="U302">
@@ -22715,12 +22715,12 @@
     <row r="328" ht="15.55" customHeight="0">
       <c s="19" t="inlineStr" r="A328">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 01</t>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="B328">
         <is>
-          <t xml:space="preserve">TR01-MESA TRANSPORTADORA</t>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
         </is>
       </c>
       <c s="21" t="inlineStr" r="D328">
@@ -22732,11 +22732,11 @@
         <v>46308.2916666667</v>
       </c>
       <c s="22" r="G328">
-        <v>46308.3020833333</v>
+        <v>46308.2986111111</v>
       </c>
       <c s="21" t="inlineStr" r="H328">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c s="21" t="str" r="I328"/>
@@ -22763,18 +22763,18 @@
       </c>
       <c s="20" t="inlineStr" r="O328">
         <is>
-          <t xml:space="preserve">dds e assinatura dos documentos</t>
+          <t xml:space="preserve">dds</t>
         </is>
       </c>
       <c s="20" t="str" r="P328"/>
       <c s="20" t="inlineStr" r="R328">
         <is>
-          <t xml:space="preserve">49ee6680-c6ef-11f1-b32a-f2050a003223</t>
+          <t xml:space="preserve">90a4c9e0-c6f2-11f1-c266-f2050a003223</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="S328">
         <is>
-          <t xml:space="preserve">10048955    </t>
+          <t xml:space="preserve">10048445    </t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="U328">
@@ -22787,12 +22787,12 @@
     <row r="329" ht="15.6" customHeight="0">
       <c s="15" t="inlineStr" r="A329">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 05</t>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="B329">
         <is>
-          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+          <t xml:space="preserve">TR01-MESA TRANSPORTADORA</t>
         </is>
       </c>
       <c s="17" t="inlineStr" r="D329">
@@ -22804,11 +22804,11 @@
         <v>46308.2916666667</v>
       </c>
       <c s="18" r="G329">
-        <v>46308.2986111111</v>
+        <v>46308.3020833333</v>
       </c>
       <c s="17" t="inlineStr" r="H329">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c s="17" t="str" r="I329"/>
@@ -22835,18 +22835,18 @@
       </c>
       <c s="16" t="inlineStr" r="O329">
         <is>
-          <t xml:space="preserve">dds</t>
+          <t xml:space="preserve">dds e assinatura dos documentos</t>
         </is>
       </c>
       <c s="16" t="str" r="P329"/>
       <c s="16" t="inlineStr" r="R329">
         <is>
-          <t xml:space="preserve">90a4c9e0-c6f2-11f1-c266-f2050a003223</t>
+          <t xml:space="preserve">49ee6680-c6ef-11f1-b32a-f2050a003223</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="S329">
         <is>
-          <t xml:space="preserve">10048445    </t>
+          <t xml:space="preserve">10048955    </t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="U329">
@@ -30296,12 +30296,12 @@
     <row r="435" ht="15.6" customHeight="0">
       <c s="15" t="inlineStr" r="A435">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 05</t>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="B435">
         <is>
-          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
         </is>
       </c>
       <c s="17" t="inlineStr" r="D435">
@@ -30344,18 +30344,18 @@
       </c>
       <c s="16" t="inlineStr" r="O435">
         <is>
-          <t xml:space="preserve">falta de demanda</t>
+          <t xml:space="preserve">Tempo livre.</t>
         </is>
       </c>
       <c s="16" t="str" r="P435"/>
       <c s="16" t="inlineStr" r="R435">
         <is>
-          <t xml:space="preserve">0aabc980-c808-11f1-987a-f2050a003223</t>
+          <t xml:space="preserve">27757a20-c808-11f1-b1c6-f2050a003223</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="S435">
         <is>
-          <t xml:space="preserve">10048447    </t>
+          <t xml:space="preserve">10049342    </t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="U435">
@@ -30368,12 +30368,12 @@
     <row r="436" ht="15.55" customHeight="0">
       <c s="19" t="inlineStr" r="A436">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 02</t>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="B436">
         <is>
-          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
         </is>
       </c>
       <c s="21" t="inlineStr" r="D436">
@@ -30416,18 +30416,18 @@
       </c>
       <c s="20" t="inlineStr" r="O436">
         <is>
-          <t xml:space="preserve">Tempo livre.</t>
+          <t xml:space="preserve">falta de demanda</t>
         </is>
       </c>
       <c s="20" t="str" r="P436"/>
       <c s="20" t="inlineStr" r="R436">
         <is>
-          <t xml:space="preserve">27757a20-c808-11f1-b1c6-f2050a003223</t>
+          <t xml:space="preserve">0aabc980-c808-11f1-987a-f2050a003223</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="S436">
         <is>
-          <t xml:space="preserve">10049342    </t>
+          <t xml:space="preserve">10048447    </t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="U436">
@@ -33145,14 +33145,10 @@
     <row r="475" ht="15.6" customHeight="0">
       <c s="15" t="inlineStr" r="A475">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 05</t>
-        </is>
-      </c>
-      <c s="16" t="inlineStr" r="B475">
-        <is>
-          <t xml:space="preserve">TR05-CARRO DE ENTRADA</t>
-        </is>
-      </c>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B475"/>
       <c s="17" t="inlineStr" r="D475">
         <is>
           <t xml:space="preserve">TURNO A</t>
@@ -33162,11 +33158,11 @@
         <v>46310.5659722222</v>
       </c>
       <c s="18" r="G475">
-        <v>46310.5763888889</v>
+        <v>46310.5736111111</v>
       </c>
       <c s="17" t="inlineStr" r="H475">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c s="17" t="str" r="I475"/>
@@ -33193,18 +33189,18 @@
       </c>
       <c s="16" t="inlineStr" r="O475">
         <is>
-          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 11 minutos</t>
         </is>
       </c>
       <c s="16" t="str" r="P475"/>
       <c s="16" t="inlineStr" r="R475">
         <is>
-          <t xml:space="preserve">64c87d60-c8b6-11f1-8443-f2050a003223</t>
+          <t xml:space="preserve">76f72ef0-c8b6-11f1-c9bc-f2050a003223</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="S475">
         <is>
-          <t xml:space="preserve">10049656    </t>
+          <t xml:space="preserve">10049344    </t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="U475">
@@ -33217,10 +33213,14 @@
     <row r="476" ht="15.55" customHeight="0">
       <c s="19" t="inlineStr" r="A476">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 02</t>
-        </is>
-      </c>
-      <c s="20" t="str" r="B476"/>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B476">
+        <is>
+          <t xml:space="preserve">TR05-CARRO DE ENTRADA</t>
+        </is>
+      </c>
       <c s="21" t="inlineStr" r="D476">
         <is>
           <t xml:space="preserve">TURNO A</t>
@@ -33230,11 +33230,11 @@
         <v>46310.5659722222</v>
       </c>
       <c s="22" r="G476">
-        <v>46310.5736111111</v>
+        <v>46310.5763888889</v>
       </c>
       <c s="21" t="inlineStr" r="H476">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c s="21" t="str" r="I476"/>
@@ -33261,18 +33261,18 @@
       </c>
       <c s="20" t="inlineStr" r="O476">
         <is>
-          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 11 minutos</t>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
         </is>
       </c>
       <c s="20" t="str" r="P476"/>
       <c s="20" t="inlineStr" r="R476">
         <is>
-          <t xml:space="preserve">76f72ef0-c8b6-11f1-c9bc-f2050a003223</t>
+          <t xml:space="preserve">64c87d60-c8b6-11f1-8443-f2050a003223</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="S476">
         <is>
-          <t xml:space="preserve">10049344    </t>
+          <t xml:space="preserve">10049656    </t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="U476">
@@ -34001,12 +34001,12 @@
     <row r="487" ht="15.6" customHeight="0">
       <c s="15" t="inlineStr" r="A487">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 02</t>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="B487">
         <is>
-          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
         </is>
       </c>
       <c s="17" t="inlineStr" r="D487">
@@ -34049,18 +34049,18 @@
       </c>
       <c s="16" t="inlineStr" r="O487">
         <is>
-          <t xml:space="preserve">Tempo livre.</t>
+          <t xml:space="preserve">falta de demanda</t>
         </is>
       </c>
       <c s="16" t="str" r="P487"/>
       <c s="16" t="inlineStr" r="R487">
         <is>
-          <t xml:space="preserve">50c39080-c94b-11f1-b296-f2050a003223</t>
+          <t xml:space="preserve">7e9605c0-c94a-11f1-bd8b-f2050a003223</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="S487">
         <is>
-          <t xml:space="preserve">10049747    </t>
+          <t xml:space="preserve">10049658    </t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="U487">
@@ -34073,12 +34073,12 @@
     <row r="488" ht="15.55" customHeight="0">
       <c s="19" t="inlineStr" r="A488">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 05</t>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="B488">
         <is>
-          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
         </is>
       </c>
       <c s="21" t="inlineStr" r="D488">
@@ -34121,18 +34121,18 @@
       </c>
       <c s="20" t="inlineStr" r="O488">
         <is>
-          <t xml:space="preserve">falta de demanda</t>
+          <t xml:space="preserve">Tempo livre.</t>
         </is>
       </c>
       <c s="20" t="str" r="P488"/>
       <c s="20" t="inlineStr" r="R488">
         <is>
-          <t xml:space="preserve">7e9605c0-c94a-11f1-bd8b-f2050a003223</t>
+          <t xml:space="preserve">50c39080-c94b-11f1-b296-f2050a003223</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="S488">
         <is>
-          <t xml:space="preserve">10049658    </t>
+          <t xml:space="preserve">10049747    </t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="U488">
@@ -34353,12 +34353,12 @@
     <row r="492" ht="15.6" customHeight="0">
       <c s="19" t="inlineStr" r="A492">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 01</t>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="B492">
         <is>
-          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
         </is>
       </c>
       <c s="21" t="inlineStr" r="D492">
@@ -34370,11 +34370,11 @@
         <v>46311.2916666667</v>
       </c>
       <c s="22" r="G492">
-        <v>46311.3097222222</v>
+        <v>46311.2986111111</v>
       </c>
       <c s="21" t="inlineStr" r="H492">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c s="21" t="str" r="I492"/>
@@ -34401,18 +34401,18 @@
       </c>
       <c s="20" t="inlineStr" r="O492">
         <is>
-          <t xml:space="preserve">dds e assinatura dos documentos</t>
+          <t xml:space="preserve">dds</t>
         </is>
       </c>
       <c s="20" t="str" r="P492"/>
       <c s="20" t="inlineStr" r="R492">
         <is>
-          <t xml:space="preserve">158af8d0-c94d-11f1-c8f5-f2050a003223</t>
+          <t xml:space="preserve">6cb0ce60-c94c-11f1-bf37-f2050a003223</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="S492">
         <is>
-          <t xml:space="preserve">10049812    </t>
+          <t xml:space="preserve">10049658    </t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="U492">
@@ -34425,12 +34425,12 @@
     <row r="493" ht="15.55" customHeight="0">
       <c s="15" t="inlineStr" r="A493">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 05</t>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="B493">
         <is>
-          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
         </is>
       </c>
       <c s="17" t="inlineStr" r="D493">
@@ -34442,11 +34442,11 @@
         <v>46311.2916666667</v>
       </c>
       <c s="18" r="G493">
-        <v>46311.2986111111</v>
+        <v>46311.3097222222</v>
       </c>
       <c s="17" t="inlineStr" r="H493">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c s="17" t="str" r="I493"/>
@@ -34473,18 +34473,18 @@
       </c>
       <c s="16" t="inlineStr" r="O493">
         <is>
-          <t xml:space="preserve">dds</t>
+          <t xml:space="preserve">dds e assinatura dos documentos</t>
         </is>
       </c>
       <c s="16" t="str" r="P493"/>
       <c s="16" t="inlineStr" r="R493">
         <is>
-          <t xml:space="preserve">6cb0ce60-c94c-11f1-bf37-f2050a003223</t>
+          <t xml:space="preserve">158af8d0-c94d-11f1-c8f5-f2050a003223</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="S493">
         <is>
-          <t xml:space="preserve">10049658    </t>
+          <t xml:space="preserve">10049812    </t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="U493">
@@ -37542,12 +37542,12 @@
     <row r="537" ht="15.6" customHeight="0">
       <c s="15" t="inlineStr" r="A537">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 04</t>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="B537">
         <is>
-          <t xml:space="preserve">TR04-ENDIREITADEIRA</t>
+          <t xml:space="preserve">TR01-CARRO DE ENTRADA</t>
         </is>
       </c>
       <c s="17" t="inlineStr" r="D537">
@@ -37559,11 +37559,11 @@
         <v>46311.5840277778</v>
       </c>
       <c s="18" r="G537">
-        <v>46311.5944444444</v>
+        <v>46311.5916666667</v>
       </c>
       <c s="17" t="inlineStr" r="H537">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c s="17" t="str" r="I537"/>
@@ -37574,34 +37574,34 @@
       </c>
       <c s="16" t="inlineStr" r="K537">
         <is>
-          <t xml:space="preserve">Setup/Regulagem</t>
+          <t xml:space="preserve">Operacional</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="L537">
         <is>
-          <t xml:space="preserve">Setup/Regulagem</t>
+          <t xml:space="preserve">Operacional</t>
         </is>
       </c>
       <c s="16" t="str" r="M537"/>
       <c s="16" t="inlineStr" r="N537">
         <is>
-          <t xml:space="preserve">SETUP COMPLETO</t>
+          <t xml:space="preserve">PASSAGEM DE ESPECIAIS</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="O537">
         <is>
-          <t xml:space="preserve">TROCAR 0.43X1.000 PARA 1.55X1.000 E FAZER REGULAGRM</t>
+          <t xml:space="preserve">VOLTA BOBINA ZIN, ESPECIAL PARA O NESTOQUE</t>
         </is>
       </c>
       <c s="16" t="str" r="P537"/>
       <c s="16" t="inlineStr" r="R537">
         <is>
-          <t xml:space="preserve">52276f00-c987-11f1-bb7f-f2050a003223</t>
+          <t xml:space="preserve">3e83cd80-c983-11f1-bbe1-f2050a003223</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="S537">
         <is>
-          <t xml:space="preserve">10049820    </t>
+          <t xml:space="preserve">10050154    </t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="U537">
@@ -37614,12 +37614,12 @@
     <row r="538" ht="15.55" customHeight="0">
       <c s="19" t="inlineStr" r="A538">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 01</t>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="B538">
         <is>
-          <t xml:space="preserve">TR01-CARRO DE ENTRADA</t>
+          <t xml:space="preserve">TR04-ENDIREITADEIRA</t>
         </is>
       </c>
       <c s="21" t="inlineStr" r="D538">
@@ -37631,11 +37631,11 @@
         <v>46311.5840277778</v>
       </c>
       <c s="22" r="G538">
-        <v>46311.5916666667</v>
+        <v>46311.5944444444</v>
       </c>
       <c s="21" t="inlineStr" r="H538">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c s="21" t="str" r="I538"/>
@@ -37646,34 +37646,34 @@
       </c>
       <c s="20" t="inlineStr" r="K538">
         <is>
-          <t xml:space="preserve">Operacional</t>
+          <t xml:space="preserve">Setup/Regulagem</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="L538">
         <is>
-          <t xml:space="preserve">Operacional</t>
+          <t xml:space="preserve">Setup/Regulagem</t>
         </is>
       </c>
       <c s="20" t="str" r="M538"/>
       <c s="20" t="inlineStr" r="N538">
         <is>
-          <t xml:space="preserve">PASSAGEM DE ESPECIAIS</t>
+          <t xml:space="preserve">SETUP COMPLETO</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="O538">
         <is>
-          <t xml:space="preserve">VOLTA BOBINA ZIN, ESPECIAL PARA O NESTOQUE</t>
+          <t xml:space="preserve">TROCAR 0.43X1.000 PARA 1.55X1.000 E FAZER REGULAGRM</t>
         </is>
       </c>
       <c s="20" t="str" r="P538"/>
       <c s="20" t="inlineStr" r="R538">
         <is>
-          <t xml:space="preserve">3e83cd80-c983-11f1-bbe1-f2050a003223</t>
+          <t xml:space="preserve">52276f00-c987-11f1-bb7f-f2050a003223</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="S538">
         <is>
-          <t xml:space="preserve">10050154    </t>
+          <t xml:space="preserve">10049820    </t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="U538">
@@ -38619,11 +38619,11 @@
         <v>46311.6986111111</v>
       </c>
       <c s="22" r="G552">
-        <v>46314.2984616551</v>
+        <v>46314.2909722222</v>
       </c>
       <c s="21" t="inlineStr" r="H552">
         <is>
-          <t xml:space="preserve">3.744</t>
+          <t xml:space="preserve">3.733</t>
         </is>
       </c>
       <c s="21" t="str" r="I552"/>
@@ -38940,81 +38940,4287 @@
       <c s="5" t="str" r="V556"/>
     </row>
     <row r="557" ht="15.55" customHeight="0">
-      <c s="23" t="inlineStr" r="A557">
+      <c s="15" t="inlineStr" r="A557">
         <is>
           <t xml:space="preserve">TRANSVERSAL 05</t>
         </is>
       </c>
-      <c s="24" t="inlineStr" r="B557">
+      <c s="16" t="inlineStr" r="B557">
         <is>
           <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
         </is>
       </c>
-      <c s="10" t="str" r="C557"/>
-      <c s="25" t="inlineStr" r="D557">
+      <c s="17" t="inlineStr" r="D557">
         <is>
           <t xml:space="preserve">TURNO B</t>
         </is>
       </c>
-      <c s="26" r="E557">
+      <c s="18" r="E557">
         <v>46311.7111111111</v>
       </c>
-      <c s="10" t="str" r="F557"/>
-      <c s="26" r="G557">
+      <c s="18" r="G557">
         <v>46314.2909722222</v>
       </c>
-      <c s="25" t="inlineStr" r="H557">
+      <c s="17" t="inlineStr" r="H557">
         <is>
           <t xml:space="preserve">3.715</t>
         </is>
       </c>
-      <c s="25" t="str" r="I557"/>
-      <c s="25" t="inlineStr" r="J557">
-        <is>
-          <t xml:space="preserve">X</t>
-        </is>
-      </c>
-      <c s="24" t="inlineStr" r="K557">
+      <c s="17" t="str" r="I557"/>
+      <c s="17" t="inlineStr" r="J557">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K557">
         <is>
           <t xml:space="preserve">Tempo Livre</t>
         </is>
       </c>
-      <c s="24" t="inlineStr" r="L557">
+      <c s="16" t="inlineStr" r="L557">
         <is>
           <t xml:space="preserve">Tempo Livre</t>
         </is>
       </c>
-      <c s="24" t="str" r="M557"/>
-      <c s="24" t="inlineStr" r="N557">
+      <c s="16" t="str" r="M557"/>
+      <c s="16" t="inlineStr" r="N557">
         <is>
           <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
         </is>
       </c>
-      <c s="24" t="inlineStr" r="O557">
+      <c s="16" t="inlineStr" r="O557">
         <is>
           <t xml:space="preserve">espera fim de semana</t>
         </is>
       </c>
-      <c s="24" t="str" r="P557"/>
-      <c s="10" t="str" r="Q557"/>
-      <c s="24" t="inlineStr" r="R557">
+      <c s="16" t="str" r="P557"/>
+      <c s="16" t="inlineStr" r="R557">
         <is>
           <t xml:space="preserve">903b0c60-cba4-11f1-bdb2-f2050a003223</t>
         </is>
       </c>
-      <c s="24" t="inlineStr" r="S557">
+      <c s="16" t="inlineStr" r="S557">
         <is>
           <t xml:space="preserve">10049659    </t>
         </is>
       </c>
-      <c s="10" t="str" r="T557"/>
-      <c s="24" t="inlineStr" r="U557">
-        <is>
-          <t xml:space="preserve">Sim</t>
-        </is>
-      </c>
-      <c s="11" t="str" r="V557"/>
-    </row>
+      <c s="16" t="inlineStr" r="U557">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V557"/>
+    </row>
+    <row r="558" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A558">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B558">
+        <is>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D558">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E558">
+        <v>46314.2847222222</v>
+      </c>
+      <c s="22" r="G558">
+        <v>46314.2916666667</v>
+      </c>
+      <c s="21" t="inlineStr" r="H558">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I558"/>
+      <c s="21" t="inlineStr" r="J558">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K558">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L558">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M558"/>
+      <c s="20" t="inlineStr" r="N558">
+        <is>
+          <t xml:space="preserve">DDS</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O558">
+        <is>
+          <t xml:space="preserve">DDS</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P558"/>
+      <c s="20" t="inlineStr" r="R558">
+        <is>
+          <t xml:space="preserve">c89b9950-cbac-11f1-b593-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S558">
+        <is>
+          <t xml:space="preserve">10050029    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U558">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V558"/>
+    </row>
+    <row r="559" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A559">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B559">
+        <is>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D559">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E559">
+        <v>46314.2916666667</v>
+      </c>
+      <c s="18" r="G559">
+        <v>46314.2986111111</v>
+      </c>
+      <c s="17" t="inlineStr" r="H559">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I559"/>
+      <c s="17" t="inlineStr" r="J559">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K559">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L559">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M559"/>
+      <c s="16" t="inlineStr" r="N559">
+        <is>
+          <t xml:space="preserve">DDS</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O559">
+        <is>
+          <t xml:space="preserve">dds</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P559"/>
+      <c s="16" t="inlineStr" r="R559">
+        <is>
+          <t xml:space="preserve">ce0da880-cba5-11f1-b5fe-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S559">
+        <is>
+          <t xml:space="preserve">10049659    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U559">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V559"/>
+    </row>
+    <row r="560" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A560">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B560">
+        <is>
+          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D560">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E560">
+        <v>46314.2916666667</v>
+      </c>
+      <c s="22" r="G560">
+        <v>46314.2986111111</v>
+      </c>
+      <c s="21" t="inlineStr" r="H560">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I560"/>
+      <c s="21" t="inlineStr" r="J560">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K560">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L560">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M560"/>
+      <c s="20" t="inlineStr" r="N560">
+        <is>
+          <t xml:space="preserve">DDS</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O560">
+        <is>
+          <t xml:space="preserve">DDS.</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P560"/>
+      <c s="20" t="inlineStr" r="R560">
+        <is>
+          <t xml:space="preserve">8446cdd0-cbc3-11f1-b78f-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S560">
+        <is>
+          <t xml:space="preserve">10049746    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U560">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V560"/>
+    </row>
+    <row r="561" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A561">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B561">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D561">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E561">
+        <v>46314.2916666667</v>
+      </c>
+      <c s="18" r="G561">
+        <v>46314.3020833333</v>
+      </c>
+      <c s="17" t="inlineStr" r="H561">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I561"/>
+      <c s="17" t="inlineStr" r="J561">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K561">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L561">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M561"/>
+      <c s="16" t="inlineStr" r="N561">
+        <is>
+          <t xml:space="preserve">DDS</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O561">
+        <is>
+          <t xml:space="preserve">dds e assinatura dos documentos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P561"/>
+      <c s="16" t="inlineStr" r="R561">
+        <is>
+          <t xml:space="preserve">8a194e80-cba6-11f1-b75b-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S561">
+        <is>
+          <t xml:space="preserve">10050212    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U561">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V561"/>
+    </row>
+    <row r="562" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A562">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B562">
+        <is>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D562">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E562">
+        <v>46314.2923611111</v>
+      </c>
+      <c s="22" r="G562">
+        <v>46314.3201388889</v>
+      </c>
+      <c s="21" t="inlineStr" r="H562">
+        <is>
+          <t xml:space="preserve">40</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I562"/>
+      <c s="21" t="inlineStr" r="J562">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K562">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L562">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M562"/>
+      <c s="20" t="inlineStr" r="N562">
+        <is>
+          <t xml:space="preserve">REUNIÃO/TREINAMENTO NÃO PROGRAMADO</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O562">
+        <is>
+          <t xml:space="preserve">REUNIÃO COM SUPERVISOR</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P562"/>
+      <c s="20" t="inlineStr" r="R562">
+        <is>
+          <t xml:space="preserve">f5b92100-cbac-11f1-b9ff-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S562">
+        <is>
+          <t xml:space="preserve">10050029    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U562">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V562"/>
+    </row>
+    <row r="563" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A563">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B563">
+        <is>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D563">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E563">
+        <v>46314.3208333333</v>
+      </c>
+      <c s="18" r="G563">
+        <v>46314.33125</v>
+      </c>
+      <c s="17" t="inlineStr" r="H563">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I563"/>
+      <c s="17" t="inlineStr" r="J563">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K563">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L563">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M563"/>
+      <c s="16" t="inlineStr" r="N563">
+        <is>
+          <t xml:space="preserve">ASSINATURA DE DOCUMENTOS</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O563">
+        <is>
+          <t xml:space="preserve">Assinatura de documentos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P563"/>
+      <c s="16" t="inlineStr" r="R563">
+        <is>
+          <t xml:space="preserve">257659d0-cbad-11f1-8c7a-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S563">
+        <is>
+          <t xml:space="preserve">10050029    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U563">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V563"/>
+    </row>
+    <row r="564" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A564">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B564"/>
+      <c s="21" t="inlineStr" r="D564">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E564">
+        <v>46314.3263888889</v>
+      </c>
+      <c s="22" r="G564">
+        <v>46314.3291666667</v>
+      </c>
+      <c s="21" t="inlineStr" r="H564">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I564"/>
+      <c s="21" t="inlineStr" r="J564">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K564">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L564">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M564"/>
+      <c s="20" t="inlineStr" r="N564">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O564">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 4 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P564"/>
+      <c s="20" t="inlineStr" r="R564">
+        <is>
+          <t xml:space="preserve">d87967f0-cbaa-11f1-c1ae-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S564">
+        <is>
+          <t xml:space="preserve">10049746    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U564">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V564"/>
+    </row>
+    <row r="565" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A565">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B565">
+        <is>
+          <t xml:space="preserve">TR05-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D565">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E565">
+        <v>46314.3270833333</v>
+      </c>
+      <c s="18" r="G565">
+        <v>46314.3333333333</v>
+      </c>
+      <c s="17" t="inlineStr" r="H565">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I565"/>
+      <c s="17" t="inlineStr" r="J565">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K565">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L565">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M565"/>
+      <c s="16" t="inlineStr" r="N565">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O565">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 9 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P565"/>
+      <c s="16" t="inlineStr" r="R565">
+        <is>
+          <t xml:space="preserve">0be21c90-cbab-11f1-9576-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S565">
+        <is>
+          <t xml:space="preserve">10049659    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U565">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V565"/>
+    </row>
+    <row r="566" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A566">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B566">
+        <is>
+          <t xml:space="preserve">TR01-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D566">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E566">
+        <v>46314.3465277778</v>
+      </c>
+      <c s="22" r="G566">
+        <v>46314.6944444444</v>
+      </c>
+      <c s="21" t="inlineStr" r="H566">
+        <is>
+          <t xml:space="preserve">501</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I566"/>
+      <c s="21" t="inlineStr" r="J566">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K566">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L566">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M566"/>
+      <c s="20" t="inlineStr" r="N566">
+        <is>
+          <t xml:space="preserve">MANUTENÇÃO PREVENTIVA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O566">
+        <is>
+          <t xml:space="preserve">manutenção preventiva</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P566"/>
+      <c s="20" t="inlineStr" r="R566">
+        <is>
+          <t xml:space="preserve">40678f00-cbaf-11f1-9d24-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S566">
+        <is>
+          <t xml:space="preserve">10050024    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U566">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V566"/>
+    </row>
+    <row r="567" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A567">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B567"/>
+      <c s="17" t="inlineStr" r="D567">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E567">
+        <v>46314.3583333333</v>
+      </c>
+      <c s="18" r="G567">
+        <v>46314.36875</v>
+      </c>
+      <c s="17" t="inlineStr" r="H567">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I567"/>
+      <c s="17" t="inlineStr" r="J567">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K567">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L567">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M567"/>
+      <c s="16" t="inlineStr" r="N567">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O567">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P567"/>
+      <c s="16" t="inlineStr" r="R567">
+        <is>
+          <t xml:space="preserve">62656c60-cbb1-11f1-adc6-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S567">
+        <is>
+          <t xml:space="preserve">10049746    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U567">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V567"/>
+    </row>
+    <row r="568" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A568">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B568">
+        <is>
+          <t xml:space="preserve">TR05-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D568">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E568">
+        <v>46314.3875</v>
+      </c>
+      <c s="22" r="G568">
+        <v>46314.3923611111</v>
+      </c>
+      <c s="21" t="inlineStr" r="H568">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I568"/>
+      <c s="21" t="inlineStr" r="J568">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K568">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L568">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M568"/>
+      <c s="20" t="inlineStr" r="N568">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O568">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 7 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P568"/>
+      <c s="20" t="inlineStr" r="R568">
+        <is>
+          <t xml:space="preserve">22230490-cbb7-11f1-c1cd-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S568">
+        <is>
+          <t xml:space="preserve">10049659    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U568">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V568"/>
+    </row>
+    <row r="569" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A569">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B569">
+        <is>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D569">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E569">
+        <v>46314.4020833333</v>
+      </c>
+      <c s="18" r="G569">
+        <v>46314.4055555556</v>
+      </c>
+      <c s="17" t="inlineStr" r="H569">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I569"/>
+      <c s="17" t="inlineStr" r="J569">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K569">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L569">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M569"/>
+      <c s="16" t="inlineStr" r="N569">
+        <is>
+          <t xml:space="preserve">TROCA DAS CASTANHAS DO MANDRIL</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O569">
+        <is>
+          <t xml:space="preserve">colocar castanhas</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P569"/>
+      <c s="16" t="inlineStr" r="R569">
+        <is>
+          <t xml:space="preserve">13bdd6c0-cbba-11f1-97f4-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S569">
+        <is>
+          <t xml:space="preserve">10050029    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U569">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V569"/>
+    </row>
+    <row r="570" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A570">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B570"/>
+      <c s="21" t="inlineStr" r="D570">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E570">
+        <v>46314.4138888889</v>
+      </c>
+      <c s="22" r="G570">
+        <v>46314.4243055556</v>
+      </c>
+      <c s="21" t="inlineStr" r="H570">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I570"/>
+      <c s="21" t="inlineStr" r="J570">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K570">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L570">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M570"/>
+      <c s="20" t="inlineStr" r="N570">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O570">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P570"/>
+      <c s="20" t="inlineStr" r="R570">
+        <is>
+          <t xml:space="preserve">8d9098f1-cbbc-11f1-8c63-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S570">
+        <is>
+          <t xml:space="preserve">10049746    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U570">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V570"/>
+    </row>
+    <row r="571" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A571">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B571">
+        <is>
+          <t xml:space="preserve">TR04-MESA TRANSPORTADORA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D571">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E571">
+        <v>46314.4173611111</v>
+      </c>
+      <c s="18" r="G571">
+        <v>46314.4194444444</v>
+      </c>
+      <c s="17" t="inlineStr" r="H571">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I571"/>
+      <c s="17" t="inlineStr" r="J571">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K571">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L571">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M571"/>
+      <c s="16" t="inlineStr" r="N571">
+        <is>
+          <t xml:space="preserve">SETUP PARCIAL</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O571">
+        <is>
+          <t xml:space="preserve">regulando esteira transportadora</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P571"/>
+      <c s="16" t="inlineStr" r="R571">
+        <is>
+          <t xml:space="preserve">35a72540-cbbd-11f1-876d-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S571">
+        <is>
+          <t xml:space="preserve">10050261    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U571">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V571"/>
+    </row>
+    <row r="572" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A572">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B572">
+        <is>
+          <t xml:space="preserve">TR04-MESA TRANSPORTADORA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D572">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E572">
+        <v>46314.4305555556</v>
+      </c>
+      <c s="22" r="G572">
+        <v>46314.4333333333</v>
+      </c>
+      <c s="21" t="inlineStr" r="H572">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I572"/>
+      <c s="21" t="inlineStr" r="J572">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K572">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L572">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M572"/>
+      <c s="20" t="inlineStr" r="N572">
+        <is>
+          <t xml:space="preserve">SETUP PARCIAL</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O572">
+        <is>
+          <t xml:space="preserve">regulando esteira transportadora</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P572"/>
+      <c s="20" t="inlineStr" r="R572">
+        <is>
+          <t xml:space="preserve">dc4c0e40-cbbf-11f1-9dc9-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S572">
+        <is>
+          <t xml:space="preserve">10050261    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U572">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V572"/>
+    </row>
+    <row r="573" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A573">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B573">
+        <is>
+          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D573">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E573">
+        <v>46314.4347222222</v>
+      </c>
+      <c s="18" r="G573">
+        <v>46314.4430555556</v>
+      </c>
+      <c s="17" t="inlineStr" r="H573">
+        <is>
+          <t xml:space="preserve">12</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I573"/>
+      <c s="17" t="inlineStr" r="J573">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K573">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L573">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M573"/>
+      <c s="16" t="inlineStr" r="N573">
+        <is>
+          <t xml:space="preserve">QUALIDADE DA MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O573">
+        <is>
+          <t xml:space="preserve">Material 2.00mm 6000x1200 UD 2003980977 com ondulação  o material foi liberado para produzir.</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P573"/>
+      <c s="16" t="inlineStr" r="R573">
+        <is>
+          <t xml:space="preserve">e782e2b0-cbc0-11f1-cfbf-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S573">
+        <is>
+          <t xml:space="preserve">10049746    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U573">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V573"/>
+    </row>
+    <row r="574" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A574">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B574">
+        <is>
+          <t xml:space="preserve">TR04-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D574">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E574">
+        <v>46314.4361111111</v>
+      </c>
+      <c s="22" r="G574">
+        <v>46314.4430555556</v>
+      </c>
+      <c s="21" t="inlineStr" r="H574">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I574"/>
+      <c s="21" t="inlineStr" r="J574">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K574">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L574">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M574"/>
+      <c s="20" t="inlineStr" r="N574">
+        <is>
+          <t xml:space="preserve">CINTAGEM DE MATERIAL</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O574">
+        <is>
+          <t xml:space="preserve">cintagem e retirada de material e regulagem da mesa</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P574"/>
+      <c s="20" t="inlineStr" r="R574">
+        <is>
+          <t xml:space="preserve">00fc2fd0-cbc1-11f1-85f5-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S574">
+        <is>
+          <t xml:space="preserve">10050261    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U574">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V574"/>
+    </row>
+    <row r="575" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A575">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B575">
+        <is>
+          <t xml:space="preserve">TR05-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D575">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E575">
+        <v>46314.4458333333</v>
+      </c>
+      <c s="18" r="G575">
+        <v>46314.4520833333</v>
+      </c>
+      <c s="17" t="inlineStr" r="H575">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I575"/>
+      <c s="17" t="inlineStr" r="J575">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K575">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L575">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M575"/>
+      <c s="16" t="inlineStr" r="N575">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O575">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 9 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P575"/>
+      <c s="16" t="inlineStr" r="R575">
+        <is>
+          <t xml:space="preserve">e491cb50-cbc2-11f1-9957-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S575">
+        <is>
+          <t xml:space="preserve">10049659    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U575">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V575"/>
+    </row>
+    <row r="576" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A576">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B576">
+        <is>
+          <t xml:space="preserve">TR04-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D576">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E576">
+        <v>46314.4472222222</v>
+      </c>
+      <c s="22" r="G576">
+        <v>46314.4506944444</v>
+      </c>
+      <c s="21" t="inlineStr" r="H576">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I576"/>
+      <c s="21" t="inlineStr" r="J576">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K576">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L576">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M576"/>
+      <c s="20" t="inlineStr" r="N576">
+        <is>
+          <t xml:space="preserve">AJUSTE DE MESA GUIA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O576">
+        <is>
+          <t xml:space="preserve">ajuste</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P576"/>
+      <c s="20" t="inlineStr" r="R576">
+        <is>
+          <t xml:space="preserve">42977740-cbc3-11f1-ba50-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S576">
+        <is>
+          <t xml:space="preserve">10050261    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U576">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V576"/>
+    </row>
+    <row r="577" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A577">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B577">
+        <is>
+          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D577">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E577">
+        <v>46314.45</v>
+      </c>
+      <c s="18" r="G577">
+        <v>46314.4520833333</v>
+      </c>
+      <c s="17" t="inlineStr" r="H577">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I577"/>
+      <c s="17" t="inlineStr" r="J577">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K577">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L577">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M577"/>
+      <c s="16" t="inlineStr" r="N577">
+        <is>
+          <t xml:space="preserve">QUALIDADE DA MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O577">
+        <is>
+          <t xml:space="preserve">Material 2.00mm 2295x1200 UD 2003980977 com ondulação  o material foi liberado para produzir.</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P577"/>
+      <c s="16" t="inlineStr" r="R577">
+        <is>
+          <t xml:space="preserve">25fc5b40-cbc4-11f1-8e95-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S577">
+        <is>
+          <t xml:space="preserve">10050101    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U577">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V577"/>
+    </row>
+    <row r="578" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A578">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B578">
+        <is>
+          <t xml:space="preserve">TR02-ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D578">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E578">
+        <v>46314.4534722222</v>
+      </c>
+      <c s="22" r="G578">
+        <v>46314.4576388889</v>
+      </c>
+      <c s="21" t="inlineStr" r="H578">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I578"/>
+      <c s="21" t="inlineStr" r="J578">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K578">
+        <is>
+          <t xml:space="preserve">Manutenção Corretiva Elétrica</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L578">
+        <is>
+          <t xml:space="preserve">Manutenção Corretiva Elétrica</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M578"/>
+      <c s="20" t="inlineStr" r="N578">
+        <is>
+          <t xml:space="preserve">FALHA NO ACIONAMENTO</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O578">
+        <is>
+          <t xml:space="preserve">falha no conversor da endireitadeira..</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="P578">
+        <is>
+          <t xml:space="preserve">000010035804</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="R578">
+        <is>
+          <t xml:space="preserve">830a87d0-cbc4-11f1-9260-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S578">
+        <is>
+          <t xml:space="preserve">10050101    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U578">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V578"/>
+    </row>
+    <row r="579" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A579">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B579">
+        <is>
+          <t xml:space="preserve">TR04-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D579">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E579">
+        <v>46314.4625</v>
+      </c>
+      <c s="18" r="G579">
+        <v>46314.4659722222</v>
+      </c>
+      <c s="17" t="inlineStr" r="H579">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I579"/>
+      <c s="17" t="inlineStr" r="J579">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K579">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L579">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M579"/>
+      <c s="16" t="inlineStr" r="N579">
+        <is>
+          <t xml:space="preserve">CINTAGEM DE MATERIAL</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O579">
+        <is>
+          <t xml:space="preserve">cintagem e retirada de material</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P579"/>
+      <c s="16" t="inlineStr" r="R579">
+        <is>
+          <t xml:space="preserve">546e6480-cbc6-11f1-cbc7-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S579">
+        <is>
+          <t xml:space="preserve">10050261    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U579">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V579"/>
+    </row>
+    <row r="580" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A580">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B580"/>
+      <c s="21" t="inlineStr" r="D580">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E580">
+        <v>46314.4715277778</v>
+      </c>
+      <c s="22" r="G580">
+        <v>46314.4770833333</v>
+      </c>
+      <c s="21" t="inlineStr" r="H580">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I580"/>
+      <c s="21" t="inlineStr" r="J580">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K580">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L580">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M580"/>
+      <c s="20" t="inlineStr" r="N580">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O580">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 8 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P580"/>
+      <c s="20" t="inlineStr" r="R580">
+        <is>
+          <t xml:space="preserve">2294a260-cbc8-11f1-c7d6-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S580">
+        <is>
+          <t xml:space="preserve">10050261    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U580">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V580"/>
+    </row>
+    <row r="581" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A581">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B581">
+        <is>
+          <t xml:space="preserve">TR04-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D581">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E581">
+        <v>46314.4777777778</v>
+      </c>
+      <c s="18" r="G581">
+        <v>46314.4791666667</v>
+      </c>
+      <c s="17" t="inlineStr" r="H581">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I581"/>
+      <c s="17" t="inlineStr" r="J581">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K581">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L581">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M581"/>
+      <c s="16" t="inlineStr" r="N581">
+        <is>
+          <t xml:space="preserve">RETIRADA DE PNC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O581">
+        <is>
+          <t xml:space="preserve">Retirada de PNC</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P581"/>
+      <c s="16" t="inlineStr" r="R581">
+        <is>
+          <t xml:space="preserve">42ae24d0-cbc9-11f1-97b3-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S581">
+        <is>
+          <t xml:space="preserve">10050261    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U581">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V581"/>
+    </row>
+    <row r="582" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A582">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B582">
+        <is>
+          <t xml:space="preserve">TR04-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D582">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E582">
+        <v>46314.4902777778</v>
+      </c>
+      <c s="22" r="G582">
+        <v>46314.4930555556</v>
+      </c>
+      <c s="21" t="inlineStr" r="H582">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I582"/>
+      <c s="21" t="inlineStr" r="J582">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K582">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L582">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M582"/>
+      <c s="20" t="inlineStr" r="N582">
+        <is>
+          <t xml:space="preserve">CINTAGEM DE MATERIAL</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O582">
+        <is>
+          <t xml:space="preserve">cintagem e retirada de material</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P582"/>
+      <c s="20" t="inlineStr" r="R582">
+        <is>
+          <t xml:space="preserve">e6991df0-cbcb-11f1-b742-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S582">
+        <is>
+          <t xml:space="preserve">10050261    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U582">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V582"/>
+    </row>
+    <row r="583" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A583">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B583"/>
+      <c s="17" t="inlineStr" r="D583">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E583">
+        <v>46314.4930555556</v>
+      </c>
+      <c s="18" r="G583">
+        <v>46314.5034722222</v>
+      </c>
+      <c s="17" t="inlineStr" r="H583">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I583"/>
+      <c s="17" t="inlineStr" r="J583">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K583">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L583">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M583"/>
+      <c s="16" t="inlineStr" r="N583">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O583">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P583"/>
+      <c s="16" t="inlineStr" r="R583">
+        <is>
+          <t xml:space="preserve">6c508820-cbcc-11f1-9813-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S583">
+        <is>
+          <t xml:space="preserve">10049748    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U583">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V583"/>
+    </row>
+    <row r="584" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A584">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B584">
+        <is>
+          <t xml:space="preserve">TR04-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D584">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E584">
+        <v>46314.5</v>
+      </c>
+      <c s="22" r="G584">
+        <v>46314.5055555556</v>
+      </c>
+      <c s="21" t="inlineStr" r="H584">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I584"/>
+      <c s="21" t="inlineStr" r="J584">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K584">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L584">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M584"/>
+      <c s="20" t="inlineStr" r="N584">
+        <is>
+          <t xml:space="preserve">RETIRADA DE PNC</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O584">
+        <is>
+          <t xml:space="preserve">RETIRA PEÇAS AMASSADA</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P584"/>
+      <c s="20" t="inlineStr" r="R584">
+        <is>
+          <t xml:space="preserve">d6196a00-cbcd-11f1-b56b-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S584">
+        <is>
+          <t xml:space="preserve">10050261    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U584">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V584"/>
+    </row>
+    <row r="585" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A585">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B585">
+        <is>
+          <t xml:space="preserve">TR05-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D585">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E585">
+        <v>46314.5020833333</v>
+      </c>
+      <c s="18" r="G585">
+        <v>46314.5076388889</v>
+      </c>
+      <c s="17" t="inlineStr" r="H585">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I585"/>
+      <c s="17" t="inlineStr" r="J585">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K585">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L585">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M585"/>
+      <c s="16" t="inlineStr" r="N585">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O585">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 8 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P585"/>
+      <c s="16" t="inlineStr" r="R585">
+        <is>
+          <t xml:space="preserve">3644b510-cbce-11f1-96a0-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S585">
+        <is>
+          <t xml:space="preserve">10049659    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U585">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V585"/>
+    </row>
+    <row r="586" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A586">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B586">
+        <is>
+          <t xml:space="preserve">TR05-GUILHOTINA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D586">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E586">
+        <v>46314.5083333333</v>
+      </c>
+      <c s="22" r="G586">
+        <v>46314.5131944444</v>
+      </c>
+      <c s="21" t="inlineStr" r="H586">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I586"/>
+      <c s="21" t="inlineStr" r="J586">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K586">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L586">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M586"/>
+      <c s="20" t="inlineStr" r="N586">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE CHAPA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O586">
+        <is>
+          <t xml:space="preserve">chapa amassou tivemos que voltar e passar novamente</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P586"/>
+      <c s="20" t="inlineStr" r="R586">
+        <is>
+          <t xml:space="preserve">7e2f64a0-cbcf-11f1-b289-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S586">
+        <is>
+          <t xml:space="preserve">10049659    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U586">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V586"/>
+    </row>
+    <row r="587" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A587">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B587">
+        <is>
+          <t xml:space="preserve">TR04-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D587">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E587">
+        <v>46314.5173611111</v>
+      </c>
+      <c s="18" r="G587">
+        <v>46314.5208333333</v>
+      </c>
+      <c s="17" t="inlineStr" r="H587">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I587"/>
+      <c s="17" t="inlineStr" r="J587">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K587">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L587">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M587"/>
+      <c s="16" t="inlineStr" r="N587">
+        <is>
+          <t xml:space="preserve">CINTAGEM DE MATERIAL</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O587">
+        <is>
+          <t xml:space="preserve">cintagem e retirada de material</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P587"/>
+      <c s="16" t="inlineStr" r="R587">
+        <is>
+          <t xml:space="preserve">5ddec540-cbd1-11f1-cdc1-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S587">
+        <is>
+          <t xml:space="preserve">10050261    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U587">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V587"/>
+    </row>
+    <row r="588" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A588">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B588">
+        <is>
+          <t xml:space="preserve">TR05-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D588">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E588">
+        <v>46314.51875</v>
+      </c>
+      <c s="22" r="G588">
+        <v>46314.525</v>
+      </c>
+      <c s="21" t="inlineStr" r="H588">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I588"/>
+      <c s="21" t="inlineStr" r="J588">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K588">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L588">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M588"/>
+      <c s="20" t="inlineStr" r="N588">
+        <is>
+          <t xml:space="preserve">AGUARDANDO INSPEÇÃO DE  QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O588">
+        <is>
+          <t xml:space="preserve">aguardando inspeção da qualidade para o material de UD  : 2003993996 O MESMO APRESENTA OXIDAÇÃO GALVÂNICA  
+após a inspeção foi autorizado passar  1167 kg de pnc o restante como bom</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P588"/>
+      <c s="20" t="inlineStr" r="R588">
+        <is>
+          <t xml:space="preserve">c34728a0-cbd1-11f1-ad68-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S588">
+        <is>
+          <t xml:space="preserve">10049659    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U588">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V588"/>
+    </row>
+    <row r="589" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A589">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B589">
+        <is>
+          <t xml:space="preserve">TR05-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D589">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E589">
+        <v>46314.5256944444</v>
+      </c>
+      <c s="18" r="G589">
+        <v>46314.5284722222</v>
+      </c>
+      <c s="17" t="inlineStr" r="H589">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I589"/>
+      <c s="17" t="inlineStr" r="J589">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K589">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L589">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M589"/>
+      <c s="16" t="inlineStr" r="N589">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE FARDO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O589">
+        <is>
+          <t xml:space="preserve">passagem de fardo</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P589"/>
+      <c s="16" t="inlineStr" r="R589">
+        <is>
+          <t xml:space="preserve">0ccbd920-cbd3-11f1-aa77-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S589">
+        <is>
+          <t xml:space="preserve">10049659    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U589">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V589"/>
+    </row>
+    <row r="590" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A590">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B590">
+        <is>
+          <t xml:space="preserve">TR04-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D590">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E590">
+        <v>46314.5368055556</v>
+      </c>
+      <c s="22" r="G590">
+        <v>46314.5395833333</v>
+      </c>
+      <c s="21" t="inlineStr" r="H590">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I590"/>
+      <c s="21" t="inlineStr" r="J590">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K590">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L590">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M590"/>
+      <c s="20" t="inlineStr" r="N590">
+        <is>
+          <t xml:space="preserve">CINTAGEM DE MATERIAL</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O590">
+        <is>
+          <t xml:space="preserve">cintagem e retirada de material</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P590"/>
+      <c s="20" t="inlineStr" r="R590">
+        <is>
+          <t xml:space="preserve">32c35250-cbd5-11f1-92b4-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S590">
+        <is>
+          <t xml:space="preserve">10050261    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U590">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V590"/>
+    </row>
+    <row r="591" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A591">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B591">
+        <is>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D591">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E591">
+        <v>46314.5465277778</v>
+      </c>
+      <c s="18" r="G591">
+        <v>46314.5604166667</v>
+      </c>
+      <c s="17" t="inlineStr" r="H591">
+        <is>
+          <t xml:space="preserve">20</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I591"/>
+      <c s="17" t="inlineStr" r="J591">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K591">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L591">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M591"/>
+      <c s="16" t="inlineStr" r="N591">
+        <is>
+          <t xml:space="preserve">SETUP COMPLETO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O591">
+        <is>
+          <t xml:space="preserve">colocar as castanhas e trocar espessura e fazer regulagem</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P591"/>
+      <c s="16" t="inlineStr" r="R591">
+        <is>
+          <t xml:space="preserve">2bb47550-cbd7-11f1-8eaa-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S591">
+        <is>
+          <t xml:space="preserve">10050261    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U591">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V591"/>
+    </row>
+    <row r="592" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A592">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B592">
+        <is>
+          <t xml:space="preserve">TR04-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D592">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E592">
+        <v>46314.5673611111</v>
+      </c>
+      <c s="22" r="G592">
+        <v>46314.5694444444</v>
+      </c>
+      <c s="21" t="inlineStr" r="H592">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I592"/>
+      <c s="21" t="inlineStr" r="J592">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K592">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L592">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M592"/>
+      <c s="20" t="inlineStr" r="N592">
+        <is>
+          <t xml:space="preserve">CINTAGEM DE MATERIAL</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O592">
+        <is>
+          <t xml:space="preserve">cintagem e retirada de material</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P592"/>
+      <c s="20" t="inlineStr" r="R592">
+        <is>
+          <t xml:space="preserve">5e5aa070-cbdb-11f1-86c2-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S592">
+        <is>
+          <t xml:space="preserve">10050261    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U592">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V592"/>
+    </row>
+    <row r="593" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A593">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B593"/>
+      <c s="17" t="inlineStr" r="D593">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E593">
+        <v>46314.5680555556</v>
+      </c>
+      <c s="18" r="G593">
+        <v>46314.575</v>
+      </c>
+      <c s="17" t="inlineStr" r="H593">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I593"/>
+      <c s="17" t="inlineStr" r="J593">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K593">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L593">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M593"/>
+      <c s="16" t="inlineStr" r="N593">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O593">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 10 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P593"/>
+      <c s="16" t="inlineStr" r="R593">
+        <is>
+          <t xml:space="preserve">7a539390-cbdb-11f1-b4f7-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S593">
+        <is>
+          <t xml:space="preserve">10049748    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U593">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V593"/>
+    </row>
+    <row r="594" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A594">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B594">
+        <is>
+          <t xml:space="preserve">TR04-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D594">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E594">
+        <v>46314.5798611111</v>
+      </c>
+      <c s="22" r="G594">
+        <v>46314.5826388889</v>
+      </c>
+      <c s="21" t="inlineStr" r="H594">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I594"/>
+      <c s="21" t="inlineStr" r="J594">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K594">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L594">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M594"/>
+      <c s="20" t="inlineStr" r="N594">
+        <is>
+          <t xml:space="preserve">CINTAGEM DE MATERIAL</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O594">
+        <is>
+          <t xml:space="preserve">cintagem e retirada de material</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P594"/>
+      <c s="20" t="inlineStr" r="R594">
+        <is>
+          <t xml:space="preserve">d9f418e0-cbdd-11f1-b479-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S594">
+        <is>
+          <t xml:space="preserve">10050391    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U594">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V594"/>
+    </row>
+    <row r="595" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A595">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B595">
+        <is>
+          <t xml:space="preserve">TR05-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D595">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E595">
+        <v>46314.5861111111</v>
+      </c>
+      <c s="18" r="G595">
+        <v>46314.5930555556</v>
+      </c>
+      <c s="17" t="inlineStr" r="H595">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I595"/>
+      <c s="17" t="inlineStr" r="J595">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K595">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L595">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M595"/>
+      <c s="16" t="inlineStr" r="N595">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O595">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 10 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P595"/>
+      <c s="16" t="inlineStr" r="R595">
+        <is>
+          <t xml:space="preserve">19f61820-cbdf-11f1-8823-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S595">
+        <is>
+          <t xml:space="preserve">10049831    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U595">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V595"/>
+    </row>
+    <row r="596" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A596">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B596">
+        <is>
+          <t xml:space="preserve">TR04-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D596">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E596">
+        <v>46314.5895833333</v>
+      </c>
+      <c s="22" r="G596">
+        <v>46314.5923611111</v>
+      </c>
+      <c s="21" t="inlineStr" r="H596">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I596"/>
+      <c s="21" t="inlineStr" r="J596">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K596">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L596">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M596"/>
+      <c s="20" t="inlineStr" r="N596">
+        <is>
+          <t xml:space="preserve">CINTAGEM DE MATERIAL</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O596">
+        <is>
+          <t xml:space="preserve">cintagem e retirada de material</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P596"/>
+      <c s="20" t="inlineStr" r="R596">
+        <is>
+          <t xml:space="preserve">ced977a0-cbdf-11f1-8443-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S596">
+        <is>
+          <t xml:space="preserve">10050391    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U596">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V596"/>
+    </row>
+    <row r="597" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A597">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B597">
+        <is>
+          <t xml:space="preserve">TR05-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D597">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E597">
+        <v>46314.5972222222</v>
+      </c>
+      <c s="18" r="G597">
+        <v>46314.5993055556</v>
+      </c>
+      <c s="17" t="inlineStr" r="H597">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I597"/>
+      <c s="17" t="inlineStr" r="J597">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K597">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L597">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M597"/>
+      <c s="16" t="inlineStr" r="N597">
+        <is>
+          <t xml:space="preserve">AGUARDANDO INSPEÇÃO DE  QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O597">
+        <is>
+          <t xml:space="preserve">aguardando a inspeção do material de UD: 2003993937 oxidação galvânica  foi retirado mais 1661 kg com pnc</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P597"/>
+      <c s="16" t="inlineStr" r="R597">
+        <is>
+          <t xml:space="preserve">fcee1ea0-cbe1-11f1-ba2c-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S597">
+        <is>
+          <t xml:space="preserve">10049831    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U597">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V597"/>
+    </row>
+    <row r="598" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A598">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B598">
+        <is>
+          <t xml:space="preserve">TR04-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D598">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E598">
+        <v>46314.5993055556</v>
+      </c>
+      <c s="22" r="G598">
+        <v>46314.6013888889</v>
+      </c>
+      <c s="21" t="inlineStr" r="H598">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I598"/>
+      <c s="21" t="inlineStr" r="J598">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K598">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L598">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M598"/>
+      <c s="20" t="inlineStr" r="N598">
+        <is>
+          <t xml:space="preserve">CINTAGEM DE MATERIAL</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O598">
+        <is>
+          <t xml:space="preserve">cintagem e retirada de material</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P598"/>
+      <c s="20" t="inlineStr" r="R598">
+        <is>
+          <t xml:space="preserve">cbf1af10-cbe1-11f1-c4b1-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S598">
+        <is>
+          <t xml:space="preserve">10050391    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U598">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V598"/>
+    </row>
+    <row r="599" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A599">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B599">
+        <is>
+          <t xml:space="preserve">TR04-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D599">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E599">
+        <v>46314.6083333333</v>
+      </c>
+      <c s="18" r="G599">
+        <v>46314.6104166667</v>
+      </c>
+      <c s="17" t="inlineStr" r="H599">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I599"/>
+      <c s="17" t="inlineStr" r="J599">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K599">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L599">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M599"/>
+      <c s="16" t="inlineStr" r="N599">
+        <is>
+          <t xml:space="preserve">CINTAGEM DE MATERIAL</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O599">
+        <is>
+          <t xml:space="preserve">cintagem e retirada de material</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P599"/>
+      <c s="16" t="inlineStr" r="R599">
+        <is>
+          <t xml:space="preserve">920a4f80-cbe3-11f1-8303-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S599">
+        <is>
+          <t xml:space="preserve">10050391    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U599">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V599"/>
+    </row>
+    <row r="600" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A600">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B600">
+        <is>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D600">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E600">
+        <v>46314.6145833333</v>
+      </c>
+      <c s="22" r="G600">
+        <v>46314.625</v>
+      </c>
+      <c s="21" t="inlineStr" r="H600">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I600"/>
+      <c s="21" t="inlineStr" r="J600">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K600">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L600">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M600"/>
+      <c s="20" t="inlineStr" r="N600">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O600">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P600"/>
+      <c s="20" t="inlineStr" r="R600">
+        <is>
+          <t xml:space="preserve">d3ac1c10-cbe4-11f1-b483-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S600">
+        <is>
+          <t xml:space="preserve">10050391    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U600">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V600"/>
+    </row>
+    <row r="601" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A601">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B601">
+        <is>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D601">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E601">
+        <v>46314.6256944444</v>
+      </c>
+      <c s="18" r="G601">
+        <v>46314.6402777778</v>
+      </c>
+      <c s="17" t="inlineStr" r="H601">
+        <is>
+          <t xml:space="preserve">21</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I601"/>
+      <c s="17" t="inlineStr" r="J601">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K601">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L601">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M601"/>
+      <c s="16" t="inlineStr" r="N601">
+        <is>
+          <t xml:space="preserve">MEP - MOVIMENTAÇÃO INTERNA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O601">
+        <is>
+          <t xml:space="preserve">esperando movimentar bobina 1.20x1.000</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P601"/>
+      <c s="16" t="inlineStr" r="R601">
+        <is>
+          <t xml:space="preserve">12b51880-cbea-11f1-ce95-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S601">
+        <is>
+          <t xml:space="preserve">10050391    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U601">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V601"/>
+    </row>
+    <row r="602" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A602">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B602">
+        <is>
+          <t xml:space="preserve">TR04-ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D602">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E602">
+        <v>46314.6409722222</v>
+      </c>
+      <c s="22" r="G602">
+        <v>46314.64375</v>
+      </c>
+      <c s="21" t="inlineStr" r="H602">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I602"/>
+      <c s="21" t="inlineStr" r="J602">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K602">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L602">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M602"/>
+      <c s="20" t="inlineStr" r="N602">
+        <is>
+          <t xml:space="preserve">SETUP COMPLETO</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O602">
+        <is>
+          <t xml:space="preserve">trocar 1.20x1.000 para 0.95x1.000 e fazer regulagem</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P602"/>
+      <c s="20" t="inlineStr" r="R602">
+        <is>
+          <t xml:space="preserve">25cc0730-cbea-11f1-c913-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S602">
+        <is>
+          <t xml:space="preserve">10050391    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U602">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V602"/>
+    </row>
+    <row r="603" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A603">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B603">
+        <is>
+          <t xml:space="preserve">TR05-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D603">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E603">
+        <v>46314.6444444444</v>
+      </c>
+      <c s="18" r="G603">
+        <v>46314.6465277778</v>
+      </c>
+      <c s="17" t="inlineStr" r="H603">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I603"/>
+      <c s="17" t="inlineStr" r="J603">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K603">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L603">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M603"/>
+      <c s="16" t="inlineStr" r="N603">
+        <is>
+          <t xml:space="preserve">AJUSTE DE MESA GUIA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O603">
+        <is>
+          <t xml:space="preserve">ajuste do batedor</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P603"/>
+      <c s="16" t="inlineStr" r="R603">
+        <is>
+          <t xml:space="preserve">f28a9430-cbea-11f1-8fab-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S603">
+        <is>
+          <t xml:space="preserve">10049831    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U603">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V603"/>
+    </row>
+    <row r="604" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A604">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B604"/>
+      <c s="21" t="inlineStr" r="D604">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E604">
+        <v>46314.6458333333</v>
+      </c>
+      <c s="22" r="G604">
+        <v>46314.6548611111</v>
+      </c>
+      <c s="21" t="inlineStr" r="H604">
+        <is>
+          <t xml:space="preserve">13</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I604"/>
+      <c s="21" t="inlineStr" r="J604">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K604">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L604">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M604"/>
+      <c s="20" t="inlineStr" r="N604">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O604">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 13 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P604"/>
+      <c s="20" t="inlineStr" r="R604">
+        <is>
+          <t xml:space="preserve">1a33ee00-cbeb-11f1-cd13-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S604">
+        <is>
+          <t xml:space="preserve">10049748    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U604">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V604"/>
+    </row>
+    <row r="605" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A605">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B605">
+        <is>
+          <t xml:space="preserve">TR04-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D605">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E605">
+        <v>46314.6541666667</v>
+      </c>
+      <c s="18" r="G605">
+        <v>46314.6569444444</v>
+      </c>
+      <c s="17" t="inlineStr" r="H605">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I605"/>
+      <c s="17" t="inlineStr" r="J605">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K605">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L605">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M605"/>
+      <c s="16" t="inlineStr" r="N605">
+        <is>
+          <t xml:space="preserve">CINTAGEM DE MATERIAL</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O605">
+        <is>
+          <t xml:space="preserve">cintagem e retirada de material</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P605"/>
+      <c s="16" t="inlineStr" r="R605">
+        <is>
+          <t xml:space="preserve">c95e0ae0-cbec-11f1-b8c8-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S605">
+        <is>
+          <t xml:space="preserve">10050391    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U605">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V605"/>
+    </row>
+    <row r="606" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A606">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B606">
+        <is>
+          <t xml:space="preserve">TR05-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D606">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E606">
+        <v>46314.6597222222</v>
+      </c>
+      <c s="22" r="G606">
+        <v>46314.6618055556</v>
+      </c>
+      <c s="21" t="inlineStr" r="H606">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I606"/>
+      <c s="21" t="inlineStr" r="J606">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K606">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L606">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M606"/>
+      <c s="20" t="inlineStr" r="N606">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE FARDO</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O606">
+        <is>
+          <t xml:space="preserve">passagem de fardo</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P606"/>
+      <c s="20" t="inlineStr" r="R606">
+        <is>
+          <t xml:space="preserve">00875481-cbee-11f1-bff5-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S606">
+        <is>
+          <t xml:space="preserve">10049761    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U606">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V606"/>
+    </row>
+    <row r="607" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A607">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B607">
+        <is>
+          <t xml:space="preserve">TR05-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D607">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E607">
+        <v>46314.6659722222</v>
+      </c>
+      <c s="18" r="G607">
+        <v>46314.6729166667</v>
+      </c>
+      <c s="17" t="inlineStr" r="H607">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I607"/>
+      <c s="17" t="inlineStr" r="J607">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K607">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L607">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M607"/>
+      <c s="16" t="inlineStr" r="N607">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O607">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 10 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P607"/>
+      <c s="16" t="inlineStr" r="R607">
+        <is>
+          <t xml:space="preserve">43f44420-cbef-11f1-991b-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S607">
+        <is>
+          <t xml:space="preserve">10049761    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U607">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V607"/>
+    </row>
+    <row r="608" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A608">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B608">
+        <is>
+          <t xml:space="preserve">TR04-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D608">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E608">
+        <v>46314.6680555556</v>
+      </c>
+      <c s="22" r="G608">
+        <v>46314.6736111111</v>
+      </c>
+      <c s="21" t="inlineStr" r="H608">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I608"/>
+      <c s="21" t="inlineStr" r="J608">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K608">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L608">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M608"/>
+      <c s="20" t="inlineStr" r="N608">
+        <is>
+          <t xml:space="preserve">CINTAGEM DE MATERIAL</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O608">
+        <is>
+          <t xml:space="preserve">cintagem e retirada de material</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P608"/>
+      <c s="20" t="inlineStr" r="R608">
+        <is>
+          <t xml:space="preserve">b3a763b0-cbef-11f1-b65f-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S608">
+        <is>
+          <t xml:space="preserve">10050415    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U608">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V608"/>
+    </row>
+    <row r="609" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A609">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B609">
+        <is>
+          <t xml:space="preserve">TR05-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D609">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E609">
+        <v>46314.675</v>
+      </c>
+      <c s="18" r="G609">
+        <v>46314.6770833333</v>
+      </c>
+      <c s="17" t="inlineStr" r="H609">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I609"/>
+      <c s="17" t="inlineStr" r="J609">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K609">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L609">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M609"/>
+      <c s="16" t="inlineStr" r="N609">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE FARDO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O609">
+        <is>
+          <t xml:space="preserve">passagem de fardo</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P609"/>
+      <c s="16" t="inlineStr" r="R609">
+        <is>
+          <t xml:space="preserve">061321b0-cbf1-11f1-c55c-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S609">
+        <is>
+          <t xml:space="preserve">10049761    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U609">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V609"/>
+    </row>
+    <row r="610" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A610">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B610">
+        <is>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D610">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E610">
+        <v>46314.6798611111</v>
+      </c>
+      <c s="22" r="G610">
+        <v>46314.6902777778</v>
+      </c>
+      <c s="21" t="inlineStr" r="H610">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I610"/>
+      <c s="21" t="inlineStr" r="J610">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K610">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L610">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M610"/>
+      <c s="20" t="inlineStr" r="N610">
+        <is>
+          <t xml:space="preserve">MEP - MOVIMENTAÇÃO INTERNA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O610">
+        <is>
+          <t xml:space="preserve">esperando abastecer bobina 0.95x1.000</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P610"/>
+      <c s="20" t="inlineStr" r="R610">
+        <is>
+          <t xml:space="preserve">fcb010f0-cbf1-11f1-ad65-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S610">
+        <is>
+          <t xml:space="preserve">10050415    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U610">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V610"/>
+    </row>
+    <row r="611" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A611">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B611">
+        <is>
+          <t xml:space="preserve">TR05-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D611">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E611">
+        <v>46314.6861111111</v>
+      </c>
+      <c s="18" r="G611">
+        <v>46314.6888888889</v>
+      </c>
+      <c s="17" t="inlineStr" r="H611">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I611"/>
+      <c s="17" t="inlineStr" r="J611">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K611">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L611">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M611"/>
+      <c s="16" t="inlineStr" r="N611">
+        <is>
+          <t xml:space="preserve">AGUARDANDO INSPEÇÃO DE  QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O611">
+        <is>
+          <t xml:space="preserve">aguardando inspeção da matéria prima de UD: 2003994097 oxidação galvânica foi retirado 1307 kg de pnc o restante foi autorizado como bom</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P611"/>
+      <c s="16" t="inlineStr" r="R611">
+        <is>
+          <t xml:space="preserve">d3c599b0-cbf3-11f1-cbba-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S611">
+        <is>
+          <t xml:space="preserve">10049761    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U611">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V611"/>
+    </row>
+    <row r="612" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A612">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B612">
+        <is>
+          <t xml:space="preserve">TR01-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D612">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E612">
+        <v>46314.6951388889</v>
+      </c>
+      <c s="22" r="G612">
+        <v>46315.2909722222</v>
+      </c>
+      <c s="21" t="inlineStr" r="H612">
+        <is>
+          <t xml:space="preserve">858</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I612"/>
+      <c s="21" t="inlineStr" r="J612">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K612">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L612">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M612"/>
+      <c s="20" t="inlineStr" r="N612">
+        <is>
+          <t xml:space="preserve">FALTA DEMANDA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O612">
+        <is>
+          <t xml:space="preserve">tempo livre</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P612"/>
+      <c s="20" t="inlineStr" r="R612">
+        <is>
+          <t xml:space="preserve">f2ec6240-cbf5-11f1-8b83-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="S612"/>
+      <c s="20" t="inlineStr" r="U612">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V612"/>
+    </row>
+    <row r="613" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A613">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B613">
+        <is>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D613">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E613">
+        <v>46314.6979166667</v>
+      </c>
+      <c s="18" r="G613">
+        <v>46315.3236009259</v>
+      </c>
+      <c s="17" t="inlineStr" r="H613">
+        <is>
+          <t xml:space="preserve">901</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I613"/>
+      <c s="17" t="inlineStr" r="J613">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K613">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L613">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M613"/>
+      <c s="16" t="inlineStr" r="N613">
+        <is>
+          <t xml:space="preserve">FALTA DEMANDA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O613">
+        <is>
+          <t xml:space="preserve">falta de demanda</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P613"/>
+      <c s="16" t="inlineStr" r="R613">
+        <is>
+          <t xml:space="preserve">996ba230-cbf5-11f1-c9f6-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S613">
+        <is>
+          <t xml:space="preserve">10049761    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U613">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V613"/>
+    </row>
+    <row r="614" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A614">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B614"/>
+      <c s="21" t="inlineStr" r="D614">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E614">
+        <v>46314.7013888889</v>
+      </c>
+      <c s="22" r="G614">
+        <v>46315.2840277778</v>
+      </c>
+      <c s="21" t="inlineStr" r="H614">
+        <is>
+          <t xml:space="preserve">839</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I614"/>
+      <c s="21" t="inlineStr" r="J614">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K614">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L614">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M614"/>
+      <c s="20" t="inlineStr" r="N614">
+        <is>
+          <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O614">
+        <is>
+          <t xml:space="preserve">Parada registrada automaticamente pelo sistema</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P614"/>
+      <c s="20" t="inlineStr" r="R614">
+        <is>
+          <t xml:space="preserve">452ce700-cbf6-11f1-9fed-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S614">
+        <is>
+          <t xml:space="preserve">10049748    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U614">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V614"/>
+    </row>
+    <row r="615" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A615">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 03</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B615"/>
+      <c s="17" t="inlineStr" r="D615">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E615">
+        <v>46314.7013888889</v>
+      </c>
+      <c s="18" r="G615">
+        <v>46315.2840277778</v>
+      </c>
+      <c s="17" t="inlineStr" r="H615">
+        <is>
+          <t xml:space="preserve">839</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I615"/>
+      <c s="17" t="inlineStr" r="J615">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K615">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L615">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M615"/>
+      <c s="16" t="inlineStr" r="N615">
+        <is>
+          <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O615">
+        <is>
+          <t xml:space="preserve">Parada registrada automaticamente pelo sistema</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P615"/>
+      <c s="16" t="inlineStr" r="R615">
+        <is>
+          <t xml:space="preserve">4541f5a0-cbf6-11f1-c041-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="S615"/>
+      <c s="16" t="inlineStr" r="U615">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V615"/>
+    </row>
+    <row r="616" ht="15.55" customHeight="0">
+      <c s="23" t="inlineStr" r="A616">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="24" t="str" r="B616"/>
+      <c s="10" t="str" r="C616"/>
+      <c s="25" t="inlineStr" r="D616">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="26" r="E616">
+        <v>46314.7013888889</v>
+      </c>
+      <c s="10" t="str" r="F616"/>
+      <c s="26" r="G616">
+        <v>46315.2840277778</v>
+      </c>
+      <c s="25" t="inlineStr" r="H616">
+        <is>
+          <t xml:space="preserve">839</t>
+        </is>
+      </c>
+      <c s="25" t="str" r="I616"/>
+      <c s="25" t="inlineStr" r="J616">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="K616">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="L616">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="24" t="str" r="M616"/>
+      <c s="24" t="inlineStr" r="N616">
+        <is>
+          <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="O616">
+        <is>
+          <t xml:space="preserve">Parada registrada automaticamente pelo sistema</t>
+        </is>
+      </c>
+      <c s="24" t="str" r="P616"/>
+      <c s="10" t="str" r="Q616"/>
+      <c s="24" t="inlineStr" r="R616">
+        <is>
+          <t xml:space="preserve">45583cc0-cbf6-11f1-850f-f2050a003223</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="S616">
+        <is>
+          <t xml:space="preserve">10050415    </t>
+        </is>
+      </c>
+      <c s="10" t="str" r="T616"/>
+      <c s="24" t="inlineStr" r="U616">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="11" t="str" r="V616"/>
+    </row>
+    <row r="617" ht="0.05" customHeight="1"/>
   </sheetData>
   <mergeCells>
     <mergeCell ref="A3:B8"/>
@@ -41733,6 +45939,301 @@
     <mergeCell ref="P557:Q557"/>
     <mergeCell ref="S557:T557"/>
     <mergeCell ref="U557:V557"/>
+    <mergeCell ref="B558:C558"/>
+    <mergeCell ref="E558:F558"/>
+    <mergeCell ref="P558:Q558"/>
+    <mergeCell ref="S558:T558"/>
+    <mergeCell ref="U558:V558"/>
+    <mergeCell ref="B559:C559"/>
+    <mergeCell ref="E559:F559"/>
+    <mergeCell ref="P559:Q559"/>
+    <mergeCell ref="S559:T559"/>
+    <mergeCell ref="U559:V559"/>
+    <mergeCell ref="B560:C560"/>
+    <mergeCell ref="E560:F560"/>
+    <mergeCell ref="P560:Q560"/>
+    <mergeCell ref="S560:T560"/>
+    <mergeCell ref="U560:V560"/>
+    <mergeCell ref="B561:C561"/>
+    <mergeCell ref="E561:F561"/>
+    <mergeCell ref="P561:Q561"/>
+    <mergeCell ref="S561:T561"/>
+    <mergeCell ref="U561:V561"/>
+    <mergeCell ref="B562:C562"/>
+    <mergeCell ref="E562:F562"/>
+    <mergeCell ref="P562:Q562"/>
+    <mergeCell ref="S562:T562"/>
+    <mergeCell ref="U562:V562"/>
+    <mergeCell ref="B563:C563"/>
+    <mergeCell ref="E563:F563"/>
+    <mergeCell ref="P563:Q563"/>
+    <mergeCell ref="S563:T563"/>
+    <mergeCell ref="U563:V563"/>
+    <mergeCell ref="B564:C564"/>
+    <mergeCell ref="E564:F564"/>
+    <mergeCell ref="P564:Q564"/>
+    <mergeCell ref="S564:T564"/>
+    <mergeCell ref="U564:V564"/>
+    <mergeCell ref="B565:C565"/>
+    <mergeCell ref="E565:F565"/>
+    <mergeCell ref="P565:Q565"/>
+    <mergeCell ref="S565:T565"/>
+    <mergeCell ref="U565:V565"/>
+    <mergeCell ref="B566:C566"/>
+    <mergeCell ref="E566:F566"/>
+    <mergeCell ref="P566:Q566"/>
+    <mergeCell ref="S566:T566"/>
+    <mergeCell ref="U566:V566"/>
+    <mergeCell ref="B567:C567"/>
+    <mergeCell ref="E567:F567"/>
+    <mergeCell ref="P567:Q567"/>
+    <mergeCell ref="S567:T567"/>
+    <mergeCell ref="U567:V567"/>
+    <mergeCell ref="B568:C568"/>
+    <mergeCell ref="E568:F568"/>
+    <mergeCell ref="P568:Q568"/>
+    <mergeCell ref="S568:T568"/>
+    <mergeCell ref="U568:V568"/>
+    <mergeCell ref="B569:C569"/>
+    <mergeCell ref="E569:F569"/>
+    <mergeCell ref="P569:Q569"/>
+    <mergeCell ref="S569:T569"/>
+    <mergeCell ref="U569:V569"/>
+    <mergeCell ref="B570:C570"/>
+    <mergeCell ref="E570:F570"/>
+    <mergeCell ref="P570:Q570"/>
+    <mergeCell ref="S570:T570"/>
+    <mergeCell ref="U570:V570"/>
+    <mergeCell ref="B571:C571"/>
+    <mergeCell ref="E571:F571"/>
+    <mergeCell ref="P571:Q571"/>
+    <mergeCell ref="S571:T571"/>
+    <mergeCell ref="U571:V571"/>
+    <mergeCell ref="B572:C572"/>
+    <mergeCell ref="E572:F572"/>
+    <mergeCell ref="P572:Q572"/>
+    <mergeCell ref="S572:T572"/>
+    <mergeCell ref="U572:V572"/>
+    <mergeCell ref="B573:C573"/>
+    <mergeCell ref="E573:F573"/>
+    <mergeCell ref="P573:Q573"/>
+    <mergeCell ref="S573:T573"/>
+    <mergeCell ref="U573:V573"/>
+    <mergeCell ref="B574:C574"/>
+    <mergeCell ref="E574:F574"/>
+    <mergeCell ref="P574:Q574"/>
+    <mergeCell ref="S574:T574"/>
+    <mergeCell ref="U574:V574"/>
+    <mergeCell ref="B575:C575"/>
+    <mergeCell ref="E575:F575"/>
+    <mergeCell ref="P575:Q575"/>
+    <mergeCell ref="S575:T575"/>
+    <mergeCell ref="U575:V575"/>
+    <mergeCell ref="B576:C576"/>
+    <mergeCell ref="E576:F576"/>
+    <mergeCell ref="P576:Q576"/>
+    <mergeCell ref="S576:T576"/>
+    <mergeCell ref="U576:V576"/>
+    <mergeCell ref="B577:C577"/>
+    <mergeCell ref="E577:F577"/>
+    <mergeCell ref="P577:Q577"/>
+    <mergeCell ref="S577:T577"/>
+    <mergeCell ref="U577:V577"/>
+    <mergeCell ref="B578:C578"/>
+    <mergeCell ref="E578:F578"/>
+    <mergeCell ref="P578:Q578"/>
+    <mergeCell ref="S578:T578"/>
+    <mergeCell ref="U578:V578"/>
+    <mergeCell ref="B579:C579"/>
+    <mergeCell ref="E579:F579"/>
+    <mergeCell ref="P579:Q579"/>
+    <mergeCell ref="S579:T579"/>
+    <mergeCell ref="U579:V579"/>
+    <mergeCell ref="B580:C580"/>
+    <mergeCell ref="E580:F580"/>
+    <mergeCell ref="P580:Q580"/>
+    <mergeCell ref="S580:T580"/>
+    <mergeCell ref="U580:V580"/>
+    <mergeCell ref="B581:C581"/>
+    <mergeCell ref="E581:F581"/>
+    <mergeCell ref="P581:Q581"/>
+    <mergeCell ref="S581:T581"/>
+    <mergeCell ref="U581:V581"/>
+    <mergeCell ref="B582:C582"/>
+    <mergeCell ref="E582:F582"/>
+    <mergeCell ref="P582:Q582"/>
+    <mergeCell ref="S582:T582"/>
+    <mergeCell ref="U582:V582"/>
+    <mergeCell ref="B583:C583"/>
+    <mergeCell ref="E583:F583"/>
+    <mergeCell ref="P583:Q583"/>
+    <mergeCell ref="S583:T583"/>
+    <mergeCell ref="U583:V583"/>
+    <mergeCell ref="B584:C584"/>
+    <mergeCell ref="E584:F584"/>
+    <mergeCell ref="P584:Q584"/>
+    <mergeCell ref="S584:T584"/>
+    <mergeCell ref="U584:V584"/>
+    <mergeCell ref="B585:C585"/>
+    <mergeCell ref="E585:F585"/>
+    <mergeCell ref="P585:Q585"/>
+    <mergeCell ref="S585:T585"/>
+    <mergeCell ref="U585:V585"/>
+    <mergeCell ref="B586:C586"/>
+    <mergeCell ref="E586:F586"/>
+    <mergeCell ref="P586:Q586"/>
+    <mergeCell ref="S586:T586"/>
+    <mergeCell ref="U586:V586"/>
+    <mergeCell ref="B587:C587"/>
+    <mergeCell ref="E587:F587"/>
+    <mergeCell ref="P587:Q587"/>
+    <mergeCell ref="S587:T587"/>
+    <mergeCell ref="U587:V587"/>
+    <mergeCell ref="B588:C588"/>
+    <mergeCell ref="E588:F588"/>
+    <mergeCell ref="P588:Q588"/>
+    <mergeCell ref="S588:T588"/>
+    <mergeCell ref="U588:V588"/>
+    <mergeCell ref="B589:C589"/>
+    <mergeCell ref="E589:F589"/>
+    <mergeCell ref="P589:Q589"/>
+    <mergeCell ref="S589:T589"/>
+    <mergeCell ref="U589:V589"/>
+    <mergeCell ref="B590:C590"/>
+    <mergeCell ref="E590:F590"/>
+    <mergeCell ref="P590:Q590"/>
+    <mergeCell ref="S590:T590"/>
+    <mergeCell ref="U590:V590"/>
+    <mergeCell ref="B591:C591"/>
+    <mergeCell ref="E591:F591"/>
+    <mergeCell ref="P591:Q591"/>
+    <mergeCell ref="S591:T591"/>
+    <mergeCell ref="U591:V591"/>
+    <mergeCell ref="B592:C592"/>
+    <mergeCell ref="E592:F592"/>
+    <mergeCell ref="P592:Q592"/>
+    <mergeCell ref="S592:T592"/>
+    <mergeCell ref="U592:V592"/>
+    <mergeCell ref="B593:C593"/>
+    <mergeCell ref="E593:F593"/>
+    <mergeCell ref="P593:Q593"/>
+    <mergeCell ref="S593:T593"/>
+    <mergeCell ref="U593:V593"/>
+    <mergeCell ref="B594:C594"/>
+    <mergeCell ref="E594:F594"/>
+    <mergeCell ref="P594:Q594"/>
+    <mergeCell ref="S594:T594"/>
+    <mergeCell ref="U594:V594"/>
+    <mergeCell ref="B595:C595"/>
+    <mergeCell ref="E595:F595"/>
+    <mergeCell ref="P595:Q595"/>
+    <mergeCell ref="S595:T595"/>
+    <mergeCell ref="U595:V595"/>
+    <mergeCell ref="B596:C596"/>
+    <mergeCell ref="E596:F596"/>
+    <mergeCell ref="P596:Q596"/>
+    <mergeCell ref="S596:T596"/>
+    <mergeCell ref="U596:V596"/>
+    <mergeCell ref="B597:C597"/>
+    <mergeCell ref="E597:F597"/>
+    <mergeCell ref="P597:Q597"/>
+    <mergeCell ref="S597:T597"/>
+    <mergeCell ref="U597:V597"/>
+    <mergeCell ref="B598:C598"/>
+    <mergeCell ref="E598:F598"/>
+    <mergeCell ref="P598:Q598"/>
+    <mergeCell ref="S598:T598"/>
+    <mergeCell ref="U598:V598"/>
+    <mergeCell ref="B599:C599"/>
+    <mergeCell ref="E599:F599"/>
+    <mergeCell ref="P599:Q599"/>
+    <mergeCell ref="S599:T599"/>
+    <mergeCell ref="U599:V599"/>
+    <mergeCell ref="B600:C600"/>
+    <mergeCell ref="E600:F600"/>
+    <mergeCell ref="P600:Q600"/>
+    <mergeCell ref="S600:T600"/>
+    <mergeCell ref="U600:V600"/>
+    <mergeCell ref="B601:C601"/>
+    <mergeCell ref="E601:F601"/>
+    <mergeCell ref="P601:Q601"/>
+    <mergeCell ref="S601:T601"/>
+    <mergeCell ref="U601:V601"/>
+    <mergeCell ref="B602:C602"/>
+    <mergeCell ref="E602:F602"/>
+    <mergeCell ref="P602:Q602"/>
+    <mergeCell ref="S602:T602"/>
+    <mergeCell ref="U602:V602"/>
+    <mergeCell ref="B603:C603"/>
+    <mergeCell ref="E603:F603"/>
+    <mergeCell ref="P603:Q603"/>
+    <mergeCell ref="S603:T603"/>
+    <mergeCell ref="U603:V603"/>
+    <mergeCell ref="B604:C604"/>
+    <mergeCell ref="E604:F604"/>
+    <mergeCell ref="P604:Q604"/>
+    <mergeCell ref="S604:T604"/>
+    <mergeCell ref="U604:V604"/>
+    <mergeCell ref="B605:C605"/>
+    <mergeCell ref="E605:F605"/>
+    <mergeCell ref="P605:Q605"/>
+    <mergeCell ref="S605:T605"/>
+    <mergeCell ref="U605:V605"/>
+    <mergeCell ref="B606:C606"/>
+    <mergeCell ref="E606:F606"/>
+    <mergeCell ref="P606:Q606"/>
+    <mergeCell ref="S606:T606"/>
+    <mergeCell ref="U606:V606"/>
+    <mergeCell ref="B607:C607"/>
+    <mergeCell ref="E607:F607"/>
+    <mergeCell ref="P607:Q607"/>
+    <mergeCell ref="S607:T607"/>
+    <mergeCell ref="U607:V607"/>
+    <mergeCell ref="B608:C608"/>
+    <mergeCell ref="E608:F608"/>
+    <mergeCell ref="P608:Q608"/>
+    <mergeCell ref="S608:T608"/>
+    <mergeCell ref="U608:V608"/>
+    <mergeCell ref="B609:C609"/>
+    <mergeCell ref="E609:F609"/>
+    <mergeCell ref="P609:Q609"/>
+    <mergeCell ref="S609:T609"/>
+    <mergeCell ref="U609:V609"/>
+    <mergeCell ref="B610:C610"/>
+    <mergeCell ref="E610:F610"/>
+    <mergeCell ref="P610:Q610"/>
+    <mergeCell ref="S610:T610"/>
+    <mergeCell ref="U610:V610"/>
+    <mergeCell ref="B611:C611"/>
+    <mergeCell ref="E611:F611"/>
+    <mergeCell ref="P611:Q611"/>
+    <mergeCell ref="S611:T611"/>
+    <mergeCell ref="U611:V611"/>
+    <mergeCell ref="B612:C612"/>
+    <mergeCell ref="E612:F612"/>
+    <mergeCell ref="P612:Q612"/>
+    <mergeCell ref="S612:T612"/>
+    <mergeCell ref="U612:V612"/>
+    <mergeCell ref="B613:C613"/>
+    <mergeCell ref="E613:F613"/>
+    <mergeCell ref="P613:Q613"/>
+    <mergeCell ref="S613:T613"/>
+    <mergeCell ref="U613:V613"/>
+    <mergeCell ref="B614:C614"/>
+    <mergeCell ref="E614:F614"/>
+    <mergeCell ref="P614:Q614"/>
+    <mergeCell ref="S614:T614"/>
+    <mergeCell ref="U614:V614"/>
+    <mergeCell ref="B615:C615"/>
+    <mergeCell ref="E615:F615"/>
+    <mergeCell ref="P615:Q615"/>
+    <mergeCell ref="S615:T615"/>
+    <mergeCell ref="U615:V615"/>
+    <mergeCell ref="B616:C616"/>
+    <mergeCell ref="E616:F616"/>
+    <mergeCell ref="P616:Q616"/>
+    <mergeCell ref="S616:T616"/>
+    <mergeCell ref="U616:V616"/>
   </mergeCells>
   <pageMargins left="0.0393700787401575" right="0.0393700787401575" top="0.0393700787401575" bottom="0.0393700787401575" header="0.0393700787401575" footer="0.0393700787401575"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>

--- a/Base_Interrupcoes.xlsx
+++ b/Base_Interrupcoes.xlsx
@@ -466,7 +466,7 @@
       <c s="4" t="str" r="A7"/>
       <c s="7" t="inlineStr" r="T7">
         <is>
-          <t xml:space="preserve">Emissão: 20/10/2026</t>
+          <t xml:space="preserve">Emissão: 21/10/2026</t>
         </is>
       </c>
       <c s="5" t="str" r="V7"/>
@@ -475,7 +475,7 @@
       <c s="4" t="str" r="A8"/>
       <c s="8" t="inlineStr" r="F8">
         <is>
-          <t xml:space="preserve">Período: 01/10/2026 até 19/10/2026; Turno: Todos; Tempo: Calendário</t>
+          <t xml:space="preserve">Período: 01/10/2026 até 20/10/2026; Turno: Todos; Tempo: Calendário</t>
         </is>
       </c>
       <c s="5" t="str" r="V8"/>
@@ -2838,14 +2838,10 @@
     <row r="48" ht="15.55" customHeight="0">
       <c s="19" t="inlineStr" r="A48">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 05</t>
-        </is>
-      </c>
-      <c s="20" t="inlineStr" r="B48">
-        <is>
-          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
-        </is>
-      </c>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B48"/>
       <c s="21" t="inlineStr" r="D48">
         <is>
           <t xml:space="preserve">TURNO B</t>
@@ -2881,25 +2877,21 @@
       <c s="20" t="str" r="M48"/>
       <c s="20" t="inlineStr" r="N48">
         <is>
-          <t xml:space="preserve">FALTA DEMANDA</t>
+          <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="O48">
         <is>
-          <t xml:space="preserve">falta de demanda</t>
+          <t xml:space="preserve">Parada registrada automaticamente pelo sistema</t>
         </is>
       </c>
       <c s="20" t="str" r="P48"/>
       <c s="20" t="inlineStr" r="R48">
         <is>
-          <t xml:space="preserve">4a25c5c0-bdd1-11f1-86c2-f2050a003223</t>
-        </is>
-      </c>
-      <c s="20" t="inlineStr" r="S48">
-        <is>
-          <t xml:space="preserve">10046135    </t>
-        </is>
-      </c>
+          <t xml:space="preserve">49cef330-bdd1-11f1-8f07-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="S48"/>
       <c s="20" t="inlineStr" r="U48">
         <is>
           <t xml:space="preserve">Sim</t>
@@ -2910,7 +2902,7 @@
     <row r="49" ht="15.6" customHeight="0">
       <c s="15" t="inlineStr" r="A49">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 02</t>
+          <t xml:space="preserve">TRANSVERSAL 03</t>
         </is>
       </c>
       <c s="16" t="str" r="B49"/>
@@ -2960,7 +2952,7 @@
       <c s="16" t="str" r="P49"/>
       <c s="16" t="inlineStr" r="R49">
         <is>
-          <t xml:space="preserve">49cef330-bdd1-11f1-8f07-f2050a003223</t>
+          <t xml:space="preserve">49efe8b0-bdd1-11f1-cb5a-f2050a003223</t>
         </is>
       </c>
       <c s="16" t="str" r="S49"/>
@@ -2974,10 +2966,14 @@
     <row r="50" ht="15.6" customHeight="0">
       <c s="19" t="inlineStr" r="A50">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 03</t>
-        </is>
-      </c>
-      <c s="20" t="str" r="B50"/>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B50">
+        <is>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
       <c s="21" t="inlineStr" r="D50">
         <is>
           <t xml:space="preserve">TURNO B</t>
@@ -3013,21 +3009,25 @@
       <c s="20" t="str" r="M50"/>
       <c s="20" t="inlineStr" r="N50">
         <is>
-          <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
+          <t xml:space="preserve">FALTA DEMANDA</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="O50">
         <is>
-          <t xml:space="preserve">Parada registrada automaticamente pelo sistema</t>
+          <t xml:space="preserve">falta de demanda</t>
         </is>
       </c>
       <c s="20" t="str" r="P50"/>
       <c s="20" t="inlineStr" r="R50">
         <is>
-          <t xml:space="preserve">49efe8b0-bdd1-11f1-cb5a-f2050a003223</t>
-        </is>
-      </c>
-      <c s="20" t="str" r="S50"/>
+          <t xml:space="preserve">4a25c5c0-bdd1-11f1-86c2-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S50">
+        <is>
+          <t xml:space="preserve">10046135    </t>
+        </is>
+      </c>
       <c s="20" t="inlineStr" r="U50">
         <is>
           <t xml:space="preserve">Sim</t>
@@ -3110,12 +3110,12 @@
     <row r="52" ht="15.6" customHeight="0">
       <c s="19" t="inlineStr" r="A52">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 04</t>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="B52">
         <is>
-          <t xml:space="preserve">TR04-DESENROLADOR</t>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
         </is>
       </c>
       <c s="21" t="inlineStr" r="D52">
@@ -3127,11 +3127,11 @@
         <v>46297.2916666667</v>
       </c>
       <c s="22" r="G52">
-        <v>46297.2986111111</v>
+        <v>46297.3020833333</v>
       </c>
       <c s="21" t="inlineStr" r="H52">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c s="21" t="str" r="I52"/>
@@ -3158,18 +3158,18 @@
       </c>
       <c s="20" t="inlineStr" r="O52">
         <is>
-          <t xml:space="preserve">DDS</t>
+          <t xml:space="preserve">dds e assinatura dos documentos</t>
         </is>
       </c>
       <c s="20" t="str" r="P52"/>
       <c s="20" t="inlineStr" r="R52">
         <is>
-          <t xml:space="preserve">942e4bd0-be4c-11f1-ca85-f2050a003223</t>
+          <t xml:space="preserve">61a3b7a0-be4b-11f1-9cbf-f2050a003223</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="S52">
         <is>
-          <t xml:space="preserve">10047019    </t>
+          <t xml:space="preserve">10046873    </t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="U52">
@@ -3182,12 +3182,12 @@
     <row r="53" ht="15.55" customHeight="0">
       <c s="15" t="inlineStr" r="A53">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 01</t>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="B53">
         <is>
-          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
         </is>
       </c>
       <c s="17" t="inlineStr" r="D53">
@@ -3199,11 +3199,11 @@
         <v>46297.2916666667</v>
       </c>
       <c s="18" r="G53">
-        <v>46297.3020833333</v>
+        <v>46297.3055555556</v>
       </c>
       <c s="17" t="inlineStr" r="H53">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c s="17" t="str" r="I53"/>
@@ -3230,18 +3230,18 @@
       </c>
       <c s="16" t="inlineStr" r="O53">
         <is>
-          <t xml:space="preserve">dds e assinatura dos documentos</t>
+          <t xml:space="preserve">dds com supervisor QUEDA DE MATERIAIS</t>
         </is>
       </c>
       <c s="16" t="str" r="P53"/>
       <c s="16" t="inlineStr" r="R53">
         <is>
-          <t xml:space="preserve">61a3b7a0-be4b-11f1-9cbf-f2050a003223</t>
+          <t xml:space="preserve">167ccc00-be4e-11f1-cdcf-f2050a003223</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="S53">
         <is>
-          <t xml:space="preserve">10046873    </t>
+          <t xml:space="preserve">10046135    </t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="U53">
@@ -3254,12 +3254,12 @@
     <row r="54" ht="15.6" customHeight="0">
       <c s="19" t="inlineStr" r="A54">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 05</t>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="B54">
         <is>
-          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
         </is>
       </c>
       <c s="21" t="inlineStr" r="D54">
@@ -3271,11 +3271,11 @@
         <v>46297.2916666667</v>
       </c>
       <c s="22" r="G54">
-        <v>46297.3055555556</v>
+        <v>46297.2986111111</v>
       </c>
       <c s="21" t="inlineStr" r="H54">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c s="21" t="str" r="I54"/>
@@ -3302,18 +3302,18 @@
       </c>
       <c s="20" t="inlineStr" r="O54">
         <is>
-          <t xml:space="preserve">dds com supervisor QUEDA DE MATERIAIS</t>
+          <t xml:space="preserve">DDS</t>
         </is>
       </c>
       <c s="20" t="str" r="P54"/>
       <c s="20" t="inlineStr" r="R54">
         <is>
-          <t xml:space="preserve">167ccc00-be4e-11f1-cdcf-f2050a003223</t>
+          <t xml:space="preserve">942e4bd0-be4c-11f1-ca85-f2050a003223</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="S54">
         <is>
-          <t xml:space="preserve">10046135    </t>
+          <t xml:space="preserve">10047019    </t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="U54">
@@ -10319,14 +10319,10 @@
     <row r="153" ht="15.6" customHeight="0">
       <c s="15" t="inlineStr" r="A153">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 04</t>
-        </is>
-      </c>
-      <c s="16" t="inlineStr" r="B153">
-        <is>
-          <t xml:space="preserve">TR04-CARRO DE ENTRADA</t>
-        </is>
-      </c>
+          <t xml:space="preserve">TRANSVERSAL 03</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B153"/>
       <c s="17" t="inlineStr" r="D153">
         <is>
           <t xml:space="preserve">TURNO B</t>
@@ -10362,7 +10358,7 @@
       <c s="16" t="str" r="M153"/>
       <c s="16" t="inlineStr" r="N153">
         <is>
-          <t xml:space="preserve">FALTA DEMANDA</t>
+          <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="O153">
@@ -10373,14 +10369,10 @@
       <c s="16" t="str" r="P153"/>
       <c s="16" t="inlineStr" r="R153">
         <is>
-          <t xml:space="preserve">f4fe8f00-c0f5-11f1-ad1e-f2050a003223</t>
-        </is>
-      </c>
-      <c s="16" t="inlineStr" r="S153">
-        <is>
-          <t xml:space="preserve">10048032    </t>
-        </is>
-      </c>
+          <t xml:space="preserve">f4dfe370-c0f5-11f1-c191-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="S153"/>
       <c s="16" t="inlineStr" r="U153">
         <is>
           <t xml:space="preserve">Sim</t>
@@ -10391,10 +10383,14 @@
     <row r="154" ht="15.55" customHeight="0">
       <c s="19" t="inlineStr" r="A154">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 03</t>
-        </is>
-      </c>
-      <c s="20" t="str" r="B154"/>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B154">
+        <is>
+          <t xml:space="preserve">TR04-CARRO DE ENTRADA</t>
+        </is>
+      </c>
       <c s="21" t="inlineStr" r="D154">
         <is>
           <t xml:space="preserve">TURNO B</t>
@@ -10430,7 +10426,7 @@
       <c s="20" t="str" r="M154"/>
       <c s="20" t="inlineStr" r="N154">
         <is>
-          <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
+          <t xml:space="preserve">FALTA DEMANDA</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="O154">
@@ -10441,10 +10437,14 @@
       <c s="20" t="str" r="P154"/>
       <c s="20" t="inlineStr" r="R154">
         <is>
-          <t xml:space="preserve">f4dfe370-c0f5-11f1-c191-f2050a003223</t>
-        </is>
-      </c>
-      <c s="20" t="str" r="S154"/>
+          <t xml:space="preserve">f4fe8f00-c0f5-11f1-ad1e-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S154">
+        <is>
+          <t xml:space="preserve">10048032    </t>
+        </is>
+      </c>
       <c s="20" t="inlineStr" r="U154">
         <is>
           <t xml:space="preserve">Sim</t>
@@ -10671,12 +10671,12 @@
     <row r="158" ht="15.6" customHeight="0">
       <c s="19" t="inlineStr" r="A158">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 01</t>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="B158">
         <is>
-          <t xml:space="preserve">TR01-MESA TRANSPORTADORA</t>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
         </is>
       </c>
       <c s="21" t="inlineStr" r="D158">
@@ -10688,11 +10688,11 @@
         <v>46301.2916666667</v>
       </c>
       <c s="22" r="G158">
-        <v>46301.3020833333</v>
+        <v>46301.2986111111</v>
       </c>
       <c s="21" t="inlineStr" r="H158">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c s="21" t="str" r="I158"/>
@@ -10719,18 +10719,18 @@
       </c>
       <c s="20" t="inlineStr" r="O158">
         <is>
-          <t xml:space="preserve">dds  e assinatura dos documentos</t>
+          <t xml:space="preserve">DDS</t>
         </is>
       </c>
       <c s="20" t="str" r="P158"/>
       <c s="20" t="inlineStr" r="R158">
         <is>
-          <t xml:space="preserve">fa2e6070-c16f-11f1-a1bf-f2050a003223</t>
+          <t xml:space="preserve">00542e40-c174-11f1-b395-f2050a003223</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="S158">
         <is>
-          <t xml:space="preserve">10047271    </t>
+          <t xml:space="preserve">10048032    </t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="U158">
@@ -10743,12 +10743,12 @@
     <row r="159" ht="15.55" customHeight="0">
       <c s="15" t="inlineStr" r="A159">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 04</t>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="B159">
         <is>
-          <t xml:space="preserve">TR04-DESENROLADOR</t>
+          <t xml:space="preserve">TR01-MESA TRANSPORTADORA</t>
         </is>
       </c>
       <c s="17" t="inlineStr" r="D159">
@@ -10760,11 +10760,11 @@
         <v>46301.2916666667</v>
       </c>
       <c s="18" r="G159">
-        <v>46301.2986111111</v>
+        <v>46301.3020833333</v>
       </c>
       <c s="17" t="inlineStr" r="H159">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c s="17" t="str" r="I159"/>
@@ -10791,18 +10791,18 @@
       </c>
       <c s="16" t="inlineStr" r="O159">
         <is>
-          <t xml:space="preserve">DDS</t>
+          <t xml:space="preserve">dds  e assinatura dos documentos</t>
         </is>
       </c>
       <c s="16" t="str" r="P159"/>
       <c s="16" t="inlineStr" r="R159">
         <is>
-          <t xml:space="preserve">00542e40-c174-11f1-b395-f2050a003223</t>
+          <t xml:space="preserve">fa2e6070-c16f-11f1-a1bf-f2050a003223</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="S159">
         <is>
-          <t xml:space="preserve">10048032    </t>
+          <t xml:space="preserve">10047271    </t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="U159">
@@ -15587,12 +15587,12 @@
     <row r="227" ht="15.6" customHeight="0">
       <c s="15" t="inlineStr" r="A227">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 05</t>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="B227">
         <is>
-          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+          <t xml:space="preserve">TR01-MESA TRANSPORTADORA</t>
         </is>
       </c>
       <c s="17" t="inlineStr" r="D227">
@@ -15604,11 +15604,11 @@
         <v>46302.2916666667</v>
       </c>
       <c s="18" r="G227">
-        <v>46302.3055555556</v>
+        <v>46302.3020833333</v>
       </c>
       <c s="17" t="inlineStr" r="H227">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c s="17" t="str" r="I227"/>
@@ -15635,18 +15635,18 @@
       </c>
       <c s="16" t="inlineStr" r="O227">
         <is>
-          <t xml:space="preserve">dds</t>
+          <t xml:space="preserve">dds e assinatura dos documentos</t>
         </is>
       </c>
       <c s="16" t="str" r="P227"/>
       <c s="16" t="inlineStr" r="R227">
         <is>
-          <t xml:space="preserve">0bb05300-c23b-11f1-bbbb-f2050a003223</t>
+          <t xml:space="preserve">e92b60c0-c237-11f1-ab7f-f2050a003223</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="S227">
         <is>
-          <t xml:space="preserve">10046774    </t>
+          <t xml:space="preserve">10048039    </t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="U227">
@@ -15659,12 +15659,12 @@
     <row r="228" ht="15.6" customHeight="0">
       <c s="19" t="inlineStr" r="A228">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 01</t>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="B228">
         <is>
-          <t xml:space="preserve">TR01-MESA TRANSPORTADORA</t>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
         </is>
       </c>
       <c s="21" t="inlineStr" r="D228">
@@ -15676,11 +15676,11 @@
         <v>46302.2916666667</v>
       </c>
       <c s="22" r="G228">
-        <v>46302.3020833333</v>
+        <v>46302.3055555556</v>
       </c>
       <c s="21" t="inlineStr" r="H228">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c s="21" t="str" r="I228"/>
@@ -15707,18 +15707,18 @@
       </c>
       <c s="20" t="inlineStr" r="O228">
         <is>
-          <t xml:space="preserve">dds e assinatura dos documentos</t>
+          <t xml:space="preserve">dds</t>
         </is>
       </c>
       <c s="20" t="str" r="P228"/>
       <c s="20" t="inlineStr" r="R228">
         <is>
-          <t xml:space="preserve">e92b60c0-c237-11f1-ab7f-f2050a003223</t>
+          <t xml:space="preserve">0bb05300-c23b-11f1-bbbb-f2050a003223</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="S228">
         <is>
-          <t xml:space="preserve">10048039    </t>
+          <t xml:space="preserve">10046774    </t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="U228">
@@ -18551,12 +18551,12 @@
     <row r="269" ht="15.6" customHeight="0">
       <c s="15" t="inlineStr" r="A269">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 02</t>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="B269">
         <is>
-          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
         </is>
       </c>
       <c s="17" t="inlineStr" r="D269">
@@ -18568,11 +18568,11 @@
         <v>46303.2916666667</v>
       </c>
       <c s="18" r="G269">
-        <v>46303.2986111111</v>
+        <v>46303.3020833333</v>
       </c>
       <c s="17" t="inlineStr" r="H269">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c s="17" t="str" r="I269"/>
@@ -18599,18 +18599,18 @@
       </c>
       <c s="16" t="inlineStr" r="O269">
         <is>
-          <t xml:space="preserve">DDS</t>
+          <t xml:space="preserve">dds e assinatura dos documentos</t>
         </is>
       </c>
       <c s="16" t="str" r="P269"/>
       <c s="16" t="inlineStr" r="R269">
         <is>
-          <t xml:space="preserve">6e8883a0-c301-11f1-9a54-f2050a003223</t>
+          <t xml:space="preserve">065f5d20-c302-11f1-8108-f2050a003223</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="S269">
         <is>
-          <t xml:space="preserve">10048465    </t>
+          <t xml:space="preserve">10048233    </t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="U269">
@@ -18623,12 +18623,12 @@
     <row r="270" ht="15.6" customHeight="0">
       <c s="19" t="inlineStr" r="A270">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 01</t>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="B270">
         <is>
-          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
         </is>
       </c>
       <c s="21" t="inlineStr" r="D270">
@@ -18640,11 +18640,11 @@
         <v>46303.2916666667</v>
       </c>
       <c s="22" r="G270">
-        <v>46303.3020833333</v>
+        <v>46303.2986111111</v>
       </c>
       <c s="21" t="inlineStr" r="H270">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c s="21" t="str" r="I270"/>
@@ -18671,18 +18671,18 @@
       </c>
       <c s="20" t="inlineStr" r="O270">
         <is>
-          <t xml:space="preserve">dds e assinatura dos documentos</t>
+          <t xml:space="preserve">DDS</t>
         </is>
       </c>
       <c s="20" t="str" r="P270"/>
       <c s="20" t="inlineStr" r="R270">
         <is>
-          <t xml:space="preserve">065f5d20-c302-11f1-8108-f2050a003223</t>
+          <t xml:space="preserve">6e8883a0-c301-11f1-9a54-f2050a003223</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="S270">
         <is>
-          <t xml:space="preserve">10048233    </t>
+          <t xml:space="preserve">10048465    </t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="U270">
@@ -22715,12 +22715,12 @@
     <row r="328" ht="15.55" customHeight="0">
       <c s="19" t="inlineStr" r="A328">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 05</t>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="B328">
         <is>
-          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+          <t xml:space="preserve">TR01-MESA TRANSPORTADORA</t>
         </is>
       </c>
       <c s="21" t="inlineStr" r="D328">
@@ -22732,11 +22732,11 @@
         <v>46308.2916666667</v>
       </c>
       <c s="22" r="G328">
-        <v>46308.2986111111</v>
+        <v>46308.3020833333</v>
       </c>
       <c s="21" t="inlineStr" r="H328">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c s="21" t="str" r="I328"/>
@@ -22763,18 +22763,18 @@
       </c>
       <c s="20" t="inlineStr" r="O328">
         <is>
-          <t xml:space="preserve">dds</t>
+          <t xml:space="preserve">dds e assinatura dos documentos</t>
         </is>
       </c>
       <c s="20" t="str" r="P328"/>
       <c s="20" t="inlineStr" r="R328">
         <is>
-          <t xml:space="preserve">90a4c9e0-c6f2-11f1-c266-f2050a003223</t>
+          <t xml:space="preserve">49ee6680-c6ef-11f1-b32a-f2050a003223</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="S328">
         <is>
-          <t xml:space="preserve">10048445    </t>
+          <t xml:space="preserve">10048955    </t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="U328">
@@ -22787,12 +22787,12 @@
     <row r="329" ht="15.6" customHeight="0">
       <c s="15" t="inlineStr" r="A329">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 01</t>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="B329">
         <is>
-          <t xml:space="preserve">TR01-MESA TRANSPORTADORA</t>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
         </is>
       </c>
       <c s="17" t="inlineStr" r="D329">
@@ -22804,11 +22804,11 @@
         <v>46308.2916666667</v>
       </c>
       <c s="18" r="G329">
-        <v>46308.3020833333</v>
+        <v>46308.2986111111</v>
       </c>
       <c s="17" t="inlineStr" r="H329">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c s="17" t="str" r="I329"/>
@@ -22835,18 +22835,18 @@
       </c>
       <c s="16" t="inlineStr" r="O329">
         <is>
-          <t xml:space="preserve">dds e assinatura dos documentos</t>
+          <t xml:space="preserve">dds</t>
         </is>
       </c>
       <c s="16" t="str" r="P329"/>
       <c s="16" t="inlineStr" r="R329">
         <is>
-          <t xml:space="preserve">49ee6680-c6ef-11f1-b32a-f2050a003223</t>
+          <t xml:space="preserve">90a4c9e0-c6f2-11f1-c266-f2050a003223</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="S329">
         <is>
-          <t xml:space="preserve">10048955    </t>
+          <t xml:space="preserve">10048445    </t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="U329">
@@ -25691,12 +25691,12 @@
     <row r="370" ht="15.55" customHeight="0">
       <c s="19" t="inlineStr" r="A370">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 05</t>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="B370">
         <is>
-          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
         </is>
       </c>
       <c s="21" t="inlineStr" r="D370">
@@ -25708,11 +25708,11 @@
         <v>46308.6958333333</v>
       </c>
       <c s="22" r="G370">
-        <v>46309.2909722222</v>
+        <v>46308.70625</v>
       </c>
       <c s="21" t="inlineStr" r="H370">
         <is>
-          <t xml:space="preserve">857</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c s="21" t="str" r="I370"/>
@@ -25723,34 +25723,34 @@
       </c>
       <c s="20" t="inlineStr" r="K370">
         <is>
-          <t xml:space="preserve">Tempo Livre</t>
+          <t xml:space="preserve">Operacional</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="L370">
         <is>
-          <t xml:space="preserve">Tempo Livre</t>
+          <t xml:space="preserve">Operacional</t>
         </is>
       </c>
       <c s="20" t="str" r="M370"/>
       <c s="20" t="inlineStr" r="N370">
         <is>
-          <t xml:space="preserve">FALTA DEMANDA</t>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="O370">
         <is>
-          <t xml:space="preserve">falta de demanda</t>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
         </is>
       </c>
       <c s="20" t="str" r="P370"/>
       <c s="20" t="inlineStr" r="R370">
         <is>
-          <t xml:space="preserve">4f550df0-c73e-11f1-918f-f2050a003223</t>
+          <t xml:space="preserve">e2f474c0-c73d-11f1-a003-f2050a003223</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="S370">
         <is>
-          <t xml:space="preserve">10048460    </t>
+          <t xml:space="preserve">10048771    </t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="U370">
@@ -25763,12 +25763,12 @@
     <row r="371" ht="15.6" customHeight="0">
       <c s="15" t="inlineStr" r="A371">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 01</t>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="B371">
         <is>
-          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
         </is>
       </c>
       <c s="17" t="inlineStr" r="D371">
@@ -25780,11 +25780,11 @@
         <v>46308.6958333333</v>
       </c>
       <c s="18" r="G371">
-        <v>46308.70625</v>
+        <v>46309.2909722222</v>
       </c>
       <c s="17" t="inlineStr" r="H371">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">857</t>
         </is>
       </c>
       <c s="17" t="str" r="I371"/>
@@ -25795,34 +25795,34 @@
       </c>
       <c s="16" t="inlineStr" r="K371">
         <is>
-          <t xml:space="preserve">Operacional</t>
+          <t xml:space="preserve">Tempo Livre</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="L371">
         <is>
-          <t xml:space="preserve">Operacional</t>
+          <t xml:space="preserve">Tempo Livre</t>
         </is>
       </c>
       <c s="16" t="str" r="M371"/>
       <c s="16" t="inlineStr" r="N371">
         <is>
-          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+          <t xml:space="preserve">FALTA DEMANDA</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="O371">
         <is>
-          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
+          <t xml:space="preserve">falta de demanda</t>
         </is>
       </c>
       <c s="16" t="str" r="P371"/>
       <c s="16" t="inlineStr" r="R371">
         <is>
-          <t xml:space="preserve">e2f474c0-c73d-11f1-a003-f2050a003223</t>
+          <t xml:space="preserve">4f550df0-c73e-11f1-918f-f2050a003223</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="S371">
         <is>
-          <t xml:space="preserve">10048771    </t>
+          <t xml:space="preserve">10048460    </t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="U371">
@@ -30296,12 +30296,12 @@
     <row r="435" ht="15.6" customHeight="0">
       <c s="15" t="inlineStr" r="A435">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 02</t>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="B435">
         <is>
-          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
         </is>
       </c>
       <c s="17" t="inlineStr" r="D435">
@@ -30344,18 +30344,18 @@
       </c>
       <c s="16" t="inlineStr" r="O435">
         <is>
-          <t xml:space="preserve">Tempo livre.</t>
+          <t xml:space="preserve">falta de demanda</t>
         </is>
       </c>
       <c s="16" t="str" r="P435"/>
       <c s="16" t="inlineStr" r="R435">
         <is>
-          <t xml:space="preserve">27757a20-c808-11f1-b1c6-f2050a003223</t>
+          <t xml:space="preserve">0aabc980-c808-11f1-987a-f2050a003223</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="S435">
         <is>
-          <t xml:space="preserve">10049342    </t>
+          <t xml:space="preserve">10048447    </t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="U435">
@@ -30368,12 +30368,12 @@
     <row r="436" ht="15.55" customHeight="0">
       <c s="19" t="inlineStr" r="A436">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 05</t>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="B436">
         <is>
-          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
         </is>
       </c>
       <c s="21" t="inlineStr" r="D436">
@@ -30416,18 +30416,18 @@
       </c>
       <c s="20" t="inlineStr" r="O436">
         <is>
-          <t xml:space="preserve">falta de demanda</t>
+          <t xml:space="preserve">Tempo livre.</t>
         </is>
       </c>
       <c s="20" t="str" r="P436"/>
       <c s="20" t="inlineStr" r="R436">
         <is>
-          <t xml:space="preserve">0aabc980-c808-11f1-987a-f2050a003223</t>
+          <t xml:space="preserve">27757a20-c808-11f1-b1c6-f2050a003223</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="S436">
         <is>
-          <t xml:space="preserve">10048447    </t>
+          <t xml:space="preserve">10049342    </t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="U436">
@@ -30440,10 +30440,14 @@
     <row r="437" ht="15.6" customHeight="0">
       <c s="15" t="inlineStr" r="A437">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 03</t>
-        </is>
-      </c>
-      <c s="16" t="str" r="B437"/>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B437">
+        <is>
+          <t xml:space="preserve">TR04-CARRO DE ENTRADA</t>
+        </is>
+      </c>
       <c s="17" t="inlineStr" r="D437">
         <is>
           <t xml:space="preserve">TURNO B</t>
@@ -30479,7 +30483,7 @@
       <c s="16" t="str" r="M437"/>
       <c s="16" t="inlineStr" r="N437">
         <is>
-          <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
+          <t xml:space="preserve">FALTA DEMANDA</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="O437">
@@ -30490,10 +30494,14 @@
       <c s="16" t="str" r="P437"/>
       <c s="16" t="inlineStr" r="R437">
         <is>
-          <t xml:space="preserve">735a0910-c808-11f1-ad2c-f2050a003223</t>
-        </is>
-      </c>
-      <c s="16" t="str" r="S437"/>
+          <t xml:space="preserve">73727310-c808-11f1-9a96-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S437">
+        <is>
+          <t xml:space="preserve">10049635    </t>
+        </is>
+      </c>
       <c s="16" t="inlineStr" r="U437">
         <is>
           <t xml:space="preserve">Sim</t>
@@ -30504,14 +30512,10 @@
     <row r="438" ht="15.6" customHeight="0">
       <c s="19" t="inlineStr" r="A438">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 04</t>
-        </is>
-      </c>
-      <c s="20" t="inlineStr" r="B438">
-        <is>
-          <t xml:space="preserve">TR04-CARRO DE ENTRADA</t>
-        </is>
-      </c>
+          <t xml:space="preserve">TRANSVERSAL 03</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B438"/>
       <c s="21" t="inlineStr" r="D438">
         <is>
           <t xml:space="preserve">TURNO B</t>
@@ -30547,7 +30551,7 @@
       <c s="20" t="str" r="M438"/>
       <c s="20" t="inlineStr" r="N438">
         <is>
-          <t xml:space="preserve">FALTA DEMANDA</t>
+          <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="O438">
@@ -30558,14 +30562,10 @@
       <c s="20" t="str" r="P438"/>
       <c s="20" t="inlineStr" r="R438">
         <is>
-          <t xml:space="preserve">73727310-c808-11f1-9a96-f2050a003223</t>
-        </is>
-      </c>
-      <c s="20" t="inlineStr" r="S438">
-        <is>
-          <t xml:space="preserve">10049635    </t>
-        </is>
-      </c>
+          <t xml:space="preserve">735a0910-c808-11f1-ad2c-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="S438"/>
       <c s="20" t="inlineStr" r="U438">
         <is>
           <t xml:space="preserve">Sim</t>
@@ -33145,10 +33145,14 @@
     <row r="475" ht="15.6" customHeight="0">
       <c s="15" t="inlineStr" r="A475">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 02</t>
-        </is>
-      </c>
-      <c s="16" t="str" r="B475"/>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B475">
+        <is>
+          <t xml:space="preserve">TR05-CARRO DE ENTRADA</t>
+        </is>
+      </c>
       <c s="17" t="inlineStr" r="D475">
         <is>
           <t xml:space="preserve">TURNO A</t>
@@ -33158,11 +33162,11 @@
         <v>46310.5659722222</v>
       </c>
       <c s="18" r="G475">
-        <v>46310.5736111111</v>
+        <v>46310.5763888889</v>
       </c>
       <c s="17" t="inlineStr" r="H475">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c s="17" t="str" r="I475"/>
@@ -33189,18 +33193,18 @@
       </c>
       <c s="16" t="inlineStr" r="O475">
         <is>
-          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 11 minutos</t>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
         </is>
       </c>
       <c s="16" t="str" r="P475"/>
       <c s="16" t="inlineStr" r="R475">
         <is>
-          <t xml:space="preserve">76f72ef0-c8b6-11f1-c9bc-f2050a003223</t>
+          <t xml:space="preserve">64c87d60-c8b6-11f1-8443-f2050a003223</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="S475">
         <is>
-          <t xml:space="preserve">10049344    </t>
+          <t xml:space="preserve">10049656    </t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="U475">
@@ -33213,14 +33217,10 @@
     <row r="476" ht="15.55" customHeight="0">
       <c s="19" t="inlineStr" r="A476">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 05</t>
-        </is>
-      </c>
-      <c s="20" t="inlineStr" r="B476">
-        <is>
-          <t xml:space="preserve">TR05-CARRO DE ENTRADA</t>
-        </is>
-      </c>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B476"/>
       <c s="21" t="inlineStr" r="D476">
         <is>
           <t xml:space="preserve">TURNO A</t>
@@ -33230,11 +33230,11 @@
         <v>46310.5659722222</v>
       </c>
       <c s="22" r="G476">
-        <v>46310.5763888889</v>
+        <v>46310.5736111111</v>
       </c>
       <c s="21" t="inlineStr" r="H476">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c s="21" t="str" r="I476"/>
@@ -33261,18 +33261,18 @@
       </c>
       <c s="20" t="inlineStr" r="O476">
         <is>
-          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 11 minutos</t>
         </is>
       </c>
       <c s="20" t="str" r="P476"/>
       <c s="20" t="inlineStr" r="R476">
         <is>
-          <t xml:space="preserve">64c87d60-c8b6-11f1-8443-f2050a003223</t>
+          <t xml:space="preserve">76f72ef0-c8b6-11f1-c9bc-f2050a003223</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="S476">
         <is>
-          <t xml:space="preserve">10049656    </t>
+          <t xml:space="preserve">10049344    </t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="U476">
@@ -34001,12 +34001,12 @@
     <row r="487" ht="15.6" customHeight="0">
       <c s="15" t="inlineStr" r="A487">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 05</t>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="B487">
         <is>
-          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
         </is>
       </c>
       <c s="17" t="inlineStr" r="D487">
@@ -34049,18 +34049,18 @@
       </c>
       <c s="16" t="inlineStr" r="O487">
         <is>
-          <t xml:space="preserve">falta de demanda</t>
+          <t xml:space="preserve">Tempo livre.</t>
         </is>
       </c>
       <c s="16" t="str" r="P487"/>
       <c s="16" t="inlineStr" r="R487">
         <is>
-          <t xml:space="preserve">7e9605c0-c94a-11f1-bd8b-f2050a003223</t>
+          <t xml:space="preserve">50c39080-c94b-11f1-b296-f2050a003223</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="S487">
         <is>
-          <t xml:space="preserve">10049658    </t>
+          <t xml:space="preserve">10049747    </t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="U487">
@@ -34073,12 +34073,12 @@
     <row r="488" ht="15.55" customHeight="0">
       <c s="19" t="inlineStr" r="A488">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 02</t>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="B488">
         <is>
-          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
         </is>
       </c>
       <c s="21" t="inlineStr" r="D488">
@@ -34121,18 +34121,18 @@
       </c>
       <c s="20" t="inlineStr" r="O488">
         <is>
-          <t xml:space="preserve">Tempo livre.</t>
+          <t xml:space="preserve">falta de demanda</t>
         </is>
       </c>
       <c s="20" t="str" r="P488"/>
       <c s="20" t="inlineStr" r="R488">
         <is>
-          <t xml:space="preserve">50c39080-c94b-11f1-b296-f2050a003223</t>
+          <t xml:space="preserve">7e9605c0-c94a-11f1-bd8b-f2050a003223</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="S488">
         <is>
-          <t xml:space="preserve">10049747    </t>
+          <t xml:space="preserve">10049658    </t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="U488">
@@ -34353,12 +34353,12 @@
     <row r="492" ht="15.6" customHeight="0">
       <c s="19" t="inlineStr" r="A492">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 05</t>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="B492">
         <is>
-          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
         </is>
       </c>
       <c s="21" t="inlineStr" r="D492">
@@ -34370,11 +34370,11 @@
         <v>46311.2916666667</v>
       </c>
       <c s="22" r="G492">
-        <v>46311.2986111111</v>
+        <v>46311.3097222222</v>
       </c>
       <c s="21" t="inlineStr" r="H492">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c s="21" t="str" r="I492"/>
@@ -34401,18 +34401,18 @@
       </c>
       <c s="20" t="inlineStr" r="O492">
         <is>
-          <t xml:space="preserve">dds</t>
+          <t xml:space="preserve">dds e assinatura dos documentos</t>
         </is>
       </c>
       <c s="20" t="str" r="P492"/>
       <c s="20" t="inlineStr" r="R492">
         <is>
-          <t xml:space="preserve">6cb0ce60-c94c-11f1-bf37-f2050a003223</t>
+          <t xml:space="preserve">158af8d0-c94d-11f1-c8f5-f2050a003223</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="S492">
         <is>
-          <t xml:space="preserve">10049658    </t>
+          <t xml:space="preserve">10049812    </t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="U492">
@@ -34425,12 +34425,12 @@
     <row r="493" ht="15.55" customHeight="0">
       <c s="15" t="inlineStr" r="A493">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 01</t>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="B493">
         <is>
-          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
         </is>
       </c>
       <c s="17" t="inlineStr" r="D493">
@@ -34442,11 +34442,11 @@
         <v>46311.2916666667</v>
       </c>
       <c s="18" r="G493">
-        <v>46311.3097222222</v>
+        <v>46311.2986111111</v>
       </c>
       <c s="17" t="inlineStr" r="H493">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c s="17" t="str" r="I493"/>
@@ -34473,18 +34473,18 @@
       </c>
       <c s="16" t="inlineStr" r="O493">
         <is>
-          <t xml:space="preserve">dds e assinatura dos documentos</t>
+          <t xml:space="preserve">dds</t>
         </is>
       </c>
       <c s="16" t="str" r="P493"/>
       <c s="16" t="inlineStr" r="R493">
         <is>
-          <t xml:space="preserve">158af8d0-c94d-11f1-c8f5-f2050a003223</t>
+          <t xml:space="preserve">6cb0ce60-c94c-11f1-bf37-f2050a003223</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="S493">
         <is>
-          <t xml:space="preserve">10049812    </t>
+          <t xml:space="preserve">10049658    </t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="U493">
@@ -36690,12 +36690,12 @@
     <row r="525" ht="15.55" customHeight="0">
       <c s="15" t="inlineStr" r="A525">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 02</t>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="B525">
         <is>
-          <t xml:space="preserve">TR02-MESA TRANSPORTADORA</t>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
         </is>
       </c>
       <c s="17" t="inlineStr" r="D525">
@@ -36707,11 +36707,11 @@
         <v>46311.5208333333</v>
       </c>
       <c s="18" r="G525">
-        <v>46311.5222222222</v>
+        <v>46311.5243055556</v>
       </c>
       <c s="17" t="inlineStr" r="H525">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c s="17" t="str" r="I525"/>
@@ -36733,23 +36733,23 @@
       <c s="16" t="str" r="M525"/>
       <c s="16" t="inlineStr" r="N525">
         <is>
-          <t xml:space="preserve">RETIRADA DE PNC</t>
+          <t xml:space="preserve">AJUSTE NO ROLO ALIMENTADOR</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="O525">
         <is>
-          <t xml:space="preserve">Retirada de pnc</t>
+          <t xml:space="preserve">ajuste do rolo alimentado e da chapa</t>
         </is>
       </c>
       <c s="16" t="str" r="P525"/>
       <c s="16" t="inlineStr" r="R525">
         <is>
-          <t xml:space="preserve">c5628c90-c976-11f1-ae4e-f2050a003223</t>
+          <t xml:space="preserve">89caf6e0-c976-11f1-a8d7-f2050a003223</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="S525">
         <is>
-          <t xml:space="preserve">10049747    </t>
+          <t xml:space="preserve">10049818    </t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="U525">
@@ -36762,12 +36762,12 @@
     <row r="526" ht="15.6" customHeight="0">
       <c s="19" t="inlineStr" r="A526">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 01</t>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="B526">
         <is>
-          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+          <t xml:space="preserve">TR02-MESA TRANSPORTADORA</t>
         </is>
       </c>
       <c s="21" t="inlineStr" r="D526">
@@ -36779,11 +36779,11 @@
         <v>46311.5208333333</v>
       </c>
       <c s="22" r="G526">
-        <v>46311.5243055556</v>
+        <v>46311.5222222222</v>
       </c>
       <c s="21" t="inlineStr" r="H526">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c s="21" t="str" r="I526"/>
@@ -36805,23 +36805,23 @@
       <c s="20" t="str" r="M526"/>
       <c s="20" t="inlineStr" r="N526">
         <is>
-          <t xml:space="preserve">AJUSTE NO ROLO ALIMENTADOR</t>
+          <t xml:space="preserve">RETIRADA DE PNC</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="O526">
         <is>
-          <t xml:space="preserve">ajuste do rolo alimentado e da chapa</t>
+          <t xml:space="preserve">Retirada de pnc</t>
         </is>
       </c>
       <c s="20" t="str" r="P526"/>
       <c s="20" t="inlineStr" r="R526">
         <is>
-          <t xml:space="preserve">89caf6e0-c976-11f1-a8d7-f2050a003223</t>
+          <t xml:space="preserve">c5628c90-c976-11f1-ae4e-f2050a003223</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="S526">
         <is>
-          <t xml:space="preserve">10049818    </t>
+          <t xml:space="preserve">10049747    </t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="U526">
@@ -39086,12 +39086,12 @@
     <row r="559" ht="15.6" customHeight="0">
       <c s="15" t="inlineStr" r="A559">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 05</t>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="B559">
         <is>
-          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
         </is>
       </c>
       <c s="17" t="inlineStr" r="D559">
@@ -39134,18 +39134,18 @@
       </c>
       <c s="16" t="inlineStr" r="O559">
         <is>
-          <t xml:space="preserve">dds</t>
+          <t xml:space="preserve">DDS.</t>
         </is>
       </c>
       <c s="16" t="str" r="P559"/>
       <c s="16" t="inlineStr" r="R559">
         <is>
-          <t xml:space="preserve">ce0da880-cba5-11f1-b5fe-f2050a003223</t>
+          <t xml:space="preserve">8446cdd0-cbc3-11f1-b78f-f2050a003223</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="S559">
         <is>
-          <t xml:space="preserve">10049659    </t>
+          <t xml:space="preserve">10049746    </t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="U559">
@@ -39158,12 +39158,12 @@
     <row r="560" ht="15.55" customHeight="0">
       <c s="19" t="inlineStr" r="A560">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 02</t>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="B560">
         <is>
-          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
         </is>
       </c>
       <c s="21" t="inlineStr" r="D560">
@@ -39175,11 +39175,11 @@
         <v>46314.2916666667</v>
       </c>
       <c s="22" r="G560">
-        <v>46314.2986111111</v>
+        <v>46314.3020833333</v>
       </c>
       <c s="21" t="inlineStr" r="H560">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c s="21" t="str" r="I560"/>
@@ -39206,18 +39206,18 @@
       </c>
       <c s="20" t="inlineStr" r="O560">
         <is>
-          <t xml:space="preserve">DDS.</t>
+          <t xml:space="preserve">dds e assinatura dos documentos</t>
         </is>
       </c>
       <c s="20" t="str" r="P560"/>
       <c s="20" t="inlineStr" r="R560">
         <is>
-          <t xml:space="preserve">8446cdd0-cbc3-11f1-b78f-f2050a003223</t>
+          <t xml:space="preserve">8a194e80-cba6-11f1-b75b-f2050a003223</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="S560">
         <is>
-          <t xml:space="preserve">10049746    </t>
+          <t xml:space="preserve">10050212    </t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="U560">
@@ -39230,12 +39230,12 @@
     <row r="561" ht="15.6" customHeight="0">
       <c s="15" t="inlineStr" r="A561">
         <is>
-          <t xml:space="preserve">TRANSVERSAL 01</t>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="B561">
         <is>
-          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
         </is>
       </c>
       <c s="17" t="inlineStr" r="D561">
@@ -39247,11 +39247,11 @@
         <v>46314.2916666667</v>
       </c>
       <c s="18" r="G561">
-        <v>46314.3020833333</v>
+        <v>46314.2986111111</v>
       </c>
       <c s="17" t="inlineStr" r="H561">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c s="17" t="str" r="I561"/>
@@ -39278,18 +39278,18 @@
       </c>
       <c s="16" t="inlineStr" r="O561">
         <is>
-          <t xml:space="preserve">dds e assinatura dos documentos</t>
+          <t xml:space="preserve">dds</t>
         </is>
       </c>
       <c s="16" t="str" r="P561"/>
       <c s="16" t="inlineStr" r="R561">
         <is>
-          <t xml:space="preserve">8a194e80-cba6-11f1-b75b-f2050a003223</t>
+          <t xml:space="preserve">ce0da880-cba5-11f1-b5fe-f2050a003223</t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="S561">
         <is>
-          <t xml:space="preserve">10050212    </t>
+          <t xml:space="preserve">10049659    </t>
         </is>
       </c>
       <c s="16" t="inlineStr" r="U561">
@@ -42964,11 +42964,11 @@
         <v>46314.6979166667</v>
       </c>
       <c s="18" r="G613">
-        <v>46315.3236009259</v>
+        <v>46315.2909722222</v>
       </c>
       <c s="17" t="inlineStr" r="H613">
         <is>
-          <t xml:space="preserve">901</t>
+          <t xml:space="preserve">854</t>
         </is>
       </c>
       <c s="17" t="str" r="I613"/>
@@ -43148,79 +43148,6056 @@
       </c>
       <c s="5" t="str" r="V615"/>
     </row>
-    <row r="616" ht="15.55" customHeight="0">
-      <c s="23" t="inlineStr" r="A616">
+    <row r="616" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A616">
         <is>
           <t xml:space="preserve">TRANSVERSAL 04</t>
         </is>
       </c>
-      <c s="24" t="str" r="B616"/>
-      <c s="10" t="str" r="C616"/>
-      <c s="25" t="inlineStr" r="D616">
+      <c s="20" t="str" r="B616"/>
+      <c s="21" t="inlineStr" r="D616">
         <is>
           <t xml:space="preserve">TURNO B</t>
         </is>
       </c>
-      <c s="26" r="E616">
+      <c s="22" r="E616">
         <v>46314.7013888889</v>
       </c>
-      <c s="10" t="str" r="F616"/>
-      <c s="26" r="G616">
+      <c s="22" r="G616">
         <v>46315.2840277778</v>
       </c>
-      <c s="25" t="inlineStr" r="H616">
+      <c s="21" t="inlineStr" r="H616">
         <is>
           <t xml:space="preserve">839</t>
         </is>
       </c>
-      <c s="25" t="str" r="I616"/>
-      <c s="25" t="inlineStr" r="J616">
-        <is>
-          <t xml:space="preserve">X</t>
-        </is>
-      </c>
-      <c s="24" t="inlineStr" r="K616">
+      <c s="21" t="str" r="I616"/>
+      <c s="21" t="inlineStr" r="J616">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K616">
         <is>
           <t xml:space="preserve">Tempo Livre</t>
         </is>
       </c>
-      <c s="24" t="inlineStr" r="L616">
+      <c s="20" t="inlineStr" r="L616">
         <is>
           <t xml:space="preserve">Tempo Livre</t>
         </is>
       </c>
-      <c s="24" t="str" r="M616"/>
-      <c s="24" t="inlineStr" r="N616">
+      <c s="20" t="str" r="M616"/>
+      <c s="20" t="inlineStr" r="N616">
         <is>
           <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
         </is>
       </c>
-      <c s="24" t="inlineStr" r="O616">
+      <c s="20" t="inlineStr" r="O616">
         <is>
           <t xml:space="preserve">Parada registrada automaticamente pelo sistema</t>
         </is>
       </c>
-      <c s="24" t="str" r="P616"/>
-      <c s="10" t="str" r="Q616"/>
-      <c s="24" t="inlineStr" r="R616">
+      <c s="20" t="str" r="P616"/>
+      <c s="20" t="inlineStr" r="R616">
         <is>
           <t xml:space="preserve">45583cc0-cbf6-11f1-850f-f2050a003223</t>
         </is>
       </c>
-      <c s="24" t="inlineStr" r="S616">
+      <c s="20" t="inlineStr" r="S616">
         <is>
           <t xml:space="preserve">10050415    </t>
         </is>
       </c>
-      <c s="10" t="str" r="T616"/>
-      <c s="24" t="inlineStr" r="U616">
-        <is>
-          <t xml:space="preserve">Sim</t>
-        </is>
-      </c>
-      <c s="11" t="str" r="V616"/>
-    </row>
-    <row r="617" ht="0.05" customHeight="1"/>
+      <c s="20" t="inlineStr" r="U616">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V616"/>
+    </row>
+    <row r="617" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A617">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B617">
+        <is>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D617">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E617">
+        <v>46315.2847222222</v>
+      </c>
+      <c s="18" r="G617">
+        <v>46315.2916666667</v>
+      </c>
+      <c s="17" t="inlineStr" r="H617">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I617"/>
+      <c s="17" t="inlineStr" r="J617">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K617">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L617">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M617"/>
+      <c s="16" t="inlineStr" r="N617">
+        <is>
+          <t xml:space="preserve">DDS</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O617">
+        <is>
+          <t xml:space="preserve">DDS</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P617"/>
+      <c s="16" t="inlineStr" r="R617">
+        <is>
+          <t xml:space="preserve">cd7180c0-cc6f-11f1-8c3e-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S617">
+        <is>
+          <t xml:space="preserve">10050415    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U617">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V617"/>
+    </row>
+    <row r="618" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A618">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B618">
+        <is>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D618">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E618">
+        <v>46315.2916666667</v>
+      </c>
+      <c s="22" r="G618">
+        <v>46315.2986111111</v>
+      </c>
+      <c s="21" t="inlineStr" r="H618">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I618"/>
+      <c s="21" t="inlineStr" r="J618">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K618">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L618">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M618"/>
+      <c s="20" t="inlineStr" r="N618">
+        <is>
+          <t xml:space="preserve">DDS</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O618">
+        <is>
+          <t xml:space="preserve">dds</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P618"/>
+      <c s="20" t="inlineStr" r="R618">
+        <is>
+          <t xml:space="preserve">c8f3dc50-cc79-11f1-8026-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S618">
+        <is>
+          <t xml:space="preserve">10049761    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U618">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V618"/>
+    </row>
+    <row r="619" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A619">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B619">
+        <is>
+          <t xml:space="preserve">TR01-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D619">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E619">
+        <v>46315.2916666667</v>
+      </c>
+      <c s="18" r="G619">
+        <v>46315.3069444444</v>
+      </c>
+      <c s="17" t="inlineStr" r="H619">
+        <is>
+          <t xml:space="preserve">22</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I619"/>
+      <c s="17" t="inlineStr" r="J619">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K619">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L619">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M619"/>
+      <c s="16" t="inlineStr" r="N619">
+        <is>
+          <t xml:space="preserve">DDS</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O619">
+        <is>
+          <t xml:space="preserve">DDS</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P619"/>
+      <c s="16" t="inlineStr" r="R619">
+        <is>
+          <t xml:space="preserve">1c2cfd71-cc70-11f1-98cc-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S619">
+        <is>
+          <t xml:space="preserve">10050024    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U619">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V619"/>
+    </row>
+    <row r="620" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A620">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B620">
+        <is>
+          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D620">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E620">
+        <v>46315.2916666667</v>
+      </c>
+      <c s="22" r="G620">
+        <v>46315.2986111111</v>
+      </c>
+      <c s="21" t="inlineStr" r="H620">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I620"/>
+      <c s="21" t="inlineStr" r="J620">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K620">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L620">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M620"/>
+      <c s="20" t="inlineStr" r="N620">
+        <is>
+          <t xml:space="preserve">DDS</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O620">
+        <is>
+          <t xml:space="preserve">DDS.</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P620"/>
+      <c s="20" t="inlineStr" r="R620">
+        <is>
+          <t xml:space="preserve">e130a0e0-cc70-11f1-c326-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S620">
+        <is>
+          <t xml:space="preserve">10049748    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U620">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V620"/>
+    </row>
+    <row r="621" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A621">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B621">
+        <is>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D621">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E621">
+        <v>46315.2923611111</v>
+      </c>
+      <c s="18" r="G621">
+        <v>46315.3027777778</v>
+      </c>
+      <c s="17" t="inlineStr" r="H621">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I621"/>
+      <c s="17" t="inlineStr" r="J621">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K621">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L621">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M621"/>
+      <c s="16" t="inlineStr" r="N621">
+        <is>
+          <t xml:space="preserve">ASSINATURA DE DOCUMENTOS</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O621">
+        <is>
+          <t xml:space="preserve">Assinatura de documentos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P621"/>
+      <c s="16" t="inlineStr" r="R621">
+        <is>
+          <t xml:space="preserve">e9e8a490-cc6f-11f1-b8b0-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S621">
+        <is>
+          <t xml:space="preserve">10050415    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U621">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V621"/>
+    </row>
+    <row r="622" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A622">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B622">
+        <is>
+          <t xml:space="preserve">TR01-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D622">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E622">
+        <v>46315.3076388889</v>
+      </c>
+      <c s="22" r="G622">
+        <v>46315.3173611111</v>
+      </c>
+      <c s="21" t="inlineStr" r="H622">
+        <is>
+          <t xml:space="preserve">14</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I622"/>
+      <c s="21" t="inlineStr" r="J622">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K622">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L622">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M622"/>
+      <c s="20" t="inlineStr" r="N622">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O622">
+        <is>
+          <t xml:space="preserve">passagem de chapa amassada</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P622"/>
+      <c s="20" t="inlineStr" r="R622">
+        <is>
+          <t xml:space="preserve">46eb1150-cc70-11f1-9349-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S622">
+        <is>
+          <t xml:space="preserve">10050024    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U622">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V622"/>
+    </row>
+    <row r="623" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A623">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B623">
+        <is>
+          <t xml:space="preserve">TR04-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D623">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E623">
+        <v>46315.3090277778</v>
+      </c>
+      <c s="18" r="G623">
+        <v>46315.3131944444</v>
+      </c>
+      <c s="17" t="inlineStr" r="H623">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I623"/>
+      <c s="17" t="inlineStr" r="J623">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K623">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L623">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M623"/>
+      <c s="16" t="inlineStr" r="N623">
+        <is>
+          <t xml:space="preserve">CINTAGEM DE MATERIAL</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O623">
+        <is>
+          <t xml:space="preserve">cintagem e retirada de material</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P623"/>
+      <c s="16" t="inlineStr" r="R623">
+        <is>
+          <t xml:space="preserve">9957fd40-cc70-11f1-c833-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S623">
+        <is>
+          <t xml:space="preserve">10050415    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U623">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V623"/>
+    </row>
+    <row r="624" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A624">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B624"/>
+      <c s="21" t="inlineStr" r="D624">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E624">
+        <v>46315.3180555556</v>
+      </c>
+      <c s="22" r="G624">
+        <v>46315.3222222222</v>
+      </c>
+      <c s="21" t="inlineStr" r="H624">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I624"/>
+      <c s="21" t="inlineStr" r="J624">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K624">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L624">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M624"/>
+      <c s="20" t="inlineStr" r="N624">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O624">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 6 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P624"/>
+      <c s="20" t="inlineStr" r="R624">
+        <is>
+          <t xml:space="preserve">72005b00-cc72-11f1-c27a-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S624">
+        <is>
+          <t xml:space="preserve">10050024    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U624">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V624"/>
+    </row>
+    <row r="625" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A625">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B625">
+        <is>
+          <t xml:space="preserve">TR04-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D625">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E625">
+        <v>46315.3215277778</v>
+      </c>
+      <c s="18" r="G625">
+        <v>46315.3243055556</v>
+      </c>
+      <c s="17" t="inlineStr" r="H625">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I625"/>
+      <c s="17" t="inlineStr" r="J625">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K625">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L625">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M625"/>
+      <c s="16" t="inlineStr" r="N625">
+        <is>
+          <t xml:space="preserve">CINTAGEM DE MATERIAL</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O625">
+        <is>
+          <t xml:space="preserve">cintagem e retirada de material</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P625"/>
+      <c s="16" t="inlineStr" r="R625">
+        <is>
+          <t xml:space="preserve">17b96f50-cc73-11f1-9ef3-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S625">
+        <is>
+          <t xml:space="preserve">10050415    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U625">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V625"/>
+    </row>
+    <row r="626" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A626">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B626">
+        <is>
+          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D626">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E626">
+        <v>46315.3305555556</v>
+      </c>
+      <c s="22" r="G626">
+        <v>46315.3493055556</v>
+      </c>
+      <c s="21" t="inlineStr" r="H626">
+        <is>
+          <t xml:space="preserve">27</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I626"/>
+      <c s="21" t="inlineStr" r="J626">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K626">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L626">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M626"/>
+      <c s="20" t="inlineStr" r="N626">
+        <is>
+          <t xml:space="preserve">SETUP COMPLETO</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O626">
+        <is>
+          <t xml:space="preserve">Regulagem da endireitadeira e guilhotina.</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P626"/>
+      <c s="20" t="inlineStr" r="R626">
+        <is>
+          <t xml:space="preserve">d0f062c1-cc79-11f1-9eec-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S626">
+        <is>
+          <t xml:space="preserve">10049748    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U626">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V626"/>
+    </row>
+    <row r="627" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A627">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B627">
+        <is>
+          <t xml:space="preserve">TR04-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D627">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E627">
+        <v>46315.3326388889</v>
+      </c>
+      <c s="18" r="G627">
+        <v>46315.3347222222</v>
+      </c>
+      <c s="17" t="inlineStr" r="H627">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I627"/>
+      <c s="17" t="inlineStr" r="J627">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K627">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L627">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M627"/>
+      <c s="16" t="inlineStr" r="N627">
+        <is>
+          <t xml:space="preserve">CINTAGEM DE MATERIAL</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O627">
+        <is>
+          <t xml:space="preserve">cintagem e retirada de material</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P627"/>
+      <c s="16" t="inlineStr" r="R627">
+        <is>
+          <t xml:space="preserve">509d92e0-cc75-11f1-acfb-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S627">
+        <is>
+          <t xml:space="preserve">10050415    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U627">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V627"/>
+    </row>
+    <row r="628" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A628">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B628"/>
+      <c s="21" t="inlineStr" r="D628">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E628">
+        <v>46315.3402777778</v>
+      </c>
+      <c s="22" r="G628">
+        <v>46315.3493055556</v>
+      </c>
+      <c s="21" t="inlineStr" r="H628">
+        <is>
+          <t xml:space="preserve">13</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I628"/>
+      <c s="21" t="inlineStr" r="J628">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K628">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L628">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M628"/>
+      <c s="20" t="inlineStr" r="N628">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O628">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 13 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P628"/>
+      <c s="20" t="inlineStr" r="R628">
+        <is>
+          <t xml:space="preserve">e70863d0-cc76-11f1-c6ac-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S628">
+        <is>
+          <t xml:space="preserve">10050415    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U628">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V628"/>
+    </row>
+    <row r="629" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A629">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B629">
+        <is>
+          <t xml:space="preserve">TR04-ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D629">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E629">
+        <v>46315.35</v>
+      </c>
+      <c s="18" r="G629">
+        <v>46315.35625</v>
+      </c>
+      <c s="17" t="inlineStr" r="H629">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I629"/>
+      <c s="17" t="inlineStr" r="J629">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K629">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L629">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M629"/>
+      <c s="16" t="inlineStr" r="N629">
+        <is>
+          <t xml:space="preserve">SETUP COMPLETO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O629">
+        <is>
+          <t xml:space="preserve">trocar 0.95x1.000 para 1.20x1.000 e fazer regulagem</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P629"/>
+      <c s="16" t="inlineStr" r="R629">
+        <is>
+          <t xml:space="preserve">c7979d20-cc78-11f1-862e-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S629">
+        <is>
+          <t xml:space="preserve">10050415    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U629">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V629"/>
+    </row>
+    <row r="630" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A630">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B630">
+        <is>
+          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D630">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E630">
+        <v>46315.3625</v>
+      </c>
+      <c s="22" r="G630">
+        <v>46315.3680555556</v>
+      </c>
+      <c s="21" t="inlineStr" r="H630">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I630"/>
+      <c s="21" t="inlineStr" r="J630">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K630">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L630">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M630"/>
+      <c s="20" t="inlineStr" r="N630">
+        <is>
+          <t xml:space="preserve">QUALIDADE DA MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O630">
+        <is>
+          <t xml:space="preserve">Material 2.65mm 2295 x1200  UD 2003980709 com ondulação o material foi liberado para produzir.</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P630"/>
+      <c s="20" t="inlineStr" r="R630">
+        <is>
+          <t xml:space="preserve">959cf010-cc7b-11f1-bb34-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S630">
+        <is>
+          <t xml:space="preserve">10050106    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U630">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V630"/>
+    </row>
+    <row r="631" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A631">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B631">
+        <is>
+          <t xml:space="preserve">TR04-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D631">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E631">
+        <v>46315.3631944444</v>
+      </c>
+      <c s="18" r="G631">
+        <v>46315.3659722222</v>
+      </c>
+      <c s="17" t="inlineStr" r="H631">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I631"/>
+      <c s="17" t="inlineStr" r="J631">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K631">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L631">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M631"/>
+      <c s="16" t="inlineStr" r="N631">
+        <is>
+          <t xml:space="preserve">CINTAGEM DE MATERIAL</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O631">
+        <is>
+          <t xml:space="preserve">cintagem e retirada de material</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P631"/>
+      <c s="16" t="inlineStr" r="R631">
+        <is>
+          <t xml:space="preserve">76f13900-cc7b-11f1-b186-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S631">
+        <is>
+          <t xml:space="preserve">10050497    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U631">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V631"/>
+    </row>
+    <row r="632" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A632">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B632">
+        <is>
+          <t xml:space="preserve">TR05-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D632">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E632">
+        <v>46315.3680555556</v>
+      </c>
+      <c s="22" r="G632">
+        <v>46315.3743055556</v>
+      </c>
+      <c s="21" t="inlineStr" r="H632">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I632"/>
+      <c s="21" t="inlineStr" r="J632">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K632">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L632">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M632"/>
+      <c s="20" t="inlineStr" r="N632">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O632">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 9 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P632"/>
+      <c s="20" t="inlineStr" r="R632">
+        <is>
+          <t xml:space="preserve">6849e400-cc7c-11f1-bb5f-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S632">
+        <is>
+          <t xml:space="preserve">10049761    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U632">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V632"/>
+    </row>
+    <row r="633" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A633">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B633">
+        <is>
+          <t xml:space="preserve">TR04-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D633">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E633">
+        <v>46315.3729166667</v>
+      </c>
+      <c s="18" r="G633">
+        <v>46315.375</v>
+      </c>
+      <c s="17" t="inlineStr" r="H633">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I633"/>
+      <c s="17" t="inlineStr" r="J633">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K633">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L633">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M633"/>
+      <c s="16" t="inlineStr" r="N633">
+        <is>
+          <t xml:space="preserve">CINTAGEM DE MATERIAL</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O633">
+        <is>
+          <t xml:space="preserve">cintagem e retirada de material</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P633"/>
+      <c s="16" t="inlineStr" r="R633">
+        <is>
+          <t xml:space="preserve">5cf1ba00-cc7d-11f1-a110-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S633">
+        <is>
+          <t xml:space="preserve">10050497    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U633">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V633"/>
+    </row>
+    <row r="634" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A634">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B634">
+        <is>
+          <t xml:space="preserve">TR05-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D634">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E634">
+        <v>46315.375</v>
+      </c>
+      <c s="22" r="G634">
+        <v>46315.3888888889</v>
+      </c>
+      <c s="21" t="inlineStr" r="H634">
+        <is>
+          <t xml:space="preserve">20</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I634"/>
+      <c s="21" t="inlineStr" r="J634">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K634">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L634">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M634"/>
+      <c s="20" t="inlineStr" r="N634">
+        <is>
+          <t xml:space="preserve">AGUARDANDO INSPEÇÃO DE  QUALIDADE</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O634">
+        <is>
+          <t xml:space="preserve">aguardando inspeção da matéria prima de UD: 2004001039 oxidação galvânica após a inspeção  foi autorizado passar 973 kg de pnc o restante como bom</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P634"/>
+      <c s="20" t="inlineStr" r="R634">
+        <is>
+          <t xml:space="preserve">c9f73e60-cc80-11f1-b6c4-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S634">
+        <is>
+          <t xml:space="preserve">10049761    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U634">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V634"/>
+    </row>
+    <row r="635" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A635">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B635">
+        <is>
+          <t xml:space="preserve">TR04-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D635">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E635">
+        <v>46315.3875</v>
+      </c>
+      <c s="18" r="G635">
+        <v>46315.3902777778</v>
+      </c>
+      <c s="17" t="inlineStr" r="H635">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I635"/>
+      <c s="17" t="inlineStr" r="J635">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K635">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L635">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M635"/>
+      <c s="16" t="inlineStr" r="N635">
+        <is>
+          <t xml:space="preserve">CINTAGEM DE MATERIAL</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O635">
+        <is>
+          <t xml:space="preserve">cintagem e retirada de material</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P635"/>
+      <c s="16" t="inlineStr" r="R635">
+        <is>
+          <t xml:space="preserve">4b5aad30-cc80-11f1-97c2-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S635">
+        <is>
+          <t xml:space="preserve">10050497    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U635">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V635"/>
+    </row>
+    <row r="636" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A636">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B636">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D636">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E636">
+        <v>46315.3965277778</v>
+      </c>
+      <c s="22" r="G636">
+        <v>46315.3986111111</v>
+      </c>
+      <c s="21" t="inlineStr" r="H636">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I636"/>
+      <c s="21" t="inlineStr" r="J636">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K636">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L636">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M636"/>
+      <c s="20" t="inlineStr" r="N636">
+        <is>
+          <t xml:space="preserve">AJUSTE DA MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O636">
+        <is>
+          <t xml:space="preserve">ajuste da chapa</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P636"/>
+      <c s="20" t="inlineStr" r="R636">
+        <is>
+          <t xml:space="preserve">27f9c090-cc82-11f1-b840-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S636">
+        <is>
+          <t xml:space="preserve">10050035    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U636">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V636"/>
+    </row>
+    <row r="637" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A637">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B637"/>
+      <c s="17" t="inlineStr" r="D637">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E637">
+        <v>46315.3986111111</v>
+      </c>
+      <c s="18" r="G637">
+        <v>46315.4090277778</v>
+      </c>
+      <c s="17" t="inlineStr" r="H637">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I637"/>
+      <c s="17" t="inlineStr" r="J637">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K637">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L637">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M637"/>
+      <c s="16" t="inlineStr" r="N637">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O637">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P637"/>
+      <c s="16" t="inlineStr" r="R637">
+        <is>
+          <t xml:space="preserve">9a2fba70-cc82-11f1-c12b-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S637">
+        <is>
+          <t xml:space="preserve">10050497    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U637">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V637"/>
+    </row>
+    <row r="638" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A638">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B638"/>
+      <c s="21" t="inlineStr" r="D638">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E638">
+        <v>46315.4034722222</v>
+      </c>
+      <c s="22" r="G638">
+        <v>46315.4138888889</v>
+      </c>
+      <c s="21" t="inlineStr" r="H638">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I638"/>
+      <c s="21" t="inlineStr" r="J638">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K638">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L638">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M638"/>
+      <c s="20" t="inlineStr" r="N638">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O638">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P638"/>
+      <c s="20" t="inlineStr" r="R638">
+        <is>
+          <t xml:space="preserve">9aaf2e30-cc83-11f1-92cc-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S638">
+        <is>
+          <t xml:space="preserve">10050035    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U638">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V638"/>
+    </row>
+    <row r="639" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A639">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B639">
+        <is>
+          <t xml:space="preserve">TR04-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D639">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E639">
+        <v>46315.4118055556</v>
+      </c>
+      <c s="18" r="G639">
+        <v>46315.41875</v>
+      </c>
+      <c s="17" t="inlineStr" r="H639">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I639"/>
+      <c s="17" t="inlineStr" r="J639">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K639">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L639">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M639"/>
+      <c s="16" t="inlineStr" r="N639">
+        <is>
+          <t xml:space="preserve">SETUP COMPLETO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O639">
+        <is>
+          <t xml:space="preserve">trocar 1.20x1.000 para 0.47x1000 e fazer regulagem</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P639"/>
+      <c s="16" t="inlineStr" r="R639">
+        <is>
+          <t xml:space="preserve">4ce74e60-cc85-11f1-be64-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S639">
+        <is>
+          <t xml:space="preserve">10050497    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U639">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V639"/>
+    </row>
+    <row r="640" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A640">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B640">
+        <is>
+          <t xml:space="preserve">TR01-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D640">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E640">
+        <v>46315.4145833333</v>
+      </c>
+      <c s="22" r="G640">
+        <v>46315.4229166667</v>
+      </c>
+      <c s="21" t="inlineStr" r="H640">
+        <is>
+          <t xml:space="preserve">12</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I640"/>
+      <c s="21" t="inlineStr" r="J640">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K640">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L640">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M640"/>
+      <c s="20" t="inlineStr" r="N640">
+        <is>
+          <t xml:space="preserve">TROCA DAS CASTANHAS DO MANDRIL</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O640">
+        <is>
+          <t xml:space="preserve">troca das castanhas</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P640"/>
+      <c s="20" t="inlineStr" r="R640">
+        <is>
+          <t xml:space="preserve">6e5a9f00-cc87-11f1-befa-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S640">
+        <is>
+          <t xml:space="preserve">10050035    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U640">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V640"/>
+    </row>
+    <row r="641" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A641">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B641">
+        <is>
+          <t xml:space="preserve">TR02-GUILHOTINA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D641">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E641">
+        <v>46315.4152777778</v>
+      </c>
+      <c s="18" r="G641">
+        <v>46315.4409722222</v>
+      </c>
+      <c s="17" t="inlineStr" r="H641">
+        <is>
+          <t xml:space="preserve">37</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I641"/>
+      <c s="17" t="inlineStr" r="J641">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K641">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L641">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M641"/>
+      <c s="16" t="inlineStr" r="N641">
+        <is>
+          <t xml:space="preserve">SETUP COMPLETO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O641">
+        <is>
+          <t xml:space="preserve">Setup completo, regulagem da guilhotina e endireitadeira e retirada das castanhas.</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P641"/>
+      <c s="16" t="inlineStr" r="R641">
+        <is>
+          <t xml:space="preserve">2d665e40-cc8b-11f1-a81b-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S641">
+        <is>
+          <t xml:space="preserve">10050107    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U641">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V641"/>
+    </row>
+    <row r="642" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A642">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B642">
+        <is>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D642">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E642">
+        <v>46315.4222222222</v>
+      </c>
+      <c s="22" r="G642">
+        <v>46315.425</v>
+      </c>
+      <c s="21" t="inlineStr" r="H642">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I642"/>
+      <c s="21" t="inlineStr" r="J642">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K642">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L642">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M642"/>
+      <c s="20" t="inlineStr" r="N642">
+        <is>
+          <t xml:space="preserve">TROCA DAS CASTANHAS DO MANDRIL</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O642">
+        <is>
+          <t xml:space="preserve">retirar castanhas do mandril</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P642"/>
+      <c s="20" t="inlineStr" r="R642">
+        <is>
+          <t xml:space="preserve">5b2d9040-cc87-11f1-b446-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S642">
+        <is>
+          <t xml:space="preserve">10050497    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U642">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V642"/>
+    </row>
+    <row r="643" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A643">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B643">
+        <is>
+          <t xml:space="preserve">TR04-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D643">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E643">
+        <v>46315.4319444444</v>
+      </c>
+      <c s="18" r="G643">
+        <v>46315.4340277778</v>
+      </c>
+      <c s="17" t="inlineStr" r="H643">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I643"/>
+      <c s="17" t="inlineStr" r="J643">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K643">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L643">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M643"/>
+      <c s="16" t="inlineStr" r="N643">
+        <is>
+          <t xml:space="preserve">RETIRADA DE PNC</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O643">
+        <is>
+          <t xml:space="preserve">retirar peças amassadas</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P643"/>
+      <c s="16" t="inlineStr" r="R643">
+        <is>
+          <t xml:space="preserve">5ecc7700-cc89-11f1-8f03-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S643">
+        <is>
+          <t xml:space="preserve">10050553    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U643">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V643"/>
+    </row>
+    <row r="644" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A644">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B644">
+        <is>
+          <t xml:space="preserve">TR04-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D644">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E644">
+        <v>46315.4458333333</v>
+      </c>
+      <c s="22" r="G644">
+        <v>46315.4486111111</v>
+      </c>
+      <c s="21" t="inlineStr" r="H644">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I644"/>
+      <c s="21" t="inlineStr" r="J644">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K644">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L644">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M644"/>
+      <c s="20" t="inlineStr" r="N644">
+        <is>
+          <t xml:space="preserve">CINTAGEM DE MATERIAL</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O644">
+        <is>
+          <t xml:space="preserve">cintagem e retirada de material</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P644"/>
+      <c s="20" t="inlineStr" r="R644">
+        <is>
+          <t xml:space="preserve">0b78f440-cc8c-11f1-b53f-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S644">
+        <is>
+          <t xml:space="preserve">10050553    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U644">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V644"/>
+    </row>
+    <row r="645" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A645">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B645">
+        <is>
+          <t xml:space="preserve">TR05-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D645">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E645">
+        <v>46315.4493055556</v>
+      </c>
+      <c s="18" r="G645">
+        <v>46315.4513888889</v>
+      </c>
+      <c s="17" t="inlineStr" r="H645">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I645"/>
+      <c s="17" t="inlineStr" r="J645">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K645">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L645">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M645"/>
+      <c s="16" t="inlineStr" r="N645">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE FARDO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O645">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE FARDO</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P645"/>
+      <c s="16" t="inlineStr" r="R645">
+        <is>
+          <t xml:space="preserve">d7154860-cc8c-11f1-a0ca-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S645">
+        <is>
+          <t xml:space="preserve">10049761    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U645">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V645"/>
+    </row>
+    <row r="646" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A646">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B646"/>
+      <c s="21" t="inlineStr" r="D646">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E646">
+        <v>46315.4534722222</v>
+      </c>
+      <c s="22" r="G646">
+        <v>46315.4604166667</v>
+      </c>
+      <c s="21" t="inlineStr" r="H646">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I646"/>
+      <c s="21" t="inlineStr" r="J646">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K646">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L646">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M646"/>
+      <c s="20" t="inlineStr" r="N646">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O646">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 10 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P646"/>
+      <c s="20" t="inlineStr" r="R646">
+        <is>
+          <t xml:space="preserve">a7983060-cc8d-11f1-c7a7-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S646">
+        <is>
+          <t xml:space="preserve">10050036    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U646">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V646"/>
+    </row>
+    <row r="647" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A647">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B647">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D647">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E647">
+        <v>46315.4611111111</v>
+      </c>
+      <c s="18" r="G647">
+        <v>46315.4631944444</v>
+      </c>
+      <c s="17" t="inlineStr" r="H647">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I647"/>
+      <c s="17" t="inlineStr" r="J647">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K647">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L647">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M647"/>
+      <c s="16" t="inlineStr" r="N647">
+        <is>
+          <t xml:space="preserve">RETIRADA DE INSUMOS</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O647">
+        <is>
+          <t xml:space="preserve">retirada de insumos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P647"/>
+      <c s="16" t="inlineStr" r="R647">
+        <is>
+          <t xml:space="preserve">08525880-cc8f-11f1-b834-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S647">
+        <is>
+          <t xml:space="preserve">10050036    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U647">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V647"/>
+    </row>
+    <row r="648" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A648">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B648">
+        <is>
+          <t xml:space="preserve">TR04-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D648">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E648">
+        <v>46315.4645833333</v>
+      </c>
+      <c s="22" r="G648">
+        <v>46315.4666666667</v>
+      </c>
+      <c s="21" t="inlineStr" r="H648">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I648"/>
+      <c s="21" t="inlineStr" r="J648">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K648">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L648">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M648"/>
+      <c s="20" t="inlineStr" r="N648">
+        <is>
+          <t xml:space="preserve">CINTAGEM DE MATERIAL</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O648">
+        <is>
+          <t xml:space="preserve">cintagem e retirada de material</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P648"/>
+      <c s="20" t="inlineStr" r="R648">
+        <is>
+          <t xml:space="preserve">ce5bac20-cc8f-11f1-c975-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S648">
+        <is>
+          <t xml:space="preserve">10050553    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U648">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V648"/>
+    </row>
+    <row r="649" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A649">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B649">
+        <is>
+          <t xml:space="preserve">TR05-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D649">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E649">
+        <v>46315.4694444444</v>
+      </c>
+      <c s="18" r="G649">
+        <v>46315.4763888889</v>
+      </c>
+      <c s="17" t="inlineStr" r="H649">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I649"/>
+      <c s="17" t="inlineStr" r="J649">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K649">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L649">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M649"/>
+      <c s="16" t="inlineStr" r="N649">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O649">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE CHAPA</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P649"/>
+      <c s="16" t="inlineStr" r="R649">
+        <is>
+          <t xml:space="preserve">d73815d0-cc90-11f1-8294-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S649">
+        <is>
+          <t xml:space="preserve">10049761    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U649">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V649"/>
+    </row>
+    <row r="650" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A650">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B650"/>
+      <c s="21" t="inlineStr" r="D650">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E650">
+        <v>46315.4763888889</v>
+      </c>
+      <c s="22" r="G650">
+        <v>46315.4868055556</v>
+      </c>
+      <c s="21" t="inlineStr" r="H650">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I650"/>
+      <c s="21" t="inlineStr" r="J650">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K650">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L650">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M650"/>
+      <c s="20" t="inlineStr" r="N650">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O650">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P650"/>
+      <c s="20" t="inlineStr" r="R650">
+        <is>
+          <t xml:space="preserve">497fa670-cc92-11f1-b4f0-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S650">
+        <is>
+          <t xml:space="preserve">10050425    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U650">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V650"/>
+    </row>
+    <row r="651" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A651">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B651">
+        <is>
+          <t xml:space="preserve">TR04-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D651">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E651">
+        <v>46315.4833333333</v>
+      </c>
+      <c s="18" r="G651">
+        <v>46315.4875</v>
+      </c>
+      <c s="17" t="inlineStr" r="H651">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I651"/>
+      <c s="17" t="inlineStr" r="J651">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K651">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L651">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M651"/>
+      <c s="16" t="inlineStr" r="N651">
+        <is>
+          <t xml:space="preserve">CINTAGEM DE MATERIAL</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O651">
+        <is>
+          <t xml:space="preserve">cintagem e retirada de material</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P651"/>
+      <c s="16" t="inlineStr" r="R651">
+        <is>
+          <t xml:space="preserve">b4e82e90-cc93-11f1-8b46-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S651">
+        <is>
+          <t xml:space="preserve">10050553    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U651">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V651"/>
+    </row>
+    <row r="652" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A652">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B652">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D652">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E652">
+        <v>46315.4847222222</v>
+      </c>
+      <c s="22" r="G652">
+        <v>46315.4861111111</v>
+      </c>
+      <c s="21" t="inlineStr" r="H652">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I652"/>
+      <c s="21" t="inlineStr" r="J652">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K652">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L652">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M652"/>
+      <c s="20" t="inlineStr" r="N652">
+        <is>
+          <t xml:space="preserve">AJUSTE DA MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O652">
+        <is>
+          <t xml:space="preserve">AJUSTE DA MESA</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P652"/>
+      <c s="20" t="inlineStr" r="R652">
+        <is>
+          <t xml:space="preserve">f2833560-cc93-11f1-8e1e-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S652">
+        <is>
+          <t xml:space="preserve">10050037    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U652">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V652"/>
+    </row>
+    <row r="653" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A653">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B653">
+        <is>
+          <t xml:space="preserve">TR05-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D653">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E653">
+        <v>46315.4875</v>
+      </c>
+      <c s="18" r="G653">
+        <v>46315.4923611111</v>
+      </c>
+      <c s="17" t="inlineStr" r="H653">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I653"/>
+      <c s="17" t="inlineStr" r="J653">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K653">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L653">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M653"/>
+      <c s="16" t="inlineStr" r="N653">
+        <is>
+          <t xml:space="preserve">REGULAGEM DE FACA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O653">
+        <is>
+          <t xml:space="preserve">REGULAGEM DA MESA DE 1000 PARA 12000</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P653"/>
+      <c s="16" t="inlineStr" r="R653">
+        <is>
+          <t xml:space="preserve">86574b50-cc94-11f1-ab86-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S653">
+        <is>
+          <t xml:space="preserve">10049761    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U653">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V653"/>
+    </row>
+    <row r="654" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A654">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B654">
+        <is>
+          <t xml:space="preserve">TR05-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D654">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E654">
+        <v>46315.5020833333</v>
+      </c>
+      <c s="22" r="G654">
+        <v>46315.5055555556</v>
+      </c>
+      <c s="21" t="inlineStr" r="H654">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I654"/>
+      <c s="21" t="inlineStr" r="J654">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K654">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L654">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M654"/>
+      <c s="20" t="inlineStr" r="N654">
+        <is>
+          <t xml:space="preserve">RETIRADA DE PNC</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O654">
+        <is>
+          <t xml:space="preserve">RETIRADA DE PNC</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P654"/>
+      <c s="20" t="inlineStr" r="R654">
+        <is>
+          <t xml:space="preserve">58f5d570-cc97-11f1-c1e7-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S654">
+        <is>
+          <t xml:space="preserve">10050384    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U654">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V654"/>
+    </row>
+    <row r="655" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A655">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B655"/>
+      <c s="17" t="inlineStr" r="D655">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E655">
+        <v>46315.5041666667</v>
+      </c>
+      <c s="18" r="G655">
+        <v>46315.5097222222</v>
+      </c>
+      <c s="17" t="inlineStr" r="H655">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I655"/>
+      <c s="17" t="inlineStr" r="J655">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K655">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L655">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M655"/>
+      <c s="16" t="inlineStr" r="N655">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O655">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 8 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P655"/>
+      <c s="16" t="inlineStr" r="R655">
+        <is>
+          <t xml:space="preserve">dad47240-cc97-11f1-8947-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S655">
+        <is>
+          <t xml:space="preserve">10050037    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U655">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V655"/>
+    </row>
+    <row r="656" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A656">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B656">
+        <is>
+          <t xml:space="preserve">TR04-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D656">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E656">
+        <v>46315.5083333333</v>
+      </c>
+      <c s="22" r="G656">
+        <v>46315.5131944444</v>
+      </c>
+      <c s="21" t="inlineStr" r="H656">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I656"/>
+      <c s="21" t="inlineStr" r="J656">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K656">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L656">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M656"/>
+      <c s="20" t="inlineStr" r="N656">
+        <is>
+          <t xml:space="preserve">CINTAGEM DE MATERIAL</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O656">
+        <is>
+          <t xml:space="preserve">cintagem e retirada de material</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P656"/>
+      <c s="20" t="inlineStr" r="R656">
+        <is>
+          <t xml:space="preserve">b1efbcd0-cc98-11f1-ae64-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S656">
+        <is>
+          <t xml:space="preserve">10050553    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U656">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V656"/>
+    </row>
+    <row r="657" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A657">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B657">
+        <is>
+          <t xml:space="preserve">TR01-MESA FIXA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D657">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E657">
+        <v>46315.5104166667</v>
+      </c>
+      <c s="18" r="G657">
+        <v>46315.5145833333</v>
+      </c>
+      <c s="17" t="inlineStr" r="H657">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I657"/>
+      <c s="17" t="inlineStr" r="J657">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K657">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L657">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M657"/>
+      <c s="16" t="inlineStr" r="N657">
+        <is>
+          <t xml:space="preserve">PESAGEM DE FARDO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O657">
+        <is>
+          <t xml:space="preserve">AQUARDANDO OP: DE PONTE RETIRA MATERIAL</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P657"/>
+      <c s="16" t="inlineStr" r="R657">
+        <is>
+          <t xml:space="preserve">154bae60-cc99-11f1-bc98-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S657">
+        <is>
+          <t xml:space="preserve">10050037    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U657">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V657"/>
+    </row>
+    <row r="658" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A658">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B658">
+        <is>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D658">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E658">
+        <v>46315.5166666667</v>
+      </c>
+      <c s="22" r="G658">
+        <v>46315.5270833333</v>
+      </c>
+      <c s="21" t="inlineStr" r="H658">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I658"/>
+      <c s="21" t="inlineStr" r="J658">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K658">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L658">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M658"/>
+      <c s="20" t="inlineStr" r="N658">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O658">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P658"/>
+      <c s="20" t="inlineStr" r="R658">
+        <is>
+          <t xml:space="preserve">be088570-cc9c-11f1-b4b7-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S658">
+        <is>
+          <t xml:space="preserve">10050553    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U658">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V658"/>
+    </row>
+    <row r="659" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A659">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B659">
+        <is>
+          <t xml:space="preserve">TR05-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D659">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E659">
+        <v>46315.5236111111</v>
+      </c>
+      <c s="18" r="G659">
+        <v>46315.5256944444</v>
+      </c>
+      <c s="17" t="inlineStr" r="H659">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I659"/>
+      <c s="17" t="inlineStr" r="J659">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K659">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L659">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M659"/>
+      <c s="16" t="inlineStr" r="N659">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE FARDO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O659">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE FARDO</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P659"/>
+      <c s="16" t="inlineStr" r="R659">
+        <is>
+          <t xml:space="preserve">c9085640-cc9b-11f1-bcd3-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S659">
+        <is>
+          <t xml:space="preserve">10050384    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U659">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V659"/>
+    </row>
+    <row r="660" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A660">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B660">
+        <is>
+          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D660">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E660">
+        <v>46315.5284722222</v>
+      </c>
+      <c s="22" r="G660">
+        <v>46315.5354166667</v>
+      </c>
+      <c s="21" t="inlineStr" r="H660">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I660"/>
+      <c s="21" t="inlineStr" r="J660">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K660">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L660">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M660"/>
+      <c s="20" t="inlineStr" r="N660">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O660">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 10 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P660"/>
+      <c s="20" t="inlineStr" r="R660">
+        <is>
+          <t xml:space="preserve">b2f80840-cc9c-11f1-a448-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S660">
+        <is>
+          <t xml:space="preserve">10050425    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U660">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V660"/>
+    </row>
+    <row r="661" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A661">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B661">
+        <is>
+          <t xml:space="preserve">TR02-GUILHOTINA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D661">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E661">
+        <v>46315.5361111111</v>
+      </c>
+      <c s="18" r="G661">
+        <v>46315.5465277778</v>
+      </c>
+      <c s="17" t="inlineStr" r="H661">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I661"/>
+      <c s="17" t="inlineStr" r="J661">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K661">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L661">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M661"/>
+      <c s="16" t="inlineStr" r="N661">
+        <is>
+          <t xml:space="preserve">SETUP COMPLETO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O661">
+        <is>
+          <t xml:space="preserve">Setup completo</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P661"/>
+      <c s="16" t="inlineStr" r="R661">
+        <is>
+          <t xml:space="preserve">64b9d510-cca0-11f1-bc48-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S661">
+        <is>
+          <t xml:space="preserve">10050425    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U661">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V661"/>
+    </row>
+    <row r="662" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A662">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B662">
+        <is>
+          <t xml:space="preserve">TR04-ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D662">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E662">
+        <v>46315.5423611111</v>
+      </c>
+      <c s="22" r="G662">
+        <v>46315.5479166667</v>
+      </c>
+      <c s="21" t="inlineStr" r="H662">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I662"/>
+      <c s="21" t="inlineStr" r="J662">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K662">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L662">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M662"/>
+      <c s="20" t="inlineStr" r="N662">
+        <is>
+          <t xml:space="preserve">AJUSTE DE ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O662">
+        <is>
+          <t xml:space="preserve">regulagem</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P662"/>
+      <c s="20" t="inlineStr" r="R662">
+        <is>
+          <t xml:space="preserve">7a64aa80-cc9f-11f1-9cb3-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S662">
+        <is>
+          <t xml:space="preserve">10050553    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U662">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V662"/>
+    </row>
+    <row r="663" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A663">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B663">
+        <is>
+          <t xml:space="preserve">TR05-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D663">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E663">
+        <v>46315.5465277778</v>
+      </c>
+      <c s="18" r="G663">
+        <v>46315.5486111111</v>
+      </c>
+      <c s="17" t="inlineStr" r="H663">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I663"/>
+      <c s="17" t="inlineStr" r="J663">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K663">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L663">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M663"/>
+      <c s="16" t="inlineStr" r="N663">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE FARDO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O663">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE FARDO</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P663"/>
+      <c s="16" t="inlineStr" r="R663">
+        <is>
+          <t xml:space="preserve">6a5dec90-cca0-11f1-9cb4-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S663">
+        <is>
+          <t xml:space="preserve">10050033    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U663">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V663"/>
+    </row>
+    <row r="664" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A664">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B664">
+        <is>
+          <t xml:space="preserve">TR04-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D664">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E664">
+        <v>46315.5486111111</v>
+      </c>
+      <c s="22" r="G664">
+        <v>46315.5506944444</v>
+      </c>
+      <c s="21" t="inlineStr" r="H664">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I664"/>
+      <c s="21" t="inlineStr" r="J664">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K664">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L664">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M664"/>
+      <c s="20" t="inlineStr" r="N664">
+        <is>
+          <t xml:space="preserve">RETIRADA DE PNC</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O664">
+        <is>
+          <t xml:space="preserve">retirada de PNC</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P664"/>
+      <c s="20" t="inlineStr" r="R664">
+        <is>
+          <t xml:space="preserve">d5a39fe0-cca0-11f1-bef9-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S664">
+        <is>
+          <t xml:space="preserve">10050553    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U664">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V664"/>
+    </row>
+    <row r="665" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A665">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B665">
+        <is>
+          <t xml:space="preserve">TR04-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D665">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E665">
+        <v>46315.5520833333</v>
+      </c>
+      <c s="18" r="G665">
+        <v>46315.5555555556</v>
+      </c>
+      <c s="17" t="inlineStr" r="H665">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I665"/>
+      <c s="17" t="inlineStr" r="J665">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K665">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L665">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M665"/>
+      <c s="16" t="inlineStr" r="N665">
+        <is>
+          <t xml:space="preserve">CINTAGEM DE MATERIAL</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O665">
+        <is>
+          <t xml:space="preserve">cintagem e retirada de material</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P665"/>
+      <c s="16" t="inlineStr" r="R665">
+        <is>
+          <t xml:space="preserve">7d59bcb0-cca1-11f1-9e51-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S665">
+        <is>
+          <t xml:space="preserve">10050553    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U665">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V665"/>
+    </row>
+    <row r="666" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A666">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B666"/>
+      <c s="21" t="inlineStr" r="D666">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E666">
+        <v>46315.5527777778</v>
+      </c>
+      <c s="22" r="G666">
+        <v>46315.5618055556</v>
+      </c>
+      <c s="21" t="inlineStr" r="H666">
+        <is>
+          <t xml:space="preserve">13</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I666"/>
+      <c s="21" t="inlineStr" r="J666">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K666">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L666">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M666"/>
+      <c s="20" t="inlineStr" r="N666">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O666">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 13 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P666"/>
+      <c s="20" t="inlineStr" r="R666">
+        <is>
+          <t xml:space="preserve">9e357320-cca1-11f1-bd76-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S666">
+        <is>
+          <t xml:space="preserve">10050037    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U666">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V666"/>
+    </row>
+    <row r="667" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A667">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B667">
+        <is>
+          <t xml:space="preserve">TR05-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D667">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E667">
+        <v>46315.5555555556</v>
+      </c>
+      <c s="18" r="G667">
+        <v>46315.5694444444</v>
+      </c>
+      <c s="17" t="inlineStr" r="H667">
+        <is>
+          <t xml:space="preserve">20</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I667"/>
+      <c s="17" t="inlineStr" r="J667">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K667">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L667">
+        <is>
+          <t xml:space="preserve">Paradas Programadas</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M667"/>
+      <c s="16" t="inlineStr" r="N667">
+        <is>
+          <t xml:space="preserve">ASSINATURA DE DOCUMENTOS</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O667">
+        <is>
+          <t xml:space="preserve">ASSINATURA DE DOCUMENTOS E AGUARDANDO SUPERVISOR PARA  ASSINAR APR</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P667"/>
+      <c s="16" t="inlineStr" r="R667">
+        <is>
+          <t xml:space="preserve">2396a700-cca2-11f1-8eaf-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S667">
+        <is>
+          <t xml:space="preserve">10050033    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U667">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V667"/>
+    </row>
+    <row r="668" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A668">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B668">
+        <is>
+          <t xml:space="preserve">TR04-MESA TRANSPORTADORA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D668">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E668">
+        <v>46315.55625</v>
+      </c>
+      <c s="22" r="G668">
+        <v>46315.5583333333</v>
+      </c>
+      <c s="21" t="inlineStr" r="H668">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I668"/>
+      <c s="21" t="inlineStr" r="J668">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K668">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L668">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M668"/>
+      <c s="20" t="inlineStr" r="N668">
+        <is>
+          <t xml:space="preserve">AJUSTE DE MESA GUIA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O668">
+        <is>
+          <t xml:space="preserve">ajuste</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P668"/>
+      <c s="20" t="inlineStr" r="R668">
+        <is>
+          <t xml:space="preserve">4b014a21-cca2-11f1-abe8-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S668">
+        <is>
+          <t xml:space="preserve">10050553    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U668">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V668"/>
+    </row>
+    <row r="669" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A669">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B669">
+        <is>
+          <t xml:space="preserve">TR02-MESA FIXA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D669">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E669">
+        <v>46315.5583333333</v>
+      </c>
+      <c s="18" r="G669">
+        <v>46315.5611111111</v>
+      </c>
+      <c s="17" t="inlineStr" r="H669">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I669"/>
+      <c s="17" t="inlineStr" r="J669">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K669">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L669">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M669"/>
+      <c s="16" t="inlineStr" r="N669">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O669">
+        <is>
+          <t xml:space="preserve">Mesa cheia , material 4.75mm x 6.000mm x 1.200mm</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P669"/>
+      <c s="16" t="inlineStr" r="R669">
+        <is>
+          <t xml:space="preserve">bcb2d1c0-cca2-11f1-8555-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S669">
+        <is>
+          <t xml:space="preserve">10050427    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U669">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V669"/>
+    </row>
+    <row r="670" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A670">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B670">
+        <is>
+          <t xml:space="preserve">TR04-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D670">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E670">
+        <v>46315.5659722222</v>
+      </c>
+      <c s="22" r="G670">
+        <v>46315.56875</v>
+      </c>
+      <c s="21" t="inlineStr" r="H670">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I670"/>
+      <c s="21" t="inlineStr" r="J670">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K670">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L670">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M670"/>
+      <c s="20" t="inlineStr" r="N670">
+        <is>
+          <t xml:space="preserve">AJUSTE DA MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O670">
+        <is>
+          <t xml:space="preserve">regulagem</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P670"/>
+      <c s="20" t="inlineStr" r="R670">
+        <is>
+          <t xml:space="preserve">3e025880-cca4-11f1-cee1-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S670">
+        <is>
+          <t xml:space="preserve">10050553    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U670">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V670"/>
+    </row>
+    <row r="671" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A671">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B671">
+        <is>
+          <t xml:space="preserve">TR05-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D671">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E671">
+        <v>46315.5708333333</v>
+      </c>
+      <c s="18" r="G671">
+        <v>46315.5798611111</v>
+      </c>
+      <c s="17" t="inlineStr" r="H671">
+        <is>
+          <t xml:space="preserve">13</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I671"/>
+      <c s="17" t="inlineStr" r="J671">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K671">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L671">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M671"/>
+      <c s="16" t="inlineStr" r="N671">
+        <is>
+          <t xml:space="preserve">TROCA DAS CASTANHAS DO MANDRIL</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O671">
+        <is>
+          <t xml:space="preserve">TROCA DAS CASTANHAS</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P671"/>
+      <c s="16" t="inlineStr" r="R671">
+        <is>
+          <t xml:space="preserve">c53549b0-cca5-11f1-91fd-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S671">
+        <is>
+          <t xml:space="preserve">10050033    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U671">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V671"/>
+    </row>
+    <row r="672" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A672">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B672">
+        <is>
+          <t xml:space="preserve">TR01-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D672">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E672">
+        <v>46315.5715277778</v>
+      </c>
+      <c s="22" r="G672">
+        <v>46315.5729166667</v>
+      </c>
+      <c s="21" t="inlineStr" r="H672">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I672"/>
+      <c s="21" t="inlineStr" r="J672">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K672">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L672">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M672"/>
+      <c s="20" t="inlineStr" r="N672">
+        <is>
+          <t xml:space="preserve">AJUSTE DA MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O672">
+        <is>
+          <t xml:space="preserve">AJUSTE DA CHAPA</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P672"/>
+      <c s="20" t="inlineStr" r="R672">
+        <is>
+          <t xml:space="preserve">6e565da0-cca5-11f1-8d07-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S672">
+        <is>
+          <t xml:space="preserve">10050382    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U672">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V672"/>
+    </row>
+    <row r="673" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A673">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B673"/>
+      <c s="17" t="inlineStr" r="D673">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E673">
+        <v>46315.5722222222</v>
+      </c>
+      <c s="18" r="G673">
+        <v>46315.5826388889</v>
+      </c>
+      <c s="17" t="inlineStr" r="H673">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I673"/>
+      <c s="17" t="inlineStr" r="J673">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K673">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L673">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M673"/>
+      <c s="16" t="inlineStr" r="N673">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O673">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P673"/>
+      <c s="16" t="inlineStr" r="R673">
+        <is>
+          <t xml:space="preserve">8a04b330-cca5-11f1-bd8e-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S673">
+        <is>
+          <t xml:space="preserve">10050427    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U673">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V673"/>
+    </row>
+    <row r="674" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A674">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B674">
+        <is>
+          <t xml:space="preserve">TR04-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D674">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E674">
+        <v>46315.5736111111</v>
+      </c>
+      <c s="22" r="G674">
+        <v>46315.5805555556</v>
+      </c>
+      <c s="21" t="inlineStr" r="H674">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I674"/>
+      <c s="21" t="inlineStr" r="J674">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K674">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L674">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M674"/>
+      <c s="20" t="inlineStr" r="N674">
+        <is>
+          <t xml:space="preserve">CINTAGEM DE MATERIAL</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O674">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P674"/>
+      <c s="20" t="inlineStr" r="R674">
+        <is>
+          <t xml:space="preserve">de5ca640-cca5-11f1-89cf-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S674">
+        <is>
+          <t xml:space="preserve">10050553    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U674">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V674"/>
+    </row>
+    <row r="675" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A675">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B675">
+        <is>
+          <t xml:space="preserve">TR05-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D675">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E675">
+        <v>46315.5805555556</v>
+      </c>
+      <c s="18" r="G675">
+        <v>46315.5909722222</v>
+      </c>
+      <c s="17" t="inlineStr" r="H675">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I675"/>
+      <c s="17" t="inlineStr" r="J675">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K675">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L675">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M675"/>
+      <c s="16" t="inlineStr" r="N675">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O675">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P675"/>
+      <c s="16" t="inlineStr" r="R675">
+        <is>
+          <t xml:space="preserve">30d5aab0-cca7-11f1-af3c-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S675">
+        <is>
+          <t xml:space="preserve">10050033    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U675">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V675"/>
+    </row>
+    <row r="676" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A676">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B676">
+        <is>
+          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D676">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E676">
+        <v>46315.5833333333</v>
+      </c>
+      <c s="22" r="G676">
+        <v>46315.5854166667</v>
+      </c>
+      <c s="21" t="inlineStr" r="H676">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I676"/>
+      <c s="21" t="inlineStr" r="J676">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K676">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L676">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M676"/>
+      <c s="20" t="inlineStr" r="N676">
+        <is>
+          <t xml:space="preserve">RETIRADA DE PNC</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O676">
+        <is>
+          <t xml:space="preserve">Retirada de pnc.</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P676"/>
+      <c s="20" t="inlineStr" r="R676">
+        <is>
+          <t xml:space="preserve">38126e20-cca8-11f1-815e-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S676">
+        <is>
+          <t xml:space="preserve">10050427    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U676">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V676"/>
+    </row>
+    <row r="677" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A677">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B677">
+        <is>
+          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D677">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E677">
+        <v>46315.5861111111</v>
+      </c>
+      <c s="18" r="G677">
+        <v>46315.6027777778</v>
+      </c>
+      <c s="17" t="inlineStr" r="H677">
+        <is>
+          <t xml:space="preserve">24</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I677"/>
+      <c s="17" t="inlineStr" r="J677">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K677">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L677">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M677"/>
+      <c s="16" t="inlineStr" r="N677">
+        <is>
+          <t xml:space="preserve">QUALIDADE DA MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O677">
+        <is>
+          <t xml:space="preserve">Material 4.75mm 6000x1200 UD 5012372933 está com quebra de superfície foi cortada algumas chapas de 2m e apontada como pnc
+OBS;</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P677"/>
+      <c s="16" t="inlineStr" r="R677">
+        <is>
+          <t xml:space="preserve">81610ff0-cca8-11f1-98d8-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S677">
+        <is>
+          <t xml:space="preserve">10050427    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U677">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V677"/>
+    </row>
+    <row r="678" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A678">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B678">
+        <is>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D678">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="22" r="E678">
+        <v>46315.5881944444</v>
+      </c>
+      <c s="22" r="G678">
+        <v>46315.5909722222</v>
+      </c>
+      <c s="21" t="inlineStr" r="H678">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I678"/>
+      <c s="21" t="inlineStr" r="J678">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K678">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L678">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M678"/>
+      <c s="20" t="inlineStr" r="N678">
+        <is>
+          <t xml:space="preserve">CINTAGEM DE MATERIAL</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O678">
+        <is>
+          <t xml:space="preserve">cintagem e retirada de material</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P678"/>
+      <c s="20" t="inlineStr" r="R678">
+        <is>
+          <t xml:space="preserve">ae7744a0-cca8-11f1-89d7-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S678">
+        <is>
+          <t xml:space="preserve">10050591    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U678">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V678"/>
+    </row>
+    <row r="679" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A679">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B679"/>
+      <c s="17" t="inlineStr" r="D679">
+        <is>
+          <t xml:space="preserve">TURNO A</t>
+        </is>
+      </c>
+      <c s="18" r="E679">
+        <v>46315.5916666667</v>
+      </c>
+      <c s="18" r="G679">
+        <v>46315.5993055556</v>
+      </c>
+      <c s="17" t="inlineStr" r="H679">
+        <is>
+          <t xml:space="preserve">11</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I679"/>
+      <c s="17" t="inlineStr" r="J679">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K679">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L679">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M679"/>
+      <c s="16" t="inlineStr" r="N679">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O679">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 11 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P679"/>
+      <c s="16" t="inlineStr" r="R679">
+        <is>
+          <t xml:space="preserve">70449c40-cca9-11f1-aa27-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S679">
+        <is>
+          <t xml:space="preserve">10050382    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U679">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V679"/>
+    </row>
+    <row r="680" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A680">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B680"/>
+      <c s="21" t="inlineStr" r="D680">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E680">
+        <v>46315.5979166667</v>
+      </c>
+      <c s="22" r="G680">
+        <v>46315.6055555556</v>
+      </c>
+      <c s="21" t="inlineStr" r="H680">
+        <is>
+          <t xml:space="preserve">11</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I680"/>
+      <c s="21" t="inlineStr" r="J680">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K680">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L680">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M680"/>
+      <c s="20" t="inlineStr" r="N680">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O680">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 11 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P680"/>
+      <c s="20" t="inlineStr" r="R680">
+        <is>
+          <t xml:space="preserve">acf7bea0-ccaa-11f1-9a5e-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S680">
+        <is>
+          <t xml:space="preserve">10050591    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U680">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V680"/>
+    </row>
+    <row r="681" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A681">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B681">
+        <is>
+          <t xml:space="preserve">TR05-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D681">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E681">
+        <v>46315.5986111111</v>
+      </c>
+      <c s="18" r="G681">
+        <v>46315.60625</v>
+      </c>
+      <c s="17" t="inlineStr" r="H681">
+        <is>
+          <t xml:space="preserve">11</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I681"/>
+      <c s="17" t="inlineStr" r="J681">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K681">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L681">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M681"/>
+      <c s="16" t="inlineStr" r="N681">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE CHAPA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O681">
+        <is>
+          <t xml:space="preserve">colaborador apertou o botão de emergencia sem querer, tivemos que voltar e passar o material novamente.</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P681"/>
+      <c s="16" t="inlineStr" r="R681">
+        <is>
+          <t xml:space="preserve">e3da57c0-ccaa-11f1-9c4c-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S681">
+        <is>
+          <t xml:space="preserve">10050034    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U681">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V681"/>
+    </row>
+    <row r="682" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A682">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B682">
+        <is>
+          <t xml:space="preserve">TR02-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D682">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E682">
+        <v>46315.6041666667</v>
+      </c>
+      <c s="22" r="G682">
+        <v>46315.6222222222</v>
+      </c>
+      <c s="21" t="inlineStr" r="H682">
+        <is>
+          <t xml:space="preserve">26</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I682"/>
+      <c s="21" t="inlineStr" r="J682">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K682">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L682">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M682"/>
+      <c s="20" t="inlineStr" r="N682">
+        <is>
+          <t xml:space="preserve">ACERTO DE SETUP</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O682">
+        <is>
+          <t xml:space="preserve">Regulagem dos fusos da mesa e guilhotina.</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P682"/>
+      <c s="20" t="inlineStr" r="R682">
+        <is>
+          <t xml:space="preserve">a9a6cca0-ccaf-11f1-cf8c-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S682">
+        <is>
+          <t xml:space="preserve">10050427    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U682">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V682"/>
+    </row>
+    <row r="683" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A683">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B683">
+        <is>
+          <t xml:space="preserve">TR04-ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D683">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E683">
+        <v>46315.6083333333</v>
+      </c>
+      <c s="18" r="G683">
+        <v>46315.6131944444</v>
+      </c>
+      <c s="17" t="inlineStr" r="H683">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I683"/>
+      <c s="17" t="inlineStr" r="J683">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K683">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L683">
+        <is>
+          <t xml:space="preserve">Setup/Regulagem</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M683"/>
+      <c s="16" t="inlineStr" r="N683">
+        <is>
+          <t xml:space="preserve">SETUP COMPLETO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O683">
+        <is>
+          <t xml:space="preserve">trocar 1.50x1.000 para 0.75x1.000 e fazer regulagem</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P683"/>
+      <c s="16" t="inlineStr" r="R683">
+        <is>
+          <t xml:space="preserve">c357fa00-ccac-11f1-b353-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S683">
+        <is>
+          <t xml:space="preserve">10050591    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U683">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V683"/>
+    </row>
+    <row r="684" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A684">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B684">
+        <is>
+          <t xml:space="preserve">TR04-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D684">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E684">
+        <v>46315.6243055556</v>
+      </c>
+      <c s="22" r="G684">
+        <v>46315.6277777778</v>
+      </c>
+      <c s="21" t="inlineStr" r="H684">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I684"/>
+      <c s="21" t="inlineStr" r="J684">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K684">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L684">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M684"/>
+      <c s="20" t="inlineStr" r="N684">
+        <is>
+          <t xml:space="preserve">CINTAGEM DE MATERIAL</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O684">
+        <is>
+          <t xml:space="preserve">cintagem e retirada de material</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P684"/>
+      <c s="20" t="inlineStr" r="R684">
+        <is>
+          <t xml:space="preserve">ff6d91f0-ccaf-11f1-b088-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S684">
+        <is>
+          <t xml:space="preserve">10050592    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U684">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V684"/>
+    </row>
+    <row r="685" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A685">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B685"/>
+      <c s="17" t="inlineStr" r="D685">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E685">
+        <v>46315.6326388889</v>
+      </c>
+      <c s="18" r="G685">
+        <v>46315.6409722222</v>
+      </c>
+      <c s="17" t="inlineStr" r="H685">
+        <is>
+          <t xml:space="preserve">12</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I685"/>
+      <c s="17" t="inlineStr" r="J685">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K685">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L685">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M685"/>
+      <c s="16" t="inlineStr" r="N685">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O685">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 12 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P685"/>
+      <c s="16" t="inlineStr" r="R685">
+        <is>
+          <t xml:space="preserve">b79d19c0-ccb1-11f1-bd0b-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S685">
+        <is>
+          <t xml:space="preserve">10050427    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U685">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V685"/>
+    </row>
+    <row r="686" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A686">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B686"/>
+      <c s="21" t="inlineStr" r="D686">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E686">
+        <v>46315.6361111111</v>
+      </c>
+      <c s="22" r="G686">
+        <v>46315.6444444444</v>
+      </c>
+      <c s="21" t="inlineStr" r="H686">
+        <is>
+          <t xml:space="preserve">12</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I686"/>
+      <c s="21" t="inlineStr" r="J686">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K686">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L686">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M686"/>
+      <c s="20" t="inlineStr" r="N686">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O686">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 12 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P686"/>
+      <c s="20" t="inlineStr" r="R686">
+        <is>
+          <t xml:space="preserve">54d58380-ccb2-11f1-891d-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S686">
+        <is>
+          <t xml:space="preserve">10050382    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U686">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V686"/>
+    </row>
+    <row r="687" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A687">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B687">
+        <is>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D687">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E687">
+        <v>46315.6388888889</v>
+      </c>
+      <c s="18" r="G687">
+        <v>46315.6416666667</v>
+      </c>
+      <c s="17" t="inlineStr" r="H687">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I687"/>
+      <c s="17" t="inlineStr" r="J687">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K687">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L687">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M687"/>
+      <c s="16" t="inlineStr" r="N687">
+        <is>
+          <t xml:space="preserve">QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O687">
+        <is>
+          <t xml:space="preserve">Bobina 0.75x1000 de UD. 2003977045 com oxidação OBS. Inspetor de qualidade Alisson autorizou cortar.</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P687"/>
+      <c s="16" t="inlineStr" r="R687">
+        <is>
+          <t xml:space="preserve">f1c57290-ccb2-11f1-b6b2-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S687">
+        <is>
+          <t xml:space="preserve">10050592    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U687">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V687"/>
+    </row>
+    <row r="688" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A688">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B688">
+        <is>
+          <t xml:space="preserve">TR01-MESA FIXA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D688">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E688">
+        <v>46315.6451388889</v>
+      </c>
+      <c s="22" r="G688">
+        <v>46315.6479166667</v>
+      </c>
+      <c s="21" t="inlineStr" r="H688">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I688"/>
+      <c s="21" t="inlineStr" r="J688">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K688">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L688">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M688"/>
+      <c s="20" t="inlineStr" r="N688">
+        <is>
+          <t xml:space="preserve">PESAGEM DE FARDO</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O688">
+        <is>
+          <t xml:space="preserve">aguardando op:de ponte retira material</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P688"/>
+      <c s="20" t="inlineStr" r="R688">
+        <is>
+          <t xml:space="preserve">1b1a8b20-ccb4-11f1-a5d7-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S688">
+        <is>
+          <t xml:space="preserve">10050382    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U688">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V688"/>
+    </row>
+    <row r="689" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A689">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B689">
+        <is>
+          <t xml:space="preserve">TR04-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D689">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E689">
+        <v>46315.6534722222</v>
+      </c>
+      <c s="18" r="G689">
+        <v>46315.65625</v>
+      </c>
+      <c s="17" t="inlineStr" r="H689">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I689"/>
+      <c s="17" t="inlineStr" r="J689">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K689">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L689">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M689"/>
+      <c s="16" t="inlineStr" r="N689">
+        <is>
+          <t xml:space="preserve">CINTAGEM DE MATERIAL</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O689">
+        <is>
+          <t xml:space="preserve">cintagem e retirada de material</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P689"/>
+      <c s="16" t="inlineStr" r="R689">
+        <is>
+          <t xml:space="preserve">e1df2300-ccb5-11f1-b2a2-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S689">
+        <is>
+          <t xml:space="preserve">10050592    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U689">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V689"/>
+    </row>
+    <row r="690" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A690">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B690">
+        <is>
+          <t xml:space="preserve">TR04-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D690">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E690">
+        <v>46315.6666666667</v>
+      </c>
+      <c s="22" r="G690">
+        <v>46315.6701388889</v>
+      </c>
+      <c s="21" t="inlineStr" r="H690">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I690"/>
+      <c s="21" t="inlineStr" r="J690">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K690">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L690">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M690"/>
+      <c s="20" t="inlineStr" r="N690">
+        <is>
+          <t xml:space="preserve">RETIRADA DE PNC</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O690">
+        <is>
+          <t xml:space="preserve">retirar peças amassadas</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P690"/>
+      <c s="20" t="inlineStr" r="R690">
+        <is>
+          <t xml:space="preserve">88b925c0-ccb8-11f1-91ab-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S690">
+        <is>
+          <t xml:space="preserve">10050592    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U690">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V690"/>
+    </row>
+    <row r="691" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A691">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B691">
+        <is>
+          <t xml:space="preserve">TR05-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D691">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E691">
+        <v>46315.6701388889</v>
+      </c>
+      <c s="18" r="G691">
+        <v>46315.6805555556</v>
+      </c>
+      <c s="17" t="inlineStr" r="H691">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I691"/>
+      <c s="17" t="inlineStr" r="J691">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K691">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L691">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M691"/>
+      <c s="16" t="inlineStr" r="N691">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O691">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 15 minutos</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P691"/>
+      <c s="16" t="inlineStr" r="R691">
+        <is>
+          <t xml:space="preserve">2d8fc950-ccb9-11f1-cf40-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S691">
+        <is>
+          <t xml:space="preserve">10050034    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U691">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V691"/>
+    </row>
+    <row r="692" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A692">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B692">
+        <is>
+          <t xml:space="preserve">TR04-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D692">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E692">
+        <v>46315.6708333333</v>
+      </c>
+      <c s="22" r="G692">
+        <v>46315.6736111111</v>
+      </c>
+      <c s="21" t="inlineStr" r="H692">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I692"/>
+      <c s="21" t="inlineStr" r="J692">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K692">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L692">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M692"/>
+      <c s="20" t="inlineStr" r="N692">
+        <is>
+          <t xml:space="preserve">CINTAGEM DE MATERIAL</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O692">
+        <is>
+          <t xml:space="preserve">cintagem e retirada de material</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P692"/>
+      <c s="20" t="inlineStr" r="R692">
+        <is>
+          <t xml:space="preserve">52587160-ccb9-11f1-b38d-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S692">
+        <is>
+          <t xml:space="preserve">10050592    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U692">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V692"/>
+    </row>
+    <row r="693" ht="15.55" customHeight="0">
+      <c s="15" t="inlineStr" r="A693">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B693">
+        <is>
+          <t xml:space="preserve">TR01-CARRO DE ENTRADA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D693">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E693">
+        <v>46315.6708333333</v>
+      </c>
+      <c s="18" r="G693">
+        <v>46315.6951388889</v>
+      </c>
+      <c s="17" t="inlineStr" r="H693">
+        <is>
+          <t xml:space="preserve">35</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I693"/>
+      <c s="17" t="inlineStr" r="J693">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K693">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L693">
+        <is>
+          <t xml:space="preserve">MEP/QUALIDADE</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M693"/>
+      <c s="16" t="inlineStr" r="N693">
+        <is>
+          <t xml:space="preserve">MEP - ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O693">
+        <is>
+          <t xml:space="preserve">aguardando op:de ponte abastece</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P693"/>
+      <c s="16" t="inlineStr" r="R693">
+        <is>
+          <t xml:space="preserve">50a17290-ccb9-11f1-bcd9-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S693">
+        <is>
+          <t xml:space="preserve">10050382    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U693">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V693"/>
+    </row>
+    <row r="694" ht="15.6" customHeight="0">
+      <c s="19" t="inlineStr" r="A694">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="B694"/>
+      <c s="21" t="inlineStr" r="D694">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E694">
+        <v>46315.6722222222</v>
+      </c>
+      <c s="22" r="G694">
+        <v>46315.6798611111</v>
+      </c>
+      <c s="21" t="inlineStr" r="H694">
+        <is>
+          <t xml:space="preserve">11</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I694"/>
+      <c s="21" t="inlineStr" r="J694">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K694">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L694">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M694"/>
+      <c s="20" t="inlineStr" r="N694">
+        <is>
+          <t xml:space="preserve">ABASTECIMENTO DE MATERIA PRIMA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O694">
+        <is>
+          <t xml:space="preserve">Parada automática de processo ABASTECIMENTO. Tempo: 11 minutos</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P694"/>
+      <c s="20" t="inlineStr" r="R694">
+        <is>
+          <t xml:space="preserve">98b104b0-ccb9-11f1-c64d-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S694">
+        <is>
+          <t xml:space="preserve">10050428    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U694">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V694"/>
+    </row>
+    <row r="695" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A695">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 04</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B695">
+        <is>
+          <t xml:space="preserve">TR04-DESENROLADOR</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D695">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E695">
+        <v>46315.6770833333</v>
+      </c>
+      <c s="18" r="G695">
+        <v>46316.3965277778</v>
+      </c>
+      <c s="17" t="inlineStr" r="H695">
+        <is>
+          <t xml:space="preserve">1.036</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I695"/>
+      <c s="17" t="inlineStr" r="J695">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K695">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L695">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M695"/>
+      <c s="16" t="inlineStr" r="N695">
+        <is>
+          <t xml:space="preserve">FALTA DEMANDA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O695">
+        <is>
+          <t xml:space="preserve">FALTA DE DEMANDA</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P695"/>
+      <c s="16" t="inlineStr" r="R695">
+        <is>
+          <t xml:space="preserve">02a74d40-ccbd-11f1-ce55-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="S695"/>
+      <c s="16" t="inlineStr" r="U695">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V695"/>
+    </row>
+    <row r="696" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A696">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B696">
+        <is>
+          <t xml:space="preserve">TR05-MESA MÓVEL</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D696">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E696">
+        <v>46315.68125</v>
+      </c>
+      <c s="22" r="G696">
+        <v>46315.6833333333</v>
+      </c>
+      <c s="21" t="inlineStr" r="H696">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I696"/>
+      <c s="21" t="inlineStr" r="J696">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K696">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L696">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M696"/>
+      <c s="20" t="inlineStr" r="N696">
+        <is>
+          <t xml:space="preserve">PASSAGEM DE FARDO</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O696">
+        <is>
+          <t xml:space="preserve">passagem de fardo</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P696"/>
+      <c s="20" t="inlineStr" r="R696">
+        <is>
+          <t xml:space="preserve">d89944f0-ccbb-11f1-b826-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S696">
+        <is>
+          <t xml:space="preserve">10050034    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U696">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V696"/>
+    </row>
+    <row r="697" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A697">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 05</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="B697">
+        <is>
+          <t xml:space="preserve">TR05-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="17" t="inlineStr" r="D697">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E697">
+        <v>46315.6958333333</v>
+      </c>
+      <c s="18" r="G697">
+        <v>46316.2909722222</v>
+      </c>
+      <c s="17" t="inlineStr" r="H697">
+        <is>
+          <t xml:space="preserve">857</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I697"/>
+      <c s="17" t="inlineStr" r="J697">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K697">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L697">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M697"/>
+      <c s="16" t="inlineStr" r="N697">
+        <is>
+          <t xml:space="preserve">FALTA DEMANDA</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O697">
+        <is>
+          <t xml:space="preserve">falta de demanda</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P697"/>
+      <c s="16" t="inlineStr" r="R697">
+        <is>
+          <t xml:space="preserve">7daf0270-ccbe-11f1-9bf9-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S697">
+        <is>
+          <t xml:space="preserve">10050034    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U697">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V697"/>
+    </row>
+    <row r="698" ht="15.55" customHeight="0">
+      <c s="19" t="inlineStr" r="A698">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 01</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="B698">
+        <is>
+          <t xml:space="preserve">TR01-ACIONAMENTO DA ENDIREITADEIRA</t>
+        </is>
+      </c>
+      <c s="21" t="inlineStr" r="D698">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="22" r="E698">
+        <v>46315.6972222222</v>
+      </c>
+      <c s="22" r="G698">
+        <v>46316.2909722222</v>
+      </c>
+      <c s="21" t="inlineStr" r="H698">
+        <is>
+          <t xml:space="preserve">855</t>
+        </is>
+      </c>
+      <c s="21" t="str" r="I698"/>
+      <c s="21" t="inlineStr" r="J698">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="K698">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="L698">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="M698"/>
+      <c s="20" t="inlineStr" r="N698">
+        <is>
+          <t xml:space="preserve">FALTA DEMANDA</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="O698">
+        <is>
+          <t xml:space="preserve">tempo livre</t>
+        </is>
+      </c>
+      <c s="20" t="str" r="P698"/>
+      <c s="20" t="inlineStr" r="R698">
+        <is>
+          <t xml:space="preserve">c13e3c90-ccbe-11f1-908c-f2050a003223</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="S698">
+        <is>
+          <t xml:space="preserve">10050382    </t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="U698">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V698"/>
+    </row>
+    <row r="699" ht="15.6" customHeight="0">
+      <c s="15" t="inlineStr" r="A699">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 02</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="B699"/>
+      <c s="17" t="inlineStr" r="D699">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="18" r="E699">
+        <v>46315.7013888889</v>
+      </c>
+      <c s="18" r="G699">
+        <v>46316.2840277778</v>
+      </c>
+      <c s="17" t="inlineStr" r="H699">
+        <is>
+          <t xml:space="preserve">839</t>
+        </is>
+      </c>
+      <c s="17" t="str" r="I699"/>
+      <c s="17" t="inlineStr" r="J699">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="K699">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="L699">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="M699"/>
+      <c s="16" t="inlineStr" r="N699">
+        <is>
+          <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="O699">
+        <is>
+          <t xml:space="preserve">Parada registrada automaticamente pelo sistema</t>
+        </is>
+      </c>
+      <c s="16" t="str" r="P699"/>
+      <c s="16" t="inlineStr" r="R699">
+        <is>
+          <t xml:space="preserve">6fae9bd0-ccbf-11f1-92db-f2050a003223</t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="S699">
+        <is>
+          <t xml:space="preserve">10050666    </t>
+        </is>
+      </c>
+      <c s="16" t="inlineStr" r="U699">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="5" t="str" r="V699"/>
+    </row>
+    <row r="700" ht="15.55" customHeight="0">
+      <c s="23" t="inlineStr" r="A700">
+        <is>
+          <t xml:space="preserve">TRANSVERSAL 03</t>
+        </is>
+      </c>
+      <c s="24" t="str" r="B700"/>
+      <c s="10" t="str" r="C700"/>
+      <c s="25" t="inlineStr" r="D700">
+        <is>
+          <t xml:space="preserve">TURNO B</t>
+        </is>
+      </c>
+      <c s="26" r="E700">
+        <v>46315.7013888889</v>
+      </c>
+      <c s="10" t="str" r="F700"/>
+      <c s="26" r="G700">
+        <v>46316.2840277778</v>
+      </c>
+      <c s="25" t="inlineStr" r="H700">
+        <is>
+          <t xml:space="preserve">839</t>
+        </is>
+      </c>
+      <c s="25" t="str" r="I700"/>
+      <c s="25" t="inlineStr" r="J700">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="K700">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="L700">
+        <is>
+          <t xml:space="preserve">Tempo Livre</t>
+        </is>
+      </c>
+      <c s="24" t="str" r="M700"/>
+      <c s="24" t="inlineStr" r="N700">
+        <is>
+          <t xml:space="preserve">ESPERA FIM DE SEMANA / FERIADO</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="O700">
+        <is>
+          <t xml:space="preserve">Parada registrada automaticamente pelo sistema</t>
+        </is>
+      </c>
+      <c s="24" t="str" r="P700"/>
+      <c s="10" t="str" r="Q700"/>
+      <c s="24" t="inlineStr" r="R700">
+        <is>
+          <t xml:space="preserve">6fc46dc0-ccbf-11f1-b548-f2050a003223</t>
+        </is>
+      </c>
+      <c s="24" t="str" r="S700"/>
+      <c s="10" t="str" r="T700"/>
+      <c s="24" t="inlineStr" r="U700">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c s="11" t="str" r="V700"/>
+    </row>
+    <row r="701" ht="0.05" customHeight="1"/>
   </sheetData>
   <mergeCells>
     <mergeCell ref="A3:B8"/>
@@ -46234,6 +52211,426 @@
     <mergeCell ref="P616:Q616"/>
     <mergeCell ref="S616:T616"/>
     <mergeCell ref="U616:V616"/>
+    <mergeCell ref="B617:C617"/>
+    <mergeCell ref="E617:F617"/>
+    <mergeCell ref="P617:Q617"/>
+    <mergeCell ref="S617:T617"/>
+    <mergeCell ref="U617:V617"/>
+    <mergeCell ref="B618:C618"/>
+    <mergeCell ref="E618:F618"/>
+    <mergeCell ref="P618:Q618"/>
+    <mergeCell ref="S618:T618"/>
+    <mergeCell ref="U618:V618"/>
+    <mergeCell ref="B619:C619"/>
+    <mergeCell ref="E619:F619"/>
+    <mergeCell ref="P619:Q619"/>
+    <mergeCell ref="S619:T619"/>
+    <mergeCell ref="U619:V619"/>
+    <mergeCell ref="B620:C620"/>
+    <mergeCell ref="E620:F620"/>
+    <mergeCell ref="P620:Q620"/>
+    <mergeCell ref="S620:T620"/>
+    <mergeCell ref="U620:V620"/>
+    <mergeCell ref="B621:C621"/>
+    <mergeCell ref="E621:F621"/>
+    <mergeCell ref="P621:Q621"/>
+    <mergeCell ref="S621:T621"/>
+    <mergeCell ref="U621:V621"/>
+    <mergeCell ref="B622:C622"/>
+    <mergeCell ref="E622:F622"/>
+    <mergeCell ref="P622:Q622"/>
+    <mergeCell ref="S622:T622"/>
+    <mergeCell ref="U622:V622"/>
+    <mergeCell ref="B623:C623"/>
+    <mergeCell ref="E623:F623"/>
+    <mergeCell ref="P623:Q623"/>
+    <mergeCell ref="S623:T623"/>
+    <mergeCell ref="U623:V623"/>
+    <mergeCell ref="B624:C624"/>
+    <mergeCell ref="E624:F624"/>
+    <mergeCell ref="P624:Q624"/>
+    <mergeCell ref="S624:T624"/>
+    <mergeCell ref="U624:V624"/>
+    <mergeCell ref="B625:C625"/>
+    <mergeCell ref="E625:F625"/>
+    <mergeCell ref="P625:Q625"/>
+    <mergeCell ref="S625:T625"/>
+    <mergeCell ref="U625:V625"/>
+    <mergeCell ref="B626:C626"/>
+    <mergeCell ref="E626:F626"/>
+    <mergeCell ref="P626:Q626"/>
+    <mergeCell ref="S626:T626"/>
+    <mergeCell ref="U626:V626"/>
+    <mergeCell ref="B627:C627"/>
+    <mergeCell ref="E627:F627"/>
+    <mergeCell ref="P627:Q627"/>
+    <mergeCell ref="S627:T627"/>
+    <mergeCell ref="U627:V627"/>
+    <mergeCell ref="B628:C628"/>
+    <mergeCell ref="E628:F628"/>
+    <mergeCell ref="P628:Q628"/>
+    <mergeCell ref="S628:T628"/>
+    <mergeCell ref="U628:V628"/>
+    <mergeCell ref="B629:C629"/>
+    <mergeCell ref="E629:F629"/>
+    <mergeCell ref="P629:Q629"/>
+    <mergeCell ref="S629:T629"/>
+    <mergeCell ref="U629:V629"/>
+    <mergeCell ref="B630:C630"/>
+    <mergeCell ref="E630:F630"/>
+    <mergeCell ref="P630:Q630"/>
+    <mergeCell ref="S630:T630"/>
+    <mergeCell ref="U630:V630"/>
+    <mergeCell ref="B631:C631"/>
+    <mergeCell ref="E631:F631"/>
+    <mergeCell ref="P631:Q631"/>
+    <mergeCell ref="S631:T631"/>
+    <mergeCell ref="U631:V631"/>
+    <mergeCell ref="B632:C632"/>
+    <mergeCell ref="E632:F632"/>
+    <mergeCell ref="P632:Q632"/>
+    <mergeCell ref="S632:T632"/>
+    <mergeCell ref="U632:V632"/>
+    <mergeCell ref="B633:C633"/>
+    <mergeCell ref="E633:F633"/>
+    <mergeCell ref="P633:Q633"/>
+    <mergeCell ref="S633:T633"/>
+    <mergeCell ref="U633:V633"/>
+    <mergeCell ref="B634:C634"/>
+    <mergeCell ref="E634:F634"/>
+    <mergeCell ref="P634:Q634"/>
+    <mergeCell ref="S634:T634"/>
+    <mergeCell ref="U634:V634"/>
+    <mergeCell ref="B635:C635"/>
+    <mergeCell ref="E635:F635"/>
+    <mergeCell ref="P635:Q635"/>
+    <mergeCell ref="S635:T635"/>
+    <mergeCell ref="U635:V635"/>
+    <mergeCell ref="B636:C636"/>
+    <mergeCell ref="E636:F636"/>
+    <mergeCell ref="P636:Q636"/>
+    <mergeCell ref="S636:T636"/>
+    <mergeCell ref="U636:V636"/>
+    <mergeCell ref="B637:C637"/>
+    <mergeCell ref="E637:F637"/>
+    <mergeCell ref="P637:Q637"/>
+    <mergeCell ref="S637:T637"/>
+    <mergeCell ref="U637:V637"/>
+    <mergeCell ref="B638:C638"/>
+    <mergeCell ref="E638:F638"/>
+    <mergeCell ref="P638:Q638"/>
+    <mergeCell ref="S638:T638"/>
+    <mergeCell ref="U638:V638"/>
+    <mergeCell ref="B639:C639"/>
+    <mergeCell ref="E639:F639"/>
+    <mergeCell ref="P639:Q639"/>
+    <mergeCell ref="S639:T639"/>
+    <mergeCell ref="U639:V639"/>
+    <mergeCell ref="B640:C640"/>
+    <mergeCell ref="E640:F640"/>
+    <mergeCell ref="P640:Q640"/>
+    <mergeCell ref="S640:T640"/>
+    <mergeCell ref="U640:V640"/>
+    <mergeCell ref="B641:C641"/>
+    <mergeCell ref="E641:F641"/>
+    <mergeCell ref="P641:Q641"/>
+    <mergeCell ref="S641:T641"/>
+    <mergeCell ref="U641:V641"/>
+    <mergeCell ref="B642:C642"/>
+    <mergeCell ref="E642:F642"/>
+    <mergeCell ref="P642:Q642"/>
+    <mergeCell ref="S642:T642"/>
+    <mergeCell ref="U642:V642"/>
+    <mergeCell ref="B643:C643"/>
+    <mergeCell ref="E643:F643"/>
+    <mergeCell ref="P643:Q643"/>
+    <mergeCell ref="S643:T643"/>
+    <mergeCell ref="U643:V643"/>
+    <mergeCell ref="B644:C644"/>
+    <mergeCell ref="E644:F644"/>
+    <mergeCell ref="P644:Q644"/>
+    <mergeCell ref="S644:T644"/>
+    <mergeCell ref="U644:V644"/>
+    <mergeCell ref="B645:C645"/>
+    <mergeCell ref="E645:F645"/>
+    <mergeCell ref="P645:Q645"/>
+    <mergeCell ref="S645:T645"/>
+    <mergeCell ref="U645:V645"/>
+    <mergeCell ref="B646:C646"/>
+    <mergeCell ref="E646:F646"/>
+    <mergeCell ref="P646:Q646"/>
+    <mergeCell ref="S646:T646"/>
+    <mergeCell ref="U646:V646"/>
+    <mergeCell ref="B647:C647"/>
+    <mergeCell ref="E647:F647"/>
+    <mergeCell ref="P647:Q647"/>
+    <mergeCell ref="S647:T647"/>
+    <mergeCell ref="U647:V647"/>
+    <mergeCell ref="B648:C648"/>
+    <mergeCell ref="E648:F648"/>
+    <mergeCell ref="P648:Q648"/>
+    <mergeCell ref="S648:T648"/>
+    <mergeCell ref="U648:V648"/>
+    <mergeCell ref="B649:C649"/>
+    <mergeCell ref="E649:F649"/>
+    <mergeCell ref="P649:Q649"/>
+    <mergeCell ref="S649:T649"/>
+    <mergeCell ref="U649:V649"/>
+    <mergeCell ref="B650:C650"/>
+    <mergeCell ref="E650:F650"/>
+    <mergeCell ref="P650:Q650"/>
+    <mergeCell ref="S650:T650"/>
+    <mergeCell ref="U650:V650"/>
+    <mergeCell ref="B651:C651"/>
+    <mergeCell ref="E651:F651"/>
+    <mergeCell ref="P651:Q651"/>
+    <mergeCell ref="S651:T651"/>
+    <mergeCell ref="U651:V651"/>
+    <mergeCell ref="B652:C652"/>
+    <mergeCell ref="E652:F652"/>
+    <mergeCell ref="P652:Q652"/>
+    <mergeCell ref="S652:T652"/>
+    <mergeCell ref="U652:V652"/>
+    <mergeCell ref="B653:C653"/>
+    <mergeCell ref="E653:F653"/>
+    <mergeCell ref="P653:Q653"/>
+    <mergeCell ref="S653:T653"/>
+    <mergeCell ref="U653:V653"/>
+    <mergeCell ref="B654:C654"/>
+    <mergeCell ref="E654:F654"/>
+    <mergeCell ref="P654:Q654"/>
+    <mergeCell ref="S654:T654"/>
+    <mergeCell ref="U654:V654"/>
+    <mergeCell ref="B655:C655"/>
+    <mergeCell ref="E655:F655"/>
+    <mergeCell ref="P655:Q655"/>
+    <mergeCell ref="S655:T655"/>
+    <mergeCell ref="U655:V655"/>
+    <mergeCell ref="B656:C656"/>
+    <mergeCell ref="E656:F656"/>
+    <mergeCell ref="P656:Q656"/>
+    <mergeCell ref="S656:T656"/>
+    <mergeCell ref="U656:V656"/>
+    <mergeCell ref="B657:C657"/>
+    <mergeCell ref="E657:F657"/>
+    <mergeCell ref="P657:Q657"/>
+    <mergeCell ref="S657:T657"/>
+    <mergeCell ref="U657:V657"/>
+    <mergeCell ref="B658:C658"/>
+    <mergeCell ref="E658:F658"/>
+    <mergeCell ref="P658:Q658"/>
+    <mergeCell ref="S658:T658"/>
+    <mergeCell ref="U658:V658"/>
+    <mergeCell ref="B659:C659"/>
+    <mergeCell ref="E659:F659"/>
+    <mergeCell ref="P659:Q659"/>
+    <mergeCell ref="S659:T659"/>
+    <mergeCell ref="U659:V659"/>
+    <mergeCell ref="B660:C660"/>
+    <mergeCell ref="E660:F660"/>
+    <mergeCell ref="P660:Q660"/>
+    <mergeCell ref="S660:T660"/>
+    <mergeCell ref="U660:V660"/>
+    <mergeCell ref="B661:C661"/>
+    <mergeCell ref="E661:F661"/>
+    <mergeCell ref="P661:Q661"/>
+    <mergeCell ref="S661:T661"/>
+    <mergeCell ref="U661:V661"/>
+    <mergeCell ref="B662:C662"/>
+    <mergeCell ref="E662:F662"/>
+    <mergeCell ref="P662:Q662"/>
+    <mergeCell ref="S662:T662"/>
+    <mergeCell ref="U662:V662"/>
+    <mergeCell ref="B663:C663"/>
+    <mergeCell ref="E663:F663"/>
+    <mergeCell ref="P663:Q663"/>
+    <mergeCell ref="S663:T663"/>
+    <mergeCell ref="U663:V663"/>
+    <mergeCell ref="B664:C664"/>
+    <mergeCell ref="E664:F664"/>
+    <mergeCell ref="P664:Q664"/>
+    <mergeCell ref="S664:T664"/>
+    <mergeCell ref="U664:V664"/>
+    <mergeCell ref="B665:C665"/>
+    <mergeCell ref="E665:F665"/>
+    <mergeCell ref="P665:Q665"/>
+    <mergeCell ref="S665:T665"/>
+    <mergeCell ref="U665:V665"/>
+    <mergeCell ref="B666:C666"/>
+    <mergeCell ref="E666:F666"/>
+    <mergeCell ref="P666:Q666"/>
+    <mergeCell ref="S666:T666"/>
+    <mergeCell ref="U666:V666"/>
+    <mergeCell ref="B667:C667"/>
+    <mergeCell ref="E667:F667"/>
+    <mergeCell ref="P667:Q667"/>
+    <mergeCell ref="S667:T667"/>
+    <mergeCell ref="U667:V667"/>
+    <mergeCell ref="B668:C668"/>
+    <mergeCell ref="E668:F668"/>
+    <mergeCell ref="P668:Q668"/>
+    <mergeCell ref="S668:T668"/>
+    <mergeCell ref="U668:V668"/>
+    <mergeCell ref="B669:C669"/>
+    <mergeCell ref="E669:F669"/>
+    <mergeCell ref="P669:Q669"/>
+    <mergeCell ref="S669:T669"/>
+    <mergeCell ref="U669:V669"/>
+    <mergeCell ref="B670:C670"/>
+    <mergeCell ref="E670:F670"/>
+    <mergeCell ref="P670:Q670"/>
+    <mergeCell ref="S670:T670"/>
+    <mergeCell ref="U670:V670"/>
+    <mergeCell ref="B671:C671"/>
+    <mergeCell ref="E671:F671"/>
+    <mergeCell ref="P671:Q671"/>
+    <mergeCell ref="S671:T671"/>
+    <mergeCell ref="U671:V671"/>
+    <mergeCell ref="B672:C672"/>
+    <mergeCell ref="E672:F672"/>
+    <mergeCell ref="P672:Q672"/>
+    <mergeCell ref="S672:T672"/>
+    <mergeCell ref="U672:V672"/>
+    <mergeCell ref="B673:C673"/>
+    <mergeCell ref="E673:F673"/>
+    <mergeCell ref="P673:Q673"/>
+    <mergeCell ref="S673:T673"/>
+    <mergeCell ref="U673:V673"/>
+    <mergeCell ref="B674:C674"/>
+    <mergeCell ref="E674:F674"/>
+    <mergeCell ref="P674:Q674"/>
+    <mergeCell ref="S674:T674"/>
+    <mergeCell ref="U674:V674"/>
+    <mergeCell ref="B675:C675"/>
+    <mergeCell ref="E675:F675"/>
+    <mergeCell ref="P675:Q675"/>
+    <mergeCell ref="S675:T675"/>
+    <mergeCell ref="U675:V675"/>
+    <mergeCell ref="B676:C676"/>
+    <mergeCell ref="E676:F676"/>
+    <mergeCell ref="P676:Q676"/>
+    <mergeCell ref="S676:T676"/>
+    <mergeCell ref="U676:V676"/>
+    <mergeCell ref="B677:C677"/>
+    <mergeCell ref="E677:F677"/>
+    <mergeCell ref="P677:Q677"/>
+    <mergeCell ref="S677:T677"/>
+    <mergeCell ref="U677:V677"/>
+    <mergeCell ref="B678:C678"/>
+    <mergeCell ref="E678:F678"/>
+    <mergeCell ref="P678:Q678"/>
+    <mergeCell ref="S678:T678"/>
+    <mergeCell ref="U678:V678"/>
+    <mergeCell ref="B679:C679"/>
+    <mergeCell ref="E679:F679"/>
+    <mergeCell ref="P679:Q679"/>
+    <mergeCell ref="S679:T679"/>
+    <mergeCell ref="U679:V679"/>
+    <mergeCell ref="B680:C680"/>
+    <mergeCell ref="E680:F680"/>
+    <mergeCell ref="P680:Q680"/>
+    <mergeCell ref="S680:T680"/>
+    <mergeCell ref="U680:V680"/>
+    <mergeCell ref="B681:C681"/>
+    <mergeCell ref="E681:F681"/>
+    <mergeCell ref="P681:Q681"/>
+    <mergeCell ref="S681:T681"/>
+    <mergeCell ref="U681:V681"/>
+    <mergeCell ref="B682:C682"/>
+    <mergeCell ref="E682:F682"/>
+    <mergeCell ref="P682:Q682"/>
+    <mergeCell ref="S682:T682"/>
+    <mergeCell ref="U682:V682"/>
+    <mergeCell ref="B683:C683"/>
+    <mergeCell ref="E683:F683"/>
+    <mergeCell ref="P683:Q683"/>
+    <mergeCell ref="S683:T683"/>
+    <mergeCell ref="U683:V683"/>
+    <mergeCell ref="B684:C684"/>
+    <mergeCell ref="E684:F684"/>
+    <mergeCell ref="P684:Q684"/>
+    <mergeCell ref="S684:T684"/>
+    <mergeCell ref="U684:V684"/>
+    <mergeCell ref="B685:C685"/>
+    <mergeCell ref="E685:F685"/>
+    <mergeCell ref="P685:Q685"/>
+    <mergeCell ref="S685:T685"/>
+    <mergeCell ref="U685:V685"/>
+    <mergeCell ref="B686:C686"/>
+    <mergeCell ref="E686:F686"/>
+    <mergeCell ref="P686:Q686"/>
+    <mergeCell ref="S686:T686"/>
+    <mergeCell ref="U686:V686"/>
+    <mergeCell ref="B687:C687"/>
+    <mergeCell ref="E687:F687"/>
+    <mergeCell ref="P687:Q687"/>
+    <mergeCell ref="S687:T687"/>
+    <mergeCell ref="U687:V687"/>
+    <mergeCell ref="B688:C688"/>
+    <mergeCell ref="E688:F688"/>
+    <mergeCell ref="P688:Q688"/>
+    <mergeCell ref="S688:T688"/>
+    <mergeCell ref="U688:V688"/>
+    <mergeCell ref="B689:C689"/>
+    <mergeCell ref="E689:F689"/>
+    <mergeCell ref="P689:Q689"/>
+    <mergeCell ref="S689:T689"/>
+    <mergeCell ref="U689:V689"/>
+    <mergeCell ref="B690:C690"/>
+    <mergeCell ref="E690:F690"/>
+    <mergeCell ref="P690:Q690"/>
+    <mergeCell ref="S690:T690"/>
+    <mergeCell ref="U690:V690"/>
+    <mergeCell ref="B691:C691"/>
+    <mergeCell ref="E691:F691"/>
+    <mergeCell ref="P691:Q691"/>
+    <mergeCell ref="S691:T691"/>
+    <mergeCell ref="U691:V691"/>
+    <mergeCell ref="B692:C692"/>
+    <mergeCell ref="E692:F692"/>
+    <mergeCell ref="P692:Q692"/>
+    <mergeCell ref="S692:T692"/>
+    <mergeCell ref="U692:V692"/>
+    <mergeCell ref="B693:C693"/>
+    <mergeCell ref="E693:F693"/>
+    <mergeCell ref="P693:Q693"/>
+    <mergeCell ref="S693:T693"/>
+    <mergeCell ref="U693:V693"/>
+    <mergeCell ref="B694:C694"/>
+    <mergeCell ref="E694:F694"/>
+    <mergeCell ref="P694:Q694"/>
+    <mergeCell ref="S694:T694"/>
+    <mergeCell ref="U694:V694"/>
+    <mergeCell ref="B695:C695"/>
+    <mergeCell ref="E695:F695"/>
+    <mergeCell ref="P695:Q695"/>
+    <mergeCell ref="S695:T695"/>
+    <mergeCell ref="U695:V695"/>
+    <mergeCell ref="B696:C696"/>
+    <mergeCell ref="E696:F696"/>
+    <mergeCell ref="P696:Q696"/>
+    <mergeCell ref="S696:T696"/>
+    <mergeCell ref="U696:V696"/>
+    <mergeCell ref="B697:C697"/>
+    <mergeCell ref="E697:F697"/>
+    <mergeCell ref="P697:Q697"/>
+    <mergeCell ref="S697:T697"/>
+    <mergeCell ref="U697:V697"/>
+    <mergeCell ref="B698:C698"/>
+    <mergeCell ref="E698:F698"/>
+    <mergeCell ref="P698:Q698"/>
+    <mergeCell ref="S698:T698"/>
+    <mergeCell ref="U698:V698"/>
+    <mergeCell ref="B699:C699"/>
+    <mergeCell ref="E699:F699"/>
+    <mergeCell ref="P699:Q699"/>
+    <mergeCell ref="S699:T699"/>
+    <mergeCell ref="U699:V699"/>
+    <mergeCell ref="B700:C700"/>
+    <mergeCell ref="E700:F700"/>
+    <mergeCell ref="P700:Q700"/>
+    <mergeCell ref="S700:T700"/>
+    <mergeCell ref="U700:V700"/>
   </mergeCells>
   <pageMargins left="0.0393700787401575" right="0.0393700787401575" top="0.0393700787401575" bottom="0.0393700787401575" header="0.0393700787401575" footer="0.0393700787401575"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
